--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/Stocks/Data/Stocks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336F171A-191B-E042-AAA3-F5DF9480024B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CF302F-E53B-F047-9748-55D69078CF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1807,20 +1807,19 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="7">
           <cell r="C7">
-            <v>9.1150000000000002</v>
+            <v>9.17</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2249,7 +2248,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$7</f>
-        <v>9.1150000000000002</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2272,7 +2271,7 @@
       </c>
       <c r="C9" s="112">
         <f>C3*'Statement Q'!J147</f>
-        <v>553854.745</v>
+        <v>557196.71</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
@@ -2290,7 +2289,7 @@
       </c>
       <c r="C11" s="112">
         <f>C9+C10</f>
-        <v>582473.745</v>
+        <v>585815.71</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2299,7 +2298,7 @@
       </c>
       <c r="C13" s="95">
         <f>C3/'Statement Q'!N25</f>
-        <v>240.78462272333044</v>
+        <v>242.23751951431049</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -2308,7 +2307,7 @@
       </c>
       <c r="C14" s="95">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$23)</f>
-        <v>1.1553469374166392</v>
+        <v>1.1623183122447154</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -22950,7 +22949,7 @@
       </c>
       <c r="C79" s="138">
         <f>(C78-Overview!C3)/Overview!C3</f>
-        <v>0.46349200299055976</v>
+        <v>0.45471424288538198</v>
       </c>
     </row>
     <row r="80" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23027,7 +23026,7 @@
       </c>
       <c r="C89" s="138">
         <f>(C88-Overview!C3)/Overview!C3</f>
-        <v>0.6920817532825374</v>
+        <v>0.68193295323558656</v>
       </c>
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.2">

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CF302F-E53B-F047-9748-55D69078CF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D854EB95-0570-3640-ACB8-BA7F64352017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1815,7 +1815,7 @@
       <sheetData sheetId="0">
         <row r="7">
           <cell r="C7">
-            <v>9.17</v>
+            <v>8.875</v>
           </cell>
         </row>
       </sheetData>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$7</f>
-        <v>9.17</v>
+        <v>8.875</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C9" s="112">
         <f>C3*'Statement Q'!J147</f>
-        <v>557196.71</v>
+        <v>539271.625</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C11" s="112">
         <f>C9+C10</f>
-        <v>585815.71</v>
+        <v>567890.625</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C13" s="95">
         <f>C3/'Statement Q'!N25</f>
-        <v>242.23751951431049</v>
+        <v>234.4447094535993</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="C14" s="95">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$23)</f>
-        <v>1.1623183122447154</v>
+        <v>1.1249263927123063</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="C79" s="138">
         <f>(C78-Overview!C3)/Overview!C3</f>
-        <v>0.45471424288538198</v>
+        <v>0.50306812476157214</v>
       </c>
     </row>
     <row r="80" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23026,7 +23026,7 @@
       </c>
       <c r="C89" s="138">
         <f>(C88-Overview!C3)/Overview!C3</f>
-        <v>0.68193295323558656</v>
+        <v>0.73783945703327647</v>
       </c>
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.2">

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D854EB95-0570-3640-ACB8-BA7F64352017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8BF77E-72D7-664C-90C3-6F56D2154941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="1" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1807,6 +1807,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
       <sheetName val="1. List_AutomaticData"/>
@@ -1815,7 +1818,7 @@
       <sheetData sheetId="0">
         <row r="7">
           <cell r="C7">
-            <v>8.875</v>
+            <v>9.67</v>
           </cell>
         </row>
       </sheetData>
@@ -2248,7 +2251,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$7</f>
-        <v>8.875</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2271,7 +2274,7 @@
       </c>
       <c r="C9" s="112">
         <f>C3*'Statement Q'!J147</f>
-        <v>539271.625</v>
+        <v>587578.21</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
@@ -2289,7 +2292,7 @@
       </c>
       <c r="C11" s="112">
         <f>C9+C10</f>
-        <v>567890.625</v>
+        <v>616197.21</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -2298,7 +2301,7 @@
       </c>
       <c r="C13" s="95">
         <f>C3/'Statement Q'!N25</f>
-        <v>234.4447094535993</v>
+        <v>255.44567215958369</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -2307,7 +2310,7 @@
       </c>
       <c r="C14" s="95">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$23)</f>
-        <v>1.1249263927123063</v>
+        <v>1.2256944470454088</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -22949,7 +22952,7 @@
       </c>
       <c r="C79" s="138">
         <f>(C78-Overview!C3)/Overview!C3</f>
-        <v>0.50306812476157214</v>
+        <v>0.37949633994404891</v>
       </c>
     </row>
     <row r="80" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23026,7 +23029,7 @@
       </c>
       <c r="C89" s="138">
         <f>(C88-Overview!C3)/Overview!C3</f>
-        <v>0.73783945703327647</v>
+        <v>0.59496640963498748</v>
       </c>
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.2">

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E654CAEA-FAAB-734E-A088-F751DD8305B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C49C1AE-CCB6-6143-901B-1135965B7280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -57,11 +57,29 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={28FFD7B9-6059-4543-B530-AE286539E9DC}</author>
+  </authors>
+  <commentList>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{28FFD7B9-6059-4543-B530-AE286539E9DC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Bond yield or for lease only debt search 10-K for Note 8 Debt and Finance lease</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={47DC635B-B951-894F-8927-C861B2D344C7}</author>
     <author>tc={D394081D-FAF9-AB4C-8C13-0F2C7A4C0BC4}</author>
   </authors>
   <commentList>
-    <comment ref="B172" authorId="0" shapeId="0" xr:uid="{47DC635B-B951-894F-8927-C861B2D344C7}">
+    <comment ref="B173" authorId="0" shapeId="0" xr:uid="{47DC635B-B951-894F-8927-C861B2D344C7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -69,7 +87,7 @@
     Actual number (not K or M)</t>
       </text>
     </comment>
-    <comment ref="B193" authorId="1" shapeId="0" xr:uid="{D394081D-FAF9-AB4C-8C13-0F2C7A4C0BC4}">
+    <comment ref="B194" authorId="1" shapeId="0" xr:uid="{D394081D-FAF9-AB4C-8C13-0F2C7A4C0BC4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -81,13 +99,13 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={C0E44C63-9A04-C843-874D-703EEBBB0F28}</author>
   </authors>
   <commentList>
-    <comment ref="B161" authorId="0" shapeId="0" xr:uid="{C0E44C63-9A04-C843-874D-703EEBBB0F28}">
+    <comment ref="B163" authorId="0" shapeId="0" xr:uid="{C0E44C63-9A04-C843-874D-703EEBBB0F28}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -99,7 +117,7 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={D02FF5CB-BB6F-684F-B674-508B6EB73B98}</author>
@@ -117,7 +135,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={97B820BD-138F-064E-B3B8-543D2F51466A}</author>
@@ -145,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="394">
   <si>
     <t>Date</t>
   </si>
@@ -1300,13 +1318,40 @@
   </si>
   <si>
     <t>EBIT margin</t>
+  </si>
+  <si>
+    <t>Adjustments</t>
+  </si>
+  <si>
+    <t>Operating Interest</t>
+  </si>
+  <si>
+    <t>Operating lease cost</t>
+  </si>
+  <si>
+    <t>EBITDAR</t>
+  </si>
+  <si>
+    <t>Cost of operating lease debt</t>
+  </si>
+  <si>
+    <t>Operating lease interest</t>
+  </si>
+  <si>
+    <t>From 10-K Leases note</t>
+  </si>
+  <si>
+    <t>Operating lease amortization</t>
+  </si>
+  <si>
+    <t>Cost of financial lease debt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
@@ -1314,6 +1359,7 @@
     <numFmt numFmtId="167" formatCode="0.00_);\(0.00\)"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
+    <numFmt numFmtId="170" formatCode="0_);\(0\)"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -1954,7 +2000,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2235,7 +2281,11 @@
     <xf numFmtId="37" fontId="1" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2243,9 +2293,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2376,10 +2423,10 @@
       <sheetData sheetId="0">
         <row r="7">
           <cell r="C7">
-            <v>10.17</v>
+            <v>9.7149999999999999</v>
           </cell>
           <cell r="F7">
-            <v>0.89490000000000003</v>
+            <v>0.90390000000000004</v>
           </cell>
         </row>
         <row r="10">
@@ -2426,38 +2473,6 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6">
-        <row r="5">
-          <cell r="C5">
-            <v>2021</v>
-          </cell>
-          <cell r="D5">
-            <v>2022</v>
-          </cell>
-          <cell r="E5">
-            <v>2023</v>
-          </cell>
-          <cell r="F5">
-            <v>2024</v>
-          </cell>
-          <cell r="G5">
-            <v>2025</v>
-          </cell>
-          <cell r="H5">
-            <v>2026</v>
-          </cell>
-          <cell r="I5">
-            <v>2027</v>
-          </cell>
-          <cell r="J5">
-            <v>2028</v>
-          </cell>
-          <cell r="K5">
-            <v>2029</v>
-          </cell>
-          <cell r="L5">
-            <v>2030</v>
-          </cell>
-        </row>
         <row r="11">
           <cell r="AB11"/>
           <cell r="AC11"/>
@@ -2801,24 +2816,32 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B172" dT="2026-01-31T00:39:50.80" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{47DC635B-B951-894F-8927-C861B2D344C7}">
-    <text>Actual number (not K or M)</text>
-  </threadedComment>
-  <threadedComment ref="B193" dT="2026-04-25T21:52:20.00" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{D394081D-FAF9-AB4C-8C13-0F2C7A4C0BC4}">
-    <text>Take the closing price of the last day of the period. In case the price has seen heavy fluctuations make an average of the last days. Info found at Yahoo Finance in the Historical Data section</text>
+  <threadedComment ref="B4" dT="2026-05-09T21:32:35.87" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{28FFD7B9-6059-4543-B530-AE286539E9DC}">
+    <text>Bond yield or for lease only debt search 10-K for Note 8 Debt and Finance lease</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B161" dT="2026-01-31T00:39:50.80" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{C0E44C63-9A04-C843-874D-703EEBBB0F28}">
+  <threadedComment ref="B173" dT="2026-01-31T00:39:50.80" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{47DC635B-B951-894F-8927-C861B2D344C7}">
+    <text>Actual number (not K or M)</text>
+  </threadedComment>
+  <threadedComment ref="B194" dT="2026-04-25T21:52:20.00" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{D394081D-FAF9-AB4C-8C13-0F2C7A4C0BC4}">
+    <text>Take the closing price of the last day of the period. In case the price has seen heavy fluctuations make an average of the last days. Info found at Yahoo Finance in the Historical Data section</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B163" dT="2026-01-31T00:39:50.80" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{C0E44C63-9A04-C843-874D-703EEBBB0F28}">
     <text>Actual number (not K or M)</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="B35" dT="2026-04-25T20:40:52.15" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{D02FF5CB-BB6F-684F-B674-508B6EB73B98}">
     <text>We use here the inverted signg as are used in the CashFlow statement which means we will Add the change in NWC to the NOPAT instead of subtracting it</text>
@@ -2826,7 +2849,7 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="B9" dT="2026-02-28T14:18:18.18" personId="{C1D857D3-F592-2946-8369-15D188CA547D}" id="{97B820BD-138F-064E-B3B8-543D2F51466A}">
     <text>10 year government bond yield</text>
@@ -2886,12 +2909,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8A3889E-47F7-E641-9FC7-1CBF49DF9C8A}">
-  <dimension ref="A2:G54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8A3889E-47F7-E641-9FC7-1CBF49DF9C8A}">
+  <dimension ref="A2:G55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" style="1" customWidth="1"/>
     <col min="3" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -2909,275 +2932,291 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$7</f>
-        <v>10.17</v>
+        <v>9.7149999999999999</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C4" s="110">
+        <v>7.4999999999999997E-2</v>
+      </c>
       <c r="E4" s="94"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="E6" s="35"/>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C5" s="110">
+        <v>7.8E-2</v>
+      </c>
+      <c r="E5" s="94"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="1" t="s">
+      <c r="E7" s="35"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="104">
-        <f>C3*'Statement Q'!J147</f>
-        <v>617959.71</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="104">
+        <f>C3*'Statement Q'!J147</f>
+        <v>590312.54500000004</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C10" s="104">
+      <c r="C11" s="104">
         <f>(Statements!S48+Statements!S49+Statements!S56+Statements!S57)-Statements!S26</f>
         <v>28619</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C11" s="104">
-        <f>C9+C10</f>
-        <v>646578.71</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" s="94">
-        <f>C3/'Statement Q'!N25</f>
-        <v>268.65382480485687</v>
+      <c r="C12" s="104">
+        <f>C10+C11</f>
+        <v>618931.54500000004</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="94">
+        <f>C3/'Statement Q'!N25</f>
+        <v>256.63440589765827</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C14" s="94">
+      <c r="C15" s="94">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$23)</f>
-        <v>1.2890705818461019</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C15" s="20"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C18" s="20">
-        <v>3302</v>
-      </c>
+        <v>1.231398299177471</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C16" s="20"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C19" s="20">
+        <v>3302</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C20" s="20">
         <f>'Statement Q'!J147</f>
         <v>60763</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B20" s="1" t="s">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C20" s="125">
-        <f>C18/C19</f>
+      <c r="C21" s="125">
+        <f>C19/C20</f>
         <v>5.4342280664220005E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B22" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B28" s="1" t="s">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C29" s="20">
         <f>Statements!S14*(1-'Statement Y'!G151)</f>
         <v>-6290.2320331117526</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B29" s="1" t="s">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C30" s="20">
         <f>Statements!S46-Statements!S26-Statements!S27</f>
         <v>556961</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B30" s="1" t="s">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B31" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C31" s="20">
         <f>SUM(Statements!S50:S54)+Statements!S47</f>
         <v>174016</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B31" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C31" s="20">
-        <f>C29-C30</f>
-        <v>382945</v>
-      </c>
-    </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C32" s="20">
+        <f>C30-C31</f>
+        <v>382945</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B33" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C32" s="125">
-        <f>C28/C31</f>
+      <c r="C33" s="125">
+        <f>C29/C32</f>
         <v>-1.6425941148498487E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="232" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="230" t="s">
         <v>256</v>
       </c>
-      <c r="B36" s="232"/>
-      <c r="C36" s="232"/>
-      <c r="D36" s="232"/>
-      <c r="E36" s="232"/>
-      <c r="F36" s="232"/>
-      <c r="G36" s="232"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>260</v>
-      </c>
+      <c r="B37" s="230"/>
+      <c r="C37" s="230"/>
+      <c r="D37" s="230"/>
+      <c r="E37" s="230"/>
+      <c r="F37" s="230"/>
+      <c r="G37" s="230"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="232" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="230" t="s">
         <v>243</v>
       </c>
-      <c r="B43" s="232"/>
-      <c r="C43" s="232"/>
-      <c r="D43" s="232"/>
-      <c r="E43" s="232"/>
-      <c r="F43" s="232"/>
-      <c r="G43" s="232"/>
-    </row>
-    <row r="44" spans="1:7" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="7" t="s">
+      <c r="B44" s="230"/>
+      <c r="C44" s="230"/>
+      <c r="D44" s="230"/>
+      <c r="E44" s="230"/>
+      <c r="F44" s="230"/>
+      <c r="G44" s="230"/>
+    </row>
+    <row r="45" spans="1:7" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B46" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C46" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D45" s="8"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
-        <v>245</v>
-      </c>
+      <c r="D46" s="8"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B48" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B55" s="1" t="s">
         <v>261</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0466832C-DE22-644B-8AF7-47F5F6316769}">
-  <dimension ref="A1:AE33"/>
+  <dimension ref="A1:AE35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="143" customWidth="1"/>
@@ -3206,60 +3245,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="141"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="230" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="238"/>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
+      <c r="S2" s="239"/>
+      <c r="T2" s="239"/>
+      <c r="U2" s="239"/>
+      <c r="V2" s="239"/>
+      <c r="W2" s="239"/>
+      <c r="X2" s="239"/>
+      <c r="Y2" s="239"/>
+      <c r="Z2" s="239"/>
+      <c r="AA2" s="239"/>
+      <c r="AB2" s="239"/>
+      <c r="AC2" s="239"/>
       <c r="AE2" s="174"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="146"/>
       <c r="B4" s="93"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="234" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
-      <c r="S4" s="238"/>
-      <c r="T4" s="238"/>
-      <c r="U4" s="238"/>
-      <c r="V4" s="238"/>
-      <c r="W4" s="238"/>
-      <c r="X4" s="238"/>
-      <c r="Y4" s="238"/>
-      <c r="Z4" s="238"/>
-      <c r="AA4" s="238"/>
-      <c r="AB4" s="238"/>
-      <c r="AC4" s="238"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
+      <c r="H4" s="234"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="234"/>
+      <c r="K4" s="234"/>
+      <c r="L4" s="234"/>
+      <c r="S4" s="239"/>
+      <c r="T4" s="239"/>
+      <c r="U4" s="239"/>
+      <c r="V4" s="239"/>
+      <c r="W4" s="239"/>
+      <c r="X4" s="239"/>
+      <c r="Y4" s="239"/>
+      <c r="Z4" s="239"/>
+      <c r="AA4" s="239"/>
+      <c r="AB4" s="239"/>
+      <c r="AC4" s="239"/>
       <c r="AE4" s="175"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -3670,7 +3709,9 @@
         <f>'COGS &amp; OpEx'!L14</f>
         <v>125828.85956495733</v>
       </c>
-      <c r="N11" s="151"/>
+      <c r="N11" s="151" t="s">
+        <v>306</v>
+      </c>
       <c r="Q11" s="151"/>
       <c r="S11" s="148"/>
       <c r="T11" s="148"/>
@@ -3730,7 +3771,9 @@
         <f>'COGS &amp; OpEx'!L15</f>
         <v>13369.316328776717</v>
       </c>
-      <c r="N12" s="151"/>
+      <c r="N12" s="151" t="s">
+        <v>306</v>
+      </c>
       <c r="Q12" s="151"/>
       <c r="S12" s="148"/>
       <c r="T12" s="148"/>
@@ -3790,7 +3833,9 @@
         <f>'COGS &amp; OpEx'!L16</f>
         <v>17301.468190181629</v>
       </c>
-      <c r="N13" s="151"/>
+      <c r="N13" s="151" t="s">
+        <v>306</v>
+      </c>
       <c r="Q13" s="151"/>
       <c r="S13" s="148"/>
       <c r="T13" s="148"/>
@@ -3867,50 +3912,47 @@
       <c r="AE14" s="150"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B15" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C15" s="154">
-        <f t="shared" ref="C15:L15" si="1">C8-C14</f>
-        <v>-116817</v>
-      </c>
-      <c r="D15" s="154">
-        <f t="shared" si="1"/>
-        <v>-176552</v>
-      </c>
-      <c r="E15" s="154">
-        <f t="shared" si="1"/>
-        <v>-136479</v>
-      </c>
-      <c r="F15" s="154">
-        <f t="shared" si="1"/>
-        <v>-58097</v>
-      </c>
-      <c r="G15" s="191">
-        <f t="shared" si="1"/>
-        <v>-6612</v>
-      </c>
-      <c r="H15" s="154">
-        <f t="shared" si="1"/>
-        <v>512.00395319168456</v>
-      </c>
-      <c r="I15" s="154">
-        <f t="shared" si="1"/>
-        <v>1632.2367447190918</v>
-      </c>
-      <c r="J15" s="154">
-        <f t="shared" si="1"/>
-        <v>26604.196462624997</v>
-      </c>
-      <c r="K15" s="154">
-        <f t="shared" si="1"/>
-        <v>56290.759647409082</v>
-      </c>
-      <c r="L15" s="154">
-        <f t="shared" si="1"/>
-        <v>79429.467600379314</v>
-      </c>
-      <c r="N15" s="151"/>
+      <c r="B15" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C15" s="148">
+        <f>'Statement Y'!D200</f>
+        <v>191.77500000000001</v>
+      </c>
+      <c r="D15" s="148">
+        <f>'Statement Y'!E200</f>
+        <v>96.224999999999994</v>
+      </c>
+      <c r="E15" s="148">
+        <f>'Statement Y'!F200</f>
+        <v>39.524999999999999</v>
+      </c>
+      <c r="F15" s="148">
+        <f>'Statement Y'!G200</f>
+        <v>120.75</v>
+      </c>
+      <c r="G15" s="149">
+        <f>'Statement Y'!H200</f>
+        <v>177.07499999999999</v>
+      </c>
+      <c r="H15" s="228">
+        <v>1318</v>
+      </c>
+      <c r="I15" s="228">
+        <v>793</v>
+      </c>
+      <c r="J15" s="228">
+        <v>292</v>
+      </c>
+      <c r="K15" s="228">
+        <v>0</v>
+      </c>
+      <c r="L15" s="228">
+        <v>0</v>
+      </c>
+      <c r="N15" s="192" t="s">
+        <v>391</v>
+      </c>
       <c r="Q15" s="151"/>
       <c r="S15" s="148"/>
       <c r="T15" s="148"/>
@@ -3925,464 +3967,582 @@
       <c r="AC15" s="150"/>
       <c r="AE15" s="150"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="233" t="s">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C16" s="148">
+        <f>'Statement Y'!D201</f>
+        <v>1127.2249999999999</v>
+      </c>
+      <c r="D16" s="148">
+        <f>'Statement Y'!E201</f>
+        <v>1800.7750000000001</v>
+      </c>
+      <c r="E16" s="148">
+        <f>'Statement Y'!F201</f>
+        <v>747.47500000000002</v>
+      </c>
+      <c r="F16" s="148">
+        <f>'Statement Y'!G201</f>
+        <v>862.25</v>
+      </c>
+      <c r="G16" s="149">
+        <f>'Statement Y'!H201</f>
+        <v>776.92499999999995</v>
+      </c>
+      <c r="H16" s="104">
+        <f>H15-H15*Overview!$C$4</f>
+        <v>1219.1500000000001</v>
+      </c>
+      <c r="I16" s="104">
+        <f>I15-I15*Overview!$C$4</f>
+        <v>733.52499999999998</v>
+      </c>
+      <c r="J16" s="104">
+        <f>J15-J15*Overview!$C$4</f>
+        <v>270.10000000000002</v>
+      </c>
+      <c r="K16" s="104">
+        <f>K15-K15*Overview!$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="104">
+        <f>L15-L15*Overview!$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="192"/>
+      <c r="Q16" s="151"/>
+      <c r="S16" s="148"/>
+      <c r="T16" s="148"/>
+      <c r="U16" s="148"/>
+      <c r="V16" s="148"/>
+      <c r="W16" s="148"/>
+      <c r="X16" s="148"/>
+      <c r="Y16" s="148"/>
+      <c r="Z16" s="148"/>
+      <c r="AA16" s="150"/>
+      <c r="AB16" s="150"/>
+      <c r="AC16" s="150"/>
+      <c r="AE16" s="150"/>
+    </row>
+    <row r="17" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B17" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" s="154">
+        <f>C8-C14+C15-C16</f>
+        <v>-117752.45000000001</v>
+      </c>
+      <c r="D17" s="154">
+        <f t="shared" ref="D17:G17" si="1">D8-D14+D15-D16</f>
+        <v>-178256.55</v>
+      </c>
+      <c r="E17" s="154">
+        <f t="shared" si="1"/>
+        <v>-137186.95000000001</v>
+      </c>
+      <c r="F17" s="154">
+        <f t="shared" si="1"/>
+        <v>-58838.5</v>
+      </c>
+      <c r="G17" s="191">
+        <f t="shared" si="1"/>
+        <v>-7211.85</v>
+      </c>
+      <c r="H17" s="154">
+        <f>H8-H14+H15*Overview!$C$4</f>
+        <v>610.85395319168458</v>
+      </c>
+      <c r="I17" s="154">
+        <f>I8-I14+I15*Overview!$C$4</f>
+        <v>1691.7117447190917</v>
+      </c>
+      <c r="J17" s="154">
+        <f>J8-J14+J15*Overview!$C$4</f>
+        <v>26626.096462624999</v>
+      </c>
+      <c r="K17" s="154">
+        <f>K8-K14+K15*Overview!$C$4</f>
+        <v>56290.759647409082</v>
+      </c>
+      <c r="L17" s="154">
+        <f>L8-L14+L15*Overview!$C$4</f>
+        <v>79429.467600379314</v>
+      </c>
+      <c r="N17" s="151"/>
+      <c r="Q17" s="151"/>
+      <c r="S17" s="148"/>
+      <c r="T17" s="148"/>
+      <c r="U17" s="148"/>
+      <c r="V17" s="148"/>
+      <c r="W17" s="148"/>
+      <c r="X17" s="148"/>
+      <c r="Y17" s="148"/>
+      <c r="Z17" s="148"/>
+      <c r="AA17" s="150"/>
+      <c r="AB17" s="150"/>
+      <c r="AC17" s="150"/>
+      <c r="AE17" s="150"/>
+    </row>
+    <row r="20" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="C20" s="234" t="s">
         <v>309</v>
       </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C19" s="64">
-        <f t="shared" ref="C19:L19" si="2">C5</f>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="234"/>
+      <c r="G20" s="234"/>
+      <c r="H20" s="234"/>
+      <c r="I20" s="234"/>
+      <c r="J20" s="234"/>
+      <c r="K20" s="234"/>
+      <c r="L20" s="234"/>
+    </row>
+    <row r="21" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="C21" s="64">
+        <f t="shared" ref="C21:L21" si="2">C5</f>
         <v>2022</v>
       </c>
-      <c r="D19" s="64">
+      <c r="D21" s="64">
         <f t="shared" si="2"/>
         <v>2023</v>
       </c>
-      <c r="E19" s="64">
+      <c r="E21" s="64">
         <f t="shared" si="2"/>
         <v>2024</v>
       </c>
-      <c r="F19" s="64">
+      <c r="F21" s="64">
         <f t="shared" si="2"/>
         <v>2025</v>
       </c>
-      <c r="G19" s="64">
+      <c r="G21" s="64">
         <f t="shared" si="2"/>
         <v>2026</v>
       </c>
-      <c r="H19" s="64">
+      <c r="H21" s="64">
         <f t="shared" si="2"/>
         <v>2027</v>
       </c>
-      <c r="I19" s="64">
+      <c r="I21" s="64">
         <f t="shared" si="2"/>
         <v>2028</v>
       </c>
-      <c r="J19" s="64">
+      <c r="J21" s="64">
         <f t="shared" si="2"/>
         <v>2029</v>
       </c>
-      <c r="K19" s="64">
+      <c r="K21" s="64">
         <f t="shared" si="2"/>
         <v>2030</v>
       </c>
-      <c r="L19" s="64">
+      <c r="L21" s="64">
         <f t="shared" si="2"/>
         <v>2031</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="1" t="s">
+    <row r="22" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="169">
+      <c r="C22" s="169">
         <f>'Statement Y'!D151</f>
         <v>1.5426474203036134E-3</v>
       </c>
-      <c r="D20" s="169">
+      <c r="D22" s="169">
         <f>'Statement Y'!E151</f>
         <v>2.7495830083739889E-3</v>
       </c>
-      <c r="E20" s="169">
+      <c r="E22" s="169">
         <f>'Statement Y'!F151</f>
         <v>1.1400747735366701E-2</v>
       </c>
-      <c r="F20" s="169">
+      <c r="F22" s="169">
         <f>'Statement Y'!G151</f>
         <v>4.8664241816129439E-2</v>
       </c>
-      <c r="G20" s="193">
-        <v>0</v>
-      </c>
-      <c r="H20" s="194">
+      <c r="G22" s="193">
+        <v>0</v>
+      </c>
+      <c r="H22" s="194">
         <v>0.21</v>
       </c>
-      <c r="I20" s="194">
+      <c r="I22" s="194">
         <v>0.21</v>
       </c>
-      <c r="J20" s="194">
+      <c r="J22" s="194">
         <v>0.21</v>
       </c>
-      <c r="K20" s="194">
+      <c r="K22" s="194">
         <v>0.21</v>
       </c>
-      <c r="L20" s="194">
+      <c r="L22" s="194">
         <v>0.21</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C23" s="233" t="s">
+    <row r="25" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="C25" s="234" t="s">
         <v>310</v>
       </c>
-      <c r="D23" s="233"/>
-      <c r="E23" s="233"/>
-      <c r="F23" s="233"/>
-      <c r="G23" s="233"/>
-      <c r="H23" s="233"/>
-      <c r="I23" s="233"/>
-      <c r="J23" s="233"/>
-      <c r="K23" s="233"/>
-      <c r="L23" s="233"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B24" s="7" t="s">
+      <c r="D25" s="234"/>
+      <c r="E25" s="234"/>
+      <c r="F25" s="234"/>
+      <c r="G25" s="234"/>
+      <c r="H25" s="234"/>
+      <c r="I25" s="234"/>
+      <c r="J25" s="234"/>
+      <c r="K25" s="234"/>
+      <c r="L25" s="234"/>
+    </row>
+    <row r="26" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B26" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C24" s="64">
-        <f t="shared" ref="C24:L24" si="3">C5</f>
+      <c r="C26" s="64">
+        <f t="shared" ref="C26:L26" si="3">C5</f>
         <v>2022</v>
       </c>
-      <c r="D24" s="64">
+      <c r="D26" s="64">
         <f t="shared" si="3"/>
         <v>2023</v>
       </c>
-      <c r="E24" s="64">
+      <c r="E26" s="64">
         <f t="shared" si="3"/>
         <v>2024</v>
       </c>
-      <c r="F24" s="64">
+      <c r="F26" s="64">
         <f t="shared" si="3"/>
         <v>2025</v>
       </c>
-      <c r="G24" s="64">
+      <c r="G26" s="64">
         <f t="shared" si="3"/>
         <v>2026</v>
       </c>
-      <c r="H24" s="64">
+      <c r="H26" s="64">
         <f t="shared" si="3"/>
         <v>2027</v>
       </c>
-      <c r="I24" s="64">
+      <c r="I26" s="64">
         <f t="shared" si="3"/>
         <v>2028</v>
       </c>
-      <c r="J24" s="64">
+      <c r="J26" s="64">
         <f t="shared" si="3"/>
         <v>2029</v>
       </c>
-      <c r="K24" s="64">
+      <c r="K26" s="64">
         <f t="shared" si="3"/>
         <v>2030</v>
       </c>
-      <c r="L24" s="64">
+      <c r="L26" s="64">
         <f t="shared" si="3"/>
         <v>2031</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
+    <row r="27" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="148">
+      <c r="C27" s="148">
         <f>'WC &amp; Investments'!C42</f>
         <v>21302</v>
       </c>
-      <c r="D25" s="148">
+      <c r="D27" s="148">
         <f>'WC &amp; Investments'!D42</f>
         <v>25304</v>
       </c>
-      <c r="E25" s="148">
+      <c r="E27" s="148">
         <f>'WC &amp; Investments'!E42</f>
         <v>29487</v>
       </c>
-      <c r="F25" s="148">
+      <c r="F27" s="148">
         <f>'WC &amp; Investments'!F42</f>
         <v>27886</v>
       </c>
-      <c r="G25" s="149">
+      <c r="G27" s="149">
         <f>'WC &amp; Investments'!G42</f>
         <v>31453</v>
       </c>
-      <c r="H25" s="148">
+      <c r="H27" s="148">
         <f>'WC &amp; Investments'!H42</f>
         <v>32768.253004263999</v>
       </c>
-      <c r="I25" s="148">
+      <c r="I27" s="148">
         <f>'WC &amp; Investments'!I42</f>
         <v>34276.971639102339</v>
       </c>
-      <c r="J25" s="148">
+      <c r="J27" s="148">
         <f>'WC &amp; Investments'!J42</f>
         <v>32516.240120986044</v>
       </c>
-      <c r="K25" s="148">
+      <c r="K27" s="148">
         <f>'WC &amp; Investments'!K42</f>
         <v>30825.892187866855</v>
       </c>
-      <c r="L25" s="148">
+      <c r="L27" s="148">
         <f>'WC &amp; Investments'!L42</f>
         <v>30670.784518958346</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B26" s="1" t="s">
+    <row r="28" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="148">
+      <c r="C28" s="148">
         <f>'WC &amp; Investments'!C45</f>
         <v>30805</v>
       </c>
-      <c r="D26" s="148">
+      <c r="D28" s="148">
         <f>'WC &amp; Investments'!D45</f>
         <v>26203</v>
       </c>
-      <c r="E26" s="148">
+      <c r="E28" s="148">
         <f>'WC &amp; Investments'!E45</f>
         <v>25097</v>
       </c>
-      <c r="F26" s="148">
+      <c r="F28" s="148">
         <f>'WC &amp; Investments'!F45</f>
         <v>24089</v>
       </c>
-      <c r="G26" s="149">
+      <c r="G28" s="149">
         <f>'WC &amp; Investments'!G45</f>
         <v>24397</v>
       </c>
-      <c r="H26" s="148">
+      <c r="H28" s="148">
         <f>'WC &amp; Investments'!H45</f>
         <v>25600.197659581248</v>
       </c>
-      <c r="I26" s="148">
+      <c r="I28" s="148">
         <f>'WC &amp; Investments'!I45</f>
         <v>27203.945745319317</v>
       </c>
-      <c r="J26" s="148">
+      <c r="J28" s="148">
         <f>'WC &amp; Investments'!J45</f>
         <v>26604.196462624943</v>
       </c>
-      <c r="K26" s="148">
+      <c r="K28" s="148">
         <f>'WC &amp; Investments'!K45</f>
         <v>30155.764096826271</v>
       </c>
-      <c r="L26" s="148">
+      <c r="L28" s="148">
         <f>'WC &amp; Investments'!L45</f>
         <v>31457.214891239331</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="1" t="s">
+    <row r="29" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="148">
+      <c r="C29" s="148">
         <f>'WC &amp; Investments'!C35</f>
         <v>-18571</v>
       </c>
-      <c r="D27" s="148">
+      <c r="D29" s="148">
         <f>'WC &amp; Investments'!D35</f>
         <v>-3862</v>
       </c>
-      <c r="E27" s="148">
+      <c r="E29" s="148">
         <f>'WC &amp; Investments'!E35</f>
         <v>-1637</v>
       </c>
-      <c r="F27" s="148">
+      <c r="F29" s="148">
         <f>'WC &amp; Investments'!F35</f>
         <v>-6493</v>
       </c>
-      <c r="G27" s="149">
+      <c r="G29" s="149">
         <f>'WC &amp; Investments'!G35</f>
         <v>-14090</v>
       </c>
-      <c r="H27" s="148">
+      <c r="H29" s="148">
         <f>'WC &amp; Investments'!H35</f>
         <v>6769.6898165339544</v>
       </c>
-      <c r="I27" s="148">
+      <c r="I29" s="148">
         <f>'WC &amp; Investments'!I35</f>
         <v>1942.9805335584442</v>
       </c>
-      <c r="J27" s="148">
+      <c r="J29" s="148">
         <f>'WC &amp; Investments'!J35</f>
         <v>382.67151442404429</v>
       </c>
-      <c r="K27" s="148">
+      <c r="K29" s="148">
         <f>'WC &amp; Investments'!K35</f>
         <v>-3509.9856065134463</v>
       </c>
-      <c r="L27" s="148">
+      <c r="L29" s="148">
         <f>'WC &amp; Investments'!L35</f>
         <v>-7628.2216284011392</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C30" s="233" t="s">
+    <row r="32" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="C32" s="234" t="s">
         <v>313</v>
       </c>
-      <c r="D30" s="233"/>
-      <c r="E30" s="233"/>
-      <c r="F30" s="233"/>
-      <c r="G30" s="233"/>
-      <c r="H30" s="233"/>
-      <c r="I30" s="233"/>
-      <c r="J30" s="233"/>
-      <c r="K30" s="233"/>
-      <c r="L30" s="233"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B31" s="7" t="s">
+      <c r="D32" s="234"/>
+      <c r="E32" s="234"/>
+      <c r="F32" s="234"/>
+      <c r="G32" s="234"/>
+      <c r="H32" s="234"/>
+      <c r="I32" s="234"/>
+      <c r="J32" s="234"/>
+      <c r="K32" s="234"/>
+      <c r="L32" s="234"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C31" s="64">
-        <f t="shared" ref="C31:L31" si="4">C5</f>
+      <c r="C33" s="64">
+        <f t="shared" ref="C33:L33" si="4">C5</f>
         <v>2022</v>
       </c>
-      <c r="D31" s="64">
+      <c r="D33" s="64">
         <f t="shared" si="4"/>
         <v>2023</v>
       </c>
-      <c r="E31" s="64">
+      <c r="E33" s="64">
         <f t="shared" si="4"/>
         <v>2024</v>
       </c>
-      <c r="F31" s="64">
+      <c r="F33" s="64">
         <f t="shared" si="4"/>
         <v>2025</v>
       </c>
-      <c r="G31" s="64">
+      <c r="G33" s="64">
         <f t="shared" si="4"/>
         <v>2026</v>
       </c>
-      <c r="H31" s="64">
+      <c r="H33" s="64">
         <f t="shared" si="4"/>
         <v>2027</v>
       </c>
-      <c r="I31" s="64">
+      <c r="I33" s="64">
         <f t="shared" si="4"/>
         <v>2028</v>
       </c>
-      <c r="J31" s="64">
+      <c r="J33" s="64">
         <f t="shared" si="4"/>
         <v>2029</v>
       </c>
-      <c r="K31" s="64">
+      <c r="K33" s="64">
         <f t="shared" si="4"/>
         <v>2030</v>
       </c>
-      <c r="L31" s="64">
+      <c r="L33" s="64">
         <f t="shared" si="4"/>
         <v>2031</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B32" s="1" t="s">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B34" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C32" s="120">
-        <f>C15*(1-C20)</f>
-        <v>-116636.79255630239</v>
-      </c>
-      <c r="D32" s="120">
-        <f t="shared" ref="D32:L32" si="5">D15*(1-D20)</f>
-        <v>-176066.55562070556</v>
-      </c>
-      <c r="E32" s="120">
+      <c r="C34" s="120">
+        <f>C17*(1-C22)</f>
+        <v>-117570.79948677307</v>
+      </c>
+      <c r="D34" s="120">
+        <f t="shared" ref="D34:L34" si="5">D17*(1-D22)</f>
+        <v>-177766.4188189886</v>
+      </c>
+      <c r="E34" s="120">
         <f t="shared" si="5"/>
-        <v>-134923.03734982488</v>
-      </c>
-      <c r="F32" s="120">
+        <v>-135622.91619046565</v>
+      </c>
+      <c r="F34" s="120">
         <f t="shared" si="5"/>
-        <v>-55269.753543208331</v>
-      </c>
-      <c r="G32" s="195">
+        <v>-55975.16900790167</v>
+      </c>
+      <c r="G34" s="195">
         <f t="shared" si="5"/>
-        <v>-6612</v>
-      </c>
-      <c r="H32" s="120">
+        <v>-7211.85</v>
+      </c>
+      <c r="H34" s="120">
         <f t="shared" si="5"/>
-        <v>404.4831230214308</v>
-      </c>
-      <c r="I32" s="120">
+        <v>482.57462302143085</v>
+      </c>
+      <c r="I34" s="120">
         <f t="shared" si="5"/>
-        <v>1289.4670283280825</v>
-      </c>
-      <c r="J32" s="120">
+        <v>1336.4522783280825</v>
+      </c>
+      <c r="J34" s="120">
         <f t="shared" si="5"/>
-        <v>21017.315205473747</v>
-      </c>
-      <c r="K32" s="120">
+        <v>21034.616205473751</v>
+      </c>
+      <c r="K34" s="120">
         <f t="shared" si="5"/>
         <v>44469.700121453177</v>
       </c>
-      <c r="L32" s="120">
+      <c r="L34" s="120">
         <f t="shared" si="5"/>
         <v>62749.279404299661</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="7" t="s">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="C33" s="154">
-        <f>C32+C25-C26+C27</f>
-        <v>-144710.79255630239</v>
-      </c>
-      <c r="D33" s="154">
-        <f t="shared" ref="D33:L33" si="6">D32+D25-D26+D27</f>
-        <v>-180827.55562070556</v>
-      </c>
-      <c r="E33" s="154">
+      <c r="C35" s="154">
+        <f>C34+C27-C28+C29</f>
+        <v>-145644.79948677309</v>
+      </c>
+      <c r="D35" s="154">
+        <f t="shared" ref="D35:L35" si="6">D34+D27-D28+D29</f>
+        <v>-182527.4188189886</v>
+      </c>
+      <c r="E35" s="154">
         <f t="shared" si="6"/>
-        <v>-132170.03734982488</v>
-      </c>
-      <c r="F33" s="154">
+        <v>-132869.91619046565</v>
+      </c>
+      <c r="F35" s="154">
         <f t="shared" si="6"/>
-        <v>-57965.753543208331</v>
-      </c>
-      <c r="G33" s="191">
+        <v>-58671.16900790167</v>
+      </c>
+      <c r="G35" s="191">
         <f t="shared" si="6"/>
-        <v>-13646</v>
-      </c>
-      <c r="H33" s="154">
+        <v>-14245.849999999999</v>
+      </c>
+      <c r="H35" s="154">
         <f t="shared" si="6"/>
-        <v>14342.228284238139</v>
-      </c>
-      <c r="I33" s="154">
+        <v>14420.319784238134</v>
+      </c>
+      <c r="I35" s="154">
         <f t="shared" si="6"/>
-        <v>10305.473455669546</v>
-      </c>
-      <c r="J33" s="154">
+        <v>10352.458705669551</v>
+      </c>
+      <c r="J35" s="154">
         <f t="shared" si="6"/>
-        <v>27312.030378258893</v>
-      </c>
-      <c r="K33" s="154">
+        <v>27329.331378258892</v>
+      </c>
+      <c r="K35" s="154">
         <f t="shared" si="6"/>
         <v>41629.84260598031</v>
       </c>
-      <c r="L33" s="154">
+      <c r="L35" s="154">
         <f t="shared" si="6"/>
         <v>54334.627403617545</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="C30:L30"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
+    <mergeCell ref="C20:L20"/>
+    <mergeCell ref="C25:L25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4442,10 +4602,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="230" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="230"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -4462,7 +4622,7 @@
       </c>
       <c r="C6" s="196">
         <f>[1]Sheet1!$C$7</f>
-        <v>10.17</v>
+        <v>9.7149999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4471,7 +4631,7 @@
       </c>
       <c r="C7" s="197">
         <f>C5*C6</f>
-        <v>617959.71</v>
+        <v>590312.54500000004</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4479,8 +4639,8 @@
         <v>319</v>
       </c>
       <c r="C8" s="177">
-        <f>Statements!S48+Statements!S56</f>
-        <v>100088</v>
+        <f>'Statement Q'!N181</f>
+        <v>102449</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4498,7 +4658,7 @@
       </c>
       <c r="C10" s="196">
         <f>[1]Sheet1!$F$7</f>
-        <v>0.89490000000000003</v>
+        <v>0.90390000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4521,16 +4681,17 @@
       <c r="B13" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C13" s="110">
-        <v>0.1</v>
+      <c r="C13" s="198">
+        <f>Overview!C5</f>
+        <v>7.8E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="230" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="230"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -4538,7 +4699,7 @@
       </c>
       <c r="C16" s="97">
         <f>C8/(C8+C7)</f>
-        <v>0.13938906650088753</v>
+        <v>0.14788494069774036</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4547,7 +4708,7 @@
       </c>
       <c r="C17" s="97">
         <f>C7/(C8+C7)</f>
-        <v>0.86061093349911244</v>
+        <v>0.85211505930225961</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4556,7 +4717,7 @@
       </c>
       <c r="C18" s="97">
         <f>C13*(1-C12)</f>
-        <v>7.9000000000000015E-2</v>
+        <v>6.1620000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4565,7 +4726,7 @@
       </c>
       <c r="C19" s="97">
         <f>C9+C10*C11</f>
-        <v>8.8385000000000005E-2</v>
+        <v>8.8834999999999997E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4574,7 +4735,7 @@
       </c>
       <c r="C20" s="97">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>8.7076833610889179E-2</v>
+        <v>8.4810311338910996E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4628,60 +4789,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="141"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="230" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237" t="s">
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="237"/>
+      <c r="H3" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="238"/>
-      <c r="T3" s="238"/>
-      <c r="U3" s="238"/>
-      <c r="V3" s="238"/>
-      <c r="W3" s="238"/>
-      <c r="X3" s="238"/>
-      <c r="Y3" s="238"/>
-      <c r="Z3" s="238"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="P3" s="239"/>
+      <c r="Q3" s="239"/>
+      <c r="R3" s="239"/>
+      <c r="S3" s="239"/>
+      <c r="T3" s="239"/>
+      <c r="U3" s="239"/>
+      <c r="V3" s="239"/>
+      <c r="W3" s="239"/>
+      <c r="X3" s="239"/>
+      <c r="Y3" s="239"/>
+      <c r="Z3" s="239"/>
       <c r="AB3" s="174"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="146"/>
       <c r="B5" s="93"/>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="234" t="s">
         <v>331</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="238"/>
-      <c r="T5" s="238"/>
-      <c r="U5" s="238"/>
-      <c r="V5" s="238"/>
-      <c r="W5" s="238"/>
-      <c r="X5" s="238"/>
-      <c r="Y5" s="238"/>
-      <c r="Z5" s="238"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="234"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="234"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="234"/>
+      <c r="P5" s="239"/>
+      <c r="Q5" s="239"/>
+      <c r="R5" s="239"/>
+      <c r="S5" s="239"/>
+      <c r="T5" s="239"/>
+      <c r="U5" s="239"/>
+      <c r="V5" s="239"/>
+      <c r="W5" s="239"/>
+      <c r="X5" s="239"/>
+      <c r="Y5" s="239"/>
+      <c r="Z5" s="239"/>
       <c r="AB5" s="175"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -4689,44 +4850,44 @@
         <v>286</v>
       </c>
       <c r="C6" s="64">
-        <f>[2]Revenue!C5</f>
-        <v>2021</v>
+        <f>Revenue!C5</f>
+        <v>2022</v>
       </c>
       <c r="D6" s="64">
-        <f>[2]Revenue!D5</f>
-        <v>2022</v>
+        <f>Revenue!D5</f>
+        <v>2023</v>
       </c>
       <c r="E6" s="64">
-        <f>[2]Revenue!E5</f>
-        <v>2023</v>
+        <f>Revenue!E5</f>
+        <v>2024</v>
       </c>
       <c r="F6" s="64">
-        <f>[2]Revenue!F5</f>
-        <v>2024</v>
+        <f>Revenue!F5</f>
+        <v>2025</v>
       </c>
       <c r="G6" s="64">
-        <f>[2]Revenue!G5</f>
-        <v>2025</v>
+        <f>Revenue!G5</f>
+        <v>2026</v>
       </c>
       <c r="H6" s="64">
-        <f>[2]Revenue!H5</f>
-        <v>2026</v>
+        <f>Revenue!H5</f>
+        <v>2027</v>
       </c>
       <c r="I6" s="64">
-        <f>[2]Revenue!I5</f>
-        <v>2027</v>
+        <f>Revenue!I5</f>
+        <v>2028</v>
       </c>
       <c r="J6" s="64">
-        <f>[2]Revenue!J5</f>
-        <v>2028</v>
+        <f>Revenue!J5</f>
+        <v>2029</v>
       </c>
       <c r="K6" s="64">
-        <f>[2]Revenue!K5</f>
-        <v>2029</v>
+        <f>Revenue!K5</f>
+        <v>2030</v>
       </c>
       <c r="L6" s="64">
-        <f>[2]Revenue!L5</f>
-        <v>2030</v>
+        <f>Revenue!L5</f>
+        <v>2031</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="176"/>
@@ -4747,43 +4908,43 @@
         <v>313</v>
       </c>
       <c r="C7" s="177">
-        <f>'FCF &amp; Other'!C33</f>
-        <v>-144710.79255630239</v>
+        <f>'FCF &amp; Other'!C35</f>
+        <v>-145644.79948677309</v>
       </c>
       <c r="D7" s="177">
-        <f>'FCF &amp; Other'!D33</f>
-        <v>-180827.55562070556</v>
+        <f>'FCF &amp; Other'!D35</f>
+        <v>-182527.4188189886</v>
       </c>
       <c r="E7" s="177">
-        <f>'FCF &amp; Other'!E33</f>
-        <v>-132170.03734982488</v>
+        <f>'FCF &amp; Other'!E35</f>
+        <v>-132869.91619046565</v>
       </c>
       <c r="F7" s="177">
-        <f>'FCF &amp; Other'!F33</f>
-        <v>-57965.753543208331</v>
+        <f>'FCF &amp; Other'!F35</f>
+        <v>-58671.16900790167</v>
       </c>
       <c r="G7" s="178">
-        <f>'FCF &amp; Other'!G33</f>
-        <v>-13646</v>
+        <f>'FCF &amp; Other'!G35</f>
+        <v>-14245.849999999999</v>
       </c>
       <c r="H7" s="177">
-        <f>'FCF &amp; Other'!H33</f>
-        <v>14342.228284238139</v>
+        <f>'FCF &amp; Other'!H35</f>
+        <v>14420.319784238134</v>
       </c>
       <c r="I7" s="177">
-        <f>'FCF &amp; Other'!I33</f>
-        <v>10305.473455669546</v>
+        <f>'FCF &amp; Other'!I35</f>
+        <v>10352.458705669551</v>
       </c>
       <c r="J7" s="177">
-        <f>'FCF &amp; Other'!J33</f>
-        <v>27312.030378258893</v>
+        <f>'FCF &amp; Other'!J35</f>
+        <v>27329.331378258892</v>
       </c>
       <c r="K7" s="177">
-        <f>'FCF &amp; Other'!K33</f>
+        <f>'FCF &amp; Other'!K35</f>
         <v>41629.84260598031</v>
       </c>
       <c r="L7" s="177">
-        <f>'FCF &amp; Other'!L33</f>
+        <f>'FCF &amp; Other'!L35</f>
         <v>54334.627403617545</v>
       </c>
       <c r="N7" s="92"/>
@@ -4834,7 +4995,7 @@
       </c>
       <c r="L8" s="120">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>826236.37652885367</v>
+        <v>855131.20993782196</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="7"/>
@@ -4888,23 +5049,23 @@
       <c r="G10" s="200"/>
       <c r="H10" s="120">
         <f>H7/(1+$C$15)^H9</f>
-        <v>13193.389685803782</v>
+        <v>13292.94129444628</v>
       </c>
       <c r="I10" s="120">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>8720.6221083986529</v>
+        <v>8797.0264476393859</v>
       </c>
       <c r="J10" s="120">
         <f t="shared" si="0"/>
-        <v>21260.489755217317</v>
+        <v>21407.580848158967</v>
       </c>
       <c r="K10" s="120">
         <f t="shared" si="0"/>
-        <v>29810.125613144821</v>
+        <v>30060.039748210795</v>
       </c>
       <c r="L10" s="120">
         <f t="shared" si="0"/>
-        <v>35791.136552507713</v>
+        <v>36166.598946149505</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -4923,14 +5084,14 @@
       <c r="K11" s="199"/>
       <c r="L11" s="120">
         <f>L8/(1+C15)^L9</f>
-        <v>544255.85285277048</v>
+        <v>569198.4834352188</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="230" t="s">
         <v>336</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="230"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -4946,14 +5107,14 @@
       </c>
       <c r="C15" s="138">
         <f>WACC!C20</f>
-        <v>8.7076833610889179E-2</v>
+        <v>8.4810311338910996E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="230" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="230"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -4961,7 +5122,7 @@
       </c>
       <c r="C19" s="150">
         <f>SUM(H10:L10)</f>
-        <v>108775.76371507229</v>
+        <v>109724.18728460494</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -4970,7 +5131,7 @@
       </c>
       <c r="C20" s="150">
         <f>L11</f>
-        <v>544255.85285277048</v>
+        <v>569198.4834352188</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -4979,7 +5140,7 @@
       </c>
       <c r="C21" s="154">
         <f>C19+C20</f>
-        <v>653031.61656784278</v>
+        <v>678922.6707198238</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -4987,7 +5148,7 @@
         <v>340</v>
       </c>
       <c r="C22" s="20">
-        <f>Statements!S26</f>
+        <f>'Statement Q'!N182</f>
         <v>73830</v>
       </c>
     </row>
@@ -4996,8 +5157,8 @@
         <v>341</v>
       </c>
       <c r="C23" s="20">
-        <f>Statements!S48+Statements!S56</f>
-        <v>100088</v>
+        <f>'Statement Q'!N181</f>
+        <v>102449</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
@@ -5006,7 +5167,7 @@
       </c>
       <c r="C24" s="154">
         <f>C21+C22-C23</f>
-        <v>626773.61656784278</v>
+        <v>650303.6707198238</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -5024,7 +5185,7 @@
       </c>
       <c r="C26" s="203">
         <f>C24/C25</f>
-        <v>10.315053841446979</v>
+        <v>10.702296968876189</v>
       </c>
     </row>
   </sheetData>
@@ -5067,37 +5228,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="141"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="230" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="146"/>
       <c r="B4" s="93"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="234" t="s">
         <v>345</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
+      <c r="H4" s="234"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="234"/>
+      <c r="K4" s="234"/>
+      <c r="L4" s="234"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
@@ -5195,43 +5356,43 @@
         <v>308</v>
       </c>
       <c r="C7" s="152">
-        <f>'FCF &amp; Other'!C15</f>
-        <v>-116817</v>
+        <f>'FCF &amp; Other'!C17</f>
+        <v>-117752.45000000001</v>
       </c>
       <c r="D7" s="152">
-        <f>'FCF &amp; Other'!D15</f>
-        <v>-176552</v>
+        <f>'FCF &amp; Other'!D17</f>
+        <v>-178256.55</v>
       </c>
       <c r="E7" s="152">
-        <f>'FCF &amp; Other'!E15</f>
-        <v>-136479</v>
+        <f>'FCF &amp; Other'!E17</f>
+        <v>-137186.95000000001</v>
       </c>
       <c r="F7" s="152">
-        <f>'FCF &amp; Other'!F15</f>
-        <v>-58097</v>
+        <f>'FCF &amp; Other'!F17</f>
+        <v>-58838.5</v>
       </c>
       <c r="G7" s="153">
-        <f>'FCF &amp; Other'!G15</f>
-        <v>-6612</v>
+        <f>'FCF &amp; Other'!G17</f>
+        <v>-7211.85</v>
       </c>
       <c r="H7" s="152">
-        <f>'FCF &amp; Other'!H15</f>
-        <v>512.00395319168456</v>
+        <f>'FCF &amp; Other'!H17</f>
+        <v>610.85395319168458</v>
       </c>
       <c r="I7" s="152">
-        <f>'FCF &amp; Other'!I15</f>
-        <v>1632.2367447190918</v>
+        <f>'FCF &amp; Other'!I17</f>
+        <v>1691.7117447190917</v>
       </c>
       <c r="J7" s="152">
-        <f>'FCF &amp; Other'!J15</f>
-        <v>26604.196462624997</v>
+        <f>'FCF &amp; Other'!J17</f>
+        <v>26626.096462624999</v>
       </c>
       <c r="K7" s="152">
-        <f>'FCF &amp; Other'!K15</f>
+        <f>'FCF &amp; Other'!K17</f>
         <v>56290.759647409082</v>
       </c>
       <c r="L7" s="152">
-        <f>'FCF &amp; Other'!L15</f>
+        <f>'FCF &amp; Other'!L17</f>
         <v>79429.467600379314</v>
       </c>
       <c r="N7" s="92"/>
@@ -5241,43 +5402,43 @@
         <v>313</v>
       </c>
       <c r="C8" s="152">
-        <f>'FCF &amp; Other'!C33</f>
-        <v>-144710.79255630239</v>
+        <f>'FCF &amp; Other'!C35</f>
+        <v>-145644.79948677309</v>
       </c>
       <c r="D8" s="152">
-        <f>'FCF &amp; Other'!D33</f>
-        <v>-180827.55562070556</v>
+        <f>'FCF &amp; Other'!D35</f>
+        <v>-182527.4188189886</v>
       </c>
       <c r="E8" s="152">
-        <f>'FCF &amp; Other'!E33</f>
-        <v>-132170.03734982488</v>
+        <f>'FCF &amp; Other'!E35</f>
+        <v>-132869.91619046565</v>
       </c>
       <c r="F8" s="152">
-        <f>'FCF &amp; Other'!F33</f>
-        <v>-57965.753543208331</v>
+        <f>'FCF &amp; Other'!F35</f>
+        <v>-58671.16900790167</v>
       </c>
       <c r="G8" s="153">
-        <f>'FCF &amp; Other'!G33</f>
-        <v>-13646</v>
+        <f>'FCF &amp; Other'!G35</f>
+        <v>-14245.849999999999</v>
       </c>
       <c r="H8" s="152">
-        <f>'FCF &amp; Other'!H33</f>
-        <v>14342.228284238139</v>
+        <f>'FCF &amp; Other'!H35</f>
+        <v>14420.319784238134</v>
       </c>
       <c r="I8" s="152">
-        <f>'FCF &amp; Other'!I33</f>
-        <v>10305.473455669546</v>
+        <f>'FCF &amp; Other'!I35</f>
+        <v>10352.458705669551</v>
       </c>
       <c r="J8" s="152">
-        <f>'FCF &amp; Other'!J33</f>
-        <v>27312.030378258893</v>
+        <f>'FCF &amp; Other'!J35</f>
+        <v>27329.331378258892</v>
       </c>
       <c r="K8" s="152">
-        <f>'FCF &amp; Other'!K33</f>
+        <f>'FCF &amp; Other'!K35</f>
         <v>41629.84260598031</v>
       </c>
       <c r="L8" s="152">
-        <f>'FCF &amp; Other'!L33</f>
+        <f>'FCF &amp; Other'!L35</f>
         <v>54334.627403617545</v>
       </c>
       <c r="N8" s="92"/>
@@ -5286,18 +5447,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="233" t="s">
+      <c r="C10" s="234" t="s">
         <v>210</v>
       </c>
-      <c r="D10" s="233"/>
-      <c r="E10" s="233"/>
-      <c r="F10" s="233"/>
-      <c r="G10" s="233"/>
-      <c r="H10" s="233"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="233"/>
-      <c r="K10" s="233"/>
-      <c r="L10" s="233"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="234"/>
+      <c r="F10" s="234"/>
+      <c r="G10" s="234"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="234"/>
+      <c r="J10" s="234"/>
+      <c r="K10" s="234"/>
+      <c r="L10" s="234"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5396,35 +5557,35 @@
       <c r="C13" s="199"/>
       <c r="D13" s="108">
         <f t="shared" ref="D13:D14" si="2">(D7-C7)/C7</f>
-        <v>0.51135536779749524</v>
+        <v>0.51382455311970132</v>
       </c>
       <c r="E13" s="108">
         <f t="shared" si="1"/>
-        <v>-0.22697562191309076</v>
+        <v>-0.23039602191336014</v>
       </c>
       <c r="F13" s="108">
         <f t="shared" si="1"/>
-        <v>-0.57431546245209886</v>
+        <v>-0.57110716434762931</v>
       </c>
       <c r="G13" s="156">
         <f t="shared" si="1"/>
-        <v>-0.8861903368504398</v>
+        <v>-0.87742974413011887</v>
       </c>
       <c r="H13" s="108">
         <f t="shared" si="1"/>
-        <v>-1.0774355646085427</v>
+        <v>-1.0847014224077989</v>
       </c>
       <c r="I13" s="108">
         <f t="shared" si="1"/>
-        <v>2.1879377777148008</v>
+        <v>1.7694209653223552</v>
       </c>
       <c r="J13" s="108">
         <f t="shared" si="1"/>
-        <v>15.299226536040019</v>
+        <v>14.73914500844602</v>
       </c>
       <c r="K13" s="108">
         <f t="shared" si="1"/>
-        <v>1.1158601698979844</v>
+        <v>1.1141198720745384</v>
       </c>
       <c r="L13" s="108">
         <f t="shared" si="1"/>
@@ -5439,35 +5600,35 @@
       <c r="C14" s="199"/>
       <c r="D14" s="108">
         <f t="shared" si="2"/>
-        <v>0.24957891824378811</v>
+        <v>0.25323677510067949</v>
       </c>
       <c r="E14" s="108">
         <f t="shared" si="1"/>
-        <v>-0.26908243107008617</v>
+        <v>-0.2720550312376247</v>
       </c>
       <c r="F14" s="108">
         <f t="shared" si="1"/>
-        <v>-0.56143045197312169</v>
+        <v>-0.55843150436101696</v>
       </c>
       <c r="G14" s="156">
         <f t="shared" si="1"/>
-        <v>-0.76458513577628007</v>
+        <v>-0.75719164555795015</v>
       </c>
       <c r="H14" s="108">
         <f t="shared" si="1"/>
-        <v>-2.051020686225864</v>
+        <v>-2.0122470603184883</v>
       </c>
       <c r="I14" s="108">
         <f t="shared" si="1"/>
-        <v>-0.28145939031000622</v>
+        <v>-0.28209229333560853</v>
       </c>
       <c r="J14" s="108">
         <f t="shared" si="1"/>
-        <v>1.6502450853660886</v>
+        <v>1.6398879875069596</v>
       </c>
       <c r="K14" s="108">
         <f t="shared" si="1"/>
-        <v>0.52423097182546996</v>
+        <v>0.523266048107485</v>
       </c>
       <c r="L14" s="108">
         <f t="shared" si="1"/>
@@ -5479,18 +5640,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="233" t="s">
+      <c r="C16" s="234" t="s">
         <v>347</v>
       </c>
-      <c r="D16" s="233"/>
-      <c r="E16" s="233"/>
-      <c r="F16" s="233"/>
-      <c r="G16" s="233"/>
-      <c r="H16" s="233"/>
-      <c r="I16" s="233"/>
-      <c r="J16" s="233"/>
-      <c r="K16" s="233"/>
-      <c r="L16" s="233"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="234"/>
+      <c r="F16" s="234"/>
+      <c r="G16" s="234"/>
+      <c r="H16" s="234"/>
+      <c r="I16" s="234"/>
+      <c r="J16" s="234"/>
+      <c r="K16" s="234"/>
+      <c r="L16" s="234"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -5624,18 +5785,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="233" t="s">
+      <c r="C21" s="234" t="s">
         <v>348</v>
       </c>
-      <c r="D21" s="233"/>
-      <c r="E21" s="233"/>
-      <c r="F21" s="233"/>
-      <c r="G21" s="233"/>
-      <c r="H21" s="233"/>
-      <c r="I21" s="233"/>
-      <c r="J21" s="233"/>
-      <c r="K21" s="233"/>
-      <c r="L21" s="233"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="234"/>
+      <c r="G21" s="234"/>
+      <c r="H21" s="234"/>
+      <c r="I21" s="234"/>
+      <c r="J21" s="234"/>
+      <c r="K21" s="234"/>
+      <c r="L21" s="234"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -5686,23 +5847,23 @@
         <v>73</v>
       </c>
       <c r="C23" s="208">
-        <f>'Statement Y'!D193</f>
+        <f>'Statement Y'!D194</f>
         <v>28.44</v>
       </c>
       <c r="D23" s="208">
-        <f>'Statement Y'!E193</f>
+        <f>'Statement Y'!E194</f>
         <v>36.19</v>
       </c>
       <c r="E23" s="208">
-        <f>'Statement Y'!F193</f>
+        <f>'Statement Y'!F194</f>
         <v>25.61</v>
       </c>
       <c r="F23" s="208">
-        <f>'Statement Y'!G193</f>
+        <f>'Statement Y'!G194</f>
         <v>29</v>
       </c>
       <c r="G23" s="209">
-        <f>'Statement Y'!H193</f>
+        <f>'Statement Y'!H194</f>
         <v>13.43</v>
       </c>
       <c r="H23" s="199"/>
@@ -5719,18 +5880,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="233" t="s">
+      <c r="C26" s="234" t="s">
         <v>349</v>
       </c>
-      <c r="D26" s="233"/>
-      <c r="E26" s="233"/>
-      <c r="F26" s="233"/>
-      <c r="G26" s="233"/>
-      <c r="H26" s="233"/>
-      <c r="I26" s="233"/>
-      <c r="J26" s="233"/>
-      <c r="K26" s="233"/>
-      <c r="L26" s="233"/>
+      <c r="D26" s="234"/>
+      <c r="E26" s="234"/>
+      <c r="F26" s="234"/>
+      <c r="G26" s="234"/>
+      <c r="H26" s="234"/>
+      <c r="I26" s="234"/>
+      <c r="J26" s="234"/>
+      <c r="K26" s="234"/>
+      <c r="L26" s="234"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -5937,23 +6098,23 @@
       </c>
       <c r="C33" s="210">
         <f>C32/C7</f>
-        <v>-9.5726368593612232</v>
+        <v>-9.4965898374089015</v>
       </c>
       <c r="D33" s="210">
         <f t="shared" ref="D33:G33" si="11">D32/D7</f>
-        <v>-9.7932484480492992</v>
+        <v>-9.6996020623085091</v>
       </c>
       <c r="E33" s="210">
         <f t="shared" si="11"/>
-        <v>-9.6809268092527052</v>
+        <v>-9.6309686161839725</v>
       </c>
       <c r="F33" s="210">
         <f t="shared" si="11"/>
-        <v>-27.576002203211871</v>
+        <v>-27.228481351496043</v>
       </c>
       <c r="G33" s="211">
         <f t="shared" si="11"/>
-        <v>-128.87717029643073</v>
+        <v>-118.15773345258151</v>
       </c>
       <c r="H33" s="199"/>
       <c r="I33" s="199"/>
@@ -5968,23 +6129,23 @@
       </c>
       <c r="C34" s="210">
         <f>C32/C8</f>
-        <v>-7.727459025317172</v>
+        <v>-7.6779035292746922</v>
       </c>
       <c r="D34" s="210">
         <f t="shared" ref="D34:G34" si="12">D32/D8</f>
-        <v>-9.5616931504991243</v>
+        <v>-9.4726458697948104</v>
       </c>
       <c r="E34" s="210">
         <f t="shared" si="12"/>
-        <v>-9.996541095792848</v>
+        <v>-9.9438853269541578</v>
       </c>
       <c r="F34" s="210">
         <f t="shared" si="12"/>
-        <v>-27.638439976559422</v>
+        <v>-27.306137359973789</v>
       </c>
       <c r="G34" s="211">
         <f t="shared" si="12"/>
-        <v>-62.445833944012897</v>
+        <v>-59.81642724021382</v>
       </c>
       <c r="H34" s="199"/>
       <c r="I34" s="199"/>
@@ -6000,10 +6161,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="230" t="s">
         <v>354</v>
       </c>
-      <c r="C37" s="232"/>
+      <c r="C37" s="230"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -6021,7 +6182,7 @@
       </c>
       <c r="C39" s="214">
         <f>WACC!C20</f>
-        <v>8.7076833610889179E-2</v>
+        <v>8.4810311338910996E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -6029,7 +6190,7 @@
         <v>356</v>
       </c>
       <c r="C40" s="215">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
@@ -6047,7 +6208,7 @@
       </c>
       <c r="C42" s="20">
         <f>(C38*C40)-G30+G31</f>
-        <v>1959478.6900094829</v>
+        <v>2356626.0280113793</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -6056,7 +6217,7 @@
       </c>
       <c r="C43" s="20">
         <f>C42/C41</f>
-        <v>21.192833460855272</v>
+        <v>25.488199078562221</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -6065,14 +6226,14 @@
       </c>
       <c r="C44" s="203">
         <f>C43/(1+C48)^5</f>
-        <v>13.960077257868976</v>
+        <v>16.965635322873371</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="232" t="s">
+      <c r="B46" s="230" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="232"/>
+      <c r="C46" s="230"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
@@ -6089,7 +6250,7 @@
       </c>
       <c r="C48" s="214">
         <f>WACC!C20</f>
-        <v>8.7076833610889179E-2</v>
+        <v>8.4810311338910996E-2</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6097,7 +6258,7 @@
         <v>117</v>
       </c>
       <c r="C49" s="215">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
@@ -6115,7 +6276,7 @@
       </c>
       <c r="C51" s="20">
         <f>(C47*C49)/C50</f>
-        <v>25.517023471526446</v>
+        <v>29.769860716780855</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -6124,14 +6285,14 @@
       </c>
       <c r="C52" s="203">
         <f>C51/(1+C48)^5</f>
-        <v>16.808494235154026</v>
+        <v>19.815625222357927</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="232" t="s">
+      <c r="B54" s="230" t="s">
         <v>360</v>
       </c>
-      <c r="C54" s="232"/>
+      <c r="C54" s="230"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
@@ -6148,7 +6309,7 @@
       </c>
       <c r="C56" s="214">
         <f>WACC!C20</f>
-        <v>8.7076833610889179E-2</v>
+        <v>8.4810311338910996E-2</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6156,7 +6317,7 @@
         <v>362</v>
       </c>
       <c r="C57" s="215">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -6174,7 +6335,7 @@
       </c>
       <c r="C59" s="20">
         <f>(C55*C57)-G30+G31</f>
-        <v>1114769.1754759685</v>
+        <v>1332107.6850904387</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -6183,7 +6344,7 @@
       </c>
       <c r="C60" s="20">
         <f>C59/C58</f>
-        <v>12.056838180282949</v>
+        <v>14.407473000847222</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -6192,7 +6353,7 @@
       </c>
       <c r="C61" s="203">
         <f>C60/(1+C56)^5</f>
-        <v>7.9420428982874549</v>
+        <v>9.5900040682790504</v>
       </c>
     </row>
   </sheetData>
@@ -6241,10 +6402,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="230" t="s">
         <v>364</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="230"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6253,7 +6414,7 @@
       </c>
       <c r="C5" s="216">
         <f>DCF!C26</f>
-        <v>10.315053841446979</v>
+        <v>10.702296968876189</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6262,7 +6423,7 @@
       </c>
       <c r="C6" s="216">
         <f>Multiples!C44</f>
-        <v>13.960077257868976</v>
+        <v>16.965635322873371</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6271,7 +6432,7 @@
       </c>
       <c r="C7" s="216">
         <f>Multiples!C52</f>
-        <v>16.808494235154026</v>
+        <v>19.815625222357927</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6280,7 +6441,7 @@
       </c>
       <c r="C8" s="216">
         <f>Multiples!C61</f>
-        <v>7.9420428982874549</v>
+        <v>9.5900040682790504</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6289,7 +6450,7 @@
       </c>
       <c r="C9" s="203">
         <f>AVERAGE(C5:C8)</f>
-        <v>12.25641705818936</v>
+        <v>14.268390395596635</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6298,7 +6459,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>10.17</v>
+        <v>9.7149999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6307,7 +6468,7 @@
       </c>
       <c r="C11" s="90">
         <f>(C9-C10)/C10</f>
-        <v>0.20515408635096952</v>
+        <v>0.46869690124515029</v>
       </c>
     </row>
   </sheetData>
@@ -6351,103 +6512,103 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="141"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="230" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237" t="s">
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="237"/>
+      <c r="H3" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="238"/>
-      <c r="T3" s="238"/>
-      <c r="U3" s="238"/>
-      <c r="V3" s="238"/>
-      <c r="W3" s="238"/>
-      <c r="X3" s="238"/>
-      <c r="Y3" s="238"/>
-      <c r="Z3" s="238"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="P3" s="239"/>
+      <c r="Q3" s="239"/>
+      <c r="R3" s="239"/>
+      <c r="S3" s="239"/>
+      <c r="T3" s="239"/>
+      <c r="U3" s="239"/>
+      <c r="V3" s="239"/>
+      <c r="W3" s="239"/>
+      <c r="X3" s="239"/>
+      <c r="Y3" s="239"/>
+      <c r="Z3" s="239"/>
       <c r="AB3" s="174"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="146"/>
       <c r="B5" s="93"/>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="234" t="s">
         <v>331</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="238"/>
-      <c r="T5" s="238"/>
-      <c r="U5" s="238"/>
-      <c r="V5" s="238"/>
-      <c r="W5" s="238"/>
-      <c r="X5" s="238"/>
-      <c r="Y5" s="238"/>
-      <c r="Z5" s="238"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="234"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="234"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="234"/>
+      <c r="P5" s="239"/>
+      <c r="Q5" s="239"/>
+      <c r="R5" s="239"/>
+      <c r="S5" s="239"/>
+      <c r="T5" s="239"/>
+      <c r="U5" s="239"/>
+      <c r="V5" s="239"/>
+      <c r="W5" s="239"/>
+      <c r="X5" s="239"/>
+      <c r="Y5" s="239"/>
+      <c r="Z5" s="239"/>
       <c r="AB5" s="175"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C6" s="228">
+      <c r="C6" s="229">
         <f>Revenue!C5</f>
         <v>2022</v>
       </c>
-      <c r="D6" s="228">
+      <c r="D6" s="229">
         <f>Revenue!D5</f>
         <v>2023</v>
       </c>
-      <c r="E6" s="228">
+      <c r="E6" s="229">
         <f>Revenue!E5</f>
         <v>2024</v>
       </c>
-      <c r="F6" s="228">
+      <c r="F6" s="229">
         <f>Revenue!F5</f>
         <v>2025</v>
       </c>
-      <c r="G6" s="228">
+      <c r="G6" s="229">
         <f>Revenue!G5</f>
         <v>2026</v>
       </c>
-      <c r="H6" s="228">
+      <c r="H6" s="229">
         <f>Revenue!H5</f>
         <v>2027</v>
       </c>
-      <c r="I6" s="228">
+      <c r="I6" s="229">
         <f>Revenue!I5</f>
         <v>2028</v>
       </c>
-      <c r="J6" s="228">
+      <c r="J6" s="229">
         <f>Revenue!J5</f>
         <v>2029</v>
       </c>
-      <c r="K6" s="228">
+      <c r="K6" s="229">
         <f>Revenue!K5</f>
         <v>2030</v>
       </c>
-      <c r="L6" s="228">
+      <c r="L6" s="229">
         <f>Revenue!L5</f>
         <v>2031</v>
       </c>
@@ -6470,20 +6631,20 @@
         <v>313</v>
       </c>
       <c r="C7" s="177">
-        <f>'FCF &amp; Other'!C33</f>
-        <v>-144710.79255630239</v>
+        <f>'FCF &amp; Other'!C35</f>
+        <v>-145644.79948677309</v>
       </c>
       <c r="D7" s="177">
-        <f>'FCF &amp; Other'!D33</f>
-        <v>-180827.55562070556</v>
+        <f>'FCF &amp; Other'!D35</f>
+        <v>-182527.4188189886</v>
       </c>
       <c r="E7" s="177">
-        <f>'FCF &amp; Other'!E33</f>
-        <v>-132170.03734982488</v>
+        <f>'FCF &amp; Other'!E35</f>
+        <v>-132869.91619046565</v>
       </c>
       <c r="F7" s="177">
-        <f>'FCF &amp; Other'!F33</f>
-        <v>-57965.753543208331</v>
+        <f>'FCF &amp; Other'!F35</f>
+        <v>-58671.16900790167</v>
       </c>
       <c r="G7" s="178">
         <v>1000</v>
@@ -6538,7 +6699,7 @@
       <c r="K8" s="199"/>
       <c r="L8" s="120">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>876880.0892563524</v>
+        <v>907546.01588276098</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="7"/>
@@ -6592,23 +6753,23 @@
       <c r="G10" s="200"/>
       <c r="H10" s="120">
         <f>H7/(1+$C$21)^H9</f>
-        <v>2069.7709034294171</v>
+        <v>2074.0953293695843</v>
       </c>
       <c r="I10" s="120">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>4283.9515926830245</v>
+        <v>4301.8714353127252</v>
       </c>
       <c r="J10" s="120">
         <f t="shared" si="1"/>
-        <v>8866.7983582354336</v>
+        <v>8922.4914515305536</v>
       </c>
       <c r="K10" s="120">
         <f t="shared" si="1"/>
-        <v>18352.241248451424</v>
+        <v>18506.097845959568</v>
       </c>
       <c r="L10" s="120">
         <f t="shared" si="1"/>
-        <v>37984.934948761918</v>
+        <v>38383.411107161264</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -6627,15 +6788,15 @@
       <c r="K11" s="199"/>
       <c r="L11" s="120">
         <f>L8/(1+C21)^L9</f>
-        <v>577615.72158420121</v>
+        <v>604087.1972450912</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="239" t="s">
+      <c r="B14" s="240" t="s">
         <v>373</v>
       </c>
-      <c r="C14" s="240"/>
+      <c r="C14" s="241"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="217" t="s">
@@ -6643,7 +6804,7 @@
       </c>
       <c r="C15" s="218">
         <f>Overview!C3</f>
-        <v>10.17</v>
+        <v>9.7149999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6652,7 +6813,7 @@
       </c>
       <c r="C16" s="218">
         <f>C36</f>
-        <v>10.251557998054119</v>
+        <v>10.697581824702942</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6662,20 +6823,20 @@
       <c r="C17" s="219">
         <v>1.25</v>
       </c>
-      <c r="E17" s="241" t="s">
+      <c r="E17" s="242" t="s">
         <v>377</v>
       </c>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="241"/>
+      <c r="F17" s="242"/>
+      <c r="G17" s="242"/>
+      <c r="H17" s="242"/>
+      <c r="I17" s="242"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="239" t="s">
+      <c r="B19" s="240" t="s">
         <v>336</v>
       </c>
-      <c r="C19" s="240"/>
+      <c r="C19" s="241"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="111" t="s">
@@ -6691,7 +6852,7 @@
       </c>
       <c r="C21" s="221">
         <f>WACC!C20</f>
-        <v>8.7076833610889179E-2</v>
+        <v>8.4810311338910996E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6709,7 +6870,7 @@
       </c>
       <c r="C23" s="222">
         <f>C15*C22</f>
-        <v>617959.71</v>
+        <v>590312.54500000004</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6736,15 +6897,15 @@
       </c>
       <c r="C26" s="223">
         <f>C23+C25-C24</f>
-        <v>644217.71</v>
+        <v>616570.54500000004</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="239" t="s">
+      <c r="B28" s="240" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="240"/>
+      <c r="C28" s="241"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="111" t="s">
@@ -6752,7 +6913,7 @@
       </c>
       <c r="C29" s="222">
         <f>SUM(H10:L10)</f>
-        <v>71557.697051561219</v>
+        <v>72187.967169333686</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6761,7 +6922,7 @@
       </c>
       <c r="C30" s="222">
         <f>L11</f>
-        <v>577615.72158420121</v>
+        <v>604087.1972450912</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6770,7 +6931,7 @@
       </c>
       <c r="C31" s="225">
         <f>C29+C30</f>
-        <v>649173.41863576241</v>
+        <v>676275.16441442491</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6797,7 +6958,7 @@
       </c>
       <c r="C34" s="225">
         <f>C31+C32-C33</f>
-        <v>622915.41863576241</v>
+        <v>650017.16441442491</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6815,22 +6976,22 @@
       </c>
       <c r="C36" s="227">
         <f>C34/C35</f>
-        <v>10.251557998054119</v>
+        <v>10.697581824702942</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="233" t="s">
+      <c r="C39" s="234" t="s">
         <v>379</v>
       </c>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
-      <c r="I39" s="233"/>
-      <c r="J39" s="233"/>
-      <c r="K39" s="233"/>
-      <c r="L39" s="233"/>
+      <c r="D39" s="234"/>
+      <c r="E39" s="234"/>
+      <c r="F39" s="234"/>
+      <c r="G39" s="234"/>
+      <c r="H39" s="234"/>
+      <c r="I39" s="234"/>
+      <c r="J39" s="234"/>
+      <c r="K39" s="234"/>
+      <c r="L39" s="234"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="64">
@@ -6880,19 +7041,19 @@
       </c>
       <c r="C41" s="177">
         <f>C7</f>
-        <v>-144710.79255630239</v>
+        <v>-145644.79948677309</v>
       </c>
       <c r="D41" s="177">
         <f t="shared" si="2"/>
-        <v>-180827.55562070556</v>
+        <v>-182527.4188189886</v>
       </c>
       <c r="E41" s="177">
         <f t="shared" si="2"/>
-        <v>-132170.03734982488</v>
+        <v>-132869.91619046565</v>
       </c>
       <c r="F41" s="177">
         <f t="shared" si="2"/>
-        <v>-57965.753543208331</v>
+        <v>-58671.16900790167</v>
       </c>
       <c r="G41" s="178">
         <f t="shared" si="2"/>
@@ -6924,24 +7085,24 @@
         <v>308</v>
       </c>
       <c r="C42" s="177">
-        <f>'FCF &amp; Other'!C15</f>
-        <v>-116817</v>
+        <f>'FCF &amp; Other'!C17</f>
+        <v>-117752.45000000001</v>
       </c>
       <c r="D42" s="177">
-        <f>'FCF &amp; Other'!D15</f>
-        <v>-176552</v>
+        <f>'FCF &amp; Other'!D17</f>
+        <v>-178256.55</v>
       </c>
       <c r="E42" s="177">
-        <f>'FCF &amp; Other'!E15</f>
-        <v>-136479</v>
+        <f>'FCF &amp; Other'!E17</f>
+        <v>-137186.95000000001</v>
       </c>
       <c r="F42" s="177">
-        <f>'FCF &amp; Other'!F15</f>
-        <v>-58097</v>
+        <f>'FCF &amp; Other'!F17</f>
+        <v>-58838.5</v>
       </c>
       <c r="G42" s="178">
-        <f>'FCF &amp; Other'!G15</f>
-        <v>-6612</v>
+        <f>'FCF &amp; Other'!G17</f>
+        <v>-7211.85</v>
       </c>
       <c r="H42" s="104">
         <f>H41/H43</f>
@@ -6970,23 +7131,23 @@
       </c>
       <c r="C43" s="108">
         <f>C41/C42</f>
-        <v>1.2387819628675825</v>
+        <v>1.2368727740847267</v>
       </c>
       <c r="D43" s="108">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
-        <v>1.0242169764188769</v>
+        <v>1.0239591129694174</v>
       </c>
       <c r="E43" s="108">
         <f t="shared" si="4"/>
-        <v>0.96842765077282866</v>
+        <v>0.96853174584365087</v>
       </c>
       <c r="F43" s="108">
         <f t="shared" si="4"/>
-        <v>0.99774090819161632</v>
+        <v>0.99715609690766538</v>
       </c>
       <c r="G43" s="156">
         <f t="shared" si="4"/>
-        <v>-0.15124016938898971</v>
+        <v>-0.13866067652544076</v>
       </c>
       <c r="H43" s="116">
         <v>0.9</v>
@@ -7055,19 +7216,19 @@
       </c>
       <c r="C45" s="108">
         <f>C41/C44</f>
-        <v>-0.67865101816464801</v>
+        <v>-0.68303123572229951</v>
       </c>
       <c r="D45" s="108">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
-        <v>-0.64372060667368758</v>
+        <v>-0.64977188002915032</v>
       </c>
       <c r="E45" s="108">
         <f t="shared" si="6"/>
-        <v>-0.37095259136238068</v>
+        <v>-0.372916893368956</v>
       </c>
       <c r="F45" s="108">
         <f t="shared" si="6"/>
-        <v>-0.13807517524042451</v>
+        <v>-0.13975548400812188</v>
       </c>
       <c r="G45" s="156">
         <f t="shared" si="6"/>
@@ -7096,19 +7257,19 @@
       <c r="C46" s="199"/>
       <c r="D46" s="108">
         <f>D41/C41-1</f>
-        <v>0.24957891824378819</v>
+        <v>0.25323677510067943</v>
       </c>
       <c r="E46" s="108">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
-        <v>-0.26908243107008623</v>
+        <v>-0.27205503123762476</v>
       </c>
       <c r="F46" s="108">
         <f t="shared" si="7"/>
-        <v>-0.56143045197312169</v>
+        <v>-0.55843150436101696</v>
       </c>
       <c r="G46" s="156">
         <f t="shared" si="7"/>
-        <v>-1.0172515656033798</v>
+        <v>-1.0170441465017566</v>
       </c>
       <c r="H46" s="117">
         <f t="shared" si="7"/>
@@ -7138,23 +7299,23 @@
       <c r="C47" s="199"/>
       <c r="D47" s="108">
         <f>D42/C42-1</f>
-        <v>0.51135536779749513</v>
+        <v>0.51382455311970121</v>
       </c>
       <c r="E47" s="108">
         <f t="shared" si="7"/>
-        <v>-0.22697562191309073</v>
+        <v>-0.23039602191336017</v>
       </c>
       <c r="F47" s="108">
         <f t="shared" si="7"/>
-        <v>-0.57431546245209886</v>
+        <v>-0.57110716434762931</v>
       </c>
       <c r="G47" s="156">
         <f t="shared" si="7"/>
-        <v>-0.8861903368504398</v>
+        <v>-0.87742974413011887</v>
       </c>
       <c r="H47" s="117">
         <f t="shared" si="7"/>
-        <v>-1.3781004234724743</v>
+        <v>-1.346651691313602</v>
       </c>
       <c r="I47" s="117">
         <f t="shared" si="7"/>
@@ -7221,23 +7382,23 @@
       </c>
       <c r="C49" s="108">
         <f>C42/C44</f>
-        <v>-0.547837342250027</v>
+        <v>-0.55222432737897043</v>
       </c>
       <c r="D49" s="108">
         <f t="shared" ref="D49:L49" si="9">D42/D44</f>
-        <v>-0.62850023139083688</v>
+        <v>-0.63456818909971158</v>
       </c>
       <c r="E49" s="108">
         <f t="shared" si="9"/>
-        <v>-0.38304626170716166</v>
+        <v>-0.3850332164839082</v>
       </c>
       <c r="F49" s="108">
         <f t="shared" si="9"/>
-        <v>-0.13838780599933781</v>
+        <v>-0.14015406859720875</v>
       </c>
       <c r="G49" s="156">
         <f t="shared" si="9"/>
-        <v>-1.3758060388147093E-2</v>
+        <v>-1.500621110257995E-2</v>
       </c>
       <c r="H49" s="117">
         <f t="shared" si="9"/>
@@ -7303,7 +7464,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="A1:T195"/>
+  <dimension ref="A1:T207"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -11463,162 +11624,159 @@
       <c r="J152" s="27"/>
       <c r="K152" s="27"/>
     </row>
-    <row r="153" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2"/>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B154" s="1"/>
-    </row>
-    <row r="155" spans="1:11" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="4"/>
-      <c r="B155" s="15" t="s">
+    <row r="153" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B153" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C153" s="29">
+        <v>2023</v>
+      </c>
+      <c r="D153" s="29">
+        <v>1319</v>
+      </c>
+      <c r="E153" s="29">
+        <v>1897</v>
+      </c>
+      <c r="F153" s="29">
+        <v>787</v>
+      </c>
+      <c r="G153" s="29">
+        <v>983</v>
+      </c>
+      <c r="H153" s="29">
+        <v>954</v>
+      </c>
+      <c r="I153" s="27"/>
+      <c r="J153" s="27"/>
+      <c r="K153" s="27"/>
+    </row>
+    <row r="154" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2"/>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B155" s="1"/>
+    </row>
+    <row r="156" spans="1:11" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="4"/>
+      <c r="B156" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C155" s="98"/>
-    </row>
-    <row r="156" spans="1:11" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="7"/>
-      <c r="B156" s="17" t="s">
+      <c r="C156" s="98"/>
+    </row>
+    <row r="157" spans="1:11" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="7"/>
+      <c r="B157" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C156" s="99"/>
-      <c r="D156" s="78">
-        <f t="shared" ref="D156:H160" si="28">IF(C5=0,
+      <c r="C157" s="99"/>
+      <c r="D157" s="78">
+        <f t="shared" ref="D157:H161" si="28">IF(C5=0,
 IF(D5=0,0,IF(D5&gt;0,1,-1)),
 (D5-C5)/ABS(C5)
 )</f>
         <v>0.43420300382708826</v>
       </c>
-      <c r="E156" s="78">
+      <c r="E157" s="78">
         <f t="shared" si="28"/>
         <v>0.31738520773051077</v>
       </c>
-      <c r="F156" s="78">
+      <c r="F157" s="78">
         <f t="shared" si="28"/>
         <v>0.26837421238118969</v>
       </c>
-      <c r="G156" s="78">
+      <c r="G157" s="78">
         <f t="shared" si="28"/>
         <v>0.17826039365813545</v>
       </c>
-      <c r="H156" s="78">
+      <c r="H157" s="78">
         <f t="shared" si="28"/>
         <v>0.14477398270182201</v>
       </c>
-      <c r="I156" s="78"/>
-      <c r="J156" s="78"/>
-      <c r="K156" s="78"/>
-    </row>
-    <row r="157" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B157" s="9" t="s">
+      <c r="I157" s="78"/>
+      <c r="J157" s="78"/>
+      <c r="K157" s="78"/>
+    </row>
+    <row r="158" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B158" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C157" s="100"/>
-      <c r="D157" s="77">
+      <c r="C158" s="100"/>
+      <c r="D158" s="77">
         <f t="shared" si="28"/>
         <v>0.55362119650288244</v>
       </c>
-      <c r="E157" s="77">
+      <c r="E158" s="77">
         <f t="shared" si="28"/>
         <v>0.34254435543323342</v>
       </c>
-      <c r="F157" s="77">
+      <c r="F158" s="77">
         <f t="shared" si="28"/>
         <v>0.13493552490687949</v>
       </c>
-      <c r="G157" s="77">
+      <c r="G158" s="77">
         <f t="shared" si="28"/>
         <v>8.8080896049543986E-2</v>
       </c>
-      <c r="H157" s="77">
+      <c r="H158" s="77">
         <f t="shared" si="28"/>
         <v>0.14221026575955653</v>
       </c>
-      <c r="I157" s="77"/>
-      <c r="J157" s="77"/>
-      <c r="K157" s="77"/>
-    </row>
-    <row r="158" spans="1:11" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="7"/>
-      <c r="B158" s="17" t="s">
+      <c r="I158" s="77"/>
+      <c r="J158" s="77"/>
+      <c r="K158" s="77"/>
+    </row>
+    <row r="159" spans="1:11" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="7"/>
+      <c r="B159" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C158" s="99"/>
-      <c r="D158" s="78">
+      <c r="C159" s="99"/>
+      <c r="D159" s="78">
         <f t="shared" si="28"/>
         <v>0.3692349233053972</v>
       </c>
-      <c r="E158" s="78">
+      <c r="E159" s="78">
         <f t="shared" si="28"/>
         <v>0.30185445030149038</v>
       </c>
-      <c r="F158" s="78">
+      <c r="F159" s="78">
         <f t="shared" si="28"/>
         <v>0.35332055487261349</v>
       </c>
-      <c r="G158" s="78">
+      <c r="G159" s="78">
         <f t="shared" si="28"/>
         <v>0.22640429122468658</v>
       </c>
-      <c r="H158" s="78">
+      <c r="H159" s="78">
         <f t="shared" si="28"/>
         <v>0.14598829678565287</v>
       </c>
-      <c r="I158" s="78"/>
-      <c r="J158" s="78"/>
-      <c r="K158" s="78"/>
-    </row>
-    <row r="159" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B159" s="9" t="s">
+      <c r="I159" s="78"/>
+      <c r="J159" s="78"/>
+      <c r="K159" s="78"/>
+    </row>
+    <row r="160" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B160" s="9" t="s">
         <v>9</v>
-      </c>
-      <c r="C159" s="100"/>
-      <c r="D159" s="77">
-        <f t="shared" si="28"/>
-        <v>1.476519594154333</v>
-      </c>
-      <c r="E159" s="77">
-        <f t="shared" si="28"/>
-        <v>0.4213642044333355</v>
-      </c>
-      <c r="F159" s="77">
-        <f t="shared" si="28"/>
-        <v>-2.8129813635852787E-2</v>
-      </c>
-      <c r="G159" s="77">
-        <f t="shared" si="28"/>
-        <v>-0.17603803874619067</v>
-      </c>
-      <c r="H159" s="77">
-        <f t="shared" si="28"/>
-        <v>-0.17242774232429889</v>
-      </c>
-      <c r="I159" s="77"/>
-      <c r="J159" s="77"/>
-      <c r="K159" s="77"/>
-    </row>
-    <row r="160" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B160" s="12" t="s">
-        <v>10</v>
       </c>
       <c r="C160" s="100"/>
       <c r="D160" s="77">
         <f t="shared" si="28"/>
-        <v>1.3103615949076119</v>
+        <v>1.476519594154333</v>
       </c>
       <c r="E160" s="77">
         <f t="shared" si="28"/>
-        <v>0.74579546541662678</v>
+        <v>0.4213642044333355</v>
       </c>
       <c r="F160" s="77">
         <f t="shared" si="28"/>
-        <v>0.23127000131515496</v>
+        <v>-2.8129813635852787E-2</v>
       </c>
       <c r="G160" s="77">
         <f t="shared" si="28"/>
-        <v>4.4665586669752372E-2</v>
+        <v>-0.17603803874619067</v>
       </c>
       <c r="H160" s="77">
         <f t="shared" si="28"/>
-        <v>3.5078899832998195E-2</v>
+        <v>-0.17242774232429889</v>
       </c>
       <c r="I160" s="77"/>
       <c r="J160" s="77"/>
@@ -11626,619 +11784,896 @@
     </row>
     <row r="161" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B161" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C161" s="100"/>
       <c r="D161" s="77">
-        <f t="shared" ref="D161:H162" si="29">IF(C13=0,
+        <f t="shared" si="28"/>
+        <v>1.3103615949076119</v>
+      </c>
+      <c r="E161" s="77">
+        <f t="shared" si="28"/>
+        <v>0.74579546541662678</v>
+      </c>
+      <c r="F161" s="77">
+        <f t="shared" si="28"/>
+        <v>0.23127000131515496</v>
+      </c>
+      <c r="G161" s="77">
+        <f t="shared" si="28"/>
+        <v>4.4665586669752372E-2</v>
+      </c>
+      <c r="H161" s="77">
+        <f t="shared" si="28"/>
+        <v>3.5078899832998195E-2</v>
+      </c>
+      <c r="I161" s="77"/>
+      <c r="J161" s="77"/>
+      <c r="K161" s="77"/>
+    </row>
+    <row r="162" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B162" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" s="100"/>
+      <c r="D162" s="77">
+        <f t="shared" ref="D162:H163" si="29">IF(C13=0,
 IF(D13=0,0,IF(D13&gt;0,1,-1)),
 (D13-C13)/ABS(C13)
 )</f>
         <v>1.0388481658221413</v>
       </c>
-      <c r="E161" s="77">
+      <c r="E162" s="77">
         <f t="shared" si="29"/>
         <v>0.40027426788170289</v>
       </c>
-      <c r="F161" s="77">
+      <c r="F162" s="77">
         <f t="shared" si="29"/>
         <v>5.9081836327345309E-2</v>
       </c>
-      <c r="G161" s="77">
+      <c r="G162" s="77">
         <f t="shared" si="29"/>
         <v>-6.9938470633218272E-2</v>
       </c>
-      <c r="H161" s="77">
+      <c r="H162" s="77">
         <f t="shared" si="29"/>
         <v>-2.885333084530696E-2</v>
       </c>
-      <c r="I161" s="77"/>
-      <c r="J161" s="77"/>
-      <c r="K161" s="77"/>
-    </row>
-    <row r="162" spans="1:11" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="7"/>
-      <c r="B162" s="17" t="s">
+      <c r="I162" s="77"/>
+      <c r="J162" s="77"/>
+      <c r="K162" s="77"/>
+    </row>
+    <row r="163" spans="1:11" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="7"/>
+      <c r="B163" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C162" s="99"/>
-      <c r="D162" s="78">
+      <c r="C163" s="99"/>
+      <c r="D163" s="78">
         <f t="shared" si="29"/>
         <v>-3.5505434147481596</v>
       </c>
-      <c r="E162" s="78">
+      <c r="E163" s="78">
         <f t="shared" si="29"/>
         <v>-0.51135536779749524</v>
       </c>
-      <c r="F162" s="78">
+      <c r="F163" s="78">
         <f t="shared" si="29"/>
         <v>0.22697562191309076</v>
       </c>
-      <c r="G162" s="78">
+      <c r="G163" s="78">
         <f t="shared" si="29"/>
         <v>0.57431546245209886</v>
       </c>
-      <c r="H162" s="78">
+      <c r="H163" s="78">
         <f t="shared" si="29"/>
         <v>0.8861903368504398</v>
       </c>
-      <c r="I162" s="78"/>
-      <c r="J162" s="78"/>
-      <c r="K162" s="78"/>
-    </row>
-    <row r="163" spans="1:11" s="79" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="7"/>
-      <c r="B163" s="80" t="s">
+      <c r="I163" s="78"/>
+      <c r="J163" s="78"/>
+      <c r="K163" s="78"/>
+    </row>
+    <row r="164" spans="1:11" s="79" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="7"/>
+      <c r="B164" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="C163" s="99"/>
-      <c r="D163" s="81">
+      <c r="C164" s="99"/>
+      <c r="D164" s="81">
         <f>IF(C19=0,
 IF(D19=0,0,IF(D19&gt;0,1,-1)),
 (D19-C19)/ABS(C19)
 )</f>
         <v>-3.3306170392394376</v>
       </c>
-      <c r="E163" s="81">
+      <c r="E164" s="81">
         <f>IF(D19=0,
 IF(E19=0,0,IF(E19&gt;0,1,-1)),
 (E19-D19)/ABS(D19)
 )</f>
         <v>-0.488934471388976</v>
       </c>
-      <c r="F163" s="81">
+      <c r="F164" s="81">
         <f>IF(E19=0,
 IF(F19=0,0,IF(F19&gt;0,1,-1)),
 (F19-E19)/ABS(E19)
 )</f>
         <v>0.22953610037401159</v>
       </c>
-      <c r="G163" s="81">
+      <c r="G164" s="81">
         <f>IF(F19=0,
 IF(G19=0,0,IF(G19&gt;0,1,-1)),
 (G19-F19)/ABS(F19)
 )</f>
         <v>0.58762985621610442</v>
       </c>
-      <c r="H163" s="81">
+      <c r="H164" s="81">
         <f>IF(G19=0,
 IF(H19=0,0,IF(H19&gt;0,1,-1)),
 (H19-G19)/ABS(G19)
 )</f>
         <v>0.83981652362437509</v>
       </c>
-      <c r="I163" s="81"/>
-      <c r="J163" s="81"/>
-      <c r="K163" s="81"/>
-    </row>
-    <row r="164" spans="1:11" s="79" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="7"/>
-      <c r="B164" s="80" t="s">
+      <c r="I164" s="81"/>
+      <c r="J164" s="81"/>
+      <c r="K164" s="81"/>
+    </row>
+    <row r="165" spans="1:11" s="79" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="7"/>
+      <c r="B165" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C164" s="99"/>
-      <c r="D164" s="81">
+      <c r="C165" s="99"/>
+      <c r="D165" s="81">
         <f>IF(C21=0,
 IF(D21=0,0,IF(D21&gt;0,1,-1)),
 (D21-C21)/ABS(C21)
 )</f>
         <v>-3.3295104792613222</v>
       </c>
-      <c r="E164" s="81">
+      <c r="E165" s="81">
         <f>IF(D21=0,
 IF(E21=0,0,IF(E21&gt;0,1,-1)),
 (E21-D21)/ABS(D21)
 )</f>
         <v>-0.49072875144929379</v>
       </c>
-      <c r="F164" s="81">
+      <c r="F165" s="81">
         <f>IF(E21=0,
 IF(F21=0,0,IF(F21&gt;0,1,-1)),
 (F21-E21)/ABS(E21)
 )</f>
         <v>0.22288896710683184</v>
       </c>
-      <c r="G164" s="81">
+      <c r="G165" s="81">
         <f>IF(F21=0,
 IF(G21=0,0,IF(G21&gt;0,1,-1)),
 (G21-F21)/ABS(F21)
 )</f>
         <v>0.57243671695218612</v>
       </c>
-      <c r="H164" s="81">
+      <c r="H165" s="81">
         <f>IF(G21=0,
 IF(H21=0,0,IF(H21&gt;0,1,-1)),
 (H21-G21)/ABS(G21)
 )</f>
         <v>1.039400618517949</v>
       </c>
-      <c r="I164" s="81"/>
-      <c r="J164" s="81"/>
-      <c r="K164" s="81"/>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B165" s="1"/>
-    </row>
-    <row r="166" spans="1:11" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="4"/>
-      <c r="B166" s="15" t="s">
+      <c r="I165" s="81"/>
+      <c r="J165" s="81"/>
+      <c r="K165" s="81"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B166" s="1"/>
+    </row>
+    <row r="167" spans="1:11" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="4"/>
+      <c r="B167" s="15" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="167" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B167" s="9" t="s">
+    <row r="168" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B168" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C167" s="77">
-        <f t="shared" ref="C167:H167" si="30">C7/C5</f>
+      <c r="C168" s="77">
+        <f t="shared" ref="C168:H168" si="30">C7/C5</f>
         <v>0.64765229322625562</v>
       </c>
-      <c r="D167" s="77">
+      <c r="D168" s="77">
         <f t="shared" si="30"/>
         <v>0.61831423841525468</v>
       </c>
-      <c r="E167" s="77">
+      <c r="E168" s="77">
         <f t="shared" si="30"/>
         <v>0.6110248834146168</v>
       </c>
-      <c r="F167" s="77">
+      <c r="F168" s="77">
         <f t="shared" si="30"/>
         <v>0.65194681994616877</v>
       </c>
-      <c r="G167" s="77">
+      <c r="G168" s="77">
         <f t="shared" si="30"/>
         <v>0.67858546543341913</v>
       </c>
-      <c r="H167" s="77">
+      <c r="H168" s="77">
         <f t="shared" si="30"/>
         <v>0.67930527205045454</v>
-      </c>
-      <c r="I167" s="77"/>
-      <c r="J167" s="77"/>
-      <c r="K167" s="77"/>
-    </row>
-    <row r="168" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B168" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C168" s="77">
-        <f t="shared" ref="C168:H168" si="31">C14/C5</f>
-        <v>-0.17266288666034424</v>
-      </c>
-      <c r="D168" s="77">
-        <f t="shared" si="31"/>
-        <v>-0.547837342250027</v>
-      </c>
-      <c r="E168" s="77">
-        <f t="shared" si="31"/>
-        <v>-0.62850023139083688</v>
-      </c>
-      <c r="F168" s="77">
-        <f t="shared" si="31"/>
-        <v>-0.38304626170716166</v>
-      </c>
-      <c r="G168" s="77">
-        <f t="shared" si="31"/>
-        <v>-0.13838780599933781</v>
-      </c>
-      <c r="H168" s="77">
-        <f t="shared" si="31"/>
-        <v>-1.3758060388147093E-2</v>
       </c>
       <c r="I168" s="77"/>
       <c r="J168" s="77"/>
       <c r="K168" s="77"/>
     </row>
-    <row r="169" spans="1:11" s="84" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="1"/>
-      <c r="B169" s="82" t="s">
+    <row r="169" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B169" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C169" s="77">
+        <f t="shared" ref="C169:H169" si="31">C14/C5</f>
+        <v>-0.17266288666034424</v>
+      </c>
+      <c r="D169" s="77">
+        <f t="shared" si="31"/>
+        <v>-0.547837342250027</v>
+      </c>
+      <c r="E169" s="77">
+        <f t="shared" si="31"/>
+        <v>-0.62850023139083688</v>
+      </c>
+      <c r="F169" s="77">
+        <f t="shared" si="31"/>
+        <v>-0.38304626170716166</v>
+      </c>
+      <c r="G169" s="77">
+        <f t="shared" si="31"/>
+        <v>-0.13838780599933781</v>
+      </c>
+      <c r="H169" s="77">
+        <f t="shared" si="31"/>
+        <v>-1.3758060388147093E-2</v>
+      </c>
+      <c r="I169" s="77"/>
+      <c r="J169" s="77"/>
+      <c r="K169" s="77"/>
+    </row>
+    <row r="170" spans="1:11" s="84" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="1"/>
+      <c r="B170" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="C169" s="83">
-        <f t="shared" ref="C169:H169" si="32">C21/C5</f>
+      <c r="C170" s="83">
+        <f t="shared" ref="C170:H170" si="32">C21/C5</f>
         <v>-0.18356571628429413</v>
       </c>
-      <c r="D169" s="83">
+      <c r="D170" s="83">
         <f t="shared" si="32"/>
         <v>-0.55414030661295388</v>
       </c>
-      <c r="E169" s="83">
+      <c r="E170" s="83">
         <f t="shared" si="32"/>
         <v>-0.62705492862482648</v>
       </c>
-      <c r="F169" s="83">
+      <c r="F170" s="83">
         <f t="shared" si="32"/>
         <v>-0.384185754099787</v>
       </c>
-      <c r="G169" s="83">
+      <c r="G170" s="83">
         <f t="shared" si="32"/>
         <v>-0.13941207156519689</v>
       </c>
-      <c r="H169" s="83">
+      <c r="H170" s="83">
         <f t="shared" si="32"/>
         <v>4.7982588105062313E-3</v>
       </c>
-      <c r="I169" s="83"/>
-      <c r="J169" s="83"/>
-      <c r="K169" s="83"/>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B170" s="1"/>
-    </row>
-    <row r="171" spans="1:11" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="4"/>
-      <c r="B171" s="15" t="s">
+      <c r="I170" s="83"/>
+      <c r="J170" s="83"/>
+      <c r="K170" s="83"/>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B171" s="1"/>
+    </row>
+    <row r="172" spans="1:11" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="4"/>
+      <c r="B172" s="15" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B172" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C172" s="27">
-        <v>1711</v>
-      </c>
-      <c r="D172" s="27">
-        <v>2074</v>
-      </c>
-      <c r="E172" s="27">
-        <v>2856</v>
-      </c>
-      <c r="F172" s="27">
-        <v>3601</v>
-      </c>
-      <c r="G172" s="27">
-        <v>4203</v>
-      </c>
-      <c r="H172" s="27">
-        <v>4514</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B173" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C173" s="27">
+        <v>1711</v>
+      </c>
+      <c r="D173" s="27">
+        <v>2074</v>
+      </c>
+      <c r="E173" s="27">
+        <v>2856</v>
+      </c>
+      <c r="F173" s="27">
+        <v>3601</v>
+      </c>
+      <c r="G173" s="27">
+        <v>4203</v>
+      </c>
+      <c r="H173" s="27">
+        <v>4514</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B174" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C173" s="115">
-        <f t="shared" ref="C173:H173" si="33">C181/C172</f>
+      <c r="C174" s="115">
+        <f t="shared" ref="C174:H174" si="33">C182/C173</f>
         <v>40.351841028638226</v>
       </c>
-      <c r="D173" s="115">
+      <c r="D174" s="115">
         <f t="shared" si="33"/>
         <v>46.053037608486015</v>
       </c>
-      <c r="E173" s="115">
+      <c r="E174" s="115">
         <f t="shared" si="33"/>
         <v>45.159313725490193</v>
       </c>
-      <c r="F173" s="115">
+      <c r="F174" s="115">
         <f t="shared" si="33"/>
         <v>45.94168286587059</v>
       </c>
-      <c r="G173" s="115">
+      <c r="G174" s="115">
         <f t="shared" si="33"/>
         <v>46.754699024506309</v>
       </c>
-      <c r="H173" s="115">
+      <c r="H174" s="115">
         <f t="shared" si="33"/>
         <v>48.61785556047851</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B174" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C174" s="27">
-        <v>1997000</v>
-      </c>
-      <c r="D174" s="27">
-        <v>2768000</v>
-      </c>
-      <c r="E174" s="27">
-        <v>3284000</v>
-      </c>
-      <c r="F174" s="27">
-        <v>3947000</v>
-      </c>
-      <c r="G174" s="27">
-        <v>4420000</v>
-      </c>
-      <c r="H174" s="27">
-        <v>4873000</v>
-      </c>
-      <c r="I174" s="27"/>
-    </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B175" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C175" s="101">
-        <v>0.81</v>
-      </c>
-      <c r="D175" s="101">
-        <v>0.79</v>
-      </c>
-      <c r="E175" s="101">
-        <v>0.8</v>
-      </c>
-      <c r="F175" s="101">
-        <v>0.82</v>
-      </c>
-      <c r="G175" s="101">
-        <v>0.81</v>
-      </c>
-      <c r="H175" s="101">
-        <v>0.83</v>
+        <v>182</v>
+      </c>
+      <c r="C175" s="27">
+        <v>1997000</v>
+      </c>
+      <c r="D175" s="27">
+        <v>2768000</v>
+      </c>
+      <c r="E175" s="27">
+        <v>3284000</v>
+      </c>
+      <c r="F175" s="27">
+        <v>3947000</v>
+      </c>
+      <c r="G175" s="27">
+        <v>4420000</v>
+      </c>
+      <c r="H175" s="27">
+        <v>4873000</v>
       </c>
       <c r="I175" s="27"/>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B176" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C176" s="102">
-        <v>3.0800000000000001E-2</v>
-      </c>
-      <c r="D176" s="102">
-        <v>2.98E-2</v>
-      </c>
-      <c r="E176" s="102">
-        <v>2.98E-2</v>
-      </c>
-      <c r="F176" s="102">
-        <v>2.92E-2</v>
-      </c>
-      <c r="G176" s="102">
-        <v>2.8299999999999999E-2</v>
-      </c>
-      <c r="H176" s="138">
-        <f>H182/(H174*H175)</f>
-        <v>3.0029990678906885E-2</v>
+        <v>180</v>
+      </c>
+      <c r="C176" s="101">
+        <v>0.81</v>
+      </c>
+      <c r="D176" s="101">
+        <v>0.79</v>
+      </c>
+      <c r="E176" s="101">
+        <v>0.8</v>
+      </c>
+      <c r="F176" s="101">
+        <v>0.82</v>
+      </c>
+      <c r="G176" s="101">
+        <v>0.81</v>
+      </c>
+      <c r="H176" s="101">
+        <v>0.83</v>
       </c>
       <c r="I176" s="27"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B177" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C177" s="102">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="D177" s="102">
+        <v>2.98E-2</v>
+      </c>
+      <c r="E177" s="102">
+        <v>2.98E-2</v>
+      </c>
+      <c r="F177" s="102">
+        <v>2.92E-2</v>
+      </c>
+      <c r="G177" s="102">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="H177" s="138">
+        <f>H183/(H175*H176)</f>
+        <v>3.0029990678906885E-2</v>
+      </c>
+      <c r="I177" s="27"/>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B178" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C177" s="27"/>
-      <c r="D177" s="27"/>
-      <c r="E177" s="27">
+      <c r="C178" s="27"/>
+      <c r="D178" s="27"/>
+      <c r="E178" s="27">
         <v>120000</v>
       </c>
-      <c r="F177" s="27">
+      <c r="F178" s="27">
         <v>150000</v>
       </c>
-      <c r="G177" s="27">
+      <c r="G178" s="27">
         <v>170000</v>
       </c>
-      <c r="H177" s="27">
+      <c r="H178" s="27">
         <v>180000</v>
       </c>
-      <c r="I177" s="27"/>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C178" s="34"/>
-      <c r="D178" s="34"/>
-      <c r="E178" s="34"/>
-      <c r="F178" s="34"/>
-      <c r="G178" s="27"/>
-      <c r="H178" s="27"/>
       <c r="I178" s="27"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B179" s="1"/>
-    </row>
-    <row r="180" spans="1:9" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="4"/>
-      <c r="B180" s="15" t="s">
+      <c r="C179" s="34"/>
+      <c r="D179" s="34"/>
+      <c r="E179" s="34"/>
+      <c r="F179" s="34"/>
+      <c r="G179" s="27"/>
+      <c r="H179" s="27"/>
+      <c r="I179" s="27"/>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B180" s="1"/>
+    </row>
+    <row r="181" spans="1:9" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="4"/>
+      <c r="B181" s="15" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B181" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C181" s="27">
-        <v>69042</v>
-      </c>
-      <c r="D181" s="27">
-        <v>95514</v>
-      </c>
-      <c r="E181" s="27">
-        <v>128975</v>
-      </c>
-      <c r="F181" s="27">
-        <v>165436</v>
-      </c>
-      <c r="G181" s="27">
-        <v>196510</v>
-      </c>
-      <c r="H181" s="27">
-        <v>219461</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B182" s="9" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="C182" s="27">
-        <v>49900</v>
+        <v>69042</v>
       </c>
       <c r="D182" s="27">
-        <v>65201</v>
+        <v>95514</v>
       </c>
       <c r="E182" s="27">
-        <v>78368</v>
+        <v>128975</v>
       </c>
       <c r="F182" s="27">
-        <v>94610</v>
+        <v>165436</v>
       </c>
       <c r="G182" s="27">
-        <v>101740</v>
+        <v>196510</v>
       </c>
       <c r="H182" s="27">
-        <v>121459</v>
+        <v>219461</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B183" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C183" s="27">
+        <v>49900</v>
+      </c>
+      <c r="D183" s="27">
+        <v>65201</v>
+      </c>
+      <c r="E183" s="27">
+        <v>78368</v>
+      </c>
+      <c r="F183" s="27">
+        <v>94610</v>
+      </c>
+      <c r="G183" s="27">
+        <v>101740</v>
+      </c>
+      <c r="H183" s="27">
+        <v>121459</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B184" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C183" s="27">
+      <c r="C184" s="27">
         <v>29735</v>
       </c>
-      <c r="D183" s="27">
+      <c r="D184" s="27">
         <v>52518</v>
       </c>
-      <c r="E183" s="27">
+      <c r="E184" s="27">
         <v>73567</v>
       </c>
-      <c r="F183" s="27">
+      <c r="F184" s="27">
         <v>96253</v>
       </c>
-      <c r="G183" s="27">
+      <c r="G184" s="27">
         <v>121563</v>
       </c>
-      <c r="H183" s="27">
+      <c r="H184" s="27">
         <v>139671</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C184" s="34"/>
-      <c r="D184" s="34"/>
-      <c r="E184" s="34"/>
-      <c r="F184" s="34"/>
-      <c r="G184" s="27"/>
-      <c r="H184" s="27"/>
-    </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B185" s="1"/>
-    </row>
-    <row r="186" spans="1:9" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="4"/>
-      <c r="B186" s="15" t="s">
+      <c r="C185" s="34"/>
+      <c r="D185" s="34"/>
+      <c r="E185" s="34"/>
+      <c r="F185" s="34"/>
+      <c r="G185" s="27"/>
+      <c r="H185" s="27"/>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B186" s="1"/>
+    </row>
+    <row r="187" spans="1:9" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="4"/>
+      <c r="B187" s="15" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B187" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C187" s="137"/>
-      <c r="D187" s="137"/>
-      <c r="E187" s="137">
-        <f>E177/E172</f>
-        <v>42.016806722689076</v>
-      </c>
-      <c r="F187" s="137">
-        <f>F177/F172</f>
-        <v>41.655095806720354</v>
-      </c>
-      <c r="G187" s="137">
-        <f>G177/G172</f>
-        <v>40.447299547941945</v>
-      </c>
-      <c r="H187" s="137">
-        <f>H177/H172</f>
-        <v>39.875941515285774</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B188" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C188" s="137"/>
+      <c r="D188" s="137"/>
+      <c r="E188" s="137">
+        <f>E178/E173</f>
+        <v>42.016806722689076</v>
+      </c>
+      <c r="F188" s="137">
+        <f>F178/F173</f>
+        <v>41.655095806720354</v>
+      </c>
+      <c r="G188" s="137">
+        <f>G178/G173</f>
+        <v>40.447299547941945</v>
+      </c>
+      <c r="H188" s="137">
+        <f>H178/H173</f>
+        <v>39.875941515285774</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B189" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C188" s="88"/>
-      <c r="D188" s="88"/>
-      <c r="E188" s="105">
-        <f>E183/E177</f>
+      <c r="C189" s="88"/>
+      <c r="D189" s="88"/>
+      <c r="E189" s="105">
+        <f>E184/E178</f>
         <v>0.61305833333333337</v>
       </c>
-      <c r="F188" s="105">
-        <f t="shared" ref="F188:H188" si="34">F183/F177</f>
+      <c r="F189" s="105">
+        <f t="shared" ref="F189:H189" si="34">F184/F178</f>
         <v>0.64168666666666663</v>
       </c>
-      <c r="G188" s="105">
+      <c r="G189" s="105">
         <f t="shared" si="34"/>
         <v>0.71507647058823531</v>
       </c>
-      <c r="H188" s="105">
+      <c r="H189" s="105">
         <f t="shared" si="34"/>
         <v>0.77595000000000003</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C189" s="88"/>
-      <c r="D189" s="88"/>
-      <c r="E189" s="88"/>
-      <c r="F189" s="88"/>
-    </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C190" s="89"/>
-      <c r="D190" s="89"/>
-      <c r="E190" s="89"/>
-      <c r="F190" s="89"/>
+      <c r="C190" s="88"/>
+      <c r="D190" s="88"/>
+      <c r="E190" s="88"/>
+      <c r="F190" s="88"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B191" s="1"/>
-    </row>
-    <row r="192" spans="1:9" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="4"/>
-      <c r="B192" s="15" t="s">
+      <c r="C191" s="89"/>
+      <c r="D191" s="89"/>
+      <c r="E191" s="89"/>
+      <c r="F191" s="89"/>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B192" s="1"/>
+    </row>
+    <row r="193" spans="1:15" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="4"/>
+      <c r="B193" s="15" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="193" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B193" s="9" t="s">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B194" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="C193" s="31">
+      <c r="C194" s="31">
         <v>65.290000000000006</v>
       </c>
-      <c r="D193" s="31">
+      <c r="D194" s="31">
         <v>28.44</v>
       </c>
-      <c r="E193" s="31">
+      <c r="E194" s="31">
         <v>36.19</v>
       </c>
-      <c r="F193" s="31">
+      <c r="F194" s="31">
         <v>25.61</v>
       </c>
-      <c r="G193" s="31">
+      <c r="G194" s="31">
         <v>29</v>
       </c>
-      <c r="H193" s="31">
+      <c r="H194" s="31">
         <v>13.43</v>
       </c>
-      <c r="I193" s="31"/>
-      <c r="J193" s="31"/>
-      <c r="K193" s="31"/>
-      <c r="L193" s="31"/>
-      <c r="M193" s="31"/>
-      <c r="N193" s="31"/>
-      <c r="O193" s="31"/>
-    </row>
-    <row r="195" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B195" s="1"/>
+      <c r="I194" s="31"/>
+      <c r="J194" s="31"/>
+      <c r="K194" s="31"/>
+      <c r="L194" s="31"/>
+      <c r="M194" s="31"/>
+      <c r="N194" s="31"/>
+      <c r="O194" s="31"/>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B196" s="1"/>
+    </row>
+    <row r="197" spans="1:15" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="4"/>
+      <c r="B197" s="15" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B198" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="C198" s="197">
+        <f>C50+C51+C58+C59</f>
+        <v>14321</v>
+      </c>
+      <c r="D198" s="197">
+        <f t="shared" ref="D198:H198" si="35">D50+D51+D58+D59</f>
+        <v>15801</v>
+      </c>
+      <c r="E198" s="197">
+        <f t="shared" si="35"/>
+        <v>9180</v>
+      </c>
+      <c r="F198" s="197">
+        <f t="shared" si="35"/>
+        <v>11983</v>
+      </c>
+      <c r="G198" s="197">
+        <f t="shared" si="35"/>
+        <v>17803</v>
+      </c>
+      <c r="H198" s="197">
+        <f t="shared" si="35"/>
+        <v>102449</v>
+      </c>
+      <c r="I198" s="31"/>
+      <c r="J198" s="31"/>
+      <c r="K198" s="31"/>
+      <c r="L198" s="31"/>
+      <c r="M198" s="31"/>
+      <c r="N198" s="31"/>
+      <c r="O198" s="31"/>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B199" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C199" s="197">
+        <f>C28</f>
+        <v>218781</v>
+      </c>
+      <c r="D199" s="197">
+        <f t="shared" ref="D199:H199" si="36">D28</f>
+        <v>313812</v>
+      </c>
+      <c r="E199" s="197">
+        <f t="shared" si="36"/>
+        <v>176683</v>
+      </c>
+      <c r="F199" s="197">
+        <f t="shared" si="36"/>
+        <v>87520</v>
+      </c>
+      <c r="G199" s="197">
+        <f t="shared" si="36"/>
+        <v>84220</v>
+      </c>
+      <c r="H199" s="197">
+        <f t="shared" si="36"/>
+        <v>73830</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B200" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="C200" s="197">
+        <f>(C51+C59)*Overview!$C$4</f>
+        <v>223.95</v>
+      </c>
+      <c r="D200" s="197">
+        <f>(D51+D59)*Overview!$C$4</f>
+        <v>191.77500000000001</v>
+      </c>
+      <c r="E200" s="197">
+        <f>(E51+E59)*Overview!$C$4</f>
+        <v>96.224999999999994</v>
+      </c>
+      <c r="F200" s="197">
+        <f>(F51+F59)*Overview!$C$4</f>
+        <v>39.524999999999999</v>
+      </c>
+      <c r="G200" s="197">
+        <f>(G51+G59)*Overview!$C$4</f>
+        <v>120.75</v>
+      </c>
+      <c r="H200" s="197">
+        <f>(H51+H59)*Overview!$C$4</f>
+        <v>177.07499999999999</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B201" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C201" s="197">
+        <f>C153-C200</f>
+        <v>1799.05</v>
+      </c>
+      <c r="D201" s="197">
+        <f t="shared" ref="D201:H201" si="37">D153-D200</f>
+        <v>1127.2249999999999</v>
+      </c>
+      <c r="E201" s="197">
+        <f t="shared" si="37"/>
+        <v>1800.7750000000001</v>
+      </c>
+      <c r="F201" s="197">
+        <f t="shared" si="37"/>
+        <v>747.47500000000002</v>
+      </c>
+      <c r="G201" s="197">
+        <f t="shared" si="37"/>
+        <v>862.25</v>
+      </c>
+      <c r="H201" s="197">
+        <f t="shared" si="37"/>
+        <v>776.92499999999995</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B202" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="C202" s="197">
+        <f>C14+C200-C201</f>
+        <v>-27246.1</v>
+      </c>
+      <c r="D202" s="197">
+        <f t="shared" ref="D202:H202" si="38">D14+D200-D201</f>
+        <v>-117752.45000000001</v>
+      </c>
+      <c r="E202" s="197">
+        <f t="shared" si="38"/>
+        <v>-178256.55</v>
+      </c>
+      <c r="F202" s="197">
+        <f t="shared" si="38"/>
+        <v>-137186.95000000001</v>
+      </c>
+      <c r="G202" s="197">
+        <f t="shared" si="38"/>
+        <v>-58838.5</v>
+      </c>
+      <c r="H202" s="197">
+        <f t="shared" si="38"/>
+        <v>-7211.85</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B203" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C203" s="104">
+        <f>C198+C72-C199</f>
+        <v>58846</v>
+      </c>
+      <c r="D203" s="104">
+        <f t="shared" ref="D203:H203" si="39">D198+D72-D199</f>
+        <v>119269</v>
+      </c>
+      <c r="E203" s="104">
+        <f t="shared" si="39"/>
+        <v>120316</v>
+      </c>
+      <c r="F203" s="104">
+        <f t="shared" si="39"/>
+        <v>175912</v>
+      </c>
+      <c r="G203" s="104">
+        <f t="shared" si="39"/>
+        <v>198391</v>
+      </c>
+      <c r="H203" s="104">
+        <f t="shared" si="39"/>
+        <v>365826</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B204" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C204" s="104">
+        <f>C202</f>
+        <v>-27246.1</v>
+      </c>
+      <c r="D204" s="104">
+        <f t="shared" ref="D204:H204" si="40">D202</f>
+        <v>-117752.45000000001</v>
+      </c>
+      <c r="E204" s="104">
+        <f t="shared" si="40"/>
+        <v>-178256.55</v>
+      </c>
+      <c r="F204" s="104">
+        <f t="shared" si="40"/>
+        <v>-137186.95000000001</v>
+      </c>
+      <c r="G204" s="104">
+        <f t="shared" si="40"/>
+        <v>-58838.5</v>
+      </c>
+      <c r="H204" s="104">
+        <f t="shared" si="40"/>
+        <v>-7211.85</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B205" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="C205" s="104">
+        <f>C202+C153+C77</f>
+        <v>-9315.0999999999985</v>
+      </c>
+      <c r="D205" s="104">
+        <f t="shared" ref="D205:H205" si="41">D202+D153+D77</f>
+        <v>-95131.450000000012</v>
+      </c>
+      <c r="E205" s="104">
+        <f t="shared" si="41"/>
+        <v>-151055.54999999999</v>
+      </c>
+      <c r="F205" s="104">
+        <f t="shared" si="41"/>
+        <v>-106912.95000000001</v>
+      </c>
+      <c r="G205" s="104">
+        <f t="shared" si="41"/>
+        <v>-29969.5</v>
+      </c>
+      <c r="H205" s="104">
+        <f t="shared" si="41"/>
+        <v>25195.15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B207" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12252,7 +12687,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB41336-2E39-7442-9864-91E9B0A07818}">
-  <dimension ref="A1:S179"/>
+  <dimension ref="A1:S190"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -12373,11 +12808,11 @@
         <v>74</v>
       </c>
       <c r="O4" s="4"/>
-      <c r="P4" s="229" t="s">
+      <c r="P4" s="231" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="230"/>
-      <c r="R4" s="231"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="233"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
@@ -14685,6 +15120,10 @@
       <c r="K77" s="27"/>
       <c r="L77" s="27"/>
       <c r="M77" s="20"/>
+      <c r="N77" s="20">
+        <f>SUM(G77:J77)</f>
+        <v>31453</v>
+      </c>
     </row>
     <row r="78" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B78" s="12" t="s">
@@ -17028,517 +17467,864 @@
       <c r="L148" s="8"/>
       <c r="M148" s="8"/>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B149" s="1"/>
-    </row>
-    <row r="150" spans="1:19" s="65" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="1"/>
-      <c r="B150" s="15" t="s">
+    <row r="149" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B149" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C149" s="29">
+        <v>182</v>
+      </c>
+      <c r="D149" s="29">
+        <v>257</v>
+      </c>
+      <c r="E149" s="29">
+        <v>245</v>
+      </c>
+      <c r="F149" s="29">
+        <v>299</v>
+      </c>
+      <c r="G149" s="29">
+        <v>245</v>
+      </c>
+      <c r="H149" s="29">
+        <v>243</v>
+      </c>
+      <c r="I149" s="29">
+        <v>244</v>
+      </c>
+      <c r="J149" s="29">
+        <v>222</v>
+      </c>
+      <c r="K149" s="8"/>
+      <c r="L149" s="8"/>
+      <c r="M149" s="8"/>
+      <c r="N149" s="20">
+        <f>SUM(G149:J149)</f>
+        <v>954</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B150" s="12"/>
+      <c r="C150" s="28"/>
+      <c r="D150" s="28"/>
+      <c r="E150" s="28"/>
+      <c r="F150" s="28"/>
+      <c r="G150" s="28"/>
+      <c r="H150" s="28"/>
+      <c r="I150" s="28"/>
+      <c r="J150" s="28"/>
+      <c r="K150" s="8"/>
+      <c r="L150" s="8"/>
+      <c r="M150" s="8"/>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B151" s="1"/>
+    </row>
+    <row r="152" spans="1:19" s="65" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="1"/>
+      <c r="B152" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C150" s="67"/>
-      <c r="D150" s="67"/>
-      <c r="E150" s="67"/>
-      <c r="F150" s="67"/>
-      <c r="G150" s="67"/>
-      <c r="H150" s="67"/>
-      <c r="I150" s="67"/>
-      <c r="J150" s="67"/>
-      <c r="K150" s="1"/>
-      <c r="L150" s="1"/>
-      <c r="M150" s="1"/>
-      <c r="O150" s="4"/>
-      <c r="S150" s="4"/>
-    </row>
-    <row r="151" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B151" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C151" s="27"/>
-      <c r="D151" s="27"/>
-      <c r="E151" s="27"/>
-      <c r="F151" s="27"/>
-      <c r="G151" s="27"/>
-      <c r="H151" s="27"/>
-      <c r="I151" s="27"/>
-      <c r="J151" s="27"/>
-    </row>
-    <row r="152" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B152" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C152" s="27"/>
-      <c r="D152" s="27"/>
-      <c r="E152" s="27"/>
-      <c r="F152" s="27"/>
-      <c r="G152" s="27"/>
-      <c r="H152" s="27"/>
-      <c r="I152" s="27"/>
-      <c r="J152" s="27"/>
+      <c r="C152" s="67"/>
+      <c r="D152" s="67"/>
+      <c r="E152" s="67"/>
+      <c r="F152" s="67"/>
+      <c r="G152" s="67"/>
+      <c r="H152" s="67"/>
+      <c r="I152" s="67"/>
+      <c r="J152" s="67"/>
+      <c r="K152" s="1"/>
+      <c r="L152" s="1"/>
+      <c r="M152" s="1"/>
+      <c r="O152" s="4"/>
+      <c r="S152" s="4"/>
     </row>
     <row r="153" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B153" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C153" s="34"/>
-      <c r="D153" s="34"/>
-      <c r="E153" s="34"/>
-      <c r="F153" s="34"/>
-      <c r="G153" s="34"/>
-      <c r="H153" s="34"/>
-      <c r="I153" s="34"/>
-      <c r="J153" s="34"/>
+        <v>77</v>
+      </c>
+      <c r="C153" s="27"/>
+      <c r="D153" s="27"/>
+      <c r="E153" s="27"/>
+      <c r="F153" s="27"/>
+      <c r="G153" s="27"/>
+      <c r="H153" s="27"/>
+      <c r="I153" s="27"/>
+      <c r="J153" s="27"/>
     </row>
     <row r="154" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B154" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C154" s="66"/>
-      <c r="D154" s="66"/>
-      <c r="E154" s="66"/>
-      <c r="F154" s="66"/>
-      <c r="G154" s="66"/>
-      <c r="H154" s="66"/>
-      <c r="I154" s="66"/>
-      <c r="J154" s="66"/>
+        <v>78</v>
+      </c>
+      <c r="C154" s="27"/>
+      <c r="D154" s="27"/>
+      <c r="E154" s="27"/>
+      <c r="F154" s="27"/>
+      <c r="G154" s="27"/>
+      <c r="H154" s="27"/>
+      <c r="I154" s="27"/>
+      <c r="J154" s="27"/>
     </row>
     <row r="155" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B155" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C155" s="31"/>
-      <c r="D155" s="31"/>
-      <c r="E155" s="31"/>
-      <c r="F155" s="31"/>
-      <c r="G155" s="31"/>
-      <c r="H155" s="31"/>
-      <c r="I155" s="31"/>
-      <c r="J155" s="31"/>
+        <v>82</v>
+      </c>
+      <c r="C155" s="34"/>
+      <c r="D155" s="34"/>
+      <c r="E155" s="34"/>
+      <c r="F155" s="34"/>
+      <c r="G155" s="34"/>
+      <c r="H155" s="34"/>
+      <c r="I155" s="34"/>
+      <c r="J155" s="34"/>
     </row>
     <row r="156" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B156" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C156" s="31"/>
-      <c r="D156" s="31"/>
-      <c r="E156" s="31"/>
-      <c r="F156" s="31"/>
-      <c r="G156" s="31"/>
-      <c r="H156" s="31"/>
-      <c r="I156" s="31"/>
-      <c r="J156" s="31"/>
+        <v>79</v>
+      </c>
+      <c r="C156" s="66"/>
+      <c r="D156" s="66"/>
+      <c r="E156" s="66"/>
+      <c r="F156" s="66"/>
+      <c r="G156" s="66"/>
+      <c r="H156" s="66"/>
+      <c r="I156" s="66"/>
+      <c r="J156" s="66"/>
     </row>
     <row r="157" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B157" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C157" s="31"/>
+      <c r="D157" s="31"/>
+      <c r="E157" s="31"/>
+      <c r="F157" s="31"/>
+      <c r="G157" s="31"/>
+      <c r="H157" s="31"/>
+      <c r="I157" s="31"/>
+      <c r="J157" s="31"/>
+    </row>
+    <row r="158" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B158" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C158" s="31"/>
+      <c r="D158" s="31"/>
+      <c r="E158" s="31"/>
+      <c r="F158" s="31"/>
+      <c r="G158" s="31"/>
+      <c r="H158" s="31"/>
+      <c r="I158" s="31"/>
+      <c r="J158" s="31"/>
+    </row>
+    <row r="159" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B159" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C157" s="25"/>
-      <c r="D157" s="25"/>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="25"/>
-      <c r="K157" s="20"/>
-      <c r="L157" s="20"/>
-      <c r="M157" s="20"/>
-    </row>
-    <row r="158" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B158" s="12" t="s">
+      <c r="C159" s="25"/>
+      <c r="D159" s="25"/>
+      <c r="E159" s="25"/>
+      <c r="F159" s="25"/>
+      <c r="G159" s="25"/>
+      <c r="H159" s="25"/>
+      <c r="I159" s="25"/>
+      <c r="J159" s="25"/>
+      <c r="K159" s="20"/>
+      <c r="L159" s="20"/>
+      <c r="M159" s="20"/>
+    </row>
+    <row r="160" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B160" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C158" s="66"/>
-      <c r="D158" s="66"/>
-      <c r="E158" s="66"/>
-      <c r="F158" s="66"/>
-      <c r="G158" s="66"/>
-      <c r="H158" s="66"/>
-      <c r="I158" s="66"/>
-      <c r="J158" s="66"/>
-      <c r="K158" s="8"/>
-      <c r="L158" s="8"/>
-      <c r="M158" s="8"/>
-    </row>
-    <row r="159" spans="1:19" collapsed="1" x14ac:dyDescent="0.2">
-      <c r="B159" s="1"/>
-    </row>
-    <row r="160" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="4"/>
-      <c r="B160" s="15" t="s">
-        <v>108</v>
-      </c>
+      <c r="C160" s="66"/>
+      <c r="D160" s="66"/>
+      <c r="E160" s="66"/>
+      <c r="F160" s="66"/>
+      <c r="G160" s="66"/>
+      <c r="H160" s="66"/>
+      <c r="I160" s="66"/>
+      <c r="J160" s="66"/>
       <c r="K160" s="8"/>
       <c r="L160" s="8"/>
       <c r="M160" s="8"/>
-      <c r="O160" s="1"/>
-      <c r="S160" s="1"/>
-    </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B161" s="9" t="s">
+    </row>
+    <row r="161" spans="1:19" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B161" s="1"/>
+    </row>
+    <row r="162" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="4"/>
+      <c r="B162" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="K162" s="8"/>
+      <c r="L162" s="8"/>
+      <c r="M162" s="8"/>
+      <c r="O162" s="1"/>
+      <c r="S162" s="1"/>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B163" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="C161" s="27">
+      <c r="C163" s="27">
         <v>4065</v>
       </c>
-      <c r="D161" s="27">
+      <c r="D163" s="27">
         <v>4169</v>
       </c>
-      <c r="E161" s="27">
+      <c r="E163" s="27">
         <v>4237</v>
       </c>
-      <c r="F161" s="27">
+      <c r="F163" s="27">
         <v>4341</v>
       </c>
-      <c r="G161" s="27">
+      <c r="G163" s="27">
         <v>4411</v>
       </c>
-      <c r="H161" s="27">
+      <c r="H163" s="27">
         <v>4467</v>
       </c>
-      <c r="I161" s="27">
+      <c r="I163" s="27">
         <v>4520</v>
       </c>
-      <c r="J161" s="27">
+      <c r="J163" s="27">
         <v>4658</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B162" s="9" t="s">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B164" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C162" s="115">
-        <f t="shared" ref="C162:J162" si="41">C170/C161</f>
+      <c r="C164" s="115">
+        <f t="shared" ref="C164:J164" si="41">C172/C163</f>
         <v>11.498646986469865</v>
       </c>
-      <c r="D162" s="115">
+      <c r="D164" s="115">
         <f t="shared" si="41"/>
         <v>11.660350203885823</v>
       </c>
-      <c r="E162" s="115">
+      <c r="E164" s="115">
         <f t="shared" si="41"/>
         <v>11.650460231295728</v>
       </c>
-      <c r="F162" s="115">
+      <c r="F164" s="115">
         <f t="shared" si="41"/>
         <v>11.931121861322277</v>
       </c>
-      <c r="G162" s="115">
+      <c r="G164" s="115">
         <f t="shared" si="41"/>
         <v>12.322602584447971</v>
       </c>
-      <c r="H162" s="115">
+      <c r="H164" s="115">
         <f t="shared" si="41"/>
         <v>12.021938661293934</v>
       </c>
-      <c r="I162" s="115">
+      <c r="I164" s="115">
         <f t="shared" si="41"/>
         <v>12.274336283185841</v>
       </c>
-      <c r="J162" s="115">
+      <c r="J164" s="115">
         <f t="shared" si="41"/>
         <v>12.006011163589523</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B163" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C163" s="27">
-        <v>1166000</v>
-      </c>
-      <c r="D163" s="27">
-        <v>1093000</v>
-      </c>
-      <c r="E163" s="27">
-        <v>1081000</v>
-      </c>
-      <c r="F163" s="27">
-        <v>1080000</v>
-      </c>
-      <c r="G163" s="27">
-        <v>1314000</v>
-      </c>
-      <c r="H163" s="27">
-        <v>1250000</v>
-      </c>
-      <c r="I163" s="27">
-        <v>1181000</v>
-      </c>
-      <c r="J163" s="27">
-        <v>1128000</v>
-      </c>
-    </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B164" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C164" s="101">
-        <v>0.81</v>
-      </c>
-      <c r="D164" s="101">
-        <v>0.81</v>
-      </c>
-      <c r="E164" s="101">
-        <v>0.81</v>
-      </c>
-      <c r="F164" s="101">
-        <v>0.82</v>
-      </c>
-      <c r="G164" s="101">
-        <v>0.82</v>
-      </c>
-      <c r="H164" s="101">
-        <v>0.82</v>
-      </c>
-      <c r="I164" s="101">
-        <v>0.85</v>
-      </c>
-      <c r="J164" s="101">
-        <v>0.84</v>
-      </c>
-    </row>
     <row r="165" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B165" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C165" s="102">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="D165" s="102">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="E165" s="102">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="F165" s="102">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="G165" s="102">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="H165" s="102">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="I165" s="102">
-        <v>2.7E-2</v>
-      </c>
-      <c r="J165" s="138">
-        <f>J171/(J163*J164)</f>
-        <v>3.7698412698412696E-2</v>
+        <v>182</v>
+      </c>
+      <c r="C165" s="27">
+        <v>1166000</v>
+      </c>
+      <c r="D165" s="27">
+        <v>1093000</v>
+      </c>
+      <c r="E165" s="27">
+        <v>1081000</v>
+      </c>
+      <c r="F165" s="27">
+        <v>1080000</v>
+      </c>
+      <c r="G165" s="27">
+        <v>1314000</v>
+      </c>
+      <c r="H165" s="27">
+        <v>1250000</v>
+      </c>
+      <c r="I165" s="27">
+        <v>1181000</v>
+      </c>
+      <c r="J165" s="27">
+        <v>1128000</v>
       </c>
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B166" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C166" s="101">
+        <v>0.81</v>
+      </c>
+      <c r="D166" s="101">
+        <v>0.81</v>
+      </c>
+      <c r="E166" s="101">
+        <v>0.81</v>
+      </c>
+      <c r="F166" s="101">
+        <v>0.82</v>
+      </c>
+      <c r="G166" s="101">
+        <v>0.82</v>
+      </c>
+      <c r="H166" s="101">
+        <v>0.82</v>
+      </c>
+      <c r="I166" s="101">
+        <v>0.85</v>
+      </c>
+      <c r="J166" s="101">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B167" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C167" s="102">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D167" s="102">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E167" s="102">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F167" s="102">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G167" s="102">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H167" s="102">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I167" s="102">
+        <v>2.7E-2</v>
+      </c>
+      <c r="J167" s="138">
+        <f>J173/(J165*J166)</f>
+        <v>3.7698412698412696E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B168" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C166" s="115">
-        <f t="shared" ref="C166:J166" si="42">C172/C161</f>
+      <c r="C168" s="115">
+        <f t="shared" ref="C168:J168" si="42">C174/C163</f>
         <v>6.7441574415744157</v>
       </c>
-      <c r="D166" s="115">
+      <c r="D168" s="115">
         <f t="shared" si="42"/>
         <v>6.7649316382825617</v>
       </c>
-      <c r="E166" s="115">
+      <c r="E168" s="115">
         <f t="shared" si="42"/>
         <v>7.7255133349067737</v>
       </c>
-      <c r="F166" s="115">
+      <c r="F168" s="115">
         <f t="shared" si="42"/>
         <v>7.6507717115871916</v>
       </c>
-      <c r="G166" s="115">
+      <c r="G168" s="115">
         <f t="shared" si="42"/>
         <v>7.1766039446837455</v>
       </c>
-      <c r="H166" s="115">
+      <c r="H168" s="115">
         <f t="shared" si="42"/>
         <v>7.8712782628162081</v>
       </c>
-      <c r="I166" s="115">
+      <c r="I168" s="115">
         <f t="shared" si="42"/>
         <v>8.2811946902654867</v>
       </c>
-      <c r="J166" s="115">
+      <c r="J168" s="115">
         <f t="shared" si="42"/>
         <v>7.6047659939888366</v>
       </c>
-      <c r="K166" s="21"/>
-    </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="C167" s="34"/>
-      <c r="D167" s="34"/>
-      <c r="E167" s="34"/>
-      <c r="F167" s="34"/>
-      <c r="G167" s="34"/>
-      <c r="H167" s="34"/>
-      <c r="I167" s="34"/>
-      <c r="J167" s="34"/>
-    </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B168" s="1"/>
-    </row>
-    <row r="169" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="4"/>
-      <c r="B169" s="15" t="s">
+      <c r="K168" s="21"/>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C169" s="34"/>
+      <c r="D169" s="34"/>
+      <c r="E169" s="34"/>
+      <c r="F169" s="34"/>
+      <c r="G169" s="34"/>
+      <c r="H169" s="34"/>
+      <c r="I169" s="34"/>
+      <c r="J169" s="34"/>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B170" s="1"/>
+    </row>
+    <row r="171" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="4"/>
+      <c r="B171" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="K169" s="8"/>
-      <c r="L169" s="8"/>
-      <c r="M169" s="8"/>
-      <c r="O169" s="1"/>
-      <c r="S169" s="93"/>
-    </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B170" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C170" s="27">
-        <v>46742</v>
-      </c>
-      <c r="D170" s="27">
-        <v>48612</v>
-      </c>
-      <c r="E170" s="27">
-        <v>49363</v>
-      </c>
-      <c r="F170" s="27">
-        <v>51793</v>
-      </c>
-      <c r="G170" s="27">
-        <v>54355</v>
-      </c>
-      <c r="H170" s="27">
-        <v>53702</v>
-      </c>
-      <c r="I170" s="27">
-        <v>55480</v>
-      </c>
-      <c r="J170" s="27">
-        <v>55924</v>
-      </c>
-    </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B171" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C171" s="27">
-        <v>27060</v>
-      </c>
-      <c r="D171" s="27">
-        <v>25300</v>
-      </c>
-      <c r="E171" s="27">
-        <v>24704</v>
-      </c>
-      <c r="F171" s="27">
-        <v>24676</v>
-      </c>
-      <c r="G171" s="27">
-        <v>29925</v>
-      </c>
-      <c r="H171" s="27">
-        <v>28392</v>
-      </c>
-      <c r="I171" s="27">
-        <v>27422</v>
-      </c>
-      <c r="J171" s="27">
-        <v>35720</v>
-      </c>
+      <c r="K171" s="8"/>
+      <c r="L171" s="8"/>
+      <c r="M171" s="8"/>
+      <c r="O171" s="1"/>
+      <c r="S171" s="93"/>
     </row>
     <row r="172" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B172" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C172" s="27">
+        <v>46742</v>
+      </c>
+      <c r="D172" s="27">
+        <v>48612</v>
+      </c>
+      <c r="E172" s="27">
+        <v>49363</v>
+      </c>
+      <c r="F172" s="27">
+        <v>51793</v>
+      </c>
+      <c r="G172" s="27">
+        <v>54355</v>
+      </c>
+      <c r="H172" s="27">
+        <v>53702</v>
+      </c>
+      <c r="I172" s="27">
+        <v>55480</v>
+      </c>
+      <c r="J172" s="27">
+        <v>55924</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B173" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C173" s="27">
+        <v>27060</v>
+      </c>
+      <c r="D173" s="27">
+        <v>25300</v>
+      </c>
+      <c r="E173" s="27">
+        <v>24704</v>
+      </c>
+      <c r="F173" s="27">
+        <v>24676</v>
+      </c>
+      <c r="G173" s="27">
+        <v>29925</v>
+      </c>
+      <c r="H173" s="27">
+        <v>28392</v>
+      </c>
+      <c r="I173" s="27">
+        <v>27422</v>
+      </c>
+      <c r="J173" s="27">
+        <v>35720</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B174" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C172" s="27">
+      <c r="C174" s="27">
         <v>27415</v>
       </c>
-      <c r="D172" s="27">
+      <c r="D174" s="27">
         <v>28203</v>
       </c>
-      <c r="E172" s="27">
+      <c r="E174" s="27">
         <v>32733</v>
       </c>
-      <c r="F172" s="27">
+      <c r="F174" s="27">
         <v>33212</v>
       </c>
-      <c r="G172" s="27">
+      <c r="G174" s="27">
         <v>31656</v>
       </c>
-      <c r="H172" s="27">
+      <c r="H174" s="27">
         <v>35161</v>
       </c>
-      <c r="I172" s="27">
+      <c r="I174" s="27">
         <v>37431</v>
       </c>
-      <c r="J172" s="27">
+      <c r="J174" s="27">
         <v>35423</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="C173" s="27"/>
-      <c r="D173" s="27"/>
-      <c r="E173" s="27"/>
-      <c r="F173" s="27"/>
-      <c r="G173" s="27"/>
-      <c r="H173" s="27"/>
-      <c r="I173" s="27"/>
-      <c r="J173" s="27"/>
-    </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B174" s="1"/>
-    </row>
-    <row r="175" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="4"/>
-      <c r="B175" s="15" t="s">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C175" s="27"/>
+      <c r="D175" s="27"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="27"/>
+      <c r="J175" s="27"/>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B176" s="1"/>
+    </row>
+    <row r="177" spans="1:15" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="4"/>
+      <c r="B177" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="K175" s="1"/>
-      <c r="L175" s="1"/>
-      <c r="M175" s="1"/>
-    </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="C176" s="89"/>
-      <c r="D176" s="89"/>
-      <c r="E176" s="89"/>
-      <c r="F176" s="89"/>
-      <c r="G176" s="89"/>
-      <c r="H176" s="89"/>
-      <c r="I176" s="89"/>
-      <c r="J176" s="89"/>
-    </row>
-    <row r="177" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C177" s="88"/>
-      <c r="D177" s="88"/>
-      <c r="E177" s="88"/>
-      <c r="F177" s="88"/>
-      <c r="G177" s="88"/>
-      <c r="H177" s="88"/>
-      <c r="I177" s="88"/>
-      <c r="J177" s="88"/>
-    </row>
-    <row r="178" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C178" s="88"/>
-      <c r="D178" s="88"/>
-      <c r="E178" s="88"/>
-      <c r="F178" s="88"/>
-      <c r="G178" s="88"/>
-      <c r="H178" s="88"/>
-      <c r="I178" s="88"/>
-      <c r="J178" s="88"/>
-    </row>
-    <row r="179" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C179" s="89"/>
-      <c r="D179" s="89"/>
-      <c r="E179" s="89"/>
-      <c r="F179" s="89"/>
-      <c r="G179" s="89"/>
-      <c r="H179" s="89"/>
-      <c r="I179" s="89"/>
-      <c r="J179" s="89"/>
-      <c r="K179" s="89"/>
+      <c r="K177" s="1"/>
+      <c r="L177" s="1"/>
+      <c r="M177" s="1"/>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C178" s="89"/>
+      <c r="D178" s="89"/>
+      <c r="E178" s="89"/>
+      <c r="F178" s="89"/>
+      <c r="G178" s="89"/>
+      <c r="H178" s="89"/>
+      <c r="I178" s="89"/>
+      <c r="J178" s="89"/>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B179" s="88"/>
+      <c r="C179" s="88"/>
+      <c r="D179" s="88"/>
+      <c r="E179" s="88"/>
+      <c r="F179" s="88"/>
+      <c r="G179" s="88"/>
+      <c r="H179" s="88"/>
+      <c r="I179" s="88"/>
+      <c r="J179" s="88"/>
+    </row>
+    <row r="180" spans="1:15" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="4"/>
+      <c r="B180" s="15" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B181" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="C181" s="197">
+        <f>C50+C51+C58+C59</f>
+        <v>0</v>
+      </c>
+      <c r="D181" s="197">
+        <f t="shared" ref="D181:J181" si="43">D50+D51+D58+D59</f>
+        <v>0</v>
+      </c>
+      <c r="E181" s="197">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="F181" s="197">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="G181" s="197">
+        <f t="shared" si="43"/>
+        <v>15868</v>
+      </c>
+      <c r="H181" s="197">
+        <f t="shared" si="43"/>
+        <v>12792</v>
+      </c>
+      <c r="I181" s="197">
+        <f t="shared" si="43"/>
+        <v>10430</v>
+      </c>
+      <c r="J181" s="197">
+        <f t="shared" si="43"/>
+        <v>102449</v>
+      </c>
+      <c r="K181" s="31"/>
+      <c r="L181" s="31"/>
+      <c r="M181" s="31"/>
+      <c r="N181" s="197">
+        <f>J181</f>
+        <v>102449</v>
+      </c>
+      <c r="O181" s="31"/>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B182" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C182" s="197">
+        <f>C28</f>
+        <v>0</v>
+      </c>
+      <c r="D182" s="197">
+        <f t="shared" ref="D182:J182" si="44">D28</f>
+        <v>0</v>
+      </c>
+      <c r="E182" s="197">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="F182" s="197">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="G182" s="197">
+        <f t="shared" si="44"/>
+        <v>90871</v>
+      </c>
+      <c r="H182" s="197">
+        <f t="shared" si="44"/>
+        <v>98266</v>
+      </c>
+      <c r="I182" s="197">
+        <f t="shared" si="44"/>
+        <v>106371</v>
+      </c>
+      <c r="J182" s="197">
+        <f t="shared" si="44"/>
+        <v>73830</v>
+      </c>
+      <c r="N182" s="197">
+        <f>J182</f>
+        <v>73830</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B183" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="C183" s="197">
+        <f>(C51+C59)*Overview!$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D183" s="197">
+        <f>(D51+D59)*Overview!$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="E183" s="197">
+        <f>(E51+E59)*Overview!$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="F183" s="197">
+        <f>(F51+F59)*Overview!$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="G183" s="197">
+        <f>(G51+G59)*Overview!$C$4</f>
+        <v>101.85</v>
+      </c>
+      <c r="H183" s="197">
+        <f>(H51+H59)*Overview!$C$4</f>
+        <v>84</v>
+      </c>
+      <c r="I183" s="197">
+        <f>(I51+I59)*Overview!$C$4</f>
+        <v>65.849999999999994</v>
+      </c>
+      <c r="J183" s="197">
+        <f>(J51+J59)*Overview!$C$4</f>
+        <v>177.07499999999999</v>
+      </c>
+      <c r="N183" s="197">
+        <f>J183</f>
+        <v>177.07499999999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B184" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C184" s="197">
+        <f>C149-C183</f>
+        <v>182</v>
+      </c>
+      <c r="D184" s="197">
+        <f t="shared" ref="D184:J184" si="45">D149-D183</f>
+        <v>257</v>
+      </c>
+      <c r="E184" s="197">
+        <f t="shared" si="45"/>
+        <v>245</v>
+      </c>
+      <c r="F184" s="197">
+        <f t="shared" si="45"/>
+        <v>299</v>
+      </c>
+      <c r="G184" s="197">
+        <f t="shared" si="45"/>
+        <v>143.15</v>
+      </c>
+      <c r="H184" s="197">
+        <f t="shared" si="45"/>
+        <v>159</v>
+      </c>
+      <c r="I184" s="197">
+        <f t="shared" si="45"/>
+        <v>178.15</v>
+      </c>
+      <c r="J184" s="197">
+        <f t="shared" si="45"/>
+        <v>44.925000000000011</v>
+      </c>
+      <c r="N184" s="197">
+        <f>N149-N183</f>
+        <v>776.92499999999995</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B185" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="C185" s="197">
+        <f>C14+C183</f>
+        <v>-19420</v>
+      </c>
+      <c r="D185" s="197">
+        <f t="shared" ref="D185:J185" si="46">D14+D183</f>
+        <v>-17222</v>
+      </c>
+      <c r="E185" s="197">
+        <f t="shared" si="46"/>
+        <v>-13843</v>
+      </c>
+      <c r="F185" s="197">
+        <f t="shared" si="46"/>
+        <v>-7612</v>
+      </c>
+      <c r="G185" s="197">
+        <f t="shared" si="46"/>
+        <v>-3185.15</v>
+      </c>
+      <c r="H185" s="197">
+        <f t="shared" si="46"/>
+        <v>-1423</v>
+      </c>
+      <c r="I185" s="197">
+        <f t="shared" si="46"/>
+        <v>3804.85</v>
+      </c>
+      <c r="J185" s="197">
+        <f t="shared" si="46"/>
+        <v>-5379.9250000000002</v>
+      </c>
+      <c r="N185" s="104">
+        <f>N14+N183-N184</f>
+        <v>-7211.85</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B186" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C186" s="104">
+        <f>C181+C72-C182</f>
+        <v>0</v>
+      </c>
+      <c r="D186" s="104">
+        <f t="shared" ref="D186:J186" si="47">D181+D72-D182</f>
+        <v>0</v>
+      </c>
+      <c r="E186" s="104">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="F186" s="104">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="G186" s="104">
+        <f t="shared" si="47"/>
+        <v>207183</v>
+      </c>
+      <c r="H186" s="104">
+        <f t="shared" si="47"/>
+        <v>212513</v>
+      </c>
+      <c r="I186" s="104">
+        <f t="shared" si="47"/>
+        <v>224388</v>
+      </c>
+      <c r="J186" s="104">
+        <f t="shared" si="47"/>
+        <v>365826</v>
+      </c>
+      <c r="N186" s="104">
+        <f>J186</f>
+        <v>365826</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B187" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C187" s="104"/>
+      <c r="D187" s="104"/>
+      <c r="E187" s="104"/>
+      <c r="F187" s="104"/>
+      <c r="G187" s="104"/>
+      <c r="H187" s="104"/>
+      <c r="I187" s="104"/>
+      <c r="J187" s="104"/>
+      <c r="N187" s="104">
+        <f>N185</f>
+        <v>-7211.85</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B188" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="C188" s="104">
+        <f>C185+C149+C77</f>
+        <v>-12565</v>
+      </c>
+      <c r="D188" s="104">
+        <f t="shared" ref="D188:J188" si="48">D185+D149+D77</f>
+        <v>-9662</v>
+      </c>
+      <c r="E188" s="104">
+        <f t="shared" si="48"/>
+        <v>-6511</v>
+      </c>
+      <c r="F188" s="104">
+        <f t="shared" si="48"/>
+        <v>-490</v>
+      </c>
+      <c r="G188" s="104">
+        <f t="shared" si="48"/>
+        <v>3937.85</v>
+      </c>
+      <c r="H188" s="104">
+        <f t="shared" si="48"/>
+        <v>6229</v>
+      </c>
+      <c r="I188" s="104">
+        <f t="shared" si="48"/>
+        <v>11526.85</v>
+      </c>
+      <c r="J188" s="104">
+        <f t="shared" si="48"/>
+        <v>4530.0749999999998</v>
+      </c>
+      <c r="N188" s="104">
+        <f>N185+N149+N77</f>
+        <v>25195.15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B190" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17547,7 +18333,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="N5:N6 N18:N23 N8:N12 G47:I47 G64:I64 N14:N17" formulaRange="1"/>
+    <ignoredError sqref="N5:N6 N18:N23 N8:N12 G47:I47 G64:I64 N14:N17 N77 N149" formulaRange="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -24527,36 +25313,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="141"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="230" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
       <c r="O2" s="91"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="230" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="230"/>
+      <c r="U2" s="230"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="230"/>
+      <c r="Y2" s="230"/>
+      <c r="Z2" s="230"/>
+      <c r="AA2" s="230" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="230"/>
+      <c r="AC2" s="230"/>
       <c r="AE2" s="145" t="s">
         <v>74</v>
       </c>
@@ -24567,32 +25353,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="146"/>
       <c r="B4" s="93"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="234" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
+      <c r="H4" s="234"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="234"/>
+      <c r="K4" s="234"/>
+      <c r="L4" s="234"/>
       <c r="O4" s="91"/>
-      <c r="S4" s="234" t="s">
+      <c r="S4" s="235" t="s">
         <v>188</v>
       </c>
-      <c r="T4" s="235"/>
-      <c r="U4" s="235"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="235"/>
-      <c r="X4" s="235"/>
-      <c r="Y4" s="235"/>
-      <c r="Z4" s="235"/>
-      <c r="AA4" s="235"/>
-      <c r="AB4" s="235"/>
-      <c r="AC4" s="235"/>
+      <c r="T4" s="236"/>
+      <c r="U4" s="236"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="236"/>
+      <c r="X4" s="236"/>
+      <c r="Y4" s="236"/>
+      <c r="Z4" s="236"/>
+      <c r="AA4" s="236"/>
+      <c r="AB4" s="236"/>
+      <c r="AC4" s="236"/>
       <c r="AE4" s="147" t="s">
         <v>273</v>
       </c>
@@ -24692,27 +25478,27 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="151" t="str">
-        <f>'Statement Y'!B181</f>
+        <f>'Statement Y'!B182</f>
         <v>Subscription and related services</v>
       </c>
       <c r="C6" s="148">
-        <f>'Statement Y'!D181</f>
+        <f>'Statement Y'!D182</f>
         <v>95514</v>
       </c>
       <c r="D6" s="148">
-        <f>'Statement Y'!E181</f>
+        <f>'Statement Y'!E182</f>
         <v>128975</v>
       </c>
       <c r="E6" s="148">
-        <f>'Statement Y'!F181</f>
+        <f>'Statement Y'!F182</f>
         <v>165436</v>
       </c>
       <c r="F6" s="148">
-        <f>'Statement Y'!G181</f>
+        <f>'Statement Y'!G182</f>
         <v>196510</v>
       </c>
       <c r="G6" s="149">
-        <f>'Statement Y'!H181</f>
+        <f>'Statement Y'!H182</f>
         <v>219461</v>
       </c>
       <c r="H6" s="150">
@@ -24743,39 +25529,39 @@
         <v>197</v>
       </c>
       <c r="R6" s="159" t="str">
-        <f>'Statement Q'!B170</f>
+        <f>'Statement Q'!B172</f>
         <v>Subscription and related services</v>
       </c>
       <c r="S6" s="148">
-        <f>'Statement Q'!C170</f>
+        <f>'Statement Q'!C172</f>
         <v>46742</v>
       </c>
       <c r="T6" s="148">
-        <f>'Statement Q'!D170</f>
+        <f>'Statement Q'!D172</f>
         <v>48612</v>
       </c>
       <c r="U6" s="148">
-        <f>'Statement Q'!E170</f>
+        <f>'Statement Q'!E172</f>
         <v>49363</v>
       </c>
       <c r="V6" s="148">
-        <f>'Statement Q'!F170</f>
+        <f>'Statement Q'!F172</f>
         <v>51793</v>
       </c>
       <c r="W6" s="148">
-        <f>'Statement Q'!G170</f>
+        <f>'Statement Q'!G172</f>
         <v>54355</v>
       </c>
       <c r="X6" s="148">
-        <f>'Statement Q'!H170</f>
+        <f>'Statement Q'!H172</f>
         <v>53702</v>
       </c>
       <c r="Y6" s="148">
-        <f>'Statement Q'!I170</f>
+        <f>'Statement Q'!I172</f>
         <v>55480</v>
       </c>
       <c r="Z6" s="149">
-        <f>'Statement Q'!J170</f>
+        <f>'Statement Q'!J172</f>
         <v>55924</v>
       </c>
       <c r="AA6" s="150">
@@ -24791,27 +25577,27 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B7" s="151" t="str">
-        <f>'Statement Y'!B182</f>
+        <f>'Statement Y'!B183</f>
         <v>Payment solutions</v>
       </c>
       <c r="C7" s="148">
-        <f>'Statement Y'!D182</f>
+        <f>'Statement Y'!D183</f>
         <v>65201</v>
       </c>
       <c r="D7" s="148">
-        <f>'Statement Y'!E182</f>
+        <f>'Statement Y'!E183</f>
         <v>78368</v>
       </c>
       <c r="E7" s="148">
-        <f>'Statement Y'!F182</f>
+        <f>'Statement Y'!F183</f>
         <v>94610</v>
       </c>
       <c r="F7" s="148">
-        <f>'Statement Y'!G182</f>
+        <f>'Statement Y'!G183</f>
         <v>101740</v>
       </c>
       <c r="G7" s="149">
-        <f>'Statement Y'!H182</f>
+        <f>'Statement Y'!H183</f>
         <v>121459</v>
       </c>
       <c r="H7" s="150">
@@ -24842,39 +25628,39 @@
         <v>184</v>
       </c>
       <c r="R7" s="159" t="str">
-        <f>'Statement Q'!B171</f>
+        <f>'Statement Q'!B173</f>
         <v>Payment solutions</v>
       </c>
       <c r="S7" s="148">
-        <f>'Statement Q'!C171</f>
+        <f>'Statement Q'!C173</f>
         <v>27060</v>
       </c>
       <c r="T7" s="148">
-        <f>'Statement Q'!D171</f>
+        <f>'Statement Q'!D173</f>
         <v>25300</v>
       </c>
       <c r="U7" s="148">
-        <f>'Statement Q'!E171</f>
+        <f>'Statement Q'!E173</f>
         <v>24704</v>
       </c>
       <c r="V7" s="148">
-        <f>'Statement Q'!F171</f>
+        <f>'Statement Q'!F173</f>
         <v>24676</v>
       </c>
       <c r="W7" s="148">
-        <f>'Statement Q'!G171</f>
+        <f>'Statement Q'!G173</f>
         <v>29925</v>
       </c>
       <c r="X7" s="148">
-        <f>'Statement Q'!H171</f>
+        <f>'Statement Q'!H173</f>
         <v>28392</v>
       </c>
       <c r="Y7" s="148">
-        <f>'Statement Q'!I171</f>
+        <f>'Statement Q'!I173</f>
         <v>27422</v>
       </c>
       <c r="Z7" s="149">
-        <f>'Statement Q'!J171</f>
+        <f>'Statement Q'!J173</f>
         <v>35720</v>
       </c>
       <c r="AA7" s="150">
@@ -24890,27 +25676,27 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B8" s="151" t="str">
-        <f>'Statement Y'!B183</f>
+        <f>'Statement Y'!B184</f>
         <v>Network solutions</v>
       </c>
       <c r="C8" s="148">
-        <f>'Statement Y'!D183</f>
+        <f>'Statement Y'!D184</f>
         <v>52518</v>
       </c>
       <c r="D8" s="148">
-        <f>'Statement Y'!E183</f>
+        <f>'Statement Y'!E184</f>
         <v>73567</v>
       </c>
       <c r="E8" s="148">
-        <f>'Statement Y'!F183</f>
+        <f>'Statement Y'!F184</f>
         <v>96253</v>
       </c>
       <c r="F8" s="148">
-        <f>'Statement Y'!G183</f>
+        <f>'Statement Y'!G184</f>
         <v>121563</v>
       </c>
       <c r="G8" s="149">
-        <f>'Statement Y'!H183</f>
+        <f>'Statement Y'!H184</f>
         <v>139671</v>
       </c>
       <c r="H8" s="150">
@@ -24941,39 +25727,39 @@
         <v>277</v>
       </c>
       <c r="R8" s="159" t="str">
-        <f>'Statement Q'!B172</f>
+        <f>'Statement Q'!B174</f>
         <v>Network solutions</v>
       </c>
       <c r="S8" s="148">
-        <f>'Statement Q'!C172</f>
+        <f>'Statement Q'!C174</f>
         <v>27415</v>
       </c>
       <c r="T8" s="148">
-        <f>'Statement Q'!D172</f>
+        <f>'Statement Q'!D174</f>
         <v>28203</v>
       </c>
       <c r="U8" s="148">
-        <f>'Statement Q'!E172</f>
+        <f>'Statement Q'!E174</f>
         <v>32733</v>
       </c>
       <c r="V8" s="148">
-        <f>'Statement Q'!F172</f>
+        <f>'Statement Q'!F174</f>
         <v>33212</v>
       </c>
       <c r="W8" s="148">
-        <f>'Statement Q'!G172</f>
+        <f>'Statement Q'!G174</f>
         <v>31656</v>
       </c>
       <c r="X8" s="148">
-        <f>'Statement Q'!H172</f>
+        <f>'Statement Q'!H174</f>
         <v>35161</v>
       </c>
       <c r="Y8" s="148">
-        <f>'Statement Q'!I172</f>
+        <f>'Statement Q'!I174</f>
         <v>37431</v>
       </c>
       <c r="Z8" s="149">
-        <f>'Statement Q'!J172</f>
+        <f>'Statement Q'!J174</f>
         <v>35423</v>
       </c>
       <c r="AA8" s="150">
@@ -25087,33 +25873,33 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="233" t="s">
+      <c r="C11" s="234" t="s">
         <v>210</v>
       </c>
-      <c r="D11" s="233"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
+      <c r="D11" s="234"/>
+      <c r="E11" s="234"/>
+      <c r="F11" s="234"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="234"/>
+      <c r="I11" s="234"/>
+      <c r="J11" s="234"/>
+      <c r="K11" s="234"/>
+      <c r="L11" s="234"/>
       <c r="O11" s="91"/>
       <c r="Q11" s="92"/>
-      <c r="S11" s="234" t="s">
+      <c r="S11" s="235" t="s">
         <v>210</v>
       </c>
-      <c r="T11" s="235"/>
-      <c r="U11" s="235"/>
-      <c r="V11" s="235"/>
-      <c r="W11" s="235"/>
-      <c r="X11" s="235"/>
-      <c r="Y11" s="235"/>
-      <c r="Z11" s="235"/>
-      <c r="AA11" s="235"/>
-      <c r="AB11" s="235"/>
-      <c r="AC11" s="235"/>
+      <c r="T11" s="236"/>
+      <c r="U11" s="236"/>
+      <c r="V11" s="236"/>
+      <c r="W11" s="236"/>
+      <c r="X11" s="236"/>
+      <c r="Y11" s="236"/>
+      <c r="Z11" s="236"/>
+      <c r="AA11" s="236"/>
+      <c r="AB11" s="236"/>
+      <c r="AC11" s="236"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
@@ -25546,32 +26332,32 @@
       <c r="Q17" s="92"/>
     </row>
     <row r="18" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="234" t="s">
         <v>274</v>
       </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="234"/>
+      <c r="G18" s="234"/>
+      <c r="H18" s="234"/>
+      <c r="I18" s="234"/>
+      <c r="J18" s="234"/>
+      <c r="K18" s="234"/>
+      <c r="L18" s="234"/>
       <c r="O18" s="91"/>
-      <c r="S18" s="234" t="s">
+      <c r="S18" s="235" t="s">
         <v>210</v>
       </c>
-      <c r="T18" s="235"/>
-      <c r="U18" s="235"/>
-      <c r="V18" s="235"/>
-      <c r="W18" s="235"/>
-      <c r="X18" s="235"/>
-      <c r="Y18" s="235"/>
-      <c r="Z18" s="235"/>
-      <c r="AA18" s="235"/>
-      <c r="AB18" s="235"/>
-      <c r="AC18" s="235"/>
+      <c r="T18" s="236"/>
+      <c r="U18" s="236"/>
+      <c r="V18" s="236"/>
+      <c r="W18" s="236"/>
+      <c r="X18" s="236"/>
+      <c r="Y18" s="236"/>
+      <c r="Z18" s="236"/>
+      <c r="AA18" s="236"/>
+      <c r="AB18" s="236"/>
+      <c r="AC18" s="236"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B19" s="7"/>
@@ -25664,27 +26450,27 @@
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="str">
-        <f>'Statement Y'!B174</f>
+        <f>'Statement Y'!B175</f>
         <v>Patient payment volume</v>
       </c>
       <c r="C20" s="114">
-        <f>'Statement Y'!D174</f>
+        <f>'Statement Y'!D175</f>
         <v>2768000</v>
       </c>
       <c r="D20" s="114">
-        <f>'Statement Y'!E174</f>
+        <f>'Statement Y'!E175</f>
         <v>3284000</v>
       </c>
       <c r="E20" s="114">
-        <f>'Statement Y'!F174</f>
+        <f>'Statement Y'!F175</f>
         <v>3947000</v>
       </c>
       <c r="F20" s="114">
-        <f>'Statement Y'!G174</f>
+        <f>'Statement Y'!G175</f>
         <v>4420000</v>
       </c>
       <c r="G20" s="161">
-        <f>'Statement Y'!H174</f>
+        <f>'Statement Y'!H175</f>
         <v>4873000</v>
       </c>
       <c r="H20" s="104">
@@ -25709,39 +26495,39 @@
       </c>
       <c r="O20" s="91"/>
       <c r="R20" s="1" t="str">
-        <f>'Statement Q'!B163</f>
+        <f>'Statement Q'!B165</f>
         <v>Patient payment volume</v>
       </c>
       <c r="S20" s="114">
-        <f>'Statement Q'!C163</f>
+        <f>'Statement Q'!C165</f>
         <v>1166000</v>
       </c>
       <c r="T20" s="114">
-        <f>'Statement Q'!D163</f>
+        <f>'Statement Q'!D165</f>
         <v>1093000</v>
       </c>
       <c r="U20" s="114">
-        <f>'Statement Q'!E163</f>
+        <f>'Statement Q'!E165</f>
         <v>1081000</v>
       </c>
       <c r="V20" s="114">
-        <f>'Statement Q'!F163</f>
+        <f>'Statement Q'!F165</f>
         <v>1080000</v>
       </c>
       <c r="W20" s="114">
-        <f>'Statement Q'!G163</f>
+        <f>'Statement Q'!G165</f>
         <v>1314000</v>
       </c>
       <c r="X20" s="114">
-        <f>'Statement Q'!H163</f>
+        <f>'Statement Q'!H165</f>
         <v>1250000</v>
       </c>
       <c r="Y20" s="114">
-        <f>'Statement Q'!I163</f>
+        <f>'Statement Q'!I165</f>
         <v>1181000</v>
       </c>
       <c r="Z20" s="161">
-        <f>'Statement Q'!J163</f>
+        <f>'Statement Q'!J165</f>
         <v>1128000</v>
       </c>
       <c r="AA20" s="104">
@@ -25828,27 +26614,27 @@
     </row>
     <row r="22" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B22" s="151" t="str">
-        <f>'Statement Y'!B175</f>
+        <f>'Statement Y'!B176</f>
         <v>Payment facilitator volume</v>
       </c>
       <c r="C22" s="162">
-        <f>'Statement Y'!D175</f>
+        <f>'Statement Y'!D176</f>
         <v>0.79</v>
       </c>
       <c r="D22" s="162">
-        <f>'Statement Y'!E175</f>
+        <f>'Statement Y'!E176</f>
         <v>0.8</v>
       </c>
       <c r="E22" s="162">
-        <f>'Statement Y'!F175</f>
+        <f>'Statement Y'!F176</f>
         <v>0.82</v>
       </c>
       <c r="F22" s="162">
-        <f>'Statement Y'!G175</f>
+        <f>'Statement Y'!G176</f>
         <v>0.81</v>
       </c>
       <c r="G22" s="163">
-        <f>'Statement Y'!H175</f>
+        <f>'Statement Y'!H176</f>
         <v>0.83</v>
       </c>
       <c r="H22" s="96">
@@ -25868,39 +26654,39 @@
       </c>
       <c r="O22" s="91"/>
       <c r="R22" s="1" t="str">
-        <f>'Statement Q'!B164</f>
+        <f>'Statement Q'!B166</f>
         <v>Payment facilitator volume</v>
       </c>
       <c r="S22" s="164">
-        <f>'Statement Q'!C164</f>
+        <f>'Statement Q'!C166</f>
         <v>0.81</v>
       </c>
       <c r="T22" s="164">
-        <f>'Statement Q'!D164</f>
+        <f>'Statement Q'!D166</f>
         <v>0.81</v>
       </c>
       <c r="U22" s="164">
-        <f>'Statement Q'!E164</f>
+        <f>'Statement Q'!E166</f>
         <v>0.81</v>
       </c>
       <c r="V22" s="164">
-        <f>'Statement Q'!F164</f>
+        <f>'Statement Q'!F166</f>
         <v>0.82</v>
       </c>
       <c r="W22" s="164">
-        <f>'Statement Q'!G164</f>
+        <f>'Statement Q'!G166</f>
         <v>0.82</v>
       </c>
       <c r="X22" s="164">
-        <f>'Statement Q'!H164</f>
+        <f>'Statement Q'!H166</f>
         <v>0.82</v>
       </c>
       <c r="Y22" s="164">
-        <f>'Statement Q'!I164</f>
+        <f>'Statement Q'!I166</f>
         <v>0.85</v>
       </c>
       <c r="Z22" s="165">
-        <f>'Statement Q'!J164</f>
+        <f>'Statement Q'!J166</f>
         <v>0.84</v>
       </c>
       <c r="AA22" s="96">
@@ -25909,27 +26695,27 @@
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="str">
-        <f>'Statement Y'!B176</f>
+        <f>'Statement Y'!B177</f>
         <v>Take rate</v>
       </c>
       <c r="C23" s="164">
-        <f>'Statement Y'!D176</f>
+        <f>'Statement Y'!D177</f>
         <v>2.98E-2</v>
       </c>
       <c r="D23" s="164">
-        <f>'Statement Y'!E176</f>
+        <f>'Statement Y'!E177</f>
         <v>2.98E-2</v>
       </c>
       <c r="E23" s="164">
-        <f>'Statement Y'!F176</f>
+        <f>'Statement Y'!F177</f>
         <v>2.92E-2</v>
       </c>
       <c r="F23" s="164">
-        <f>'Statement Y'!G176</f>
+        <f>'Statement Y'!G177</f>
         <v>2.8299999999999999E-2</v>
       </c>
       <c r="G23" s="165">
-        <f>'Statement Y'!H176</f>
+        <f>'Statement Y'!H177</f>
         <v>3.0029990678906885E-2</v>
       </c>
       <c r="H23" s="103">
@@ -25949,39 +26735,39 @@
       </c>
       <c r="O23" s="91"/>
       <c r="R23" s="1" t="str">
-        <f>'Statement Q'!B165</f>
+        <f>'Statement Q'!B167</f>
         <v>Take rate</v>
       </c>
       <c r="S23" s="169">
-        <f>'Statement Q'!C165</f>
+        <f>'Statement Q'!C167</f>
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="T23" s="169">
-        <f>'Statement Q'!D165</f>
+        <f>'Statement Q'!D167</f>
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="U23" s="169">
-        <f>'Statement Q'!E165</f>
+        <f>'Statement Q'!E167</f>
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="V23" s="169">
-        <f>'Statement Q'!F165</f>
+        <f>'Statement Q'!F167</f>
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="W23" s="169">
-        <f>'Statement Q'!G165</f>
+        <f>'Statement Q'!G167</f>
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="X23" s="169">
-        <f>'Statement Q'!H165</f>
+        <f>'Statement Q'!H167</f>
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="Y23" s="169">
-        <f>'Statement Q'!I165</f>
+        <f>'Statement Q'!I167</f>
         <v>2.7E-2</v>
       </c>
       <c r="Z23" s="165">
-        <f>'Statement Q'!J165</f>
+        <f>'Statement Q'!J167</f>
         <v>3.7698412698412696E-2</v>
       </c>
       <c r="AA23" s="103">
@@ -25990,27 +26776,27 @@
     </row>
     <row r="24" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="str">
-        <f>'Statement Y'!B172</f>
+        <f>'Statement Y'!B173</f>
         <v>AHSC</v>
       </c>
       <c r="C24" s="114">
-        <f>'Statement Y'!D172</f>
+        <f>'Statement Y'!D173</f>
         <v>2074</v>
       </c>
       <c r="D24" s="114">
-        <f>'Statement Y'!E172</f>
+        <f>'Statement Y'!E173</f>
         <v>2856</v>
       </c>
       <c r="E24" s="114">
-        <f>'Statement Y'!F172</f>
+        <f>'Statement Y'!F173</f>
         <v>3601</v>
       </c>
       <c r="F24" s="114">
-        <f>'Statement Y'!G172</f>
+        <f>'Statement Y'!G173</f>
         <v>4203</v>
       </c>
       <c r="G24" s="166">
-        <f>'Statement Y'!H172</f>
+        <f>'Statement Y'!H173</f>
         <v>4514</v>
       </c>
       <c r="H24" s="104">
@@ -26035,39 +26821,39 @@
       </c>
       <c r="O24" s="91"/>
       <c r="R24" s="1" t="str">
-        <f>'Statement Q'!B161</f>
+        <f>'Statement Q'!B163</f>
         <v>AHSC</v>
       </c>
       <c r="S24" s="114">
-        <f>'Statement Q'!C161</f>
+        <f>'Statement Q'!C163</f>
         <v>4065</v>
       </c>
       <c r="T24" s="114">
-        <f>'Statement Q'!D161</f>
+        <f>'Statement Q'!D163</f>
         <v>4169</v>
       </c>
       <c r="U24" s="114">
-        <f>'Statement Q'!E161</f>
+        <f>'Statement Q'!E163</f>
         <v>4237</v>
       </c>
       <c r="V24" s="114">
-        <f>'Statement Q'!F161</f>
+        <f>'Statement Q'!F163</f>
         <v>4341</v>
       </c>
       <c r="W24" s="114">
-        <f>'Statement Q'!G161</f>
+        <f>'Statement Q'!G163</f>
         <v>4411</v>
       </c>
       <c r="X24" s="114">
-        <f>'Statement Q'!H161</f>
+        <f>'Statement Q'!H163</f>
         <v>4467</v>
       </c>
       <c r="Y24" s="114">
-        <f>'Statement Q'!I161</f>
+        <f>'Statement Q'!I163</f>
         <v>4520</v>
       </c>
       <c r="Z24" s="166">
-        <f>'Statement Q'!J161</f>
+        <f>'Statement Q'!J163</f>
         <v>4658</v>
       </c>
       <c r="AA24" s="104">
@@ -26154,27 +26940,27 @@
     </row>
     <row r="26" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="str">
-        <f>'Statement Y'!B173</f>
+        <f>'Statement Y'!B174</f>
         <v>Avg subscription revenue per AHSC</v>
       </c>
       <c r="C26" s="167">
-        <f>'Statement Y'!D173</f>
+        <f>'Statement Y'!D174</f>
         <v>46.053037608486015</v>
       </c>
       <c r="D26" s="167">
-        <f>'Statement Y'!E173</f>
+        <f>'Statement Y'!E174</f>
         <v>45.159313725490193</v>
       </c>
       <c r="E26" s="167">
-        <f>'Statement Y'!F173</f>
+        <f>'Statement Y'!F174</f>
         <v>45.94168286587059</v>
       </c>
       <c r="F26" s="167">
-        <f>'Statement Y'!G173</f>
+        <f>'Statement Y'!G174</f>
         <v>46.754699024506309</v>
       </c>
       <c r="G26" s="168">
-        <f>'Statement Y'!H173</f>
+        <f>'Statement Y'!H174</f>
         <v>48.61785556047851</v>
       </c>
       <c r="H26" s="94">
@@ -26199,39 +26985,39 @@
       </c>
       <c r="O26" s="91"/>
       <c r="R26" s="1" t="str">
-        <f>'Statement Q'!B162</f>
+        <f>'Statement Q'!B164</f>
         <v>Avg subscription revenue per AHSC</v>
       </c>
       <c r="S26" s="167">
-        <f>'Statement Q'!C162</f>
+        <f>'Statement Q'!C164</f>
         <v>11.498646986469865</v>
       </c>
       <c r="T26" s="167">
-        <f>'Statement Q'!D162</f>
+        <f>'Statement Q'!D164</f>
         <v>11.660350203885823</v>
       </c>
       <c r="U26" s="167">
-        <f>'Statement Q'!E162</f>
+        <f>'Statement Q'!E164</f>
         <v>11.650460231295728</v>
       </c>
       <c r="V26" s="167">
-        <f>'Statement Q'!F162</f>
+        <f>'Statement Q'!F164</f>
         <v>11.931121861322277</v>
       </c>
       <c r="W26" s="167">
-        <f>'Statement Q'!G162</f>
+        <f>'Statement Q'!G164</f>
         <v>12.322602584447971</v>
       </c>
       <c r="X26" s="167">
-        <f>'Statement Q'!H162</f>
+        <f>'Statement Q'!H164</f>
         <v>12.021938661293934</v>
       </c>
       <c r="Y26" s="167">
-        <f>'Statement Q'!I162</f>
+        <f>'Statement Q'!I164</f>
         <v>12.274336283185841</v>
       </c>
       <c r="Z26" s="168">
-        <f>'Statement Q'!J162</f>
+        <f>'Statement Q'!J164</f>
         <v>12.006011163589523</v>
       </c>
       <c r="AA26" s="94">
@@ -26318,24 +27104,24 @@
     </row>
     <row r="28" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="str">
-        <f>'Statement Y'!B177</f>
+        <f>'Statement Y'!B178</f>
         <v>Annual patient visits</v>
       </c>
       <c r="C28" s="155"/>
       <c r="D28" s="114">
-        <f>'Statement Y'!E177</f>
+        <f>'Statement Y'!E178</f>
         <v>120000</v>
       </c>
       <c r="E28" s="114">
-        <f>'Statement Y'!F177</f>
+        <f>'Statement Y'!F178</f>
         <v>150000</v>
       </c>
       <c r="F28" s="114">
-        <f>'Statement Y'!G177</f>
+        <f>'Statement Y'!G178</f>
         <v>170000</v>
       </c>
       <c r="G28" s="166">
-        <f>'Statement Y'!H177</f>
+        <f>'Statement Y'!H178</f>
         <v>180000</v>
       </c>
       <c r="H28" s="104">
@@ -26360,39 +27146,39 @@
       </c>
       <c r="O28" s="91"/>
       <c r="R28" s="1" t="str">
-        <f>'Statement Q'!B166</f>
+        <f>'Statement Q'!B168</f>
         <v>Network solutions revenue per AHSC</v>
       </c>
       <c r="S28" s="167">
-        <f>'Statement Q'!C166</f>
+        <f>'Statement Q'!C168</f>
         <v>6.7441574415744157</v>
       </c>
       <c r="T28" s="167">
-        <f>'Statement Q'!D166</f>
+        <f>'Statement Q'!D168</f>
         <v>6.7649316382825617</v>
       </c>
       <c r="U28" s="167">
-        <f>'Statement Q'!E166</f>
+        <f>'Statement Q'!E168</f>
         <v>7.7255133349067737</v>
       </c>
       <c r="V28" s="167">
-        <f>'Statement Q'!F166</f>
+        <f>'Statement Q'!F168</f>
         <v>7.6507717115871916</v>
       </c>
       <c r="W28" s="167">
-        <f>'Statement Q'!G166</f>
+        <f>'Statement Q'!G168</f>
         <v>7.1766039446837455</v>
       </c>
       <c r="X28" s="167">
-        <f>'Statement Q'!H166</f>
+        <f>'Statement Q'!H168</f>
         <v>7.8712782628162081</v>
       </c>
       <c r="Y28" s="167">
-        <f>'Statement Q'!I166</f>
+        <f>'Statement Q'!I168</f>
         <v>8.2811946902654867</v>
       </c>
       <c r="Z28" s="168">
-        <f>'Statement Q'!J166</f>
+        <f>'Statement Q'!J168</f>
         <v>7.6047659939888366</v>
       </c>
       <c r="AA28" s="94">
@@ -26481,24 +27267,24 @@
     </row>
     <row r="30" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="str">
-        <f>'Statement Y'!B187</f>
+        <f>'Statement Y'!B188</f>
         <v>Patient visit per AHSC</v>
       </c>
       <c r="C30" s="155"/>
       <c r="D30" s="167">
-        <f>'Statement Y'!E187</f>
+        <f>'Statement Y'!E188</f>
         <v>42.016806722689076</v>
       </c>
       <c r="E30" s="167">
-        <f>'Statement Y'!F187</f>
+        <f>'Statement Y'!F188</f>
         <v>41.655095806720354</v>
       </c>
       <c r="F30" s="167">
-        <f>'Statement Y'!G187</f>
+        <f>'Statement Y'!G188</f>
         <v>40.447299547941945</v>
       </c>
       <c r="G30" s="168">
-        <f>'Statement Y'!H187</f>
+        <f>'Statement Y'!H188</f>
         <v>39.875941515285774</v>
       </c>
       <c r="H30" s="94">
@@ -26560,24 +27346,24 @@
     </row>
     <row r="32" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="str">
-        <f>'Statement Y'!B188</f>
+        <f>'Statement Y'!B189</f>
         <v>Revenue per visit</v>
       </c>
       <c r="C32" s="155"/>
       <c r="D32" s="167">
-        <f>'Statement Y'!E188</f>
+        <f>'Statement Y'!E189</f>
         <v>0.61305833333333337</v>
       </c>
       <c r="E32" s="167">
-        <f>'Statement Y'!F188</f>
+        <f>'Statement Y'!F189</f>
         <v>0.64168666666666663</v>
       </c>
       <c r="F32" s="167">
-        <f>'Statement Y'!G188</f>
+        <f>'Statement Y'!G189</f>
         <v>0.71507647058823531</v>
       </c>
       <c r="G32" s="168">
-        <f>'Statement Y'!H188</f>
+        <f>'Statement Y'!H189</f>
         <v>0.77595000000000003</v>
       </c>
       <c r="H32" s="94">
@@ -26697,35 +27483,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="141"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="230" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237" t="s">
+      <c r="D2" s="230"/>
+      <c r="E2" s="230"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="230"/>
+      <c r="L2" s="230"/>
+      <c r="P2" s="230" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="230"/>
+      <c r="R2" s="230"/>
+      <c r="S2" s="230"/>
+      <c r="T2" s="230"/>
+      <c r="U2" s="230"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="230" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="230"/>
+      <c r="Z2" s="230"/>
       <c r="AB2" s="145" t="s">
         <v>74</v>
       </c>
@@ -26734,31 +27520,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="146"/>
       <c r="B4" s="93"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="234" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
-      <c r="P4" s="235" t="s">
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
+      <c r="H4" s="234"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="234"/>
+      <c r="K4" s="234"/>
+      <c r="L4" s="234"/>
+      <c r="P4" s="236" t="s">
         <v>188</v>
       </c>
-      <c r="Q4" s="235"/>
-      <c r="R4" s="235"/>
-      <c r="S4" s="235"/>
-      <c r="T4" s="235"/>
-      <c r="U4" s="235"/>
-      <c r="V4" s="235"/>
-      <c r="W4" s="235"/>
-      <c r="X4" s="235"/>
-      <c r="Y4" s="235"/>
-      <c r="Z4" s="235"/>
+      <c r="Q4" s="236"/>
+      <c r="R4" s="236"/>
+      <c r="S4" s="236"/>
+      <c r="T4" s="236"/>
+      <c r="U4" s="236"/>
+      <c r="V4" s="236"/>
+      <c r="W4" s="236"/>
+      <c r="X4" s="236"/>
+      <c r="Y4" s="236"/>
+      <c r="Z4" s="236"/>
       <c r="AB4" s="147" t="str">
         <f>Revenue!AE4</f>
         <v>Q2-Q3-Q4</v>
@@ -26961,32 +27747,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="233" t="s">
+      <c r="C9" s="234" t="s">
         <v>279</v>
       </c>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="234"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="234"/>
+      <c r="L9" s="234"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="235" t="s">
+      <c r="P9" s="236" t="s">
         <v>280</v>
       </c>
-      <c r="Q9" s="235"/>
-      <c r="R9" s="235"/>
-      <c r="S9" s="235"/>
-      <c r="T9" s="235"/>
-      <c r="U9" s="235"/>
-      <c r="V9" s="235"/>
-      <c r="W9" s="235"/>
-      <c r="X9" s="235"/>
-      <c r="Y9" s="235"/>
-      <c r="Z9" s="235"/>
+      <c r="Q9" s="236"/>
+      <c r="R9" s="236"/>
+      <c r="S9" s="236"/>
+      <c r="T9" s="236"/>
+      <c r="U9" s="236"/>
+      <c r="V9" s="236"/>
+      <c r="W9" s="236"/>
+      <c r="X9" s="236"/>
+      <c r="Y9" s="236"/>
+      <c r="Z9" s="236"/>
       <c r="AB9" s="147" t="str">
         <f>AB4</f>
         <v>Q2-Q3-Q4</v>
@@ -27742,31 +28528,31 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="233" t="s">
+      <c r="C20" s="234" t="s">
         <v>283</v>
       </c>
-      <c r="D20" s="233"/>
-      <c r="E20" s="233"/>
-      <c r="F20" s="233"/>
-      <c r="G20" s="233"/>
-      <c r="H20" s="233"/>
-      <c r="I20" s="233"/>
-      <c r="J20" s="233"/>
-      <c r="K20" s="233"/>
-      <c r="L20" s="233"/>
-      <c r="P20" s="235" t="s">
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="234"/>
+      <c r="G20" s="234"/>
+      <c r="H20" s="234"/>
+      <c r="I20" s="234"/>
+      <c r="J20" s="234"/>
+      <c r="K20" s="234"/>
+      <c r="L20" s="234"/>
+      <c r="P20" s="236" t="s">
         <v>283</v>
       </c>
-      <c r="Q20" s="235"/>
-      <c r="R20" s="235"/>
-      <c r="S20" s="235"/>
-      <c r="T20" s="235"/>
-      <c r="U20" s="235"/>
-      <c r="V20" s="235"/>
-      <c r="W20" s="235"/>
-      <c r="X20" s="235"/>
-      <c r="Y20" s="235"/>
-      <c r="Z20" s="235"/>
+      <c r="Q20" s="236"/>
+      <c r="R20" s="236"/>
+      <c r="S20" s="236"/>
+      <c r="T20" s="236"/>
+      <c r="U20" s="236"/>
+      <c r="V20" s="236"/>
+      <c r="W20" s="236"/>
+      <c r="X20" s="236"/>
+      <c r="Y20" s="236"/>
+      <c r="Z20" s="236"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
@@ -28402,60 +29188,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="141"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="230" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237" t="s">
+      <c r="D3" s="230"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="237"/>
+      <c r="H3" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="238"/>
-      <c r="T3" s="238"/>
-      <c r="U3" s="238"/>
-      <c r="V3" s="238"/>
-      <c r="W3" s="238"/>
-      <c r="X3" s="238"/>
-      <c r="Y3" s="238"/>
-      <c r="Z3" s="238"/>
+      <c r="I3" s="230"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="P3" s="239"/>
+      <c r="Q3" s="239"/>
+      <c r="R3" s="239"/>
+      <c r="S3" s="239"/>
+      <c r="T3" s="239"/>
+      <c r="U3" s="239"/>
+      <c r="V3" s="239"/>
+      <c r="W3" s="239"/>
+      <c r="X3" s="239"/>
+      <c r="Y3" s="239"/>
+      <c r="Z3" s="239"/>
       <c r="AB3" s="174"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="146"/>
       <c r="B5" s="93"/>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="234" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="238"/>
-      <c r="T5" s="238"/>
-      <c r="U5" s="238"/>
-      <c r="V5" s="238"/>
-      <c r="W5" s="238"/>
-      <c r="X5" s="238"/>
-      <c r="Y5" s="238"/>
-      <c r="Z5" s="238"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="234"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="234"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="234"/>
+      <c r="P5" s="239"/>
+      <c r="Q5" s="239"/>
+      <c r="R5" s="239"/>
+      <c r="S5" s="239"/>
+      <c r="T5" s="239"/>
+      <c r="U5" s="239"/>
+      <c r="V5" s="239"/>
+      <c r="W5" s="239"/>
+      <c r="X5" s="239"/>
+      <c r="Y5" s="239"/>
+      <c r="Z5" s="239"/>
       <c r="AB5" s="175"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -28641,30 +29427,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="233" t="s">
+      <c r="C11" s="234" t="s">
         <v>285</v>
       </c>
-      <c r="D11" s="233"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
+      <c r="D11" s="234"/>
+      <c r="E11" s="234"/>
+      <c r="F11" s="234"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="234"/>
+      <c r="I11" s="234"/>
+      <c r="J11" s="234"/>
+      <c r="K11" s="234"/>
+      <c r="L11" s="234"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="238"/>
-      <c r="Q11" s="238"/>
-      <c r="R11" s="238"/>
-      <c r="S11" s="238"/>
-      <c r="T11" s="238"/>
-      <c r="U11" s="238"/>
-      <c r="V11" s="238"/>
-      <c r="W11" s="238"/>
-      <c r="X11" s="238"/>
-      <c r="Y11" s="238"/>
-      <c r="Z11" s="238"/>
+      <c r="P11" s="239"/>
+      <c r="Q11" s="239"/>
+      <c r="R11" s="239"/>
+      <c r="S11" s="239"/>
+      <c r="T11" s="239"/>
+      <c r="U11" s="239"/>
+      <c r="V11" s="239"/>
+      <c r="W11" s="239"/>
+      <c r="X11" s="239"/>
+      <c r="Y11" s="239"/>
+      <c r="Z11" s="239"/>
       <c r="AB11" s="175"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -28901,18 +29687,18 @@
       <c r="D16" s="20"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="234" t="s">
         <v>290</v>
       </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="234"/>
+      <c r="G18" s="234"/>
+      <c r="H18" s="234"/>
+      <c r="I18" s="234"/>
+      <c r="J18" s="234"/>
+      <c r="K18" s="234"/>
+      <c r="L18" s="234"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
@@ -29125,23 +29911,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="238"/>
-      <c r="C25" s="238"/>
+      <c r="B25" s="239"/>
+      <c r="C25" s="239"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="174"/>
-      <c r="C26" s="233" t="s">
+      <c r="C26" s="234" t="s">
         <v>296</v>
       </c>
-      <c r="D26" s="233"/>
-      <c r="E26" s="233"/>
-      <c r="F26" s="233"/>
-      <c r="G26" s="233"/>
-      <c r="H26" s="233"/>
-      <c r="I26" s="233"/>
-      <c r="J26" s="233"/>
-      <c r="K26" s="233"/>
-      <c r="L26" s="233"/>
+      <c r="D26" s="234"/>
+      <c r="E26" s="234"/>
+      <c r="F26" s="234"/>
+      <c r="G26" s="234"/>
+      <c r="H26" s="234"/>
+      <c r="I26" s="234"/>
+      <c r="J26" s="234"/>
+      <c r="K26" s="234"/>
+      <c r="L26" s="234"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -29328,18 +30114,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="174"/>
-      <c r="C33" s="233" t="s">
+      <c r="C33" s="234" t="s">
         <v>298</v>
       </c>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
-      <c r="I33" s="233"/>
-      <c r="J33" s="233"/>
-      <c r="K33" s="233"/>
-      <c r="L33" s="233"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="234"/>
+      <c r="G33" s="234"/>
+      <c r="H33" s="234"/>
+      <c r="I33" s="234"/>
+      <c r="J33" s="234"/>
+      <c r="K33" s="234"/>
+      <c r="L33" s="234"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
@@ -29523,18 +30309,18 @@
       <c r="C39" s="190"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="233" t="s">
+      <c r="C40" s="234" t="s">
         <v>301</v>
       </c>
-      <c r="D40" s="233"/>
-      <c r="E40" s="233"/>
-      <c r="F40" s="233"/>
-      <c r="G40" s="233"/>
-      <c r="H40" s="233"/>
-      <c r="I40" s="233"/>
-      <c r="J40" s="233"/>
-      <c r="K40" s="233"/>
-      <c r="L40" s="233"/>
+      <c r="D40" s="234"/>
+      <c r="E40" s="234"/>
+      <c r="F40" s="234"/>
+      <c r="G40" s="234"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="234"/>
+      <c r="J40" s="234"/>
+      <c r="K40" s="234"/>
+      <c r="L40" s="234"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
@@ -29650,23 +30436,23 @@
         <f t="shared" si="12"/>
         <v>6.5446502327342795E-2</v>
       </c>
-      <c r="H43" s="109">
+      <c r="H43" s="108">
         <f t="shared" si="12"/>
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="I43" s="109">
+      <c r="I43" s="108">
         <f t="shared" ref="I43:L43" si="13">I42/I7</f>
         <v>6.3E-2</v>
       </c>
-      <c r="J43" s="109">
+      <c r="J43" s="108">
         <f t="shared" si="13"/>
         <v>5.5E-2</v>
       </c>
-      <c r="K43" s="109">
+      <c r="K43" s="108">
         <f t="shared" si="13"/>
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="L43" s="109">
+      <c r="L43" s="108">
         <f t="shared" si="13"/>
         <v>3.9E-2</v>
       </c>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C49C1AE-CCB6-6143-901B-1135965B7280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3566C805-DB9C-AC42-AC3C-5C2EE47E560B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="6" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -2423,15 +2423,15 @@
       <sheetData sheetId="0">
         <row r="7">
           <cell r="C7">
-            <v>9.7149999999999999</v>
+            <v>8.7750000000000004</v>
           </cell>
           <cell r="F7">
-            <v>0.90390000000000004</v>
+            <v>0.8831</v>
           </cell>
         </row>
         <row r="10">
           <cell r="C10">
-            <v>43.64</v>
+            <v>45.86</v>
           </cell>
         </row>
       </sheetData>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$7</f>
-        <v>9.7149999999999999</v>
+        <v>8.7750000000000004</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="C10" s="104">
         <f>C3*'Statement Q'!J147</f>
-        <v>590312.54500000004</v>
+        <v>533195.32500000007</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.2">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C12" s="104">
         <f>C10+C11</f>
-        <v>618931.54500000004</v>
+        <v>561814.32500000007</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C14" s="94">
         <f>C3/'Statement Q'!N25</f>
-        <v>256.63440589765827</v>
+        <v>231.80307892454468</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C15" s="94">
         <f>$C$3/('Statement Q'!$N$5/'Statement Q'!$N$23)</f>
-        <v>1.231398299177471</v>
+        <v>1.1122511657521676</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="C6" s="196">
         <f>[1]Sheet1!$C$7</f>
-        <v>9.7149999999999999</v>
+        <v>8.7750000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="C7" s="197">
         <f>C5*C6</f>
-        <v>590312.54500000004</v>
+        <v>533195.32500000007</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="C9" s="198">
         <f>[1]Sheet1!$C$10/1000</f>
-        <v>4.3639999999999998E-2</v>
+        <v>4.5859999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C10" s="196">
         <f>[1]Sheet1!$F$7</f>
-        <v>0.90390000000000004</v>
+        <v>0.8831</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C16" s="97">
         <f>C8/(C8+C7)</f>
-        <v>0.14788494069774036</v>
+        <v>0.16117346756773135</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="C17" s="97">
         <f>C7/(C8+C7)</f>
-        <v>0.85211505930225961</v>
+        <v>0.83882653243226868</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C19" s="97">
         <f>C9+C10*C11</f>
-        <v>8.8834999999999997E-2</v>
+        <v>9.0014999999999998E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="C20" s="97">
         <f>(C17*C19)+(C16*C18)</f>
-        <v>8.4810311338910996E-2</v>
+        <v>8.5438479388414271E-2</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L8" s="120">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>855131.20993782196</v>
+        <v>846922.49070662411</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="7"/>
@@ -5049,23 +5049,23 @@
       <c r="G10" s="200"/>
       <c r="H10" s="120">
         <f>H7/(1+$C$15)^H9</f>
-        <v>13292.94129444628</v>
+        <v>13285.248365585127</v>
       </c>
       <c r="I10" s="120">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>8797.0264476393859</v>
+        <v>8786.8473135188488</v>
       </c>
       <c r="J10" s="120">
         <f t="shared" si="0"/>
-        <v>21407.580848158967</v>
+        <v>21370.435184945774</v>
       </c>
       <c r="K10" s="120">
         <f t="shared" si="0"/>
-        <v>30060.039748210795</v>
+        <v>29990.514403774658</v>
       </c>
       <c r="L10" s="120">
         <f t="shared" si="0"/>
-        <v>36166.598946149505</v>
+        <v>36062.067819338685</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -5084,7 +5084,7 @@
       <c r="K11" s="199"/>
       <c r="L11" s="120">
         <f>L8/(1+C15)^L9</f>
-        <v>569198.4834352188</v>
+        <v>562105.19436730468</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="C15" s="138">
         <f>WACC!C20</f>
-        <v>8.4810311338910996E-2</v>
+        <v>8.5438479388414271E-2</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="C19" s="150">
         <f>SUM(H10:L10)</f>
-        <v>109724.18728460494</v>
+        <v>109495.11308716309</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C20" s="150">
         <f>L11</f>
-        <v>569198.4834352188</v>
+        <v>562105.19436730468</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C21" s="154">
         <f>C19+C20</f>
-        <v>678922.6707198238</v>
+        <v>671600.30745446775</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="C24" s="154">
         <f>C21+C22-C23</f>
-        <v>650303.6707198238</v>
+        <v>642981.30745446775</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C26" s="203">
         <f>C24/C25</f>
-        <v>10.702296968876189</v>
+        <v>10.581790027721931</v>
       </c>
     </row>
   </sheetData>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C39" s="214">
         <f>WACC!C20</f>
-        <v>8.4810311338910996E-2</v>
+        <v>8.5438479388414271E-2</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="C44" s="203">
         <f>C43/(1+C48)^5</f>
-        <v>16.965635322873371</v>
+        <v>16.916600107259043</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C48" s="214">
         <f>WACC!C20</f>
-        <v>8.4810311338910996E-2</v>
+        <v>8.5438479388414271E-2</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="C52" s="203">
         <f>C51/(1+C48)^5</f>
-        <v>19.815625222357927</v>
+        <v>19.758352775036073</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C56" s="214">
         <f>WACC!C20</f>
-        <v>8.4810311338910996E-2</v>
+        <v>8.5438479388414271E-2</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C61" s="203">
         <f>C60/(1+C56)^5</f>
-        <v>9.5900040682790504</v>
+        <v>9.5622863961564875</v>
       </c>
     </row>
   </sheetData>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="C5" s="216">
         <f>DCF!C26</f>
-        <v>10.702296968876189</v>
+        <v>10.581790027721931</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="C6" s="216">
         <f>Multiples!C44</f>
-        <v>16.965635322873371</v>
+        <v>16.916600107259043</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C7" s="216">
         <f>Multiples!C52</f>
-        <v>19.815625222357927</v>
+        <v>19.758352775036073</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C8" s="216">
         <f>Multiples!C61</f>
-        <v>9.5900040682790504</v>
+        <v>9.5622863961564875</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="C9" s="203">
         <f>AVERAGE(C5:C8)</f>
-        <v>14.268390395596635</v>
+        <v>14.204757326543383</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C10" s="35">
         <f>Overview!C3</f>
-        <v>9.7149999999999999</v>
+        <v>8.7750000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="C11" s="90">
         <f>(C9-C10)/C10</f>
-        <v>0.46869690124515029</v>
+        <v>0.61877576370864762</v>
       </c>
     </row>
   </sheetData>
@@ -6699,7 +6699,7 @@
       <c r="K8" s="199"/>
       <c r="L8" s="120">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>907546.01588276098</v>
+        <v>898834.14763705002</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="7"/>
@@ -6753,23 +6753,23 @@
       <c r="G10" s="200"/>
       <c r="H10" s="120">
         <f>H7/(1+$C$21)^H9</f>
-        <v>2074.0953293695843</v>
+        <v>2072.8950030109058</v>
       </c>
       <c r="I10" s="120">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>4301.8714353127252</v>
+        <v>4296.8936935075835</v>
       </c>
       <c r="J10" s="120">
         <f t="shared" si="1"/>
-        <v>8922.4914515305536</v>
+        <v>8907.0094657409445</v>
       </c>
       <c r="K10" s="120">
         <f t="shared" si="1"/>
-        <v>18506.097845959568</v>
+        <v>18463.295413305241</v>
       </c>
       <c r="L10" s="120">
         <f t="shared" si="1"/>
-        <v>38383.411107161264</v>
+        <v>38272.472801354612</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="K11" s="199"/>
       <c r="L11" s="120">
         <f>L8/(1+C21)^L9</f>
-        <v>604087.1972450912</v>
+        <v>596559.12885245436</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="C15" s="218">
         <f>Overview!C3</f>
-        <v>9.7149999999999999</v>
+        <v>8.7750000000000004</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C16" s="218">
         <f>C36</f>
-        <v>10.697581824702942</v>
+        <v>10.570802877234067</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="C21" s="221">
         <f>WACC!C20</f>
-        <v>8.4810311338910996E-2</v>
+        <v>8.5438479388414271E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="C23" s="222">
         <f>C15*C22</f>
-        <v>590312.54500000004</v>
+        <v>533195.32500000007</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="C26" s="223">
         <f>C23+C25-C24</f>
-        <v>616570.54500000004</v>
+        <v>559453.32500000007</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="C29" s="222">
         <f>SUM(H10:L10)</f>
-        <v>72187.967169333686</v>
+        <v>72012.566376919291</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="C30" s="222">
         <f>L11</f>
-        <v>604087.1972450912</v>
+        <v>596559.12885245436</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="C31" s="225">
         <f>C29+C30</f>
-        <v>676275.16441442491</v>
+        <v>668571.69522937364</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="C34" s="225">
         <f>C31+C32-C33</f>
-        <v>650017.16441442491</v>
+        <v>642313.69522937364</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="C36" s="227">
         <f>C34/C35</f>
-        <v>10.697581824702942</v>
+        <v>10.570802877234067</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -7423,17 +7423,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -30589,12 +30589,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -30602,6 +30596,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FE46CC-76F2-B44C-A97A-26E8CA5FD7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2442D2A-05E3-4B4C-99FF-3C902DF13FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -162,7 +162,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -173,7 +173,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -183,19 +204,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="429">
   <si>
     <t>Ticker</t>
   </si>
@@ -1479,6 +1509,9 @@
   </si>
   <si>
     <t>Total Revenue per AHSC</t>
+  </si>
+  <si>
+    <t>Equity Value</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1528,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1669,12 +1702,6 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="20">
@@ -2438,6 +2465,18 @@
     <xf numFmtId="9" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="12" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2445,15 +2484,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2465,13 +2495,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12792,7 +12819,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=bqw82w&amp;q=XNYS%3aPHR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12811,11 +12838,9 @@
     <v>Powered by Refinitiv</v>
     <v>32.76</v>
     <v>7.77</v>
-    <v>0.84870000000000001</v>
-    <v>0.22</v>
-    <v>2.0521999999999999E-2</v>
-    <v>0</v>
-    <v>0</v>
+    <v>0.85370000000000001</v>
+    <v>-0.05</v>
+    <v>-4.5050000000000003E-3</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12823,35 +12848,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>11.06</v>
+    <v>11.435</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46205.958333356248</v>
+    <v>46210.764675462502</v>
     <v>0</v>
-    <v>10.67</v>
-    <v>676222076</v>
+    <v>10.98</v>
+    <v>683021384</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>10.67</v>
-    <v>72.043000000000006</v>
-    <v>10.72</v>
-    <v>10.94</v>
-    <v>10.94</v>
+    <v>11.414999999999999</v>
+    <v>74.260800000000003</v>
+    <v>11.1</v>
+    <v>11.05</v>
     <v>61811890</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>1000386</v>
-    <v>1594880</v>
+    <v>319116</v>
+    <v>1364795</v>
     <v>2005</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12865,28 +12904,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>0.1</v>
-    <v>2.235E-3</v>
+    <v>-0.06</v>
+    <v>-1.338E-3</v>
     <v>US</v>
-    <v>45.05</v>
+    <v>44.91</v>
     <v>Index</v>
-    <v>3</v>
-    <v>44.53</v>
+    <v>6</v>
+    <v>44.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.03</v>
-    <v>44.75</v>
+    <v>44.57</v>
     <v>44.85</v>
+    <v>44.79</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12908,8 +12947,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12930,7 +12967,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12940,6 +12976,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12975,7 +13016,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12986,16 +13027,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13089,19 +13127,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13173,9 +13205,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13183,9 +13212,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13687,18 +13713,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="262" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="259"/>
-      <c r="E2" s="258" t="s">
+      <c r="C2" s="263"/>
+      <c r="E2" s="262" t="s">
         <v>306</v>
       </c>
-      <c r="F2" s="259"/>
-      <c r="H2" s="258" t="s">
+      <c r="F2" s="263"/>
+      <c r="H2" s="262" t="s">
         <v>348</v>
       </c>
-      <c r="I2" s="259"/>
+      <c r="I2" s="263"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -13713,7 +13739,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>688213.52</v>
+        <v>695133.4</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -13721,7 +13747,7 @@
       </c>
       <c r="I3" s="215">
         <f>'AVG target price'!C5</f>
-        <v>8.2422268230202747</v>
+        <v>7.1607437568106667</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13737,7 +13763,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>704111.52</v>
+        <v>711031.4</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -13745,7 +13771,7 @@
       </c>
       <c r="I4" s="215">
         <f>'AVG target price'!C6</f>
-        <v>15.262462679567561</v>
+        <v>14.316056156428232</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13754,7 +13780,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>262</v>
@@ -13769,23 +13795,23 @@
       </c>
       <c r="I5" s="215">
         <f>'AVG target price'!C7</f>
-        <v>16.157887697352475</v>
+        <v>15.143111467278782</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="212" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.94</v>
+      <c r="C6" s="212" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>256</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>-288.94522824784502</v>
+        <v>-291.85052761779599</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -13793,7 +13819,7 @@
       </c>
       <c r="I6" s="215">
         <f>'AVG target price'!C8</f>
-        <v>9.2359877477721071</v>
+        <v>8.5561967040819642</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13802,14 +13828,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.22</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>215</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>1.3619206198672287</v>
+        <v>1.3756145200669907</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -13817,23 +13843,23 @@
       </c>
       <c r="I7" s="216">
         <f>'AVG target price'!C9</f>
-        <v>12.224641236928106</v>
+        <v>11.29402702114991</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="189" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>284</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>-6.5386684062818177E-4</v>
+        <v>-6.4735775895677003E-4</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -13841,7 +13867,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.11742607284534792</v>
+        <v>2.2083893316733879E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13850,23 +13876,23 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.0521999999999999E-2</v>
+        <v>-4.5050000000000003E-3</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>307</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>-3.4608635209654411E-3</v>
+        <v>-3.4264114859151062E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>0</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>312</v>
@@ -13914,7 +13940,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.84870000000000001</v>
+        <v>0.85370000000000001</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>116</v>
@@ -13930,7 +13956,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1594880</v>
+        <v>1364795</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>117</v>
@@ -13946,7 +13972,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>-2.3100388960681853E-2</v>
+        <v>-2.2870430337543844E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13959,10 +13985,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="260" t="s">
+      <c r="B17" s="264" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="260"/>
+      <c r="C17" s="264"/>
       <c r="E17" s="188" t="s">
         <v>315</v>
       </c>
@@ -14035,14 +14061,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="260" t="s">
+      <c r="B25" s="264" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="260"/>
-      <c r="E25" s="258" t="s">
+      <c r="C25" s="264"/>
+      <c r="E25" s="262" t="s">
         <v>362</v>
       </c>
-      <c r="F25" s="259"/>
+      <c r="F25" s="263"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -14051,12 +14077,12 @@
       <c r="C26" s="174">
         <v>0.21</v>
       </c>
-      <c r="E26" s="189" t="e" vm="2">
+      <c r="E26" s="189" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.85</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14071,7 +14097,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14079,7 +14105,7 @@
         <v>367</v>
       </c>
       <c r="C28" s="225">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -14087,19 +14113,19 @@
         <v>368</v>
       </c>
       <c r="C29" s="225">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="261" t="s">
+      <c r="B33" s="259" t="s">
         <v>356</v>
       </c>
-      <c r="C33" s="261"/>
-      <c r="D33" s="261"/>
-      <c r="E33" s="261"/>
-      <c r="F33" s="261"/>
-      <c r="G33" s="261"/>
-      <c r="H33" s="261"/>
+      <c r="C33" s="259"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="259"/>
+      <c r="F33" s="259"/>
+      <c r="G33" s="259"/>
+      <c r="H33" s="259"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14118,24 +14144,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="261"/>
-      <c r="C39" s="261"/>
-      <c r="D39" s="261"/>
-      <c r="E39" s="261"/>
-      <c r="F39" s="261"/>
-      <c r="G39" s="261"/>
-      <c r="H39" s="261"/>
+      <c r="B39" s="259"/>
+      <c r="C39" s="259"/>
+      <c r="D39" s="259"/>
+      <c r="E39" s="259"/>
+      <c r="F39" s="259"/>
+      <c r="G39" s="259"/>
+      <c r="H39" s="259"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="261" t="s">
+      <c r="B42" s="259" t="s">
         <v>359</v>
       </c>
-      <c r="C42" s="261"/>
-      <c r="D42" s="261"/>
-      <c r="E42" s="261"/>
-      <c r="F42" s="261"/>
-      <c r="G42" s="261"/>
-      <c r="H42" s="261"/>
+      <c r="C42" s="259"/>
+      <c r="D42" s="259"/>
+      <c r="E42" s="259"/>
+      <c r="F42" s="259"/>
+      <c r="G42" s="259"/>
+      <c r="H42" s="259"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14222,24 +14248,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="261"/>
-      <c r="C55" s="261"/>
-      <c r="D55" s="261"/>
-      <c r="E55" s="261"/>
-      <c r="F55" s="261"/>
-      <c r="G55" s="261"/>
-      <c r="H55" s="261"/>
+      <c r="B55" s="259"/>
+      <c r="C55" s="259"/>
+      <c r="D55" s="259"/>
+      <c r="E55" s="259"/>
+      <c r="F55" s="259"/>
+      <c r="G55" s="259"/>
+      <c r="H55" s="259"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="261" t="s">
+      <c r="B58" s="259" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="261"/>
-      <c r="D58" s="261"/>
-      <c r="E58" s="261"/>
-      <c r="F58" s="261"/>
-      <c r="G58" s="261"/>
-      <c r="H58" s="261"/>
+      <c r="C58" s="259"/>
+      <c r="D58" s="259"/>
+      <c r="E58" s="259"/>
+      <c r="F58" s="259"/>
+      <c r="G58" s="259"/>
+      <c r="H58" s="259"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14288,28 +14314,28 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="261"/>
-      <c r="C68" s="261"/>
-      <c r="D68" s="261"/>
-      <c r="E68" s="261"/>
-      <c r="F68" s="261"/>
-      <c r="G68" s="261"/>
-      <c r="H68" s="261"/>
+      <c r="B68" s="259"/>
+      <c r="C68" s="259"/>
+      <c r="D68" s="259"/>
+      <c r="E68" s="259"/>
+      <c r="F68" s="259"/>
+      <c r="G68" s="259"/>
+      <c r="H68" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B68:H68"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14379,36 +14405,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="259" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="261" t="s">
+      <c r="S2" s="259" t="s">
         <v>125</v>
       </c>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261"/>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
-      <c r="AA2" s="261" t="s">
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
+      <c r="AA2" s="259" t="s">
         <v>126</v>
       </c>
-      <c r="AB2" s="261"/>
-      <c r="AC2" s="261"/>
+      <c r="AB2" s="259"/>
+      <c r="AC2" s="259"/>
       <c r="AE2" s="86" t="s">
         <v>127</v>
       </c>
@@ -14419,18 +14445,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="258" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="O4" s="5"/>
       <c r="S4" s="270" t="s">
         <v>128</v>
@@ -14935,18 +14961,18 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="269" t="s">
+      <c r="C11" s="258" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="269"/>
-      <c r="E11" s="269"/>
-      <c r="F11" s="269"/>
-      <c r="G11" s="269"/>
-      <c r="H11" s="269"/>
-      <c r="I11" s="269"/>
-      <c r="J11" s="269"/>
-      <c r="K11" s="269"/>
-      <c r="L11" s="269"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="92"/>
       <c r="S11" s="270" t="s">
@@ -15402,18 +15428,18 @@
       <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="269" t="s">
+      <c r="C19" s="258" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="269"/>
-      <c r="E19" s="269"/>
-      <c r="F19" s="269"/>
-      <c r="G19" s="269"/>
-      <c r="H19" s="269"/>
-      <c r="I19" s="269"/>
-      <c r="J19" s="269"/>
-      <c r="K19" s="269"/>
-      <c r="L19" s="269"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="258"/>
+      <c r="F19" s="258"/>
+      <c r="G19" s="258"/>
+      <c r="H19" s="258"/>
+      <c r="I19" s="258"/>
+      <c r="J19" s="258"/>
+      <c r="K19" s="258"/>
+      <c r="L19" s="258"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
       <c r="S19" s="270" t="s">
@@ -16665,35 +16691,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="259" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="P2" s="261" t="s">
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
+      <c r="P2" s="259" t="s">
         <v>125</v>
       </c>
-      <c r="Q2" s="261"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261" t="s">
+      <c r="Q2" s="259"/>
+      <c r="R2" s="259"/>
+      <c r="S2" s="259"/>
+      <c r="T2" s="259"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="259"/>
+      <c r="X2" s="259" t="s">
         <v>126</v>
       </c>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
+      <c r="Y2" s="259"/>
+      <c r="Z2" s="259"/>
       <c r="AB2" s="86" t="s">
         <v>127</v>
       </c>
@@ -16702,18 +16728,18 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="258" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="P4" s="271" t="s">
         <v>128</v>
       </c>
@@ -16921,18 +16947,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="269" t="s">
+      <c r="C9" s="258" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="269"/>
-      <c r="E9" s="269"/>
-      <c r="F9" s="269"/>
-      <c r="G9" s="269"/>
-      <c r="H9" s="269"/>
-      <c r="I9" s="269"/>
-      <c r="J9" s="269"/>
-      <c r="K9" s="269"/>
-      <c r="L9" s="269"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
       <c r="N9" s="92"/>
       <c r="P9" s="271" t="s">
         <v>140</v>
@@ -17704,18 +17730,18 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="269" t="s">
+      <c r="C20" s="258" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="269"/>
-      <c r="E20" s="269"/>
-      <c r="F20" s="269"/>
-      <c r="G20" s="269"/>
-      <c r="H20" s="269"/>
-      <c r="I20" s="269"/>
-      <c r="J20" s="269"/>
-      <c r="K20" s="269"/>
-      <c r="L20" s="269"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="258"/>
+      <c r="F20" s="258"/>
+      <c r="G20" s="258"/>
+      <c r="H20" s="258"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="258"/>
+      <c r="K20" s="258"/>
+      <c r="L20" s="258"/>
       <c r="P20" s="271" t="s">
         <v>142</v>
       </c>
@@ -18452,20 +18478,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="259" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -18483,18 +18509,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="269" t="s">
+      <c r="C5" s="258" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="269"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="269"/>
-      <c r="I5" s="269"/>
-      <c r="J5" s="269"/>
-      <c r="K5" s="269"/>
-      <c r="L5" s="269"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -18691,18 +18717,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="269" t="s">
+      <c r="C11" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="269"/>
-      <c r="E11" s="269"/>
-      <c r="F11" s="269"/>
-      <c r="G11" s="269"/>
-      <c r="H11" s="269"/>
-      <c r="I11" s="269"/>
-      <c r="J11" s="269"/>
-      <c r="K11" s="269"/>
-      <c r="L11" s="269"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
       <c r="N11" s="92"/>
       <c r="P11" s="272"/>
       <c r="Q11" s="272"/>
@@ -18956,18 +18982,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="269" t="s">
+      <c r="C18" s="258" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="269"/>
-      <c r="E18" s="269"/>
-      <c r="F18" s="269"/>
-      <c r="G18" s="269"/>
-      <c r="H18" s="269"/>
-      <c r="I18" s="269"/>
-      <c r="J18" s="269"/>
-      <c r="K18" s="269"/>
-      <c r="L18" s="269"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19185,18 +19211,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="269" t="s">
+      <c r="C26" s="258" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="269"/>
-      <c r="E26" s="269"/>
-      <c r="F26" s="269"/>
-      <c r="G26" s="269"/>
-      <c r="H26" s="269"/>
-      <c r="I26" s="269"/>
-      <c r="J26" s="269"/>
-      <c r="K26" s="269"/>
-      <c r="L26" s="269"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19388,18 +19414,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="269" t="s">
+      <c r="C33" s="258" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="269"/>
-      <c r="E33" s="269"/>
-      <c r="F33" s="269"/>
-      <c r="G33" s="269"/>
-      <c r="H33" s="269"/>
-      <c r="I33" s="269"/>
-      <c r="J33" s="269"/>
-      <c r="K33" s="269"/>
-      <c r="L33" s="269"/>
+      <c r="D33" s="258"/>
+      <c r="E33" s="258"/>
+      <c r="F33" s="258"/>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="258"/>
+      <c r="L33" s="258"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19583,18 +19609,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="269" t="s">
+      <c r="C40" s="258" t="s">
         <v>164</v>
       </c>
-      <c r="D40" s="269"/>
-      <c r="E40" s="269"/>
-      <c r="F40" s="269"/>
-      <c r="G40" s="269"/>
-      <c r="H40" s="269"/>
-      <c r="I40" s="269"/>
-      <c r="J40" s="269"/>
-      <c r="K40" s="269"/>
-      <c r="L40" s="269"/>
+      <c r="D40" s="258"/>
+      <c r="E40" s="258"/>
+      <c r="F40" s="258"/>
+      <c r="G40" s="258"/>
+      <c r="H40" s="258"/>
+      <c r="I40" s="258"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="258"/>
+      <c r="L40" s="258"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19863,12 +19889,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19876,6 +19896,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19913,20 +19939,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="259" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
       <c r="S2" s="272"/>
       <c r="T2" s="272"/>
       <c r="U2" s="272"/>
@@ -19944,18 +19970,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
       <c r="S4" s="272"/>
       <c r="T4" s="272"/>
       <c r="U4" s="272"/>
@@ -20329,18 +20355,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="269" t="s">
+      <c r="C13" s="258" t="s">
         <v>172</v>
       </c>
-      <c r="D13" s="269"/>
-      <c r="E13" s="269"/>
-      <c r="F13" s="269"/>
-      <c r="G13" s="269"/>
-      <c r="H13" s="269"/>
-      <c r="I13" s="269"/>
-      <c r="J13" s="269"/>
-      <c r="K13" s="269"/>
-      <c r="L13" s="269"/>
+      <c r="D13" s="258"/>
+      <c r="E13" s="258"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="258"/>
+      <c r="H13" s="258"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="258"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="258"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20433,18 +20459,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="269" t="s">
+      <c r="C18" s="258" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="269"/>
-      <c r="E18" s="269"/>
-      <c r="F18" s="269"/>
-      <c r="G18" s="269"/>
-      <c r="H18" s="269"/>
-      <c r="I18" s="269"/>
-      <c r="J18" s="269"/>
-      <c r="K18" s="269"/>
-      <c r="L18" s="269"/>
+      <c r="D18" s="258"/>
+      <c r="E18" s="258"/>
+      <c r="F18" s="258"/>
+      <c r="G18" s="258"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20636,18 +20662,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="269" t="s">
+      <c r="C25" s="258" t="s">
         <v>281</v>
       </c>
-      <c r="D25" s="269"/>
-      <c r="E25" s="269"/>
-      <c r="F25" s="269"/>
-      <c r="G25" s="269"/>
-      <c r="H25" s="269"/>
-      <c r="I25" s="269"/>
-      <c r="J25" s="269"/>
-      <c r="K25" s="269"/>
-      <c r="L25" s="269"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="258"/>
+      <c r="F25" s="258"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20785,18 +20811,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="269" t="s">
+      <c r="C31" s="258" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="269"/>
-      <c r="E31" s="269"/>
-      <c r="F31" s="269"/>
-      <c r="G31" s="269"/>
-      <c r="H31" s="269"/>
-      <c r="I31" s="269"/>
-      <c r="J31" s="269"/>
-      <c r="K31" s="269"/>
-      <c r="L31" s="269"/>
+      <c r="D31" s="258"/>
+      <c r="E31" s="258"/>
+      <c r="F31" s="258"/>
+      <c r="G31" s="258"/>
+      <c r="H31" s="258"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="258"/>
+      <c r="L31" s="258"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -20935,16 +20961,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21007,10 +21033,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="259" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="261"/>
+      <c r="C4" s="259"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21027,7 +21053,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21036,7 +21062,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>688213.52</v>
+        <v>695133.4</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21054,7 +21080,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.4850000000000001E-2</v>
+        <v>4.4789999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21063,7 +21089,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.84870000000000001</v>
+        <v>0.85370000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21095,10 +21121,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="259" t="s">
         <v>187</v>
       </c>
-      <c r="C15" s="261"/>
+      <c r="C15" s="259"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21106,7 +21132,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>0.11633533873249281</v>
+        <v>0.11531078958440823</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21115,7 +21141,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.8836646612675072</v>
+        <v>0.88468921041559179</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21133,7 +21159,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.304149999999999E-2</v>
+        <v>8.3206499999999989E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21142,7 +21168,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>7.9814183200552544E-2</v>
+        <v>7.9988579450462699E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21187,20 +21213,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="259" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -21218,18 +21244,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="269" t="s">
+      <c r="C5" s="258" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="269"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="269"/>
-      <c r="I5" s="269"/>
-      <c r="J5" s="269"/>
-      <c r="K5" s="269"/>
-      <c r="L5" s="269"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -21393,7 +21419,7 @@
       </c>
       <c r="L8" s="130">
         <f>L7*(1+C14)/(C15-C14)</f>
-        <v>692766.49939612369</v>
+        <v>615792.44390766555</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -21447,23 +21473,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f>H7/(1+$C$15)^H9</f>
-        <v>13038.389349307397</v>
+        <v>12920.926382196521</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>8516.9202112971434</v>
+        <v>8364.1534418225347</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" si="0"/>
-        <v>20519.932665859418</v>
+        <v>19970.321218412631</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" si="0"/>
-        <v>28433.742644614642</v>
+        <v>27422.86677334044</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" si="0"/>
-        <v>33737.528735380423</v>
+        <v>32244.956792243785</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -21482,14 +21508,14 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f>L8/(1+C15)^L9</f>
-        <v>430153.4913761004</v>
+        <v>365442.84364542959</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="261" t="s">
+      <c r="B13" s="259" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="261"/>
+      <c r="C13" s="259"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21505,14 +21531,14 @@
       </c>
       <c r="C15" s="139">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="261" t="s">
+      <c r="B18" s="259" t="s">
         <v>200</v>
       </c>
-      <c r="C18" s="261"/>
+      <c r="C18" s="259"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21520,7 +21546,7 @@
       </c>
       <c r="C19" s="64">
         <f>SUM(H10:L10)</f>
-        <v>104246.51360645902</v>
+        <v>100923.22460801591</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -21529,7 +21555,7 @@
       </c>
       <c r="C20" s="64">
         <f>L11</f>
-        <v>430153.4913761004</v>
+        <v>365442.84364542959</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -21538,7 +21564,7 @@
       </c>
       <c r="C21" s="95">
         <f>C19+C20</f>
-        <v>534400.00498255948</v>
+        <v>466366.0682534455</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -21565,7 +21591,7 @@
       </c>
       <c r="C24" s="95">
         <f>C21+C22-C23</f>
-        <v>518502.00498255948</v>
+        <v>450468.06825344544</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -21583,7 +21609,7 @@
       </c>
       <c r="C26" s="146">
         <f>C24/C25</f>
-        <v>8.2422268230202747</v>
+        <v>7.1607437568106667</v>
       </c>
     </row>
   </sheetData>
@@ -21604,7 +21630,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="84" customWidth="1"/>
@@ -21626,37 +21652,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="259" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268" t="s">
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="269" t="s">
+      <c r="C4" s="258" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21845,18 +21871,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="269" t="s">
+      <c r="C10" s="258" t="s">
         <v>134</v>
       </c>
-      <c r="D10" s="269"/>
-      <c r="E10" s="269"/>
-      <c r="F10" s="269"/>
-      <c r="G10" s="269"/>
-      <c r="H10" s="269"/>
-      <c r="I10" s="269"/>
-      <c r="J10" s="269"/>
-      <c r="K10" s="269"/>
-      <c r="L10" s="269"/>
+      <c r="D10" s="258"/>
+      <c r="E10" s="258"/>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="258"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22050,18 +22076,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="269" t="s">
+      <c r="C16" s="258" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="269"/>
-      <c r="E16" s="269"/>
-      <c r="F16" s="269"/>
-      <c r="G16" s="269"/>
-      <c r="H16" s="269"/>
-      <c r="I16" s="269"/>
-      <c r="J16" s="269"/>
-      <c r="K16" s="269"/>
-      <c r="L16" s="269"/>
+      <c r="D16" s="258"/>
+      <c r="E16" s="258"/>
+      <c r="F16" s="258"/>
+      <c r="G16" s="258"/>
+      <c r="H16" s="258"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="258"/>
+      <c r="K16" s="258"/>
+      <c r="L16" s="258"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22195,18 +22221,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="269" t="s">
+      <c r="C21" s="258" t="s">
         <v>213</v>
       </c>
-      <c r="D21" s="269"/>
-      <c r="E21" s="269"/>
-      <c r="F21" s="269"/>
-      <c r="G21" s="269"/>
-      <c r="H21" s="269"/>
-      <c r="I21" s="269"/>
-      <c r="J21" s="269"/>
-      <c r="K21" s="269"/>
-      <c r="L21" s="269"/>
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="258"/>
+      <c r="H21" s="258"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22290,18 +22316,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="269" t="s">
+      <c r="C26" s="258" t="s">
         <v>214</v>
       </c>
-      <c r="D26" s="269"/>
-      <c r="E26" s="269"/>
-      <c r="F26" s="269"/>
-      <c r="G26" s="269"/>
-      <c r="H26" s="269"/>
-      <c r="I26" s="269"/>
-      <c r="J26" s="269"/>
-      <c r="K26" s="269"/>
-      <c r="L26" s="269"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="258"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22571,10 +22597,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="261" t="s">
+      <c r="B37" s="259" t="s">
         <v>219</v>
       </c>
-      <c r="C37" s="261"/>
+      <c r="C37" s="259"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22592,7 +22618,7 @@
       </c>
       <c r="C39" s="139">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -22605,182 +22631,227 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C41" s="24">
+        <f>(C38*C40)</f>
+        <v>1588589.3520075863</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C42" s="24">
+        <f>C41/(1+C39)^5-G30+G31</f>
+        <v>916492.46068858716</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" s="89">
+        <f>Statement!AC111</f>
+        <v>74706</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C44" s="89">
+        <f>Statement!AC112</f>
+        <v>90604</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C45" s="24">
+        <f>C42+C43-C44</f>
+        <v>900594.46068858716</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="89">
+        <f>Statement!AC80</f>
+        <v>62908</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="145" t="s">
+        <v>223</v>
+      </c>
+      <c r="C47" s="146">
+        <f>C45/C46</f>
+        <v>14.316056156428232</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="259" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" s="259"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50" s="64">
+        <f>L6</f>
+        <v>786430.37228098325</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C51" s="139">
+        <f>Overview!C29</f>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="C52" s="107">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C53" s="24">
         <f>L18</f>
         <v>92459.495500155026</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C54" s="24">
+        <f>(C50*C52)/C53</f>
+        <v>25.517023471526446</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="145" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" s="146">
+        <f>C54/(1+C51)^5</f>
+        <v>15.143111467278782</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="259" t="s">
+        <v>342</v>
+      </c>
+      <c r="C57" s="259"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C58" s="64">
+        <f>L8</f>
+        <v>54334.627403617545</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C59" s="139">
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="C60" s="107">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C42" s="24">
-        <f>(C38*C40)</f>
-        <v>1588589.3520075863</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B43" s="1" t="s">
+      <c r="C61" s="24">
+        <f>(C58*C60)</f>
+        <v>978023.29326511582</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C43" s="24">
-        <f>C42/(1+C39)^5-G30+G31</f>
-        <v>960131.00224623608</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
+      <c r="C62" s="24">
+        <f>C61/(1+C59)^5-G30+G31</f>
+        <v>554151.2222603882</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C63" s="89">
+        <f>Statement!AC111</f>
+        <v>74706</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C64" s="89">
+        <f>Statement!AC112</f>
+        <v>90604</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C65" s="24">
+        <f>C62+C63-C64</f>
+        <v>538253.2222603882</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="89">
+      <c r="C66" s="89">
         <f>Statement!AC80</f>
         <v>62908</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="145" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="145" t="s">
         <v>223</v>
       </c>
-      <c r="C45" s="146">
-        <f>C43/C44</f>
-        <v>15.262462679567561</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="261" t="s">
-        <v>224</v>
-      </c>
-      <c r="C47" s="261"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C48" s="64">
-        <f>L6</f>
-        <v>786430.37228098325</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C49" s="139">
-        <f>Overview!C29</f>
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="39" t="s">
-        <v>226</v>
-      </c>
-      <c r="C50" s="107">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C51" s="24">
-        <f>L18</f>
-        <v>92459.495500155026</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C52" s="24">
-        <f>(C48*C50)/C51</f>
-        <v>29.769860716780855</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="145" t="s">
-        <v>223</v>
-      </c>
-      <c r="C53" s="146">
-        <f>C52/(1+C49)^5</f>
-        <v>16.157887697352475</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="261" t="s">
-        <v>342</v>
-      </c>
-      <c r="C55" s="261"/>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C56" s="64">
-        <f>L8</f>
-        <v>54334.627403617545</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C57" s="139">
-        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="C58" s="107">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C59" s="24">
-        <f>(C56*C58)</f>
-        <v>978023.29326511582</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="C60" s="24">
-        <f>C59/(1+C57)^5-G30+G31</f>
-        <v>581017.51723684766</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="89">
-        <f>Statement!AC80</f>
-        <v>62908</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="145" t="s">
-        <v>223</v>
-      </c>
-      <c r="C62" s="146">
-        <f>C60/C61</f>
-        <v>9.2359877477721071</v>
+      <c r="C67" s="146">
+        <f>C65/C66</f>
+        <v>8.5561967040819642</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -22824,10 +22895,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="259" t="s">
         <v>229</v>
       </c>
-      <c r="C4" s="261"/>
+      <c r="C4" s="259"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22836,7 +22907,7 @@
       </c>
       <c r="C5" s="137">
         <f>DCF!C26</f>
-        <v>8.2422268230202747</v>
+        <v>7.1607437568106667</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22844,8 +22915,8 @@
         <v>231</v>
       </c>
       <c r="C6" s="137">
-        <f>Multiples!C45</f>
-        <v>15.262462679567561</v>
+        <f>Multiples!C47</f>
+        <v>14.316056156428232</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22853,8 +22924,8 @@
         <v>232</v>
       </c>
       <c r="C7" s="137">
-        <f>Multiples!C53</f>
-        <v>16.157887697352475</v>
+        <f>Multiples!C55</f>
+        <v>15.143111467278782</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22862,8 +22933,8 @@
         <v>343</v>
       </c>
       <c r="C8" s="137">
-        <f>Multiples!C62</f>
-        <v>9.2359877477721071</v>
+        <f>Multiples!C67</f>
+        <v>8.5561967040819642</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22872,7 +22943,7 @@
       </c>
       <c r="C9" s="146">
         <f>AVERAGE(C5:C8)</f>
-        <v>12.224641236928106</v>
+        <v>11.29402702114991</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22881,7 +22952,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22890,7 +22961,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.11742607284534792</v>
+        <v>2.2083893316733879E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22955,20 +23026,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="259" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="268" t="s">
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
+      <c r="I3" s="259"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
+      <c r="L3" s="259"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -22986,18 +23057,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="269" t="s">
+      <c r="C5" s="258" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="269"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="269"/>
-      <c r="I5" s="269"/>
-      <c r="J5" s="269"/>
-      <c r="K5" s="269"/>
-      <c r="L5" s="269"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -23142,7 +23213,7 @@
       <c r="K8" s="141"/>
       <c r="L8" s="130">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>912554.1881250001</v>
+        <v>811159.27833333344</v>
       </c>
       <c r="N8" s="92"/>
       <c r="O8" s="16"/>
@@ -23196,23 +23267,23 @@
       <c r="G10" s="142"/>
       <c r="H10" s="130">
         <f>H7/(1+$C$21)^H9</f>
-        <v>11272.727272727272</v>
+        <v>11171.17117117117</v>
       </c>
       <c r="I10" s="130">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>15884.297520661155</v>
+        <v>15599.383166950733</v>
       </c>
       <c r="J10" s="130">
         <f t="shared" si="1"/>
-        <v>22382.419233658897</v>
+        <v>21782.922440336606</v>
       </c>
       <c r="K10" s="130">
         <f t="shared" si="1"/>
-        <v>31538.863465610266</v>
+        <v>30417.594398668236</v>
       </c>
       <c r="L10" s="130">
         <f t="shared" si="1"/>
-        <v>44441.125792450825</v>
+        <v>42475.019205347533</v>
       </c>
       <c r="N10" s="92"/>
     </row>
@@ -23231,7 +23302,7 @@
       <c r="K11" s="141"/>
       <c r="L11" s="130">
         <f>L8/(1+C21)^L9</f>
-        <v>566624.35385374806</v>
+        <v>481383.55099393876</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23247,7 +23318,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23256,7 +23327,7 @@
       </c>
       <c r="C16" s="160">
         <f>C36</f>
-        <v>10.940364122481986</v>
+        <v>9.4954319772279341</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -23295,7 +23366,7 @@
       </c>
       <c r="C21" s="226">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23313,7 +23384,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>676223.27999999991</v>
+        <v>683022.60000000009</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23340,7 +23411,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>692121.27999999991</v>
+        <v>698920.60000000009</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23356,7 +23427,7 @@
       </c>
       <c r="C29" s="165">
         <f>SUM(H10:L10)</f>
-        <v>125519.43328510842</v>
+        <v>121446.09038247429</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23365,7 +23436,7 @@
       </c>
       <c r="C30" s="165">
         <f>L11</f>
-        <v>566624.35385374806</v>
+        <v>481383.55099393876</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23374,7 +23445,7 @@
       </c>
       <c r="C31" s="168">
         <f>C29+C30</f>
-        <v>692143.78713885648</v>
+        <v>602829.64137641306</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23401,7 +23472,7 @@
       </c>
       <c r="C34" s="168">
         <f>C31+C32-C33</f>
-        <v>676245.78713885648</v>
+        <v>586931.64137641306</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -23419,22 +23490,22 @@
       </c>
       <c r="C36" s="171">
         <f>C34/C35</f>
-        <v>10.940364122481986</v>
+        <v>9.4954319772279341</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="269" t="s">
+      <c r="C39" s="258" t="s">
         <v>243</v>
       </c>
-      <c r="D39" s="269"/>
-      <c r="E39" s="269"/>
-      <c r="F39" s="269"/>
-      <c r="G39" s="269"/>
-      <c r="H39" s="269"/>
-      <c r="I39" s="269"/>
-      <c r="J39" s="269"/>
-      <c r="K39" s="269"/>
-      <c r="L39" s="269"/>
+      <c r="D39" s="258"/>
+      <c r="E39" s="258"/>
+      <c r="F39" s="258"/>
+      <c r="G39" s="258"/>
+      <c r="H39" s="258"/>
+      <c r="I39" s="258"/>
+      <c r="J39" s="258"/>
+      <c r="K39" s="258"/>
+      <c r="L39" s="258"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23866,17 +23937,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -24222,7 +24293,7 @@
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
       <c r="T7" s="22">
-        <f t="shared" ref="T7:Z7" si="2">T5-T6</f>
+        <f t="shared" ref="T7:Y7" si="2">T5-T6</f>
         <v>69304</v>
       </c>
       <c r="U7" s="22">
@@ -26156,7 +26227,7 @@
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="35">
-        <f t="shared" ref="T38:Z38" si="24">T39-T34</f>
+        <f t="shared" ref="T38:Y38" si="24">T39-T34</f>
         <v>181307</v>
       </c>
       <c r="U38" s="35">
@@ -26535,7 +26606,7 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="35">
-        <f t="shared" ref="T44:Z44" si="27">T45-T42</f>
+        <f t="shared" ref="T44:Y44" si="27">T45-T42</f>
         <v>8901</v>
       </c>
       <c r="U44" s="35">
@@ -28084,7 +28155,7 @@
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
       <c r="T72" s="40">
-        <f t="shared" ref="T72:Z72" si="35">T20-T71</f>
+        <f t="shared" ref="T72:Y72" si="35">T20-T71</f>
         <v>0</v>
       </c>
       <c r="U72" s="40">
@@ -28477,7 +28548,7 @@
         <v>1756</v>
       </c>
       <c r="T79" s="25">
-        <f t="shared" ref="T79:Z79" si="48">T78*T87</f>
+        <f t="shared" ref="T79:Y79" si="48">T78*T87</f>
         <v>0</v>
       </c>
       <c r="U79" s="25">
@@ -28548,7 +28619,7 @@
         <v>62519</v>
       </c>
       <c r="T80" s="25">
-        <f t="shared" ref="T80:Z80" si="51">T77+T79</f>
+        <f t="shared" ref="T80:Y80" si="51">T77+T79</f>
         <v>57773</v>
       </c>
       <c r="U80" s="25">
@@ -30816,7 +30887,7 @@
       <c r="AA120" s="68"/>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -30863,7 +30934,7 @@
       <c r="AA121" s="68"/>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -31246,7 +31317,7 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="229" t="str">
-        <f t="shared" ref="T136:Z136" si="124">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Y136" si="124">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U136" s="229" t="str">
@@ -31941,7 +32012,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-288.94522824784502</v>
+        <v>-291.85052761779599</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31978,7 +32049,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.3619206198672287</v>
+        <v>1.3756145200669907</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32015,7 +32086,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.8831582054638112</v>
+        <v>1.9020930685900472</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32052,7 +32123,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>688213.52</v>
+        <v>695133.4</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32089,7 +32160,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>704111.52</v>
+        <v>711031.4</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32126,7 +32197,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>1.4207540910833552</v>
+        <v>1.4347170039750601</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32163,7 +32234,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC14</f>
-        <v>205.64004672897198</v>
+        <v>207.66103971962619</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32298,7 +32369,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>-1529.3633777777777</v>
+        <v>-1544.740888888889</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32335,7 +32406,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>525.06451901565993</v>
+        <v>530.22475764354965</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32372,7 +32443,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>-6.5386684062818177E-4</v>
+        <v>-6.4735775895677003E-4</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32409,7 +32480,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-3.4608635209654411E-3</v>
+        <v>-3.4264114859151062E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33023,7 +33094,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>-2.3100388960681853E-2</v>
+        <v>-2.2870430337543844E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34621,15 +34692,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="259" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="261"/>
-      <c r="E4" s="261" t="s">
+      <c r="C4" s="259"/>
+      <c r="E4" s="259" t="s">
         <v>259</v>
       </c>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34637,7 +34708,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -34653,7 +34724,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>688213.52</v>
+        <v>695133.4</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34673,7 +34744,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>704111.52</v>
+        <v>711031.4</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34693,7 +34764,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-288.94522824784502</v>
+        <v>-291.85052761779599</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>262</v>
@@ -34713,7 +34784,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3619206198672287</v>
+        <v>1.3756145200669907</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>263</v>
@@ -34733,7 +34804,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.8831582054638112</v>
+        <v>1.9020930685900472</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34753,7 +34824,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.4207540910833552</v>
+        <v>1.4347170039750601</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34762,18 +34833,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>205.64004672897198</v>
+        <v>207.66103971962619</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="259" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="261"/>
-      <c r="E15" s="261" t="s">
+      <c r="C15" s="259"/>
+      <c r="E15" s="259" t="s">
         <v>265</v>
       </c>
-      <c r="F15" s="261"/>
+      <c r="F15" s="259"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34824,14 +34895,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="261" t="s">
+      <c r="B21" s="259" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="261"/>
-      <c r="E21" s="261" t="s">
+      <c r="C21" s="259"/>
+      <c r="E21" s="259" t="s">
         <v>268</v>
       </c>
-      <c r="F21" s="261"/>
+      <c r="F21" s="259"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34900,14 +34971,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="261" t="s">
+      <c r="B29" s="259" t="s">
         <v>269</v>
       </c>
-      <c r="C29" s="261"/>
-      <c r="E29" s="261" t="s">
+      <c r="C29" s="259"/>
+      <c r="E29" s="259" t="s">
         <v>275</v>
       </c>
-      <c r="F29" s="261"/>
+      <c r="F29" s="259"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34983,14 +35054,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="261" t="s">
+      <c r="B37" s="259" t="s">
         <v>287</v>
       </c>
-      <c r="C37" s="261"/>
-      <c r="E37" s="261" t="s">
+      <c r="C37" s="259"/>
+      <c r="E37" s="259" t="s">
         <v>290</v>
       </c>
-      <c r="F37" s="261"/>
+      <c r="F37" s="259"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34998,7 +35069,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-3.4608635209654411E-3</v>
+        <v>-3.4264114859151062E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>289</v>
@@ -35014,7 +35085,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>-6.5386684062818177E-4</v>
+        <v>-6.4735775895677003E-4</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>291</v>
@@ -35059,14 +35130,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="261" t="s">
+      <c r="B45" s="259" t="s">
         <v>298</v>
       </c>
-      <c r="C45" s="261"/>
-      <c r="E45" s="261" t="s">
+      <c r="C45" s="259"/>
+      <c r="E45" s="259" t="s">
         <v>304</v>
       </c>
-      <c r="F45" s="261"/>
+      <c r="F45" s="259"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35099,18 +35170,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>-2.3100388960681853E-2</v>
+        <v>-2.2870430337543844E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="261" t="s">
+      <c r="B51" s="259" t="s">
         <v>301</v>
       </c>
-      <c r="C51" s="261"/>
-      <c r="E51" s="261" t="s">
+      <c r="C51" s="259"/>
+      <c r="E51" s="259" t="s">
         <v>322</v>
       </c>
-      <c r="F51" s="261"/>
+      <c r="F51" s="259"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35278,7 +35349,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC120</f>
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35307,7 +35378,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>688213.52</v>
+        <v>695133.4</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35336,7 +35407,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>704111.52</v>
+        <v>711031.4</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35365,7 +35436,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-288.94522824784502</v>
+        <v>-291.85052761779599</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35394,7 +35465,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3619206198672287</v>
+        <v>1.3756145200669907</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35423,7 +35494,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.8831582054638112</v>
+        <v>1.9020930685900472</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35452,7 +35523,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.4207540910833552</v>
+        <v>1.4347170039750601</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35481,7 +35552,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>205.64004672897198</v>
+        <v>207.66103971962619</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36254,7 +36325,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-3.4608635209654411E-3</v>
+        <v>-3.4264114859151062E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36283,7 +36354,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>-6.5386684062818177E-4</v>
+        <v>-6.4735775895677003E-4</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36606,7 +36677,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>-2.3100388960681853E-2</v>
+        <v>-2.2870430337543844E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37095,14 +37166,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="265" t="s">
         <v>332</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="F3" s="266" t="s">
+      <c r="D3" s="266"/>
+      <c r="F3" s="267" t="s">
         <v>333</v>
       </c>
-      <c r="G3" s="265"/>
+      <c r="G3" s="266"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37169,19 +37240,19 @@
       <c r="B7" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="262">
+      <c r="C7" s="268">
         <f>Statement!AA91</f>
         <v>3.0440633681443646E-2</v>
       </c>
-      <c r="D7" s="263"/>
-      <c r="F7" s="262">
+      <c r="D7" s="269"/>
+      <c r="F7" s="268">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12937310240132488</v>
       </c>
-      <c r="G7" s="263"/>
+      <c r="G7" s="269"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -37208,19 +37279,19 @@
       <c r="B9" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="262">
+      <c r="C9" s="268">
         <f>Statement!AA92</f>
         <v>7.2889329041842046E-2</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="F9" s="262">
+      <c r="D9" s="269"/>
+      <c r="F9" s="268">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13842112176540128</v>
       </c>
-      <c r="G9" s="263"/>
+      <c r="G9" s="269"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -37247,19 +37318,19 @@
       <c r="B11" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C11" s="262">
+      <c r="C11" s="268">
         <f>Statement!AA93</f>
         <v>1.0660267429652618E-2</v>
       </c>
-      <c r="D11" s="263"/>
-      <c r="F11" s="262">
+      <c r="D11" s="269"/>
+      <c r="F11" s="268">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12495023821448292</v>
       </c>
-      <c r="G11" s="263"/>
+      <c r="G11" s="269"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -37286,19 +37357,19 @@
       <c r="B13" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C13" s="262">
+      <c r="C13" s="268">
         <f>Statement!AA99</f>
         <v>-0.12340351714118437</v>
       </c>
-      <c r="D13" s="263"/>
-      <c r="F13" s="262">
+      <c r="D13" s="269"/>
+      <c r="F13" s="268">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.7704231252618349E-3</v>
       </c>
-      <c r="G13" s="263"/>
+      <c r="G13" s="269"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -37325,19 +37396,19 @@
       <c r="B15" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C15" s="262">
+      <c r="C15" s="268">
         <f>Statement!AA100</f>
         <v>2.2145042289004859</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="F15" s="262">
+      <c r="D15" s="269"/>
+      <c r="F15" s="268">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>3.0532400365074537</v>
       </c>
-      <c r="G15" s="263"/>
+      <c r="G15" s="269"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -37364,19 +37435,19 @@
       <c r="B17" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C17" s="262">
+      <c r="C17" s="268">
         <f>Statement!AA102</f>
         <v>1.2870289644483193</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="F17" s="262">
+      <c r="D17" s="269"/>
+      <c r="F17" s="268">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.7570260602963721</v>
       </c>
-      <c r="G17" s="263"/>
+      <c r="G17" s="269"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -37403,22 +37474,22 @@
       <c r="B19" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="262">
+      <c r="C19" s="268">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>8.8459599655267736E-3</v>
       </c>
-      <c r="D19" s="263"/>
-      <c r="F19" s="262">
+      <c r="D19" s="269"/>
+      <c r="F19" s="268">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>5.2952258108314526E-2</v>
       </c>
-      <c r="G19" s="263"/>
+      <c r="G19" s="269"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -37445,22 +37516,22 @@
       <c r="B21" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C21" s="262">
+      <c r="C21" s="268">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.2978639930252833</v>
       </c>
-      <c r="D21" s="263"/>
-      <c r="F21" s="262">
+      <c r="D21" s="269"/>
+      <c r="F21" s="268">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.7142857142857142</v>
       </c>
-      <c r="G21" s="263"/>
+      <c r="G21" s="269"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37509,22 +37580,22 @@
       <c r="B25" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C25" s="262">
+      <c r="C25" s="268">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.7274157785566125E-2</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="F25" s="262">
+      <c r="D25" s="269"/>
+      <c r="F25" s="268">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-3.0061631864593874E-2</v>
       </c>
-      <c r="G25" s="263"/>
+      <c r="G25" s="269"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37552,22 +37623,22 @@
       <c r="B27" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C27" s="262">
+      <c r="C27" s="268">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.17416013437849945</v>
       </c>
-      <c r="D27" s="263"/>
-      <c r="F27" s="262">
+      <c r="D27" s="269"/>
+      <c r="F27" s="268">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.40153717627401836</v>
       </c>
-      <c r="G27" s="263"/>
+      <c r="G27" s="269"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37595,22 +37666,22 @@
       <c r="B29" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C29" s="262">
+      <c r="C29" s="268">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.3995709002625414E-2</v>
       </c>
-      <c r="D29" s="263"/>
-      <c r="F29" s="262">
+      <c r="D29" s="269"/>
+      <c r="F29" s="268">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.14584912812736922</v>
       </c>
-      <c r="G29" s="263"/>
+      <c r="G29" s="269"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37659,22 +37730,22 @@
       <c r="B33" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C33" s="262">
+      <c r="C33" s="268">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.0734220695577501E-2</v>
       </c>
-      <c r="D33" s="263"/>
-      <c r="F33" s="262">
+      <c r="D33" s="269"/>
+      <c r="F33" s="268">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.7331670822942641E-2</v>
       </c>
-      <c r="G33" s="263"/>
+      <c r="G33" s="269"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="239" t="str">
@@ -37702,43 +37773,25 @@
       <c r="B35" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C35" s="262">
+      <c r="C35" s="268">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-6.7286114478582681E-2</v>
       </c>
-      <c r="D35" s="263"/>
-      <c r="F35" s="262">
+      <c r="D35" s="269"/>
+      <c r="F35" s="268">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-9.1249332658182622E-2</v>
       </c>
-      <c r="G35" s="263"/>
+      <c r="G35" s="269"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -37749,6 +37802,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2442D2A-05E3-4B4C-99FF-3C902DF13FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D054ACF4-4ABC-9D41-B1AE-521764939984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -162,7 +162,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -173,28 +173,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -204,21 +183,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2465,16 +2435,7 @@
     <xf numFmtId="9" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="12" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2501,10 +2462,19 @@
     <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12819,7 +12789,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=bqw82w&amp;q=XNYS%3aPHR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12838,9 +12808,11 @@
     <v>Powered by Refinitiv</v>
     <v>32.76</v>
     <v>7.77</v>
-    <v>0.85370000000000001</v>
-    <v>-0.05</v>
-    <v>-4.5050000000000003E-3</v>
+    <v>0.85529999999999995</v>
+    <v>-0.1</v>
+    <v>-9.2420000000000002E-3</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12848,49 +12820,35 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>11.435</v>
+    <v>11.05</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46210.764675462502</v>
+    <v>46213.84033457109</v>
     <v>0</v>
-    <v>10.98</v>
-    <v>683021384</v>
+    <v>10.55</v>
+    <v>662623460</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>11.414999999999999</v>
-    <v>74.260800000000003</v>
-    <v>11.1</v>
     <v>11.05</v>
+    <v>72.043000000000006</v>
+    <v>10.82</v>
+    <v>10.72</v>
+    <v>10.72</v>
     <v>61811890</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>319116</v>
-    <v>1364795</v>
+    <v>662587</v>
+    <v>1148596</v>
     <v>2005</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12904,28 +12862,28 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.06</v>
-    <v>-1.338E-3</v>
+    <v>-0.3</v>
+    <v>-6.5659999999999998E-3</v>
     <v>US</v>
-    <v>44.91</v>
+    <v>45.81</v>
     <v>Index</v>
-    <v>6</v>
-    <v>44.57</v>
+    <v>3</v>
+    <v>45.29</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>44.57</v>
-    <v>44.85</v>
-    <v>44.79</v>
+    <v>45.77</v>
+    <v>45.69</v>
+    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12947,6 +12905,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12967,6 +12927,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12976,11 +12937,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13016,7 +12972,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13027,13 +12983,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13127,13 +13086,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13205,6 +13170,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13212,6 +13180,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13713,18 +13684,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="262" t="s">
+      <c r="B2" s="259" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="263"/>
-      <c r="E2" s="262" t="s">
+      <c r="C2" s="260"/>
+      <c r="E2" s="259" t="s">
         <v>306</v>
       </c>
-      <c r="F2" s="263"/>
-      <c r="H2" s="262" t="s">
+      <c r="F2" s="260"/>
+      <c r="H2" s="259" t="s">
         <v>348</v>
       </c>
-      <c r="I2" s="263"/>
+      <c r="I2" s="260"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -13739,7 +13710,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>695133.4</v>
+        <v>674373.76</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -13763,7 +13734,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>711031.4</v>
+        <v>690271.76</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -13780,7 +13751,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>11.05</v>
+        <v>10.72</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>262</v>
@@ -13802,16 +13773,16 @@
       <c r="B6" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="212" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="212" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>10.72</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>256</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>-291.85052761779599</v>
+        <v>-283.13462950794326</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -13828,14 +13799,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>215</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>1.3756145200669907</v>
+        <v>1.3345328194677051</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -13850,16 +13821,16 @@
       <c r="B8" s="189" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>284</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>-6.4735775895677003E-4</v>
+        <v>-6.6728574967092429E-4</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -13867,7 +13838,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>2.2083893316733879E-2</v>
+        <v>5.3547296749058712E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13876,23 +13847,23 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-4.5050000000000003E-3</v>
+        <v>-9.2420000000000002E-3</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>307</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>-3.4264114859151062E-3</v>
+        <v>-3.5318887051643583E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>312</v>
@@ -13940,7 +13911,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.85370000000000001</v>
+        <v>0.85529999999999995</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>116</v>
@@ -13956,7 +13927,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1364795</v>
+        <v>1148596</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>117</v>
@@ -13972,7 +13943,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>-2.2870430337543844E-2</v>
+        <v>-2.3574464107263011E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13985,10 +13956,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="264" t="s">
+      <c r="B17" s="261" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="264"/>
+      <c r="C17" s="261"/>
       <c r="E17" s="188" t="s">
         <v>315</v>
       </c>
@@ -14061,14 +14032,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="264" t="s">
+      <c r="B25" s="261" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="264"/>
-      <c r="E25" s="262" t="s">
+      <c r="C25" s="261"/>
+      <c r="E25" s="259" t="s">
         <v>362</v>
       </c>
-      <c r="F25" s="263"/>
+      <c r="F25" s="260"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -14077,12 +14048,12 @@
       <c r="C26" s="174">
         <v>0.21</v>
       </c>
-      <c r="E26" s="189" t="e" vm="5">
+      <c r="E26" s="189" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>44.79</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14097,7 +14068,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14117,15 +14088,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="259" t="s">
+      <c r="B33" s="258" t="s">
         <v>356</v>
       </c>
-      <c r="C33" s="259"/>
-      <c r="D33" s="259"/>
-      <c r="E33" s="259"/>
-      <c r="F33" s="259"/>
-      <c r="G33" s="259"/>
-      <c r="H33" s="259"/>
+      <c r="C33" s="258"/>
+      <c r="D33" s="258"/>
+      <c r="E33" s="258"/>
+      <c r="F33" s="258"/>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14144,24 +14115,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="259"/>
-      <c r="C39" s="259"/>
-      <c r="D39" s="259"/>
-      <c r="E39" s="259"/>
-      <c r="F39" s="259"/>
-      <c r="G39" s="259"/>
-      <c r="H39" s="259"/>
+      <c r="B39" s="258"/>
+      <c r="C39" s="258"/>
+      <c r="D39" s="258"/>
+      <c r="E39" s="258"/>
+      <c r="F39" s="258"/>
+      <c r="G39" s="258"/>
+      <c r="H39" s="258"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="259" t="s">
+      <c r="B42" s="258" t="s">
         <v>359</v>
       </c>
-      <c r="C42" s="259"/>
-      <c r="D42" s="259"/>
-      <c r="E42" s="259"/>
-      <c r="F42" s="259"/>
-      <c r="G42" s="259"/>
-      <c r="H42" s="259"/>
+      <c r="C42" s="258"/>
+      <c r="D42" s="258"/>
+      <c r="E42" s="258"/>
+      <c r="F42" s="258"/>
+      <c r="G42" s="258"/>
+      <c r="H42" s="258"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14248,24 +14219,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="259"/>
-      <c r="C55" s="259"/>
-      <c r="D55" s="259"/>
-      <c r="E55" s="259"/>
-      <c r="F55" s="259"/>
-      <c r="G55" s="259"/>
-      <c r="H55" s="259"/>
+      <c r="B55" s="258"/>
+      <c r="C55" s="258"/>
+      <c r="D55" s="258"/>
+      <c r="E55" s="258"/>
+      <c r="F55" s="258"/>
+      <c r="G55" s="258"/>
+      <c r="H55" s="258"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="259" t="s">
+      <c r="B58" s="258" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="259"/>
-      <c r="D58" s="259"/>
-      <c r="E58" s="259"/>
-      <c r="F58" s="259"/>
-      <c r="G58" s="259"/>
-      <c r="H58" s="259"/>
+      <c r="C58" s="258"/>
+      <c r="D58" s="258"/>
+      <c r="E58" s="258"/>
+      <c r="F58" s="258"/>
+      <c r="G58" s="258"/>
+      <c r="H58" s="258"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14314,13 +14285,13 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="259"/>
-      <c r="C68" s="259"/>
-      <c r="D68" s="259"/>
-      <c r="E68" s="259"/>
-      <c r="F68" s="259"/>
-      <c r="G68" s="259"/>
-      <c r="H68" s="259"/>
+      <c r="B68" s="258"/>
+      <c r="C68" s="258"/>
+      <c r="D68" s="258"/>
+      <c r="E68" s="258"/>
+      <c r="F68" s="258"/>
+      <c r="G68" s="258"/>
+      <c r="H68" s="258"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14405,36 +14376,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="259" t="s">
+      <c r="S2" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="T2" s="259"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="259"/>
-      <c r="X2" s="259"/>
-      <c r="Y2" s="259"/>
-      <c r="Z2" s="259"/>
-      <c r="AA2" s="259" t="s">
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
+      <c r="AA2" s="258" t="s">
         <v>126</v>
       </c>
-      <c r="AB2" s="259"/>
-      <c r="AC2" s="259"/>
+      <c r="AB2" s="258"/>
+      <c r="AC2" s="258"/>
       <c r="AE2" s="86" t="s">
         <v>127</v>
       </c>
@@ -14445,32 +14416,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="267" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="270" t="s">
+      <c r="S4" s="268" t="s">
         <v>128</v>
       </c>
-      <c r="T4" s="271"/>
-      <c r="U4" s="271"/>
-      <c r="V4" s="271"/>
-      <c r="W4" s="271"/>
-      <c r="X4" s="271"/>
-      <c r="Y4" s="271"/>
-      <c r="Z4" s="271"/>
-      <c r="AA4" s="271"/>
-      <c r="AB4" s="271"/>
-      <c r="AC4" s="271"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="269"/>
+      <c r="AB4" s="269"/>
+      <c r="AC4" s="269"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14961,33 +14932,33 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="267" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="92"/>
-      <c r="S11" s="270" t="s">
+      <c r="S11" s="268" t="s">
         <v>134</v>
       </c>
-      <c r="T11" s="271"/>
-      <c r="U11" s="271"/>
-      <c r="V11" s="271"/>
-      <c r="W11" s="271"/>
-      <c r="X11" s="271"/>
-      <c r="Y11" s="271"/>
-      <c r="Z11" s="271"/>
-      <c r="AA11" s="271"/>
-      <c r="AB11" s="271"/>
-      <c r="AC11" s="271"/>
+      <c r="T11" s="269"/>
+      <c r="U11" s="269"/>
+      <c r="V11" s="269"/>
+      <c r="W11" s="269"/>
+      <c r="X11" s="269"/>
+      <c r="Y11" s="269"/>
+      <c r="Z11" s="269"/>
+      <c r="AA11" s="269"/>
+      <c r="AB11" s="269"/>
+      <c r="AC11" s="269"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15428,33 +15399,33 @@
       <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="258" t="s">
+      <c r="C19" s="267" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="258"/>
-      <c r="E19" s="258"/>
-      <c r="F19" s="258"/>
-      <c r="G19" s="258"/>
-      <c r="H19" s="258"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="258"/>
-      <c r="K19" s="258"/>
-      <c r="L19" s="258"/>
+      <c r="D19" s="267"/>
+      <c r="E19" s="267"/>
+      <c r="F19" s="267"/>
+      <c r="G19" s="267"/>
+      <c r="H19" s="267"/>
+      <c r="I19" s="267"/>
+      <c r="J19" s="267"/>
+      <c r="K19" s="267"/>
+      <c r="L19" s="267"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
-      <c r="S19" s="270" t="s">
+      <c r="S19" s="268" t="s">
         <v>136</v>
       </c>
-      <c r="T19" s="271"/>
-      <c r="U19" s="271"/>
-      <c r="V19" s="271"/>
-      <c r="W19" s="271"/>
-      <c r="X19" s="271"/>
-      <c r="Y19" s="271"/>
-      <c r="Z19" s="271"/>
-      <c r="AA19" s="271"/>
-      <c r="AB19" s="271"/>
-      <c r="AC19" s="271"/>
+      <c r="T19" s="269"/>
+      <c r="U19" s="269"/>
+      <c r="V19" s="269"/>
+      <c r="W19" s="269"/>
+      <c r="X19" s="269"/>
+      <c r="Y19" s="269"/>
+      <c r="Z19" s="269"/>
+      <c r="AA19" s="269"/>
+      <c r="AB19" s="269"/>
+      <c r="AC19" s="269"/>
       <c r="AE19" s="88">
         <f>AE4</f>
         <v>0</v>
@@ -16691,35 +16662,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
-      <c r="P2" s="259" t="s">
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
+      <c r="P2" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="Q2" s="259"/>
-      <c r="R2" s="259"/>
-      <c r="S2" s="259"/>
-      <c r="T2" s="259"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="259"/>
-      <c r="X2" s="259" t="s">
+      <c r="Q2" s="258"/>
+      <c r="R2" s="258"/>
+      <c r="S2" s="258"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258" t="s">
         <v>126</v>
       </c>
-      <c r="Y2" s="259"/>
-      <c r="Z2" s="259"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
       <c r="AB2" s="86" t="s">
         <v>127</v>
       </c>
@@ -16728,31 +16699,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="267" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="P4" s="271" t="s">
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+      <c r="P4" s="269" t="s">
         <v>128</v>
       </c>
-      <c r="Q4" s="271"/>
-      <c r="R4" s="271"/>
-      <c r="S4" s="271"/>
-      <c r="T4" s="271"/>
-      <c r="U4" s="271"/>
-      <c r="V4" s="271"/>
-      <c r="W4" s="271"/>
-      <c r="X4" s="271"/>
-      <c r="Y4" s="271"/>
-      <c r="Z4" s="271"/>
+      <c r="Q4" s="269"/>
+      <c r="R4" s="269"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16947,32 +16918,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="258" t="s">
+      <c r="C9" s="267" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="271" t="s">
+      <c r="P9" s="269" t="s">
         <v>140</v>
       </c>
-      <c r="Q9" s="271"/>
-      <c r="R9" s="271"/>
-      <c r="S9" s="271"/>
-      <c r="T9" s="271"/>
-      <c r="U9" s="271"/>
-      <c r="V9" s="271"/>
-      <c r="W9" s="271"/>
-      <c r="X9" s="271"/>
-      <c r="Y9" s="271"/>
-      <c r="Z9" s="271"/>
+      <c r="Q9" s="269"/>
+      <c r="R9" s="269"/>
+      <c r="S9" s="269"/>
+      <c r="T9" s="269"/>
+      <c r="U9" s="269"/>
+      <c r="V9" s="269"/>
+      <c r="W9" s="269"/>
+      <c r="X9" s="269"/>
+      <c r="Y9" s="269"/>
+      <c r="Z9" s="269"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -17730,31 +17701,31 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="258" t="s">
+      <c r="C20" s="267" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="258"/>
-      <c r="E20" s="258"/>
-      <c r="F20" s="258"/>
-      <c r="G20" s="258"/>
-      <c r="H20" s="258"/>
-      <c r="I20" s="258"/>
-      <c r="J20" s="258"/>
-      <c r="K20" s="258"/>
-      <c r="L20" s="258"/>
-      <c r="P20" s="271" t="s">
+      <c r="D20" s="267"/>
+      <c r="E20" s="267"/>
+      <c r="F20" s="267"/>
+      <c r="G20" s="267"/>
+      <c r="H20" s="267"/>
+      <c r="I20" s="267"/>
+      <c r="J20" s="267"/>
+      <c r="K20" s="267"/>
+      <c r="L20" s="267"/>
+      <c r="P20" s="269" t="s">
         <v>142</v>
       </c>
-      <c r="Q20" s="271"/>
-      <c r="R20" s="271"/>
-      <c r="S20" s="271"/>
-      <c r="T20" s="271"/>
-      <c r="U20" s="271"/>
-      <c r="V20" s="271"/>
-      <c r="W20" s="271"/>
-      <c r="X20" s="271"/>
-      <c r="Y20" s="271"/>
-      <c r="Z20" s="271"/>
+      <c r="Q20" s="269"/>
+      <c r="R20" s="269"/>
+      <c r="S20" s="269"/>
+      <c r="T20" s="269"/>
+      <c r="U20" s="269"/>
+      <c r="V20" s="269"/>
+      <c r="W20" s="269"/>
+      <c r="X20" s="269"/>
+      <c r="Y20" s="269"/>
+      <c r="Z20" s="269"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
@@ -18478,20 +18449,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -18509,18 +18480,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="267" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -18717,18 +18688,18 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="258" t="s">
+      <c r="C11" s="267" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="258"/>
-      <c r="G11" s="258"/>
-      <c r="H11" s="258"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
+      <c r="D11" s="267"/>
+      <c r="E11" s="267"/>
+      <c r="F11" s="267"/>
+      <c r="G11" s="267"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="267"/>
+      <c r="J11" s="267"/>
+      <c r="K11" s="267"/>
+      <c r="L11" s="267"/>
       <c r="N11" s="92"/>
       <c r="P11" s="272"/>
       <c r="Q11" s="272"/>
@@ -18982,18 +18953,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="267" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19211,18 +19182,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="267" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19414,18 +19385,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="258" t="s">
+      <c r="C33" s="267" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="258"/>
-      <c r="K33" s="258"/>
-      <c r="L33" s="258"/>
+      <c r="D33" s="267"/>
+      <c r="E33" s="267"/>
+      <c r="F33" s="267"/>
+      <c r="G33" s="267"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="267"/>
+      <c r="J33" s="267"/>
+      <c r="K33" s="267"/>
+      <c r="L33" s="267"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19609,18 +19580,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="258" t="s">
+      <c r="C40" s="267" t="s">
         <v>164</v>
       </c>
-      <c r="D40" s="258"/>
-      <c r="E40" s="258"/>
-      <c r="F40" s="258"/>
-      <c r="G40" s="258"/>
-      <c r="H40" s="258"/>
-      <c r="I40" s="258"/>
-      <c r="J40" s="258"/>
-      <c r="K40" s="258"/>
-      <c r="L40" s="258"/>
+      <c r="D40" s="267"/>
+      <c r="E40" s="267"/>
+      <c r="F40" s="267"/>
+      <c r="G40" s="267"/>
+      <c r="H40" s="267"/>
+      <c r="I40" s="267"/>
+      <c r="J40" s="267"/>
+      <c r="K40" s="267"/>
+      <c r="L40" s="267"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -19939,20 +19910,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
       <c r="S2" s="272"/>
       <c r="T2" s="272"/>
       <c r="U2" s="272"/>
@@ -19970,18 +19941,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="267" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
       <c r="S4" s="272"/>
       <c r="T4" s="272"/>
       <c r="U4" s="272"/>
@@ -20355,18 +20326,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="258" t="s">
+      <c r="C13" s="267" t="s">
         <v>172</v>
       </c>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="258"/>
-      <c r="G13" s="258"/>
-      <c r="H13" s="258"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="258"/>
-      <c r="K13" s="258"/>
-      <c r="L13" s="258"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
+      <c r="F13" s="267"/>
+      <c r="G13" s="267"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="267"/>
+      <c r="J13" s="267"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="267"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20459,18 +20430,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="258" t="s">
+      <c r="C18" s="267" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="258"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
+      <c r="D18" s="267"/>
+      <c r="E18" s="267"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20662,18 +20633,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="258" t="s">
+      <c r="C25" s="267" t="s">
         <v>281</v>
       </c>
-      <c r="D25" s="258"/>
-      <c r="E25" s="258"/>
-      <c r="F25" s="258"/>
-      <c r="G25" s="258"/>
-      <c r="H25" s="258"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="258"/>
-      <c r="K25" s="258"/>
-      <c r="L25" s="258"/>
+      <c r="D25" s="267"/>
+      <c r="E25" s="267"/>
+      <c r="F25" s="267"/>
+      <c r="G25" s="267"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="267"/>
+      <c r="J25" s="267"/>
+      <c r="K25" s="267"/>
+      <c r="L25" s="267"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20811,18 +20782,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="258" t="s">
+      <c r="C31" s="267" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="258"/>
-      <c r="E31" s="258"/>
-      <c r="F31" s="258"/>
-      <c r="G31" s="258"/>
-      <c r="H31" s="258"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="258"/>
-      <c r="K31" s="258"/>
-      <c r="L31" s="258"/>
+      <c r="D31" s="267"/>
+      <c r="E31" s="267"/>
+      <c r="F31" s="267"/>
+      <c r="G31" s="267"/>
+      <c r="H31" s="267"/>
+      <c r="I31" s="267"/>
+      <c r="J31" s="267"/>
+      <c r="K31" s="267"/>
+      <c r="L31" s="267"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21033,10 +21004,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="258" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="259"/>
+      <c r="C4" s="258"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21053,7 +21024,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>11.05</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21062,7 +21033,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>695133.4</v>
+        <v>674373.76</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21080,7 +21051,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.4789999999999996E-2</v>
+        <v>4.539E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21089,7 +21060,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.85370000000000001</v>
+        <v>0.85529999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21121,10 +21092,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="259" t="s">
+      <c r="B15" s="258" t="s">
         <v>187</v>
       </c>
-      <c r="C15" s="259"/>
+      <c r="C15" s="258"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21132,7 +21103,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>0.11531078958440823</v>
+        <v>0.1184400445837798</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21141,7 +21112,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.88468921041559179</v>
+        <v>0.88155995541622023</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21159,7 +21130,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.3206499999999989E-2</v>
+        <v>8.3878499999999995E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21168,7 +21139,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>7.9988579450462699E-2</v>
+        <v>8.0493661185862458E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21213,20 +21184,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -21244,18 +21215,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="267" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -21512,10 +21483,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="259" t="s">
+      <c r="B13" s="258" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="259"/>
+      <c r="C13" s="258"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21535,10 +21506,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="259" t="s">
+      <c r="B18" s="258" t="s">
         <v>200</v>
       </c>
-      <c r="C18" s="259"/>
+      <c r="C18" s="258"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21652,37 +21623,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="259"/>
-      <c r="J2" s="259"/>
-      <c r="K2" s="259"/>
-      <c r="L2" s="259"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="267" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21871,18 +21842,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="258" t="s">
+      <c r="C10" s="267" t="s">
         <v>134</v>
       </c>
-      <c r="D10" s="258"/>
-      <c r="E10" s="258"/>
-      <c r="F10" s="258"/>
-      <c r="G10" s="258"/>
-      <c r="H10" s="258"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="258"/>
-      <c r="K10" s="258"/>
-      <c r="L10" s="258"/>
+      <c r="D10" s="267"/>
+      <c r="E10" s="267"/>
+      <c r="F10" s="267"/>
+      <c r="G10" s="267"/>
+      <c r="H10" s="267"/>
+      <c r="I10" s="267"/>
+      <c r="J10" s="267"/>
+      <c r="K10" s="267"/>
+      <c r="L10" s="267"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22076,18 +22047,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="258" t="s">
+      <c r="C16" s="267" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="258"/>
-      <c r="E16" s="258"/>
-      <c r="F16" s="258"/>
-      <c r="G16" s="258"/>
-      <c r="H16" s="258"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="258"/>
-      <c r="K16" s="258"/>
-      <c r="L16" s="258"/>
+      <c r="D16" s="267"/>
+      <c r="E16" s="267"/>
+      <c r="F16" s="267"/>
+      <c r="G16" s="267"/>
+      <c r="H16" s="267"/>
+      <c r="I16" s="267"/>
+      <c r="J16" s="267"/>
+      <c r="K16" s="267"/>
+      <c r="L16" s="267"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22221,18 +22192,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="258" t="s">
+      <c r="C21" s="267" t="s">
         <v>213</v>
       </c>
-      <c r="D21" s="258"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="258"/>
-      <c r="G21" s="258"/>
-      <c r="H21" s="258"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
+      <c r="D21" s="267"/>
+      <c r="E21" s="267"/>
+      <c r="F21" s="267"/>
+      <c r="G21" s="267"/>
+      <c r="H21" s="267"/>
+      <c r="I21" s="267"/>
+      <c r="J21" s="267"/>
+      <c r="K21" s="267"/>
+      <c r="L21" s="267"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22316,18 +22287,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="258" t="s">
+      <c r="C26" s="267" t="s">
         <v>214</v>
       </c>
-      <c r="D26" s="258"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="258"/>
-      <c r="G26" s="258"/>
-      <c r="H26" s="258"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
+      <c r="D26" s="267"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="267"/>
+      <c r="J26" s="267"/>
+      <c r="K26" s="267"/>
+      <c r="L26" s="267"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22597,10 +22568,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="259" t="s">
+      <c r="B37" s="258" t="s">
         <v>219</v>
       </c>
-      <c r="C37" s="259"/>
+      <c r="C37" s="258"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22693,10 +22664,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="259" t="s">
+      <c r="B49" s="258" t="s">
         <v>224</v>
       </c>
-      <c r="C49" s="259"/>
+      <c r="C49" s="258"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22752,10 +22723,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="259" t="s">
+      <c r="B57" s="258" t="s">
         <v>342</v>
       </c>
-      <c r="C57" s="259"/>
+      <c r="C57" s="258"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22895,10 +22866,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="258" t="s">
         <v>229</v>
       </c>
-      <c r="C4" s="259"/>
+      <c r="C4" s="258"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22952,7 +22923,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>11.05</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22961,7 +22932,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>2.2083893316733879E-2</v>
+        <v>5.3547296749058712E-2</v>
       </c>
     </row>
   </sheetData>
@@ -23026,20 +22997,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="259" t="s">
+      <c r="C3" s="258" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="260"/>
-      <c r="H3" s="261" t="s">
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="259"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="259"/>
-      <c r="L3" s="259"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -23057,18 +23028,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="258" t="s">
+      <c r="C5" s="267" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
+      <c r="D5" s="267"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
       <c r="P5" s="272"/>
       <c r="Q5" s="272"/>
       <c r="R5" s="272"/>
@@ -23318,7 +23289,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>11.05</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23384,7 +23355,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>683022.60000000009</v>
+        <v>662624.64</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23411,7 +23382,7 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>698920.60000000009</v>
+        <v>678522.64</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23494,18 +23465,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="258" t="s">
+      <c r="C39" s="267" t="s">
         <v>243</v>
       </c>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
-      <c r="I39" s="258"/>
-      <c r="J39" s="258"/>
-      <c r="K39" s="258"/>
-      <c r="L39" s="258"/>
+      <c r="D39" s="267"/>
+      <c r="E39" s="267"/>
+      <c r="F39" s="267"/>
+      <c r="G39" s="267"/>
+      <c r="H39" s="267"/>
+      <c r="I39" s="267"/>
+      <c r="J39" s="267"/>
+      <c r="K39" s="267"/>
+      <c r="L39" s="267"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -30887,7 +30858,7 @@
       <c r="AA120" s="68"/>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>11.05</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -30934,7 +30905,7 @@
       <c r="AA121" s="68"/>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>11.05</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -32012,7 +31983,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-291.85052761779599</v>
+        <v>-283.13462950794326</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32049,7 +32020,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.3756145200669907</v>
+        <v>1.3345328194677051</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32086,7 +32057,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.9020930685900472</v>
+        <v>1.8452884792113398</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32123,7 +32094,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>695133.4</v>
+        <v>674373.76</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32160,7 +32131,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>711031.4</v>
+        <v>690271.76</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32197,7 +32168,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>1.4347170039750601</v>
+        <v>1.3928282652999455</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32234,7 +32205,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC14</f>
-        <v>207.66103971962619</v>
+        <v>201.59806074766357</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32369,7 +32340,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
         <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>-1544.740888888889</v>
+        <v>-1498.6083555555556</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32406,7 +32377,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ca="1" si="153"/>
-        <v>530.22475764354965</v>
+        <v>514.7440417598807</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32443,7 +32414,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
         <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>-6.4735775895677003E-4</v>
+        <v>-6.6728574967092429E-4</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32480,7 +32451,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-3.4264114859151062E-3</v>
+        <v>-3.5318887051643583E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33094,7 +33065,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>-2.2870430337543844E-2</v>
+        <v>-2.3574464107263011E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34692,15 +34663,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="259" t="s">
+      <c r="B4" s="258" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="259"/>
-      <c r="E4" s="259" t="s">
+      <c r="C4" s="258"/>
+      <c r="E4" s="258" t="s">
         <v>259</v>
       </c>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34708,7 +34679,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>11.05</v>
+        <v>10.72</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -34724,7 +34695,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>695133.4</v>
+        <v>674373.76</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -34744,7 +34715,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>711031.4</v>
+        <v>690271.76</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -34764,7 +34735,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-291.85052761779599</v>
+        <v>-283.13462950794326</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>262</v>
@@ -34784,7 +34755,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3756145200669907</v>
+        <v>1.3345328194677051</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>263</v>
@@ -34804,7 +34775,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.9020930685900472</v>
+        <v>1.8452884792113398</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34824,7 +34795,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.4347170039750601</v>
+        <v>1.3928282652999455</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34833,18 +34804,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>207.66103971962619</v>
+        <v>201.59806074766357</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="259" t="s">
+      <c r="B15" s="258" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="259"/>
-      <c r="E15" s="259" t="s">
+      <c r="C15" s="258"/>
+      <c r="E15" s="258" t="s">
         <v>265</v>
       </c>
-      <c r="F15" s="259"/>
+      <c r="F15" s="258"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34895,14 +34866,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="259" t="s">
+      <c r="B21" s="258" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="259"/>
-      <c r="E21" s="259" t="s">
+      <c r="C21" s="258"/>
+      <c r="E21" s="258" t="s">
         <v>268</v>
       </c>
-      <c r="F21" s="259"/>
+      <c r="F21" s="258"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34971,14 +34942,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="259" t="s">
+      <c r="B29" s="258" t="s">
         <v>269</v>
       </c>
-      <c r="C29" s="259"/>
-      <c r="E29" s="259" t="s">
+      <c r="C29" s="258"/>
+      <c r="E29" s="258" t="s">
         <v>275</v>
       </c>
-      <c r="F29" s="259"/>
+      <c r="F29" s="258"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35054,14 +35025,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="259" t="s">
+      <c r="B37" s="258" t="s">
         <v>287</v>
       </c>
-      <c r="C37" s="259"/>
-      <c r="E37" s="259" t="s">
+      <c r="C37" s="258"/>
+      <c r="E37" s="258" t="s">
         <v>290</v>
       </c>
-      <c r="F37" s="259"/>
+      <c r="F37" s="258"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35069,7 +35040,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-3.4264114859151062E-3</v>
+        <v>-3.5318887051643583E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>289</v>
@@ -35085,7 +35056,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>-6.4735775895677003E-4</v>
+        <v>-6.6728574967092429E-4</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>291</v>
@@ -35130,14 +35101,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="259" t="s">
+      <c r="B45" s="258" t="s">
         <v>298</v>
       </c>
-      <c r="C45" s="259"/>
-      <c r="E45" s="259" t="s">
+      <c r="C45" s="258"/>
+      <c r="E45" s="258" t="s">
         <v>304</v>
       </c>
-      <c r="F45" s="259"/>
+      <c r="F45" s="258"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35170,18 +35141,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>-2.2870430337543844E-2</v>
+        <v>-2.3574464107263011E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="259" t="s">
+      <c r="B51" s="258" t="s">
         <v>301</v>
       </c>
-      <c r="C51" s="259"/>
-      <c r="E51" s="259" t="s">
+      <c r="C51" s="258"/>
+      <c r="E51" s="258" t="s">
         <v>322</v>
       </c>
-      <c r="F51" s="259"/>
+      <c r="F51" s="258"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35349,7 +35320,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC120</f>
-        <v>11.05</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35378,7 +35349,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>695133.4</v>
+        <v>674373.76</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35407,7 +35378,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>711031.4</v>
+        <v>690271.76</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -35436,7 +35407,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-291.85052761779599</v>
+        <v>-283.13462950794326</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35465,7 +35436,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3756145200669907</v>
+        <v>1.3345328194677051</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -35494,7 +35465,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.9020930685900472</v>
+        <v>1.8452884792113398</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -35523,7 +35494,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.4347170039750601</v>
+        <v>1.3928282652999455</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -35552,7 +35523,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>207.66103971962619</v>
+        <v>201.59806074766357</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36325,7 +36296,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-3.4264114859151062E-3</v>
+        <v>-3.5318887051643583E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36354,7 +36325,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>-6.4735775895677003E-4</v>
+        <v>-6.6728574967092429E-4</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -36677,7 +36648,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>-2.2870430337543844E-2</v>
+        <v>-2.3574464107263011E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37166,14 +37137,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="265" t="s">
+      <c r="C3" s="262" t="s">
         <v>332</v>
       </c>
-      <c r="D3" s="266"/>
-      <c r="F3" s="267" t="s">
+      <c r="D3" s="263"/>
+      <c r="F3" s="264" t="s">
         <v>333</v>
       </c>
-      <c r="G3" s="266"/>
+      <c r="G3" s="263"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37240,19 +37211,19 @@
       <c r="B7" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="268">
+      <c r="C7" s="265">
         <f>Statement!AA91</f>
         <v>3.0440633681443646E-2</v>
       </c>
-      <c r="D7" s="269"/>
-      <c r="F7" s="268">
+      <c r="D7" s="266"/>
+      <c r="F7" s="265">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12937310240132488</v>
       </c>
-      <c r="G7" s="269"/>
+      <c r="G7" s="266"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -37279,19 +37250,19 @@
       <c r="B9" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="268">
+      <c r="C9" s="265">
         <f>Statement!AA92</f>
         <v>7.2889329041842046E-2</v>
       </c>
-      <c r="D9" s="269"/>
-      <c r="F9" s="268">
+      <c r="D9" s="266"/>
+      <c r="F9" s="265">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13842112176540128</v>
       </c>
-      <c r="G9" s="269"/>
+      <c r="G9" s="266"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -37318,19 +37289,19 @@
       <c r="B11" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C11" s="268">
+      <c r="C11" s="265">
         <f>Statement!AA93</f>
         <v>1.0660267429652618E-2</v>
       </c>
-      <c r="D11" s="269"/>
-      <c r="F11" s="268">
+      <c r="D11" s="266"/>
+      <c r="F11" s="265">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12495023821448292</v>
       </c>
-      <c r="G11" s="269"/>
+      <c r="G11" s="266"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -37357,19 +37328,19 @@
       <c r="B13" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C13" s="268">
+      <c r="C13" s="265">
         <f>Statement!AA99</f>
         <v>-0.12340351714118437</v>
       </c>
-      <c r="D13" s="269"/>
-      <c r="F13" s="268">
+      <c r="D13" s="266"/>
+      <c r="F13" s="265">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.7704231252618349E-3</v>
       </c>
-      <c r="G13" s="269"/>
+      <c r="G13" s="266"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -37396,19 +37367,19 @@
       <c r="B15" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C15" s="268">
+      <c r="C15" s="265">
         <f>Statement!AA100</f>
         <v>2.2145042289004859</v>
       </c>
-      <c r="D15" s="269"/>
-      <c r="F15" s="268">
+      <c r="D15" s="266"/>
+      <c r="F15" s="265">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>3.0532400365074537</v>
       </c>
-      <c r="G15" s="269"/>
+      <c r="G15" s="266"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -37435,19 +37406,19 @@
       <c r="B17" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C17" s="268">
+      <c r="C17" s="265">
         <f>Statement!AA102</f>
         <v>1.2870289644483193</v>
       </c>
-      <c r="D17" s="269"/>
-      <c r="F17" s="268">
+      <c r="D17" s="266"/>
+      <c r="F17" s="265">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.7570260602963721</v>
       </c>
-      <c r="G17" s="269"/>
+      <c r="G17" s="266"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -37474,22 +37445,22 @@
       <c r="B19" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="268">
+      <c r="C19" s="265">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>8.8459599655267736E-3</v>
       </c>
-      <c r="D19" s="269"/>
-      <c r="F19" s="268">
+      <c r="D19" s="266"/>
+      <c r="F19" s="265">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>5.2952258108314526E-2</v>
       </c>
-      <c r="G19" s="269"/>
+      <c r="G19" s="266"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -37516,22 +37487,22 @@
       <c r="B21" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C21" s="268">
+      <c r="C21" s="265">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.2978639930252833</v>
       </c>
-      <c r="D21" s="269"/>
-      <c r="F21" s="268">
+      <c r="D21" s="266"/>
+      <c r="F21" s="265">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.7142857142857142</v>
       </c>
-      <c r="G21" s="269"/>
+      <c r="G21" s="266"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37580,22 +37551,22 @@
       <c r="B25" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C25" s="268">
+      <c r="C25" s="265">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.7274157785566125E-2</v>
       </c>
-      <c r="D25" s="269"/>
-      <c r="F25" s="268">
+      <c r="D25" s="266"/>
+      <c r="F25" s="265">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-3.0061631864593874E-2</v>
       </c>
-      <c r="G25" s="269"/>
+      <c r="G25" s="266"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37623,22 +37594,22 @@
       <c r="B27" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C27" s="268">
+      <c r="C27" s="265">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.17416013437849945</v>
       </c>
-      <c r="D27" s="269"/>
-      <c r="F27" s="268">
+      <c r="D27" s="266"/>
+      <c r="F27" s="265">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.40153717627401836</v>
       </c>
-      <c r="G27" s="269"/>
+      <c r="G27" s="266"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37666,22 +37637,22 @@
       <c r="B29" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C29" s="268">
+      <c r="C29" s="265">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.3995709002625414E-2</v>
       </c>
-      <c r="D29" s="269"/>
-      <c r="F29" s="268">
+      <c r="D29" s="266"/>
+      <c r="F29" s="265">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.14584912812736922</v>
       </c>
-      <c r="G29" s="269"/>
+      <c r="G29" s="266"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37730,22 +37701,22 @@
       <c r="B33" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C33" s="268">
+      <c r="C33" s="265">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.0734220695577501E-2</v>
       </c>
-      <c r="D33" s="269"/>
-      <c r="F33" s="268">
+      <c r="D33" s="266"/>
+      <c r="F33" s="265">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.7331670822942641E-2</v>
       </c>
-      <c r="G33" s="269"/>
+      <c r="G33" s="266"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="239" t="str">
@@ -37773,22 +37744,22 @@
       <c r="B35" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C35" s="268">
+      <c r="C35" s="265">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-6.7286114478582681E-2</v>
       </c>
-      <c r="D35" s="269"/>
-      <c r="F35" s="268">
+      <c r="D35" s="266"/>
+      <c r="F35" s="265">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-9.1249332658182622E-2</v>
       </c>
-      <c r="G35" s="269"/>
+      <c r="G35" s="266"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D054ACF4-4ABC-9D41-B1AE-521764939984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A315AFED-6AE4-344B-95E6-692BBD974FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -32,10 +32,12 @@
     <sheet name="DCF" sheetId="11" r:id="rId17"/>
     <sheet name="Multiples" sheetId="12" r:id="rId18"/>
     <sheet name="AVG target price" sheetId="13" r:id="rId19"/>
-    <sheet name="Reverse DCF" sheetId="14" r:id="rId20"/>
+    <sheet name="DDM" sheetId="21" r:id="rId20"/>
+    <sheet name="Reverse DCF" sheetId="14" r:id="rId21"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
   </externalReferences>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -195,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="440">
   <si>
     <t>Ticker</t>
   </si>
@@ -1482,6 +1484,39 @@
   </si>
   <si>
     <t>Equity Value</t>
+  </si>
+  <si>
+    <t>Dividend discount model</t>
+  </si>
+  <si>
+    <t>Dividend per share</t>
+  </si>
+  <si>
+    <t>Ratios</t>
+  </si>
+  <si>
+    <t>Payout</t>
+  </si>
+  <si>
+    <t>DDM valuation</t>
+  </si>
+  <si>
+    <t>Latest dividend</t>
+  </si>
+  <si>
+    <t>Year 1 growth rate</t>
+  </si>
+  <si>
+    <t>Year 1 dividend</t>
+  </si>
+  <si>
+    <t>Perpetual dividend growth</t>
+  </si>
+  <si>
+    <t>Manual Cost of Equity</t>
+  </si>
+  <si>
+    <t>DDM price</t>
   </si>
 </sst>
 </file>
@@ -2098,7 +2133,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="276">
+  <cellXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2435,9 +2470,6 @@
     <xf numFmtId="9" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="12" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2447,6 +2479,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2454,12 +2495,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2489,6 +2524,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12679,6 +12716,95 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Financials -&gt;"/>
+      <sheetName val="Statement"/>
+      <sheetName val="Analysis -&gt;"/>
+      <sheetName val="Basic"/>
+      <sheetName val="Yearly Analysis"/>
+      <sheetName val="Quarter analysis"/>
+      <sheetName val="Graphs Year"/>
+      <sheetName val="Graphs Quarter"/>
+      <sheetName val="Forecast -&gt;"/>
+      <sheetName val="Revenue"/>
+      <sheetName val="COGS &amp; OpEx"/>
+      <sheetName val="WC &amp; Investments"/>
+      <sheetName val="FCF &amp; Other"/>
+      <sheetName val="Valuation -&gt;"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Multiples"/>
+      <sheetName val="AVG target price"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Reverse DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="5">
+          <cell r="C5">
+            <v>2021</v>
+          </cell>
+          <cell r="D5">
+            <v>2022</v>
+          </cell>
+          <cell r="E5">
+            <v>2023</v>
+          </cell>
+          <cell r="F5">
+            <v>2024</v>
+          </cell>
+          <cell r="G5">
+            <v>2025</v>
+          </cell>
+          <cell r="H5">
+            <v>2026</v>
+          </cell>
+          <cell r="I5">
+            <v>2027</v>
+          </cell>
+          <cell r="J5">
+            <v>2028</v>
+          </cell>
+          <cell r="K5">
+            <v>2029</v>
+          </cell>
+          <cell r="L5">
+            <v>2030</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="adi dumitras" id="{A0F62302-F8D3-B346-B5DF-839B413AE710}" userId="b24535bb88af1c42" providerId="Windows Live"/>
@@ -12808,7 +12934,7 @@
     <v>Powered by Refinitiv</v>
     <v>32.76</v>
     <v>7.77</v>
-    <v>0.85529999999999995</v>
+    <v>0.85780000000000001</v>
     <v>-0.1</v>
     <v>-9.2420000000000002E-3</v>
     <v>0</v>
@@ -12823,7 +12949,7 @@
     <v>11.05</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46213.84033457109</v>
+    <v>46213.958333356248</v>
     <v>0</v>
     <v>10.55</v>
     <v>662623460</v>
@@ -12862,17 +12988,17 @@
     <v>Powered by Refinitiv</v>
     <v>46.87</v>
     <v>39.47</v>
-    <v>-0.3</v>
-    <v>-6.5659999999999998E-3</v>
+    <v>0.3</v>
+    <v>6.6090000000000003E-3</v>
     <v>US</v>
-    <v>45.81</v>
+    <v>45.71</v>
     <v>Index</v>
     <v>3</v>
-    <v>45.29</v>
+    <v>45.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.77</v>
+    <v>45.41</v>
+    <v>45.39</v>
     <v>45.69</v>
-    <v>45.39</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13684,18 +13810,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="259" t="s">
+      <c r="B2" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="260"/>
-      <c r="E2" s="259" t="s">
+      <c r="C2" s="259"/>
+      <c r="E2" s="258" t="s">
         <v>306</v>
       </c>
-      <c r="F2" s="260"/>
-      <c r="H2" s="259" t="s">
+      <c r="F2" s="259"/>
+      <c r="H2" s="258" t="s">
         <v>348</v>
       </c>
-      <c r="I2" s="260"/>
+      <c r="I2" s="259"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -13872,6 +13998,13 @@
         <f ca="1">Statement!AC164</f>
         <v>0</v>
       </c>
+      <c r="H10" s="188" t="s">
+        <v>439</v>
+      </c>
+      <c r="I10" s="216">
+        <f>DDM!C26</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="189" t="s">
@@ -13911,7 +14044,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.85529999999999995</v>
+        <v>0.85780000000000001</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>116</v>
@@ -13956,10 +14089,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="261" t="s">
+      <c r="B17" s="260" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="261"/>
+      <c r="C17" s="260"/>
       <c r="E17" s="188" t="s">
         <v>315</v>
       </c>
@@ -14032,14 +14165,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="261" t="s">
+      <c r="B25" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="261"/>
-      <c r="E25" s="259" t="s">
+      <c r="C25" s="260"/>
+      <c r="E25" s="258" t="s">
         <v>362</v>
       </c>
-      <c r="F25" s="260"/>
+      <c r="F25" s="259"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -14053,7 +14186,7 @@
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.39</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14068,7 +14201,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14081,22 +14214,22 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="188" t="s">
-        <v>368</v>
+        <v>438</v>
       </c>
       <c r="C29" s="225">
         <v>0.11</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="258" t="s">
+      <c r="B33" s="261" t="s">
         <v>356</v>
       </c>
-      <c r="C33" s="258"/>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="258"/>
+      <c r="C33" s="261"/>
+      <c r="D33" s="261"/>
+      <c r="E33" s="261"/>
+      <c r="F33" s="261"/>
+      <c r="G33" s="261"/>
+      <c r="H33" s="261"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14115,24 +14248,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="258"/>
-      <c r="C39" s="258"/>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
+      <c r="B39" s="261"/>
+      <c r="C39" s="261"/>
+      <c r="D39" s="261"/>
+      <c r="E39" s="261"/>
+      <c r="F39" s="261"/>
+      <c r="G39" s="261"/>
+      <c r="H39" s="261"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="258" t="s">
+      <c r="B42" s="261" t="s">
         <v>359</v>
       </c>
-      <c r="C42" s="258"/>
-      <c r="D42" s="258"/>
-      <c r="E42" s="258"/>
-      <c r="F42" s="258"/>
-      <c r="G42" s="258"/>
-      <c r="H42" s="258"/>
+      <c r="C42" s="261"/>
+      <c r="D42" s="261"/>
+      <c r="E42" s="261"/>
+      <c r="F42" s="261"/>
+      <c r="G42" s="261"/>
+      <c r="H42" s="261"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14219,24 +14352,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="258"/>
-      <c r="C55" s="258"/>
-      <c r="D55" s="258"/>
-      <c r="E55" s="258"/>
-      <c r="F55" s="258"/>
-      <c r="G55" s="258"/>
-      <c r="H55" s="258"/>
+      <c r="B55" s="261"/>
+      <c r="C55" s="261"/>
+      <c r="D55" s="261"/>
+      <c r="E55" s="261"/>
+      <c r="F55" s="261"/>
+      <c r="G55" s="261"/>
+      <c r="H55" s="261"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="258" t="s">
+      <c r="B58" s="261" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="258"/>
-      <c r="D58" s="258"/>
-      <c r="E58" s="258"/>
-      <c r="F58" s="258"/>
-      <c r="G58" s="258"/>
-      <c r="H58" s="258"/>
+      <c r="C58" s="261"/>
+      <c r="D58" s="261"/>
+      <c r="E58" s="261"/>
+      <c r="F58" s="261"/>
+      <c r="G58" s="261"/>
+      <c r="H58" s="261"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14285,28 +14418,28 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="258"/>
-      <c r="C68" s="258"/>
-      <c r="D68" s="258"/>
-      <c r="E68" s="258"/>
-      <c r="F68" s="258"/>
-      <c r="G68" s="258"/>
-      <c r="H68" s="258"/>
+      <c r="B68" s="261"/>
+      <c r="C68" s="261"/>
+      <c r="D68" s="261"/>
+      <c r="E68" s="261"/>
+      <c r="F68" s="261"/>
+      <c r="G68" s="261"/>
+      <c r="H68" s="261"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14376,36 +14509,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="261" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
       <c r="G2" s="270"/>
       <c r="H2" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="258" t="s">
+      <c r="S2" s="261" t="s">
         <v>125</v>
       </c>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258"/>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
-      <c r="AA2" s="258" t="s">
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="261"/>
+      <c r="W2" s="261"/>
+      <c r="X2" s="261"/>
+      <c r="Y2" s="261"/>
+      <c r="Z2" s="261"/>
+      <c r="AA2" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="AB2" s="258"/>
-      <c r="AC2" s="258"/>
+      <c r="AB2" s="261"/>
+      <c r="AC2" s="261"/>
       <c r="AE2" s="86" t="s">
         <v>127</v>
       </c>
@@ -16662,35 +16795,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="261" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
       <c r="G2" s="270"/>
       <c r="H2" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="P2" s="258" t="s">
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="P2" s="261" t="s">
         <v>125</v>
       </c>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="258"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="258"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="258"/>
-      <c r="X2" s="258" t="s">
+      <c r="Q2" s="261"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="261"/>
+      <c r="T2" s="261"/>
+      <c r="U2" s="261"/>
+      <c r="V2" s="261"/>
+      <c r="W2" s="261"/>
+      <c r="X2" s="261" t="s">
         <v>126</v>
       </c>
-      <c r="Y2" s="258"/>
-      <c r="Z2" s="258"/>
+      <c r="Y2" s="261"/>
+      <c r="Z2" s="261"/>
       <c r="AB2" s="86" t="s">
         <v>127</v>
       </c>
@@ -18449,20 +18582,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="261" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
       <c r="G3" s="270"/>
       <c r="H3" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -19860,6 +19993,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -19867,12 +20006,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19910,20 +20043,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="261" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
       <c r="G2" s="270"/>
       <c r="H2" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
       <c r="S2" s="272"/>
       <c r="T2" s="272"/>
       <c r="U2" s="272"/>
@@ -20932,16 +21065,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21004,10 +21137,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="261" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="261"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21051,7 +21184,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.539E-2</v>
+        <v>4.5689999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21060,7 +21193,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.85529999999999995</v>
+        <v>0.85780000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21092,10 +21225,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="261" t="s">
         <v>187</v>
       </c>
-      <c r="C15" s="258"/>
+      <c r="C15" s="261"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21130,7 +21263,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.3878499999999995E-2</v>
+        <v>8.4290999999999991E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21139,7 +21272,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.0493661185862458E-2</v>
+        <v>8.0857304667471638E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21184,20 +21317,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="261" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
       <c r="G3" s="270"/>
       <c r="H3" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -21483,10 +21616,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="258" t="s">
+      <c r="B13" s="261" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="258"/>
+      <c r="C13" s="261"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21506,10 +21639,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="258" t="s">
+      <c r="B18" s="261" t="s">
         <v>200</v>
       </c>
-      <c r="C18" s="258"/>
+      <c r="C18" s="261"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21623,20 +21756,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="261" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
       <c r="G2" s="270"/>
       <c r="H2" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="258"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22568,10 +22701,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="258" t="s">
+      <c r="B37" s="261" t="s">
         <v>219</v>
       </c>
-      <c r="C37" s="258"/>
+      <c r="C37" s="261"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22664,10 +22797,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="258" t="s">
+      <c r="B49" s="261" t="s">
         <v>224</v>
       </c>
-      <c r="C49" s="258"/>
+      <c r="C49" s="261"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22683,7 +22816,7 @@
         <v>368</v>
       </c>
       <c r="C51" s="139">
-        <f>Overview!C29</f>
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.11</v>
       </c>
     </row>
@@ -22723,10 +22856,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="258" t="s">
+      <c r="B57" s="261" t="s">
         <v>342</v>
       </c>
-      <c r="C57" s="258"/>
+      <c r="C57" s="261"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22866,10 +22999,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="261" t="s">
         <v>229</v>
       </c>
-      <c r="C4" s="258"/>
+      <c r="C4" s="261"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22965,6 +23098,477 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8F9C3BA-B275-8F4D-B6D7-EF7BE0F858BB}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2" style="84" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="10.83203125" style="1"/>
+    <col min="13" max="14" width="9.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="84" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4"/>
+      <c r="B1" s="83" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4"/>
+      <c r="C2" s="261" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271" t="s">
+        <v>126</v>
+      </c>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+    </row>
+    <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="87"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="267" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="267"/>
+      <c r="K4" s="267"/>
+      <c r="L4" s="267"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="12">
+        <f>[2]Revenue!C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D5" s="12">
+        <f>[2]Revenue!D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E5" s="12">
+        <f>[2]Revenue!E5</f>
+        <v>2023</v>
+      </c>
+      <c r="F5" s="12">
+        <f>[2]Revenue!F5</f>
+        <v>2024</v>
+      </c>
+      <c r="G5" s="12">
+        <f>[2]Revenue!G5</f>
+        <v>2025</v>
+      </c>
+      <c r="H5" s="12">
+        <f>[2]Revenue!H5</f>
+        <v>2026</v>
+      </c>
+      <c r="I5" s="12">
+        <f>[2]Revenue!I5</f>
+        <v>2027</v>
+      </c>
+      <c r="J5" s="12">
+        <f>[2]Revenue!J5</f>
+        <v>2028</v>
+      </c>
+      <c r="K5" s="12">
+        <f>[2]Revenue!K5</f>
+        <v>2029</v>
+      </c>
+      <c r="L5" s="12">
+        <f>[2]Revenue!L5</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B6" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="276">
+        <f>Statement!M28</f>
+        <v>-2.37</v>
+      </c>
+      <c r="D6" s="276">
+        <f>Statement!N28</f>
+        <v>-3.36</v>
+      </c>
+      <c r="E6" s="276">
+        <f>Statement!O28</f>
+        <v>-2.5099999999999998</v>
+      </c>
+      <c r="F6" s="276">
+        <f>Statement!P28</f>
+        <v>-1.02</v>
+      </c>
+      <c r="G6" s="277">
+        <f>Statement!Q28</f>
+        <v>-0.16</v>
+      </c>
+      <c r="H6" s="141"/>
+      <c r="I6" s="141"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="141"/>
+      <c r="L6" s="141"/>
+      <c r="N6" s="92"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="C7" s="276">
+        <f>Statement!M84</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="276">
+        <f>Statement!N84</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="276">
+        <f>Statement!O84</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="276">
+        <f>Statement!P84</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="277">
+        <f>Statement!Q84</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="141"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="141"/>
+      <c r="N7" s="92"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="92"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C9" s="267" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
+      <c r="N9" s="92"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="12">
+        <f t="shared" ref="C10:L10" si="0">C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="0"/>
+        <v>2027</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="N10" s="92"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C11" s="141"/>
+      <c r="D11" s="96">
+        <f>(D6-C6)/C6</f>
+        <v>0.41772151898734167</v>
+      </c>
+      <c r="E11" s="96">
+        <f>(E6-D6)/D6</f>
+        <v>-0.25297619047619052</v>
+      </c>
+      <c r="F11" s="96">
+        <f>(F6-E6)/E6</f>
+        <v>-0.59362549800796804</v>
+      </c>
+      <c r="G11" s="97">
+        <f>(G6-F6)/F6</f>
+        <v>-0.84313725490196079</v>
+      </c>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
+      <c r="N11" s="92"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" s="141"/>
+      <c r="D12" s="96">
+        <f>IF(C7=0,
+IF(D7=0,0,IF(D7&gt;0,1,-1)),
+(D7-C7)/ABS(C7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="96">
+        <f>IF(D7=0,
+IF(E7=0,0,IF(E7&gt;0,1,-1)),
+(E7-D7)/ABS(D7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="96">
+        <f>IF(E7=0,
+IF(F7=0,0,IF(F7&gt;0,1,-1)),
+(F7-E7)/ABS(E7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="97">
+        <f>IF(F7=0,
+IF(G7=0,0,IF(G7&gt;0,1,-1)),
+(G7-F7)/ABS(F7)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="141"/>
+      <c r="I12" s="141"/>
+      <c r="J12" s="141"/>
+      <c r="K12" s="141"/>
+      <c r="L12" s="141"/>
+      <c r="N12" s="92"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="92"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C14" s="267" t="s">
+        <v>431</v>
+      </c>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="267"/>
+      <c r="G14" s="267"/>
+      <c r="H14" s="267"/>
+      <c r="I14" s="267"/>
+      <c r="J14" s="267"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="267"/>
+      <c r="N14" s="92"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="C15" s="12">
+        <f>C5</f>
+        <v>2021</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" ref="D15:L15" si="1">D5</f>
+        <v>2022</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>2023</v>
+      </c>
+      <c r="F15" s="12">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="G15" s="12">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="H15" s="12">
+        <f t="shared" si="1"/>
+        <v>2026</v>
+      </c>
+      <c r="I15" s="12">
+        <f t="shared" si="1"/>
+        <v>2027</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="1"/>
+        <v>2028</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="1"/>
+        <v>2029</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="N15" s="92"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C16" s="96">
+        <f>C7/C6</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="96">
+        <f t="shared" ref="D16:G16" si="2">D7/D6</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="96">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="96">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="97">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="141"/>
+      <c r="I16" s="141"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="141"/>
+      <c r="L16" s="141"/>
+      <c r="N16" s="92"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="92"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="92"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N19" s="92"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="261" t="s">
+        <v>433</v>
+      </c>
+      <c r="C20" s="261"/>
+      <c r="N20" s="92"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C21" s="109">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C22" s="248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="39" t="s">
+        <v>436</v>
+      </c>
+      <c r="C23" s="234">
+        <f>C21*(1+C22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C24" s="139">
+        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="39" t="s">
+        <v>437</v>
+      </c>
+      <c r="C25" s="248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26" s="145" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26" s="146">
+        <f>C23/(C24-C25)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="B20:C20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0116CE1A-CCEC-514B-9208-A0DCC7740441}">
   <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -22997,20 +23601,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="258" t="s">
+      <c r="C3" s="261" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
       <c r="G3" s="270"/>
       <c r="H3" s="271" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
       <c r="P3" s="272"/>
       <c r="Q3" s="272"/>
       <c r="R3" s="272"/>
@@ -23908,17 +24512,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -34663,15 +35267,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="261" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="258"/>
-      <c r="E4" s="258" t="s">
+      <c r="C4" s="261"/>
+      <c r="E4" s="261" t="s">
         <v>259</v>
       </c>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34808,14 +35412,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="258" t="s">
+      <c r="B15" s="261" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="258"/>
-      <c r="E15" s="258" t="s">
+      <c r="C15" s="261"/>
+      <c r="E15" s="261" t="s">
         <v>265</v>
       </c>
-      <c r="F15" s="258"/>
+      <c r="F15" s="261"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34866,14 +35470,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="258" t="s">
+      <c r="B21" s="261" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="258"/>
-      <c r="E21" s="258" t="s">
+      <c r="C21" s="261"/>
+      <c r="E21" s="261" t="s">
         <v>268</v>
       </c>
-      <c r="F21" s="258"/>
+      <c r="F21" s="261"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34942,14 +35546,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="258" t="s">
+      <c r="B29" s="261" t="s">
         <v>269</v>
       </c>
-      <c r="C29" s="258"/>
-      <c r="E29" s="258" t="s">
+      <c r="C29" s="261"/>
+      <c r="E29" s="261" t="s">
         <v>275</v>
       </c>
-      <c r="F29" s="258"/>
+      <c r="F29" s="261"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35025,14 +35629,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="258" t="s">
+      <c r="B37" s="261" t="s">
         <v>287</v>
       </c>
-      <c r="C37" s="258"/>
-      <c r="E37" s="258" t="s">
+      <c r="C37" s="261"/>
+      <c r="E37" s="261" t="s">
         <v>290</v>
       </c>
-      <c r="F37" s="258"/>
+      <c r="F37" s="261"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35101,14 +35705,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="258" t="s">
+      <c r="B45" s="261" t="s">
         <v>298</v>
       </c>
-      <c r="C45" s="258"/>
-      <c r="E45" s="258" t="s">
+      <c r="C45" s="261"/>
+      <c r="E45" s="261" t="s">
         <v>304</v>
       </c>
-      <c r="F45" s="258"/>
+      <c r="F45" s="261"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35145,14 +35749,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="258" t="s">
+      <c r="B51" s="261" t="s">
         <v>301</v>
       </c>
-      <c r="C51" s="258"/>
-      <c r="E51" s="258" t="s">
+      <c r="C51" s="261"/>
+      <c r="E51" s="261" t="s">
         <v>322</v>
       </c>
-      <c r="F51" s="258"/>
+      <c r="F51" s="261"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -37137,14 +37741,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="262" t="s">
+      <c r="C3" s="264" t="s">
         <v>332</v>
       </c>
-      <c r="D3" s="263"/>
-      <c r="F3" s="264" t="s">
+      <c r="D3" s="265"/>
+      <c r="F3" s="266" t="s">
         <v>333</v>
       </c>
-      <c r="G3" s="263"/>
+      <c r="G3" s="265"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37211,19 +37815,19 @@
       <c r="B7" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="265">
+      <c r="C7" s="262">
         <f>Statement!AA91</f>
         <v>3.0440633681443646E-2</v>
       </c>
-      <c r="D7" s="266"/>
-      <c r="F7" s="265">
+      <c r="D7" s="263"/>
+      <c r="F7" s="262">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12937310240132488</v>
       </c>
-      <c r="G7" s="266"/>
+      <c r="G7" s="263"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -37250,19 +37854,19 @@
       <c r="B9" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="265">
+      <c r="C9" s="262">
         <f>Statement!AA92</f>
         <v>7.2889329041842046E-2</v>
       </c>
-      <c r="D9" s="266"/>
-      <c r="F9" s="265">
+      <c r="D9" s="263"/>
+      <c r="F9" s="262">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13842112176540128</v>
       </c>
-      <c r="G9" s="266"/>
+      <c r="G9" s="263"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -37289,19 +37893,19 @@
       <c r="B11" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C11" s="265">
+      <c r="C11" s="262">
         <f>Statement!AA93</f>
         <v>1.0660267429652618E-2</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="F11" s="265">
+      <c r="D11" s="263"/>
+      <c r="F11" s="262">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12495023821448292</v>
       </c>
-      <c r="G11" s="266"/>
+      <c r="G11" s="263"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -37328,19 +37932,19 @@
       <c r="B13" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C13" s="265">
+      <c r="C13" s="262">
         <f>Statement!AA99</f>
         <v>-0.12340351714118437</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="F13" s="265">
+      <c r="D13" s="263"/>
+      <c r="F13" s="262">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.7704231252618349E-3</v>
       </c>
-      <c r="G13" s="266"/>
+      <c r="G13" s="263"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -37367,19 +37971,19 @@
       <c r="B15" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C15" s="265">
+      <c r="C15" s="262">
         <f>Statement!AA100</f>
         <v>2.2145042289004859</v>
       </c>
-      <c r="D15" s="266"/>
-      <c r="F15" s="265">
+      <c r="D15" s="263"/>
+      <c r="F15" s="262">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>3.0532400365074537</v>
       </c>
-      <c r="G15" s="266"/>
+      <c r="G15" s="263"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -37406,19 +38010,19 @@
       <c r="B17" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C17" s="265">
+      <c r="C17" s="262">
         <f>Statement!AA102</f>
         <v>1.2870289644483193</v>
       </c>
-      <c r="D17" s="266"/>
-      <c r="F17" s="265">
+      <c r="D17" s="263"/>
+      <c r="F17" s="262">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.7570260602963721</v>
       </c>
-      <c r="G17" s="266"/>
+      <c r="G17" s="263"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -37445,22 +38049,22 @@
       <c r="B19" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="265">
+      <c r="C19" s="262">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>8.8459599655267736E-3</v>
       </c>
-      <c r="D19" s="266"/>
-      <c r="F19" s="265">
+      <c r="D19" s="263"/>
+      <c r="F19" s="262">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>5.2952258108314526E-2</v>
       </c>
-      <c r="G19" s="266"/>
+      <c r="G19" s="263"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -37487,22 +38091,22 @@
       <c r="B21" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C21" s="265">
+      <c r="C21" s="262">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.2978639930252833</v>
       </c>
-      <c r="D21" s="266"/>
-      <c r="F21" s="265">
+      <c r="D21" s="263"/>
+      <c r="F21" s="262">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.7142857142857142</v>
       </c>
-      <c r="G21" s="266"/>
+      <c r="G21" s="263"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37551,22 +38155,22 @@
       <c r="B25" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C25" s="265">
+      <c r="C25" s="262">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.7274157785566125E-2</v>
       </c>
-      <c r="D25" s="266"/>
-      <c r="F25" s="265">
+      <c r="D25" s="263"/>
+      <c r="F25" s="262">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-3.0061631864593874E-2</v>
       </c>
-      <c r="G25" s="266"/>
+      <c r="G25" s="263"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37594,22 +38198,22 @@
       <c r="B27" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C27" s="265">
+      <c r="C27" s="262">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.17416013437849945</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="F27" s="265">
+      <c r="D27" s="263"/>
+      <c r="F27" s="262">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.40153717627401836</v>
       </c>
-      <c r="G27" s="266"/>
+      <c r="G27" s="263"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37637,22 +38241,22 @@
       <c r="B29" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C29" s="265">
+      <c r="C29" s="262">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.3995709002625414E-2</v>
       </c>
-      <c r="D29" s="266"/>
-      <c r="F29" s="265">
+      <c r="D29" s="263"/>
+      <c r="F29" s="262">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.14584912812736922</v>
       </c>
-      <c r="G29" s="266"/>
+      <c r="G29" s="263"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -37701,22 +38305,22 @@
       <c r="B33" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C33" s="265">
+      <c r="C33" s="262">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.0734220695577501E-2</v>
       </c>
-      <c r="D33" s="266"/>
-      <c r="F33" s="265">
+      <c r="D33" s="263"/>
+      <c r="F33" s="262">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.7331670822942641E-2</v>
       </c>
-      <c r="G33" s="266"/>
+      <c r="G33" s="263"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="239" t="str">
@@ -37744,25 +38348,43 @@
       <c r="B35" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C35" s="265">
+      <c r="C35" s="262">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-6.7286114478582681E-2</v>
       </c>
-      <c r="D35" s="266"/>
-      <c r="F35" s="265">
+      <c r="D35" s="263"/>
+      <c r="F35" s="262">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-9.1249332658182622E-2</v>
       </c>
-      <c r="G35" s="266"/>
+      <c r="G35" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C35:D35"/>
@@ -37773,24 +38395,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/PHR.xlsx
+++ b/PHR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A315AFED-6AE4-344B-95E6-692BBD974FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC733A1-5A16-9A43-87C4-342F89D58CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -175,7 +175,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -185,12 +206,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -1474,9 +1504,6 @@
     <t>Network revenue per AHSC growth</t>
   </si>
   <si>
-    <t>30.04.2027</t>
-  </si>
-  <si>
     <t>Q1 2027</t>
   </si>
   <si>
@@ -1517,6 +1544,9 @@
   </si>
   <si>
     <t>DDM price</t>
+  </si>
+  <si>
+    <t>30.04.2026</t>
   </si>
 </sst>
 </file>
@@ -2470,6 +2500,8 @@
     <xf numFmtId="9" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="12" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2524,8 +2556,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="39" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12915,7 +12945,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=bqw82w&amp;q=XNYS%3aPHR&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12934,11 +12964,9 @@
     <v>Powered by Refinitiv</v>
     <v>32.76</v>
     <v>7.77</v>
-    <v>0.85780000000000001</v>
-    <v>-0.1</v>
-    <v>-9.2420000000000002E-3</v>
-    <v>0</v>
-    <v>0</v>
+    <v>0.82199999999999995</v>
+    <v>0.08</v>
+    <v>7.5399999999999998E-3</v>
     <v>USD</v>
     <v>Phreesia, Inc. is a provider of comprehensive software solutions that improve the operational and financial performance of healthcare organizations. The Company's solutions include software-as-a-service (SaaS)-based integrated tools that manage patient access, registration, and payments. In addition, its solutions include clinical assessments to screen patients for a variety of physical, behavioral and mental health conditions, helping providers to understand their patients and connect them to needed services, resulting in improved health outcomes. Its Technology solutions segment provides life sciences companies, health plans and other payer organizations (payers), patient advocacy, public interest and other not-for-profit organizations with a channel for direct communication with patients. The Company's solutions also include additional products and services, such as the MediFind provider directory, which helps patients find care based on providers' specific clinical expertise.</v>
     <v>1789</v>
@@ -12946,35 +12974,49 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1521 Concord Pike, Suite 301 Pmb 221, WILMINGTON, DE, 19803 US</v>
-    <v>11.05</v>
+    <v>10.81</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46213.958333356248</v>
+    <v>46234.713113657031</v>
     <v>0</v>
-    <v>10.55</v>
-    <v>662623460</v>
+    <v>10.425000000000001</v>
+    <v>660769104</v>
     <v>PHREESIA, INC.</v>
     <v>PHREESIA, INC.</v>
-    <v>11.05</v>
-    <v>72.043000000000006</v>
-    <v>10.82</v>
-    <v>10.72</v>
-    <v>10.72</v>
+    <v>10.62</v>
+    <v>71.841399999999993</v>
+    <v>10.61</v>
+    <v>10.69</v>
     <v>61811890</v>
     <v>PHR</v>
     <v>PHREESIA, INC. (XNYS:PHR)</v>
-    <v>662587</v>
-    <v>1148596</v>
+    <v>233186</v>
+    <v>893566</v>
     <v>2005</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12986,30 +13028,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>46.87</v>
+    <v>47.14</v>
     <v>39.47</v>
-    <v>0.3</v>
-    <v>6.6090000000000003E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>45.71</v>
+    <v>46.86</v>
     <v>Index</v>
-    <v>3</v>
-    <v>45.39</v>
+    <v>6</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>45.41</v>
-    <v>45.39</v>
-    <v>45.69</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13031,8 +13073,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13053,7 +13093,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13063,6 +13102,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13098,7 +13142,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13109,16 +13153,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13212,19 +13253,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13296,9 +13331,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13306,9 +13338,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13810,18 +13839,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="260" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="259"/>
-      <c r="E2" s="258" t="s">
+      <c r="C2" s="261"/>
+      <c r="E2" s="260" t="s">
         <v>306</v>
       </c>
-      <c r="F2" s="259"/>
-      <c r="H2" s="258" t="s">
+      <c r="F2" s="261"/>
+      <c r="H2" s="260" t="s">
         <v>348</v>
       </c>
-      <c r="I2" s="259"/>
+      <c r="I2" s="261"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="189" t="s">
@@ -13836,7 +13865,7 @@
       </c>
       <c r="F3" s="191">
         <f ca="1">Statement!AC153</f>
-        <v>674373.76</v>
+        <v>672486.52</v>
       </c>
       <c r="H3" s="189" t="str">
         <f>'AVG target price'!B5</f>
@@ -13860,7 +13889,7 @@
       </c>
       <c r="F4" s="192">
         <f ca="1">Statement!AC154</f>
-        <v>690271.76</v>
+        <v>688384.52</v>
       </c>
       <c r="H4" s="189" t="str">
         <f>'AVG target price'!B6</f>
@@ -13877,7 +13906,7 @@
       </c>
       <c r="C5" s="212" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>262</v>
@@ -13899,16 +13928,16 @@
       <c r="B6" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="212" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>10.72</v>
+      <c r="C6" s="212" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="189" t="s">
         <v>256</v>
       </c>
       <c r="F6" s="194">
         <f ca="1">Statement!AC150</f>
-        <v>-283.13462950794326</v>
+        <v>-282.34227513432023</v>
       </c>
       <c r="H6" s="189" t="str">
         <f>'AVG target price'!B8</f>
@@ -13925,14 +13954,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E7" s="190" t="s">
         <v>215</v>
       </c>
       <c r="F7" s="195">
         <f ca="1">Statement!AC151</f>
-        <v>1.3345328194677051</v>
+        <v>1.3307981194132243</v>
       </c>
       <c r="H7" s="188" t="str">
         <f>'AVG target price'!B9</f>
@@ -13947,16 +13976,16 @@
       <c r="B8" s="189" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="189" t="s">
         <v>284</v>
       </c>
       <c r="F8" s="196">
         <f ca="1">Statement!AC161</f>
-        <v>-6.6728574967092429E-4</v>
+        <v>-6.6915839443146014E-4</v>
       </c>
       <c r="H8" s="188" t="str">
         <f>'AVG target price'!B11</f>
@@ -13964,7 +13993,7 @@
       </c>
       <c r="I8" s="217">
         <f ca="1">'AVG target price'!C11</f>
-        <v>5.3547296749058712E-2</v>
+        <v>5.6503930883995378E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13973,23 +14002,23 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-9.2420000000000002E-3</v>
+        <v>7.5399999999999998E-3</v>
       </c>
       <c r="E9" s="189" t="s">
         <v>307</v>
       </c>
       <c r="F9" s="196">
         <f ca="1">Statement!AC162</f>
-        <v>-3.5318887051643583E-3</v>
+        <v>-3.5418004601835292E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>0</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="189" t="s">
         <v>312</v>
@@ -13999,7 +14028,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="188" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I10" s="216">
         <f>DDM!C26</f>
@@ -14044,7 +14073,7 @@
       </c>
       <c r="C13" s="213" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>0.85780000000000001</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="E13" s="189" t="s">
         <v>116</v>
@@ -14060,7 +14089,7 @@
       </c>
       <c r="C14" s="214" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1148596</v>
+        <v>893566</v>
       </c>
       <c r="E14" s="190" t="s">
         <v>117</v>
@@ -14076,7 +14105,7 @@
       </c>
       <c r="F15" s="196">
         <f ca="1">Statement!AC176</f>
-        <v>-2.3574464107263011E-2</v>
+        <v>-2.3640622565936339E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14089,10 +14118,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="260" t="s">
+      <c r="B17" s="262" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="260"/>
+      <c r="C17" s="262"/>
       <c r="E17" s="188" t="s">
         <v>315</v>
       </c>
@@ -14165,14 +14194,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="260" t="s">
+      <c r="B25" s="262" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="260"/>
-      <c r="E25" s="258" t="s">
+      <c r="C25" s="262"/>
+      <c r="E25" s="260" t="s">
         <v>362</v>
       </c>
-      <c r="F25" s="259"/>
+      <c r="F25" s="261"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="188" t="s">
@@ -14181,12 +14210,12 @@
       <c r="C26" s="174">
         <v>0.21</v>
       </c>
-      <c r="E26" s="189" t="e" vm="2">
+      <c r="E26" s="189" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="223" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>45.69</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14201,7 +14230,7 @@
       </c>
       <c r="F27" s="224">
         <f ca="1">F26/1000</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14214,22 +14243,22 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="188" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C29" s="225">
         <v>0.11</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="261" t="s">
+      <c r="B33" s="263" t="s">
         <v>356</v>
       </c>
-      <c r="C33" s="261"/>
-      <c r="D33" s="261"/>
-      <c r="E33" s="261"/>
-      <c r="F33" s="261"/>
-      <c r="G33" s="261"/>
-      <c r="H33" s="261"/>
+      <c r="C33" s="263"/>
+      <c r="D33" s="263"/>
+      <c r="E33" s="263"/>
+      <c r="F33" s="263"/>
+      <c r="G33" s="263"/>
+      <c r="H33" s="263"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14248,24 +14277,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="261"/>
-      <c r="C39" s="261"/>
-      <c r="D39" s="261"/>
-      <c r="E39" s="261"/>
-      <c r="F39" s="261"/>
-      <c r="G39" s="261"/>
-      <c r="H39" s="261"/>
+      <c r="B39" s="263"/>
+      <c r="C39" s="263"/>
+      <c r="D39" s="263"/>
+      <c r="E39" s="263"/>
+      <c r="F39" s="263"/>
+      <c r="G39" s="263"/>
+      <c r="H39" s="263"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="261" t="s">
+      <c r="B42" s="263" t="s">
         <v>359</v>
       </c>
-      <c r="C42" s="261"/>
-      <c r="D42" s="261"/>
-      <c r="E42" s="261"/>
-      <c r="F42" s="261"/>
-      <c r="G42" s="261"/>
-      <c r="H42" s="261"/>
+      <c r="C42" s="263"/>
+      <c r="D42" s="263"/>
+      <c r="E42" s="263"/>
+      <c r="F42" s="263"/>
+      <c r="G42" s="263"/>
+      <c r="H42" s="263"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14352,24 +14381,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="261"/>
-      <c r="C55" s="261"/>
-      <c r="D55" s="261"/>
-      <c r="E55" s="261"/>
-      <c r="F55" s="261"/>
-      <c r="G55" s="261"/>
-      <c r="H55" s="261"/>
+      <c r="B55" s="263"/>
+      <c r="C55" s="263"/>
+      <c r="D55" s="263"/>
+      <c r="E55" s="263"/>
+      <c r="F55" s="263"/>
+      <c r="G55" s="263"/>
+      <c r="H55" s="263"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="261" t="s">
+      <c r="B58" s="263" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="261"/>
-      <c r="D58" s="261"/>
-      <c r="E58" s="261"/>
-      <c r="F58" s="261"/>
-      <c r="G58" s="261"/>
-      <c r="H58" s="261"/>
+      <c r="C58" s="263"/>
+      <c r="D58" s="263"/>
+      <c r="E58" s="263"/>
+      <c r="F58" s="263"/>
+      <c r="G58" s="263"/>
+      <c r="H58" s="263"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14418,13 +14447,13 @@
       </c>
     </row>
     <row r="68" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="261"/>
-      <c r="C68" s="261"/>
-      <c r="D68" s="261"/>
-      <c r="E68" s="261"/>
-      <c r="F68" s="261"/>
-      <c r="G68" s="261"/>
-      <c r="H68" s="261"/>
+      <c r="B68" s="263"/>
+      <c r="C68" s="263"/>
+      <c r="D68" s="263"/>
+      <c r="E68" s="263"/>
+      <c r="F68" s="263"/>
+      <c r="G68" s="263"/>
+      <c r="H68" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14509,36 +14538,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="272"/>
+      <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="261" t="s">
+      <c r="S2" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261"/>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
-      <c r="AA2" s="261" t="s">
+      <c r="T2" s="263"/>
+      <c r="U2" s="263"/>
+      <c r="V2" s="263"/>
+      <c r="W2" s="263"/>
+      <c r="X2" s="263"/>
+      <c r="Y2" s="263"/>
+      <c r="Z2" s="263"/>
+      <c r="AA2" s="263" t="s">
         <v>126</v>
       </c>
-      <c r="AB2" s="261"/>
-      <c r="AC2" s="261"/>
+      <c r="AB2" s="263"/>
+      <c r="AC2" s="263"/>
       <c r="AE2" s="86" t="s">
         <v>127</v>
       </c>
@@ -14549,32 +14578,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="269" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="268" t="s">
+      <c r="S4" s="270" t="s">
         <v>128</v>
       </c>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
-      <c r="AA4" s="269"/>
-      <c r="AB4" s="269"/>
-      <c r="AC4" s="269"/>
+      <c r="T4" s="271"/>
+      <c r="U4" s="271"/>
+      <c r="V4" s="271"/>
+      <c r="W4" s="271"/>
+      <c r="X4" s="271"/>
+      <c r="Y4" s="271"/>
+      <c r="Z4" s="271"/>
+      <c r="AA4" s="271"/>
+      <c r="AB4" s="271"/>
+      <c r="AC4" s="271"/>
       <c r="AE4" s="88"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15065,33 +15094,33 @@
       <c r="Q10" s="92"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="269" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="269"/>
+      <c r="E11" s="269"/>
+      <c r="F11" s="269"/>
+      <c r="G11" s="269"/>
+      <c r="H11" s="269"/>
+      <c r="I11" s="269"/>
+      <c r="J11" s="269"/>
+      <c r="K11" s="269"/>
+      <c r="L11" s="269"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="92"/>
-      <c r="S11" s="268" t="s">
+      <c r="S11" s="270" t="s">
         <v>134</v>
       </c>
-      <c r="T11" s="269"/>
-      <c r="U11" s="269"/>
-      <c r="V11" s="269"/>
-      <c r="W11" s="269"/>
-      <c r="X11" s="269"/>
-      <c r="Y11" s="269"/>
-      <c r="Z11" s="269"/>
-      <c r="AA11" s="269"/>
-      <c r="AB11" s="269"/>
-      <c r="AC11" s="269"/>
+      <c r="T11" s="271"/>
+      <c r="U11" s="271"/>
+      <c r="V11" s="271"/>
+      <c r="W11" s="271"/>
+      <c r="X11" s="271"/>
+      <c r="Y11" s="271"/>
+      <c r="Z11" s="271"/>
+      <c r="AA11" s="271"/>
+      <c r="AB11" s="271"/>
+      <c r="AC11" s="271"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15532,33 +15561,33 @@
       <c r="Q18" s="92"/>
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C19" s="267" t="s">
+      <c r="C19" s="269" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="267"/>
-      <c r="E19" s="267"/>
-      <c r="F19" s="267"/>
-      <c r="G19" s="267"/>
-      <c r="H19" s="267"/>
-      <c r="I19" s="267"/>
-      <c r="J19" s="267"/>
-      <c r="K19" s="267"/>
-      <c r="L19" s="267"/>
+      <c r="D19" s="269"/>
+      <c r="E19" s="269"/>
+      <c r="F19" s="269"/>
+      <c r="G19" s="269"/>
+      <c r="H19" s="269"/>
+      <c r="I19" s="269"/>
+      <c r="J19" s="269"/>
+      <c r="K19" s="269"/>
+      <c r="L19" s="269"/>
       <c r="O19" s="5"/>
       <c r="Q19" s="92"/>
-      <c r="S19" s="268" t="s">
+      <c r="S19" s="270" t="s">
         <v>136</v>
       </c>
-      <c r="T19" s="269"/>
-      <c r="U19" s="269"/>
-      <c r="V19" s="269"/>
-      <c r="W19" s="269"/>
-      <c r="X19" s="269"/>
-      <c r="Y19" s="269"/>
-      <c r="Z19" s="269"/>
-      <c r="AA19" s="269"/>
-      <c r="AB19" s="269"/>
-      <c r="AC19" s="269"/>
+      <c r="T19" s="271"/>
+      <c r="U19" s="271"/>
+      <c r="V19" s="271"/>
+      <c r="W19" s="271"/>
+      <c r="X19" s="271"/>
+      <c r="Y19" s="271"/>
+      <c r="Z19" s="271"/>
+      <c r="AA19" s="271"/>
+      <c r="AB19" s="271"/>
+      <c r="AC19" s="271"/>
       <c r="AE19" s="88">
         <f>AE4</f>
         <v>0</v>
@@ -16795,35 +16824,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="272"/>
+      <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="P2" s="261" t="s">
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
+      <c r="P2" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="Q2" s="261"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="261"/>
-      <c r="U2" s="261"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="261"/>
-      <c r="X2" s="261" t="s">
+      <c r="Q2" s="263"/>
+      <c r="R2" s="263"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="263"/>
+      <c r="V2" s="263"/>
+      <c r="W2" s="263"/>
+      <c r="X2" s="263" t="s">
         <v>126</v>
       </c>
-      <c r="Y2" s="261"/>
-      <c r="Z2" s="261"/>
+      <c r="Y2" s="263"/>
+      <c r="Z2" s="263"/>
       <c r="AB2" s="86" t="s">
         <v>127</v>
       </c>
@@ -16832,31 +16861,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="269" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
-      <c r="P4" s="269" t="s">
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
+      <c r="P4" s="271" t="s">
         <v>128</v>
       </c>
-      <c r="Q4" s="269"/>
-      <c r="R4" s="269"/>
-      <c r="S4" s="269"/>
-      <c r="T4" s="269"/>
-      <c r="U4" s="269"/>
-      <c r="V4" s="269"/>
-      <c r="W4" s="269"/>
-      <c r="X4" s="269"/>
-      <c r="Y4" s="269"/>
-      <c r="Z4" s="269"/>
+      <c r="Q4" s="271"/>
+      <c r="R4" s="271"/>
+      <c r="S4" s="271"/>
+      <c r="T4" s="271"/>
+      <c r="U4" s="271"/>
+      <c r="V4" s="271"/>
+      <c r="W4" s="271"/>
+      <c r="X4" s="271"/>
+      <c r="Y4" s="271"/>
+      <c r="Z4" s="271"/>
       <c r="AB4" s="88"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -17051,32 +17080,32 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="269" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="269"/>
+      <c r="E9" s="269"/>
+      <c r="F9" s="269"/>
+      <c r="G9" s="269"/>
+      <c r="H9" s="269"/>
+      <c r="I9" s="269"/>
+      <c r="J9" s="269"/>
+      <c r="K9" s="269"/>
+      <c r="L9" s="269"/>
       <c r="N9" s="92"/>
-      <c r="P9" s="269" t="s">
+      <c r="P9" s="271" t="s">
         <v>140</v>
       </c>
-      <c r="Q9" s="269"/>
-      <c r="R9" s="269"/>
-      <c r="S9" s="269"/>
-      <c r="T9" s="269"/>
-      <c r="U9" s="269"/>
-      <c r="V9" s="269"/>
-      <c r="W9" s="269"/>
-      <c r="X9" s="269"/>
-      <c r="Y9" s="269"/>
-      <c r="Z9" s="269"/>
+      <c r="Q9" s="271"/>
+      <c r="R9" s="271"/>
+      <c r="S9" s="271"/>
+      <c r="T9" s="271"/>
+      <c r="U9" s="271"/>
+      <c r="V9" s="271"/>
+      <c r="W9" s="271"/>
+      <c r="X9" s="271"/>
+      <c r="Y9" s="271"/>
+      <c r="Z9" s="271"/>
       <c r="AB9" s="88">
         <f>AB4</f>
         <v>0</v>
@@ -17834,31 +17863,31 @@
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C20" s="267" t="s">
+      <c r="C20" s="269" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="267"/>
-      <c r="E20" s="267"/>
-      <c r="F20" s="267"/>
-      <c r="G20" s="267"/>
-      <c r="H20" s="267"/>
-      <c r="I20" s="267"/>
-      <c r="J20" s="267"/>
-      <c r="K20" s="267"/>
-      <c r="L20" s="267"/>
-      <c r="P20" s="269" t="s">
+      <c r="D20" s="269"/>
+      <c r="E20" s="269"/>
+      <c r="F20" s="269"/>
+      <c r="G20" s="269"/>
+      <c r="H20" s="269"/>
+      <c r="I20" s="269"/>
+      <c r="J20" s="269"/>
+      <c r="K20" s="269"/>
+      <c r="L20" s="269"/>
+      <c r="P20" s="271" t="s">
         <v>142</v>
       </c>
-      <c r="Q20" s="269"/>
-      <c r="R20" s="269"/>
-      <c r="S20" s="269"/>
-      <c r="T20" s="269"/>
-      <c r="U20" s="269"/>
-      <c r="V20" s="269"/>
-      <c r="W20" s="269"/>
-      <c r="X20" s="269"/>
-      <c r="Y20" s="269"/>
-      <c r="Z20" s="269"/>
+      <c r="Q20" s="271"/>
+      <c r="R20" s="271"/>
+      <c r="S20" s="271"/>
+      <c r="T20" s="271"/>
+      <c r="U20" s="271"/>
+      <c r="V20" s="271"/>
+      <c r="W20" s="271"/>
+      <c r="X20" s="271"/>
+      <c r="Y20" s="271"/>
+      <c r="Z20" s="271"/>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
@@ -18582,60 +18611,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="272"/>
+      <c r="H3" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="P3" s="274"/>
+      <c r="Q3" s="274"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="274"/>
+      <c r="T3" s="274"/>
+      <c r="U3" s="274"/>
+      <c r="V3" s="274"/>
+      <c r="W3" s="274"/>
+      <c r="X3" s="274"/>
+      <c r="Y3" s="274"/>
+      <c r="Z3" s="274"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="269" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="272"/>
-      <c r="T5" s="272"/>
-      <c r="U5" s="272"/>
-      <c r="V5" s="272"/>
-      <c r="W5" s="272"/>
-      <c r="X5" s="272"/>
-      <c r="Y5" s="272"/>
-      <c r="Z5" s="272"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="269"/>
+      <c r="F5" s="269"/>
+      <c r="G5" s="269"/>
+      <c r="H5" s="269"/>
+      <c r="I5" s="269"/>
+      <c r="J5" s="269"/>
+      <c r="K5" s="269"/>
+      <c r="L5" s="269"/>
+      <c r="P5" s="274"/>
+      <c r="Q5" s="274"/>
+      <c r="R5" s="274"/>
+      <c r="S5" s="274"/>
+      <c r="T5" s="274"/>
+      <c r="U5" s="274"/>
+      <c r="V5" s="274"/>
+      <c r="W5" s="274"/>
+      <c r="X5" s="274"/>
+      <c r="Y5" s="274"/>
+      <c r="Z5" s="274"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -18821,30 +18850,30 @@
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="269" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="267"/>
-      <c r="E11" s="267"/>
-      <c r="F11" s="267"/>
-      <c r="G11" s="267"/>
-      <c r="H11" s="267"/>
-      <c r="I11" s="267"/>
-      <c r="J11" s="267"/>
-      <c r="K11" s="267"/>
-      <c r="L11" s="267"/>
+      <c r="D11" s="269"/>
+      <c r="E11" s="269"/>
+      <c r="F11" s="269"/>
+      <c r="G11" s="269"/>
+      <c r="H11" s="269"/>
+      <c r="I11" s="269"/>
+      <c r="J11" s="269"/>
+      <c r="K11" s="269"/>
+      <c r="L11" s="269"/>
       <c r="N11" s="92"/>
-      <c r="P11" s="272"/>
-      <c r="Q11" s="272"/>
-      <c r="R11" s="272"/>
-      <c r="S11" s="272"/>
-      <c r="T11" s="272"/>
-      <c r="U11" s="272"/>
-      <c r="V11" s="272"/>
-      <c r="W11" s="272"/>
-      <c r="X11" s="272"/>
-      <c r="Y11" s="272"/>
-      <c r="Z11" s="272"/>
+      <c r="P11" s="274"/>
+      <c r="Q11" s="274"/>
+      <c r="R11" s="274"/>
+      <c r="S11" s="274"/>
+      <c r="T11" s="274"/>
+      <c r="U11" s="274"/>
+      <c r="V11" s="274"/>
+      <c r="W11" s="274"/>
+      <c r="X11" s="274"/>
+      <c r="Y11" s="274"/>
+      <c r="Z11" s="274"/>
       <c r="AB11" s="114"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -19086,18 +19115,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="269" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="269"/>
+      <c r="E18" s="269"/>
+      <c r="F18" s="269"/>
+      <c r="G18" s="269"/>
+      <c r="H18" s="269"/>
+      <c r="I18" s="269"/>
+      <c r="J18" s="269"/>
+      <c r="K18" s="269"/>
+      <c r="L18" s="269"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19310,23 +19339,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="272"/>
-      <c r="C25" s="272"/>
+      <c r="B25" s="274"/>
+      <c r="C25" s="274"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="113"/>
-      <c r="C26" s="267" t="s">
+      <c r="C26" s="269" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="267"/>
-      <c r="E26" s="267"/>
-      <c r="F26" s="267"/>
-      <c r="G26" s="267"/>
-      <c r="H26" s="267"/>
-      <c r="I26" s="267"/>
-      <c r="J26" s="267"/>
-      <c r="K26" s="267"/>
-      <c r="L26" s="267"/>
+      <c r="D26" s="269"/>
+      <c r="E26" s="269"/>
+      <c r="F26" s="269"/>
+      <c r="G26" s="269"/>
+      <c r="H26" s="269"/>
+      <c r="I26" s="269"/>
+      <c r="J26" s="269"/>
+      <c r="K26" s="269"/>
+      <c r="L26" s="269"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -19518,18 +19547,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="113"/>
-      <c r="C33" s="267" t="s">
+      <c r="C33" s="269" t="s">
         <v>161</v>
       </c>
-      <c r="D33" s="267"/>
-      <c r="E33" s="267"/>
-      <c r="F33" s="267"/>
-      <c r="G33" s="267"/>
-      <c r="H33" s="267"/>
-      <c r="I33" s="267"/>
-      <c r="J33" s="267"/>
-      <c r="K33" s="267"/>
-      <c r="L33" s="267"/>
+      <c r="D33" s="269"/>
+      <c r="E33" s="269"/>
+      <c r="F33" s="269"/>
+      <c r="G33" s="269"/>
+      <c r="H33" s="269"/>
+      <c r="I33" s="269"/>
+      <c r="J33" s="269"/>
+      <c r="K33" s="269"/>
+      <c r="L33" s="269"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -19713,18 +19742,18 @@
       <c r="C39" s="129"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="267" t="s">
+      <c r="C40" s="269" t="s">
         <v>164</v>
       </c>
-      <c r="D40" s="267"/>
-      <c r="E40" s="267"/>
-      <c r="F40" s="267"/>
-      <c r="G40" s="267"/>
-      <c r="H40" s="267"/>
-      <c r="I40" s="267"/>
-      <c r="J40" s="267"/>
-      <c r="K40" s="267"/>
-      <c r="L40" s="267"/>
+      <c r="D40" s="269"/>
+      <c r="E40" s="269"/>
+      <c r="F40" s="269"/>
+      <c r="G40" s="269"/>
+      <c r="H40" s="269"/>
+      <c r="I40" s="269"/>
+      <c r="J40" s="269"/>
+      <c r="K40" s="269"/>
+      <c r="L40" s="269"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -20043,60 +20072,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="272"/>
+      <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="S2" s="272"/>
-      <c r="T2" s="272"/>
-      <c r="U2" s="272"/>
-      <c r="V2" s="272"/>
-      <c r="W2" s="272"/>
-      <c r="X2" s="272"/>
-      <c r="Y2" s="272"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="272"/>
-      <c r="AB2" s="272"/>
-      <c r="AC2" s="272"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
+      <c r="S2" s="274"/>
+      <c r="T2" s="274"/>
+      <c r="U2" s="274"/>
+      <c r="V2" s="274"/>
+      <c r="W2" s="274"/>
+      <c r="X2" s="274"/>
+      <c r="Y2" s="274"/>
+      <c r="Z2" s="274"/>
+      <c r="AA2" s="274"/>
+      <c r="AB2" s="274"/>
+      <c r="AC2" s="274"/>
       <c r="AE2" s="113"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="269" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
-      <c r="S4" s="272"/>
-      <c r="T4" s="272"/>
-      <c r="U4" s="272"/>
-      <c r="V4" s="272"/>
-      <c r="W4" s="272"/>
-      <c r="X4" s="272"/>
-      <c r="Y4" s="272"/>
-      <c r="Z4" s="272"/>
-      <c r="AA4" s="272"/>
-      <c r="AB4" s="272"/>
-      <c r="AC4" s="272"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
+      <c r="S4" s="274"/>
+      <c r="T4" s="274"/>
+      <c r="U4" s="274"/>
+      <c r="V4" s="274"/>
+      <c r="W4" s="274"/>
+      <c r="X4" s="274"/>
+      <c r="Y4" s="274"/>
+      <c r="Z4" s="274"/>
+      <c r="AA4" s="274"/>
+      <c r="AB4" s="274"/>
+      <c r="AC4" s="274"/>
       <c r="AE4" s="114"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -20459,18 +20488,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="267" t="s">
+      <c r="C13" s="269" t="s">
         <v>172</v>
       </c>
-      <c r="D13" s="267"/>
-      <c r="E13" s="267"/>
-      <c r="F13" s="267"/>
-      <c r="G13" s="267"/>
-      <c r="H13" s="267"/>
-      <c r="I13" s="267"/>
-      <c r="J13" s="267"/>
-      <c r="K13" s="267"/>
-      <c r="L13" s="267"/>
+      <c r="D13" s="269"/>
+      <c r="E13" s="269"/>
+      <c r="F13" s="269"/>
+      <c r="G13" s="269"/>
+      <c r="H13" s="269"/>
+      <c r="I13" s="269"/>
+      <c r="J13" s="269"/>
+      <c r="K13" s="269"/>
+      <c r="L13" s="269"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -20563,18 +20592,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="269" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="267"/>
-      <c r="E18" s="267"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="267"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="267"/>
-      <c r="J18" s="267"/>
-      <c r="K18" s="267"/>
-      <c r="L18" s="267"/>
+      <c r="D18" s="269"/>
+      <c r="E18" s="269"/>
+      <c r="F18" s="269"/>
+      <c r="G18" s="269"/>
+      <c r="H18" s="269"/>
+      <c r="I18" s="269"/>
+      <c r="J18" s="269"/>
+      <c r="K18" s="269"/>
+      <c r="L18" s="269"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -20766,18 +20795,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="267" t="s">
+      <c r="C25" s="269" t="s">
         <v>281</v>
       </c>
-      <c r="D25" s="267"/>
-      <c r="E25" s="267"/>
-      <c r="F25" s="267"/>
-      <c r="G25" s="267"/>
-      <c r="H25" s="267"/>
-      <c r="I25" s="267"/>
-      <c r="J25" s="267"/>
-      <c r="K25" s="267"/>
-      <c r="L25" s="267"/>
+      <c r="D25" s="269"/>
+      <c r="E25" s="269"/>
+      <c r="F25" s="269"/>
+      <c r="G25" s="269"/>
+      <c r="H25" s="269"/>
+      <c r="I25" s="269"/>
+      <c r="J25" s="269"/>
+      <c r="K25" s="269"/>
+      <c r="L25" s="269"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -20915,18 +20944,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="267" t="s">
+      <c r="C31" s="269" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="267"/>
-      <c r="E31" s="267"/>
-      <c r="F31" s="267"/>
-      <c r="G31" s="267"/>
-      <c r="H31" s="267"/>
-      <c r="I31" s="267"/>
-      <c r="J31" s="267"/>
-      <c r="K31" s="267"/>
-      <c r="L31" s="267"/>
+      <c r="D31" s="269"/>
+      <c r="E31" s="269"/>
+      <c r="F31" s="269"/>
+      <c r="G31" s="269"/>
+      <c r="H31" s="269"/>
+      <c r="I31" s="269"/>
+      <c r="J31" s="269"/>
+      <c r="K31" s="269"/>
+      <c r="L31" s="269"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -21137,10 +21166,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="263" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="261"/>
+      <c r="C4" s="263"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -21157,7 +21186,7 @@
       </c>
       <c r="C6" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21166,7 +21195,7 @@
       </c>
       <c r="C7" s="138">
         <f ca="1">C5*C6</f>
-        <v>674373.76</v>
+        <v>672486.52</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21184,7 +21213,7 @@
       </c>
       <c r="C9" s="139">
         <f ca="1">Overview!F27</f>
-        <v>4.5689999999999995E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21193,7 +21222,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C13</f>
-        <v>0.85780000000000001</v>
+        <v>0.82199999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21225,10 +21254,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="263" t="s">
         <v>187</v>
       </c>
-      <c r="C15" s="261"/>
+      <c r="C15" s="263"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -21236,7 +21265,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>0.1184400445837798</v>
+        <v>0.11873296499607937</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21245,7 +21274,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.88155995541622023</v>
+        <v>0.88126703500392067</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21263,7 +21292,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>8.4290999999999991E-2</v>
+        <v>8.362E-2</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -21272,7 +21301,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>8.0857304667471638E-2</v>
+        <v>8.0257482431311034E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21317,60 +21346,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="272"/>
+      <c r="H3" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="P3" s="274"/>
+      <c r="Q3" s="274"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="274"/>
+      <c r="T3" s="274"/>
+      <c r="U3" s="274"/>
+      <c r="V3" s="274"/>
+      <c r="W3" s="274"/>
+      <c r="X3" s="274"/>
+      <c r="Y3" s="274"/>
+      <c r="Z3" s="274"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="269" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="272"/>
-      <c r="T5" s="272"/>
-      <c r="U5" s="272"/>
-      <c r="V5" s="272"/>
-      <c r="W5" s="272"/>
-      <c r="X5" s="272"/>
-      <c r="Y5" s="272"/>
-      <c r="Z5" s="272"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="269"/>
+      <c r="F5" s="269"/>
+      <c r="G5" s="269"/>
+      <c r="H5" s="269"/>
+      <c r="I5" s="269"/>
+      <c r="J5" s="269"/>
+      <c r="K5" s="269"/>
+      <c r="L5" s="269"/>
+      <c r="P5" s="274"/>
+      <c r="Q5" s="274"/>
+      <c r="R5" s="274"/>
+      <c r="S5" s="274"/>
+      <c r="T5" s="274"/>
+      <c r="U5" s="274"/>
+      <c r="V5" s="274"/>
+      <c r="W5" s="274"/>
+      <c r="X5" s="274"/>
+      <c r="Y5" s="274"/>
+      <c r="Z5" s="274"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21616,10 +21645,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="261" t="s">
+      <c r="B13" s="263" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="261"/>
+      <c r="C13" s="263"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -21639,10 +21668,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="261" t="s">
+      <c r="B18" s="263" t="s">
         <v>200</v>
       </c>
-      <c r="C18" s="261"/>
+      <c r="C18" s="263"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -21756,37 +21785,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="272"/>
+      <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="269" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21975,18 +22004,18 @@
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="267" t="s">
+      <c r="C10" s="269" t="s">
         <v>134</v>
       </c>
-      <c r="D10" s="267"/>
-      <c r="E10" s="267"/>
-      <c r="F10" s="267"/>
-      <c r="G10" s="267"/>
-      <c r="H10" s="267"/>
-      <c r="I10" s="267"/>
-      <c r="J10" s="267"/>
-      <c r="K10" s="267"/>
-      <c r="L10" s="267"/>
+      <c r="D10" s="269"/>
+      <c r="E10" s="269"/>
+      <c r="F10" s="269"/>
+      <c r="G10" s="269"/>
+      <c r="H10" s="269"/>
+      <c r="I10" s="269"/>
+      <c r="J10" s="269"/>
+      <c r="K10" s="269"/>
+      <c r="L10" s="269"/>
       <c r="N10" s="92"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22180,18 +22209,18 @@
       <c r="N15" s="92"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="267" t="s">
+      <c r="C16" s="269" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="267"/>
-      <c r="E16" s="267"/>
-      <c r="F16" s="267"/>
-      <c r="G16" s="267"/>
-      <c r="H16" s="267"/>
-      <c r="I16" s="267"/>
-      <c r="J16" s="267"/>
-      <c r="K16" s="267"/>
-      <c r="L16" s="267"/>
+      <c r="D16" s="269"/>
+      <c r="E16" s="269"/>
+      <c r="F16" s="269"/>
+      <c r="G16" s="269"/>
+      <c r="H16" s="269"/>
+      <c r="I16" s="269"/>
+      <c r="J16" s="269"/>
+      <c r="K16" s="269"/>
+      <c r="L16" s="269"/>
       <c r="N16" s="92"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -22325,18 +22354,18 @@
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="267" t="s">
+      <c r="C21" s="269" t="s">
         <v>213</v>
       </c>
-      <c r="D21" s="267"/>
-      <c r="E21" s="267"/>
-      <c r="F21" s="267"/>
-      <c r="G21" s="267"/>
-      <c r="H21" s="267"/>
-      <c r="I21" s="267"/>
-      <c r="J21" s="267"/>
-      <c r="K21" s="267"/>
-      <c r="L21" s="267"/>
+      <c r="D21" s="269"/>
+      <c r="E21" s="269"/>
+      <c r="F21" s="269"/>
+      <c r="G21" s="269"/>
+      <c r="H21" s="269"/>
+      <c r="I21" s="269"/>
+      <c r="J21" s="269"/>
+      <c r="K21" s="269"/>
+      <c r="L21" s="269"/>
       <c r="N21" s="92"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -22420,18 +22449,18 @@
       <c r="N25" s="92"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="267" t="s">
+      <c r="C26" s="269" t="s">
         <v>214</v>
       </c>
-      <c r="D26" s="267"/>
-      <c r="E26" s="267"/>
-      <c r="F26" s="267"/>
-      <c r="G26" s="267"/>
-      <c r="H26" s="267"/>
-      <c r="I26" s="267"/>
-      <c r="J26" s="267"/>
-      <c r="K26" s="267"/>
-      <c r="L26" s="267"/>
+      <c r="D26" s="269"/>
+      <c r="E26" s="269"/>
+      <c r="F26" s="269"/>
+      <c r="G26" s="269"/>
+      <c r="H26" s="269"/>
+      <c r="I26" s="269"/>
+      <c r="J26" s="269"/>
+      <c r="K26" s="269"/>
+      <c r="L26" s="269"/>
       <c r="N26" s="92"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -22701,10 +22730,10 @@
       <c r="N36" s="92"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="261" t="s">
+      <c r="B37" s="263" t="s">
         <v>219</v>
       </c>
-      <c r="C37" s="261"/>
+      <c r="C37" s="263"/>
       <c r="N37" s="92"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -22771,7 +22800,7 @@
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C45" s="24">
         <f>C42+C43-C44</f>
@@ -22797,10 +22826,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="261" t="s">
+      <c r="B49" s="263" t="s">
         <v>224</v>
       </c>
-      <c r="C49" s="261"/>
+      <c r="C49" s="263"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -22856,10 +22885,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="261" t="s">
+      <c r="B57" s="263" t="s">
         <v>342</v>
       </c>
-      <c r="C57" s="261"/>
+      <c r="C57" s="263"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -22925,7 +22954,7 @@
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C65" s="24">
         <f>C62+C63-C64</f>
@@ -22999,10 +23028,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="263" t="s">
         <v>229</v>
       </c>
-      <c r="C4" s="261"/>
+      <c r="C4" s="263"/>
       <c r="N4" s="92"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -23056,7 +23085,7 @@
       </c>
       <c r="C10" s="137">
         <f ca="1">Overview!C5</f>
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -23065,7 +23094,7 @@
       </c>
       <c r="C11" s="158">
         <f ca="1">(C9-C10)/C10</f>
-        <v>5.3547296749058712E-2</v>
+        <v>5.6503930883995378E-2</v>
       </c>
     </row>
   </sheetData>
@@ -23116,42 +23145,42 @@
     <row r="1" spans="1:14" s="84" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="83" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="261" t="s">
+      <c r="C2" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="261"/>
-      <c r="E2" s="261"/>
-      <c r="F2" s="261"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="271" t="s">
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="272"/>
+      <c r="H2" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="261"/>
-      <c r="J2" s="261"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="267" t="s">
+      <c r="C4" s="269" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="267"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="267"/>
-      <c r="K4" s="267"/>
-      <c r="L4" s="267"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -23202,23 +23231,23 @@
       <c r="B6" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="C6" s="276">
+      <c r="C6" s="258">
         <f>Statement!M28</f>
         <v>-2.37</v>
       </c>
-      <c r="D6" s="276">
+      <c r="D6" s="258">
         <f>Statement!N28</f>
         <v>-3.36</v>
       </c>
-      <c r="E6" s="276">
+      <c r="E6" s="258">
         <f>Statement!O28</f>
         <v>-2.5099999999999998</v>
       </c>
-      <c r="F6" s="276">
+      <c r="F6" s="258">
         <f>Statement!P28</f>
         <v>-1.02</v>
       </c>
-      <c r="G6" s="277">
+      <c r="G6" s="259">
         <f>Statement!Q28</f>
         <v>-0.16</v>
       </c>
@@ -23231,25 +23260,25 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="C7" s="276">
+        <v>429</v>
+      </c>
+      <c r="C7" s="258">
         <f>Statement!M84</f>
         <v>0</v>
       </c>
-      <c r="D7" s="276">
+      <c r="D7" s="258">
         <f>Statement!N84</f>
         <v>0</v>
       </c>
-      <c r="E7" s="276">
+      <c r="E7" s="258">
         <f>Statement!O84</f>
         <v>0</v>
       </c>
-      <c r="F7" s="276">
+      <c r="F7" s="258">
         <f>Statement!P84</f>
         <v>0</v>
       </c>
-      <c r="G7" s="277">
+      <c r="G7" s="259">
         <f>Statement!Q84</f>
         <v>0</v>
       </c>
@@ -23264,18 +23293,18 @@
       <c r="N8" s="92"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="269" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
+      <c r="D9" s="269"/>
+      <c r="E9" s="269"/>
+      <c r="F9" s="269"/>
+      <c r="G9" s="269"/>
+      <c r="H9" s="269"/>
+      <c r="I9" s="269"/>
+      <c r="J9" s="269"/>
+      <c r="K9" s="269"/>
+      <c r="L9" s="269"/>
       <c r="N9" s="92"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -23396,18 +23425,18 @@
       <c r="N13" s="92"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="267" t="s">
-        <v>431</v>
-      </c>
-      <c r="D14" s="267"/>
-      <c r="E14" s="267"/>
-      <c r="F14" s="267"/>
-      <c r="G14" s="267"/>
-      <c r="H14" s="267"/>
-      <c r="I14" s="267"/>
-      <c r="J14" s="267"/>
-      <c r="K14" s="267"/>
-      <c r="L14" s="267"/>
+      <c r="C14" s="269" t="s">
+        <v>430</v>
+      </c>
+      <c r="D14" s="269"/>
+      <c r="E14" s="269"/>
+      <c r="F14" s="269"/>
+      <c r="G14" s="269"/>
+      <c r="H14" s="269"/>
+      <c r="I14" s="269"/>
+      <c r="J14" s="269"/>
+      <c r="K14" s="269"/>
+      <c r="L14" s="269"/>
       <c r="N14" s="92"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -23458,7 +23487,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C16" s="96">
         <f>C7/C6</f>
@@ -23497,15 +23526,15 @@
       <c r="N19" s="92"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="261" t="s">
-        <v>433</v>
-      </c>
-      <c r="C20" s="261"/>
+      <c r="B20" s="263" t="s">
+        <v>432</v>
+      </c>
+      <c r="C20" s="263"/>
       <c r="N20" s="92"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C21" s="109">
         <f>G7</f>
@@ -23514,7 +23543,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C22" s="248">
         <v>0</v>
@@ -23522,7 +23551,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B23" s="39" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C23" s="234">
         <f>C21*(1+C22)</f>
@@ -23540,7 +23569,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B25" s="39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C25" s="248">
         <v>0</v>
@@ -23557,12 +23586,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C9:L9"/>
     <mergeCell ref="C14:L14"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23601,60 +23630,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="263" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271" t="s">
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="272"/>
+      <c r="H3" s="273" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="P3" s="274"/>
+      <c r="Q3" s="274"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="274"/>
+      <c r="T3" s="274"/>
+      <c r="U3" s="274"/>
+      <c r="V3" s="274"/>
+      <c r="W3" s="274"/>
+      <c r="X3" s="274"/>
+      <c r="Y3" s="274"/>
+      <c r="Z3" s="274"/>
       <c r="AB3" s="113"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="267" t="s">
+      <c r="C5" s="269" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="267"/>
-      <c r="K5" s="267"/>
-      <c r="L5" s="267"/>
-      <c r="P5" s="272"/>
-      <c r="Q5" s="272"/>
-      <c r="R5" s="272"/>
-      <c r="S5" s="272"/>
-      <c r="T5" s="272"/>
-      <c r="U5" s="272"/>
-      <c r="V5" s="272"/>
-      <c r="W5" s="272"/>
-      <c r="X5" s="272"/>
-      <c r="Y5" s="272"/>
-      <c r="Z5" s="272"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="269"/>
+      <c r="F5" s="269"/>
+      <c r="G5" s="269"/>
+      <c r="H5" s="269"/>
+      <c r="I5" s="269"/>
+      <c r="J5" s="269"/>
+      <c r="K5" s="269"/>
+      <c r="L5" s="269"/>
+      <c r="P5" s="274"/>
+      <c r="Q5" s="274"/>
+      <c r="R5" s="274"/>
+      <c r="S5" s="274"/>
+      <c r="T5" s="274"/>
+      <c r="U5" s="274"/>
+      <c r="V5" s="274"/>
+      <c r="W5" s="274"/>
+      <c r="X5" s="274"/>
+      <c r="Y5" s="274"/>
+      <c r="Z5" s="274"/>
       <c r="AB5" s="114"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23882,10 +23911,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="273" t="s">
+      <c r="B14" s="275" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="274"/>
+      <c r="C14" s="276"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="159" t="s">
@@ -23893,7 +23922,7 @@
       </c>
       <c r="C15" s="160">
         <f ca="1">Overview!C5</f>
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23912,20 +23941,20 @@
       <c r="C17" s="162">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E17" s="275" t="s">
+      <c r="E17" s="277" t="s">
         <v>240</v>
       </c>
-      <c r="F17" s="275"/>
-      <c r="G17" s="275"/>
-      <c r="H17" s="275"/>
-      <c r="I17" s="275"/>
+      <c r="F17" s="277"/>
+      <c r="G17" s="277"/>
+      <c r="H17" s="277"/>
+      <c r="I17" s="277"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="273" t="s">
+      <c r="B19" s="275" t="s">
         <v>198</v>
       </c>
-      <c r="C19" s="274"/>
+      <c r="C19" s="276"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="163" t="s">
@@ -23959,7 +23988,7 @@
       </c>
       <c r="C23" s="165">
         <f ca="1">C15*C22</f>
-        <v>662624.64</v>
+        <v>660770.27999999991</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23986,15 +24015,15 @@
       </c>
       <c r="C26" s="166">
         <f ca="1">C23+C25-C24</f>
-        <v>678522.64</v>
+        <v>676668.27999999991</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="273" t="s">
+      <c r="B28" s="275" t="s">
         <v>200</v>
       </c>
-      <c r="C28" s="274"/>
+      <c r="C28" s="276"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="163" t="s">
@@ -24069,18 +24098,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="267" t="s">
+      <c r="C39" s="269" t="s">
         <v>243</v>
       </c>
-      <c r="D39" s="267"/>
-      <c r="E39" s="267"/>
-      <c r="F39" s="267"/>
-      <c r="G39" s="267"/>
-      <c r="H39" s="267"/>
-      <c r="I39" s="267"/>
-      <c r="J39" s="267"/>
-      <c r="K39" s="267"/>
-      <c r="L39" s="267"/>
+      <c r="D39" s="269"/>
+      <c r="E39" s="269"/>
+      <c r="F39" s="269"/>
+      <c r="G39" s="269"/>
+      <c r="H39" s="269"/>
+      <c r="I39" s="269"/>
+      <c r="J39" s="269"/>
+      <c r="K39" s="269"/>
+      <c r="L39" s="269"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -24607,7 +24636,7 @@
         <v>86</v>
       </c>
       <c r="AA2" s="207" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -24657,7 +24686,7 @@
         <v>91</v>
       </c>
       <c r="AA3" s="207" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="59" t="s">
@@ -31452,17 +31481,33 @@
       <c r="Q120" s="26">
         <v>13.43</v>
       </c>
-      <c r="T120" s="68"/>
-      <c r="U120" s="68"/>
-      <c r="V120" s="68"/>
-      <c r="W120" s="68"/>
-      <c r="X120" s="68"/>
-      <c r="Y120" s="68"/>
-      <c r="Z120" s="68"/>
-      <c r="AA120" s="68"/>
+      <c r="T120" s="26">
+        <v>24.97</v>
+      </c>
+      <c r="U120" s="26">
+        <v>18.29</v>
+      </c>
+      <c r="V120" s="26">
+        <v>29</v>
+      </c>
+      <c r="W120" s="26">
+        <v>24.96</v>
+      </c>
+      <c r="X120" s="26">
+        <v>26.96</v>
+      </c>
+      <c r="Y120" s="26">
+        <v>22.64</v>
+      </c>
+      <c r="Z120" s="26">
+        <v>13.43</v>
+      </c>
+      <c r="AA120" s="26">
+        <v>9.2100000000000009</v>
+      </c>
       <c r="AC120" s="63">
         <f ca="1">Overview!C5</f>
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
@@ -31499,17 +31544,41 @@
         <f>Q120/Q87</f>
         <v>13.43</v>
       </c>
-      <c r="T121" s="68"/>
-      <c r="U121" s="68"/>
-      <c r="V121" s="68"/>
-      <c r="W121" s="68"/>
-      <c r="X121" s="68"/>
-      <c r="Y121" s="68"/>
-      <c r="Z121" s="68"/>
-      <c r="AA121" s="68"/>
+      <c r="T121" s="65">
+        <f t="shared" ref="T121:AA121" si="114">T120/T87</f>
+        <v>24.97</v>
+      </c>
+      <c r="U121" s="65">
+        <f t="shared" si="114"/>
+        <v>18.29</v>
+      </c>
+      <c r="V121" s="65">
+        <f t="shared" si="114"/>
+        <v>29</v>
+      </c>
+      <c r="W121" s="65">
+        <f t="shared" si="114"/>
+        <v>24.96</v>
+      </c>
+      <c r="X121" s="65">
+        <f t="shared" si="114"/>
+        <v>26.96</v>
+      </c>
+      <c r="Y121" s="65">
+        <f t="shared" si="114"/>
+        <v>22.64</v>
+      </c>
+      <c r="Z121" s="65">
+        <f t="shared" si="114"/>
+        <v>13.43</v>
+      </c>
+      <c r="AA121" s="65">
+        <f t="shared" si="114"/>
+        <v>9.2100000000000009</v>
+      </c>
       <c r="AC121" s="65">
         <f ca="1">AC120/AC87</f>
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -31623,19 +31692,19 @@
         <v>114</v>
       </c>
       <c r="M127" s="76">
-        <f t="shared" ref="M127:P127" si="114">M125*M126</f>
+        <f t="shared" ref="M127:P127" si="115">M125*M126</f>
         <v>-0.23896205275888008</v>
       </c>
       <c r="N127" s="76">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.47599694101179013</v>
       </c>
       <c r="O127" s="76">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.36963378212709885</v>
       </c>
       <c r="P127" s="76">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>-0.15068161631244933</v>
       </c>
       <c r="Q127" s="76">
@@ -31697,19 +31766,19 @@
         <v>116</v>
       </c>
       <c r="M129" s="76">
-        <f t="shared" ref="M129:P129" si="115">M127*M128</f>
+        <f t="shared" ref="M129:P129" si="116">M127*M128</f>
         <v>-0.28316957438650303</v>
       </c>
       <c r="N129" s="76">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-0.61200268224126975</v>
       </c>
       <c r="O129" s="76">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-0.54438474601211384</v>
       </c>
       <c r="P129" s="76">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>-0.22101673665448177</v>
       </c>
       <c r="Q129" s="76">
@@ -31839,35 +31908,35 @@
       <c r="P135" s="49"/>
       <c r="Q135" s="49"/>
       <c r="T135" s="25">
-        <f t="shared" ref="T135" si="116">U5</f>
+        <f t="shared" ref="T135" si="117">U5</f>
         <v>106800</v>
       </c>
       <c r="U135" s="25">
-        <f t="shared" ref="U135" si="117">V5</f>
+        <f t="shared" ref="U135" si="118">V5</f>
         <v>109681</v>
       </c>
       <c r="V135" s="25">
-        <f t="shared" ref="V135" si="118">W5</f>
+        <f t="shared" ref="V135" si="119">W5</f>
         <v>115936</v>
       </c>
       <c r="W135" s="25">
-        <f t="shared" ref="W135" si="119">X5</f>
+        <f t="shared" ref="W135" si="120">X5</f>
         <v>117255</v>
       </c>
       <c r="X135" s="25">
-        <f t="shared" ref="X135" si="120">Y5</f>
+        <f t="shared" ref="X135" si="121">Y5</f>
         <v>120333</v>
       </c>
       <c r="Y135" s="25">
-        <f t="shared" ref="Y135" si="121">Z5</f>
+        <f t="shared" ref="Y135" si="122">Z5</f>
         <v>127067</v>
       </c>
       <c r="Z135" s="25">
-        <f t="shared" ref="Z135" si="122">AA5</f>
+        <f t="shared" ref="Z135" si="123">AA5</f>
         <v>130935</v>
       </c>
       <c r="AA135" s="25">
-        <f t="shared" ref="AA135" si="123">AB5</f>
+        <f t="shared" ref="AA135" si="124">AB5</f>
         <v>0</v>
       </c>
       <c r="AC135" s="49"/>
@@ -31892,27 +31961,27 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="229" t="str">
-        <f t="shared" ref="T136:Y136" si="124">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Y136" si="125">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U136" s="229" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>BEAT</v>
       </c>
       <c r="V136" s="229" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>BEAT</v>
       </c>
       <c r="W136" s="229" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>BEAT</v>
       </c>
       <c r="X136" s="229" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>BEAT</v>
       </c>
       <c r="Y136" s="229" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>BEAT</v>
       </c>
       <c r="Z136" s="229" t="str">
@@ -32009,55 +32078,55 @@
         <v>153</v>
       </c>
       <c r="M141" s="122">
-        <f t="shared" ref="M141:Q142" si="125">M32/M5*365</f>
+        <f t="shared" ref="M141:Q142" si="126">M32/M5*365</f>
         <v>68.918178705922628</v>
       </c>
       <c r="N141" s="122">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>66.778719162721146</v>
       </c>
       <c r="O141" s="122">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>66.446986940743585</v>
       </c>
       <c r="P141" s="122">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>64.005176114127011</v>
       </c>
       <c r="Q141" s="122">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>74.013755979616761</v>
       </c>
       <c r="T141" s="122">
-        <f t="shared" ref="T141:Z141" si="126">T32/T5*90</f>
+        <f t="shared" ref="T141:Z141" si="127">T32/T5*90</f>
         <v>54.004406796259126</v>
       </c>
       <c r="U141" s="122">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>60.175280898876402</v>
       </c>
       <c r="V141" s="122">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>60.40727199788477</v>
       </c>
       <c r="W141" s="122">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>58.298630278774496</v>
       </c>
       <c r="X141" s="122">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>58.980683126519118</v>
       </c>
       <c r="Y141" s="122">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>66.009573433721428</v>
       </c>
       <c r="Z141" s="122">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>69.024766461787877</v>
       </c>
       <c r="AA141" s="122">
-        <f t="shared" ref="AA141" si="127">AA32/AA5*90</f>
+        <f t="shared" ref="AA141" si="128">AA32/AA5*90</f>
         <v>61.592622293504412</v>
       </c>
       <c r="AC141" s="122">
@@ -32070,55 +32139,55 @@
         <v>154</v>
       </c>
       <c r="M142" s="122">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="N142" s="122">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="O142" s="122">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="P142" s="122">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="Q142" s="122">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="T142" s="122">
-        <f t="shared" ref="T142:Z142" si="128">T33/T6*365</f>
+        <f t="shared" ref="T142:Z142" si="129">T33/T6*365</f>
         <v>0</v>
       </c>
       <c r="U142" s="122">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="V142" s="122">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="W142" s="122">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="X142" s="122">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="Y142" s="122">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="Z142" s="122">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="AA142" s="122">
-        <f t="shared" ref="AA142" si="129">AA33/AA6*365</f>
+        <f t="shared" ref="AA142" si="130">AA33/AA6*365</f>
         <v>0</v>
       </c>
       <c r="AC142" s="122">
@@ -32151,35 +32220,35 @@
         <v>27.180271601253548</v>
       </c>
       <c r="T143" s="122">
-        <f t="shared" ref="T143:Z143" si="130">T40/T6*90</f>
+        <f t="shared" ref="T143:Z143" si="131">T40/T6*90</f>
         <v>19.135046173539362</v>
       </c>
       <c r="U143" s="122">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>41.355647566378089</v>
       </c>
       <c r="V143" s="122">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>15.074182208186855</v>
       </c>
       <c r="W143" s="122">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>7.5754630237751215</v>
       </c>
       <c r="X143" s="122">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>15.606120985096039</v>
       </c>
       <c r="Y143" s="122">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>14.716385725931575</v>
       </c>
       <c r="Z143" s="122">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>25.573904431790048</v>
       </c>
       <c r="AA143" s="122">
-        <f t="shared" ref="AA143" si="131">AA40/AA6*90</f>
+        <f t="shared" ref="AA143" si="132">AA40/AA6*90</f>
         <v>24.696312364425165</v>
       </c>
       <c r="AC143" s="122">
@@ -32196,55 +32265,55 @@
         <v>45.961047433499175</v>
       </c>
       <c r="N144" s="122">
-        <f t="shared" ref="N144:Q144" si="132">N141+N142-N143</f>
+        <f t="shared" ref="N144:Q144" si="133">N141+N142-N143</f>
         <v>30.581697189023693</v>
       </c>
       <c r="O144" s="122">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>41.487910729762298</v>
       </c>
       <c r="P144" s="122">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>48.797519037333913</v>
       </c>
       <c r="Q144" s="122">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>46.83348437836321</v>
       </c>
       <c r="T144" s="122">
-        <f t="shared" ref="T144" si="133">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="134">T141+T142-T143</f>
         <v>34.869360622719768</v>
       </c>
       <c r="U144" s="122">
-        <f t="shared" ref="U144" si="134">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="135">U141+U142-U143</f>
         <v>18.819633332498313</v>
       </c>
       <c r="V144" s="122">
-        <f t="shared" ref="V144" si="135">V141+V142-V143</f>
+        <f t="shared" ref="V144" si="136">V141+V142-V143</f>
         <v>45.333089789697915</v>
       </c>
       <c r="W144" s="122">
-        <f t="shared" ref="W144" si="136">W141+W142-W143</f>
+        <f t="shared" ref="W144" si="137">W141+W142-W143</f>
         <v>50.723167254999375</v>
       </c>
       <c r="X144" s="122">
-        <f t="shared" ref="X144:Z144" si="137">X141+X142-X143</f>
+        <f t="shared" ref="X144:Z144" si="138">X141+X142-X143</f>
         <v>43.374562141423077</v>
       </c>
       <c r="Y144" s="122">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>51.293187707789855</v>
       </c>
       <c r="Z144" s="122">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>43.450862029997829</v>
       </c>
       <c r="AA144" s="122">
-        <f t="shared" ref="AA144" si="138">AA141+AA142-AA143</f>
+        <f t="shared" ref="AA144" si="139">AA141+AA142-AA143</f>
         <v>36.896309929079251</v>
       </c>
       <c r="AC144" s="122">
-        <f t="shared" ref="AC144" si="139">AC141+AC142-AC143</f>
+        <f t="shared" ref="AC144" si="140">AC141+AC142-AC143</f>
         <v>38.76537049942003</v>
       </c>
     </row>
@@ -32273,35 +32342,35 @@
         <v>0.29681471618323463</v>
       </c>
       <c r="T145" s="122">
-        <f t="shared" ref="T145:Z145" si="140">T112/T51</f>
+        <f t="shared" ref="T145:Z145" si="141">T112/T51</f>
         <v>5.748502994011976E-2</v>
       </c>
       <c r="U145" s="122">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>7.5249811463046754E-2</v>
       </c>
       <c r="V145" s="122">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>6.1149965257847196E-2</v>
       </c>
       <c r="W145" s="122">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>5.1419985399700906E-2</v>
       </c>
       <c r="X145" s="122">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>3.9169493971213512E-2</v>
       </c>
       <c r="Y145" s="122">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>2.9819341989017541E-2</v>
       </c>
       <c r="Z145" s="122">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.29681471618323463</v>
       </c>
       <c r="AA145" s="122">
-        <f t="shared" ref="AA145" si="141">AA112/AA51</f>
+        <f t="shared" ref="AA145" si="142">AA112/AA51</f>
         <v>0.25231557548246958</v>
       </c>
       <c r="AC145" s="122">
@@ -32334,35 +32403,35 @@
         <v>7.7869083382017576E-2</v>
       </c>
       <c r="T146" s="183">
-        <f t="shared" ref="T146:Z146" si="142">(T112-T111)/T51</f>
+        <f t="shared" ref="T146:Z146" si="143">(T112-T111)/T51</f>
         <v>-0.26796904529810811</v>
       </c>
       <c r="U146" s="183">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-0.24581290849673201</v>
       </c>
       <c r="V146" s="183">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-0.25689178574665417</v>
       </c>
       <c r="W146" s="183">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-0.2706052036599973</v>
       </c>
       <c r="X146" s="183">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-0.29059656964901154</v>
       </c>
       <c r="Y146" s="183">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>-0.30224862563177235</v>
       </c>
       <c r="Z146" s="183">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>7.7869083382017576E-2</v>
       </c>
       <c r="AA146" s="183">
-        <f t="shared" ref="AA146" si="143">(AA112-AA111)/AA51</f>
+        <f t="shared" ref="AA146" si="144">(AA112-AA111)/AA51</f>
         <v>4.4273023476008803E-2</v>
       </c>
       <c r="AC146" s="183">
@@ -32395,35 +32464,35 @@
         <v>0.93474167899105554</v>
       </c>
       <c r="T147" s="122">
-        <f t="shared" ref="T147:Z147" si="144">(T111+T32)/T42</f>
+        <f t="shared" ref="T147:Z147" si="145">(T111+T32)/T42</f>
         <v>1.4026804184354749</v>
       </c>
       <c r="U147" s="122">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>1.4024413695845277</v>
       </c>
       <c r="V147" s="122">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>1.3842558080387291</v>
       </c>
       <c r="W147" s="122">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>1.4990065028901733</v>
       </c>
       <c r="X147" s="122">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>1.6655538117658248</v>
       </c>
       <c r="Y147" s="122">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>1.9702580403510725</v>
       </c>
       <c r="Z147" s="122">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.93474167899105554</v>
       </c>
       <c r="AA147" s="122">
-        <f t="shared" ref="AA147" si="145">(AA111+AA32)/AA42</f>
+        <f t="shared" ref="AA147" si="146">(AA111+AA32)/AA42</f>
         <v>1.0802319389385244</v>
       </c>
       <c r="AC147" s="122">
@@ -32456,35 +32525,35 @@
         <v>1.527185509793114</v>
       </c>
       <c r="T148" s="122">
-        <f t="shared" ref="T148:Z148" si="146">T34/T42</f>
+        <f t="shared" ref="T148:Z148" si="147">T34/T42</f>
         <v>1.7738213119736468</v>
       </c>
       <c r="U148" s="122">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>1.736000586075219</v>
       </c>
       <c r="V148" s="122">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>1.7828420581812441</v>
       </c>
       <c r="W148" s="122">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>1.9455292630057803</v>
       </c>
       <c r="X148" s="122">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>2.1176677604984069</v>
       </c>
       <c r="Y148" s="122">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>2.4387394592186915</v>
       </c>
       <c r="Z148" s="122">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>1.527185509793114</v>
       </c>
       <c r="AA148" s="122">
-        <f t="shared" ref="AA148" si="147">AA34/AA42</f>
+        <f t="shared" ref="AA148" si="148">AA34/AA42</f>
         <v>1.7569703304866904</v>
       </c>
       <c r="AC148" s="122">
@@ -32517,35 +32586,35 @@
         <v>N/A</v>
       </c>
       <c r="T149" s="185" t="str">
-        <f t="shared" ref="T149:Z149" si="148">IF(T15&gt;=0,"N/A",IF(T14&lt;=0,"N/A",T14/-T15))</f>
+        <f t="shared" ref="T149:Z149" si="149">IF(T15&gt;=0,"N/A",IF(T14&lt;=0,"N/A",T14/-T15))</f>
         <v>N/A</v>
       </c>
       <c r="U149" s="185" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>N/A</v>
       </c>
       <c r="V149" s="185" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>N/A</v>
       </c>
       <c r="W149" s="185" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>N/A</v>
       </c>
       <c r="X149" s="185" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>N/A</v>
       </c>
       <c r="Y149" s="185" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>N/A</v>
       </c>
       <c r="Z149" s="185" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>N/A</v>
       </c>
       <c r="AA149" s="185">
-        <f t="shared" ref="AA149" si="149">IF(AA15&gt;=0,"N/A",IF(AA14&lt;=0,"N/A",AA14/-AA15))</f>
+        <f t="shared" ref="AA149" si="150">IF(AA15&gt;=0,"N/A",IF(AA14&lt;=0,"N/A",AA14/-AA15))</f>
         <v>3.3711288711288709</v>
       </c>
       <c r="AC149" s="185">
@@ -32587,7 +32656,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC121/Statement!AC28</f>
-        <v>-283.13462950794326</v>
+        <v>-282.34227513432023</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -32624,7 +32693,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC121/(Statement!AC5/Statement!AC24)</f>
-        <v>1.3345328194677051</v>
+        <v>1.3307981194132243</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -32651,17 +32720,41 @@
         <f>Q121/(Statement!Q51/Statement!Q77)</f>
         <v>2.4200182380555564</v>
       </c>
-      <c r="T152" s="49"/>
-      <c r="U152" s="49"/>
-      <c r="V152" s="49"/>
-      <c r="W152" s="49"/>
-      <c r="X152" s="49"/>
-      <c r="Y152" s="49"/>
-      <c r="Z152" s="49"/>
-      <c r="AA152" s="49"/>
+      <c r="T152" s="72">
+        <f>T121/(Statement!T51/Statement!T77)</f>
+        <v>5.7397171504167739</v>
+      </c>
+      <c r="U152" s="72">
+        <f>U121/(Statement!U51/Statement!U77)</f>
+        <v>4.1756534376571146</v>
+      </c>
+      <c r="V152" s="72">
+        <f>V121/(Statement!V51/Statement!V77)</f>
+        <v>6.4363161233799575</v>
+      </c>
+      <c r="W152" s="72">
+        <f>W121/(Statement!W51/Statement!W77)</f>
+        <v>5.2632655057302635</v>
+      </c>
+      <c r="X152" s="72">
+        <f>X121/(Statement!X51/Statement!X77)</f>
+        <v>5.4206439878249721</v>
+      </c>
+      <c r="Y152" s="72">
+        <f>Y121/(Statement!Y51/Statement!Y77)</f>
+        <v>4.2609244870117911</v>
+      </c>
+      <c r="Z152" s="72">
+        <f>Z121/(Statement!Z51/Statement!Z77)</f>
+        <v>2.4200182380555564</v>
+      </c>
+      <c r="AA152" s="72">
+        <f>AA121/(Statement!AA51/Statement!AA77)</f>
+        <v>1.5853644490239216</v>
+      </c>
       <c r="AC152" s="72">
         <f ca="1">AC121/(Statement!AC51/Statement!AC77)</f>
-        <v>1.8452884792113398</v>
+        <v>1.8401244256314571</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -32688,17 +32781,41 @@
         <f>Statement!Q121*Statement!Q80</f>
         <v>839630.16999999993</v>
       </c>
-      <c r="T153" s="49"/>
-      <c r="U153" s="49"/>
-      <c r="V153" s="49"/>
-      <c r="W153" s="49"/>
-      <c r="X153" s="49"/>
-      <c r="Y153" s="49"/>
-      <c r="Z153" s="49"/>
-      <c r="AA153" s="49"/>
+      <c r="T153" s="147">
+        <f>Statement!T121*Statement!T80</f>
+        <v>1442591.8099999998</v>
+      </c>
+      <c r="U153" s="147">
+        <f>Statement!U121*Statement!U80</f>
+        <v>1063087.96</v>
+      </c>
+      <c r="V153" s="147">
+        <f>Statement!V121*Statement!V80</f>
+        <v>1704388</v>
+      </c>
+      <c r="W153" s="147">
+        <f>Statement!W121*Statement!W80</f>
+        <v>1485219.8400000001</v>
+      </c>
+      <c r="X153" s="147">
+        <f>Statement!X121*Statement!X80</f>
+        <v>1671735.6800000002</v>
+      </c>
+      <c r="Y153" s="147">
+        <f>Statement!Y121*Statement!Y80</f>
+        <v>1400012.32</v>
+      </c>
+      <c r="Z153" s="147">
+        <f>Statement!Z121*Statement!Z80</f>
+        <v>839630.16999999993</v>
+      </c>
+      <c r="AA153" s="147">
+        <f>Statement!AA121*Statement!AA80</f>
+        <v>579382.68000000005</v>
+      </c>
       <c r="AC153" s="147">
         <f ca="1">Statement!AC121*Statement!AC80</f>
-        <v>674373.76</v>
+        <v>672486.52</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -32725,17 +32842,41 @@
         <f>Q153+Q112-Q111+Q50+Q47</f>
         <v>865888.16999999993</v>
       </c>
-      <c r="T154" s="49"/>
-      <c r="U154" s="49"/>
-      <c r="V154" s="49"/>
-      <c r="W154" s="49"/>
-      <c r="X154" s="49"/>
-      <c r="Y154" s="49"/>
-      <c r="Z154" s="49"/>
-      <c r="AA154" s="49"/>
+      <c r="T154" s="147">
+        <f t="shared" ref="T154:AA154" si="151">T153+T112-T111+T50+T47</f>
+        <v>1375241.8099999998</v>
+      </c>
+      <c r="U154" s="147">
+        <f t="shared" si="151"/>
+        <v>1000505.96</v>
+      </c>
+      <c r="V154" s="147">
+        <f t="shared" si="151"/>
+        <v>1636361</v>
+      </c>
+      <c r="W154" s="147">
+        <f t="shared" si="151"/>
+        <v>1408858.84</v>
+      </c>
+      <c r="X154" s="147">
+        <f t="shared" si="151"/>
+        <v>1585141.6800000002</v>
+      </c>
+      <c r="Y154" s="147">
+        <f t="shared" si="151"/>
+        <v>1303193.32</v>
+      </c>
+      <c r="Z154" s="147">
+        <f t="shared" si="151"/>
+        <v>865888.16999999993</v>
+      </c>
+      <c r="AA154" s="147">
+        <f t="shared" si="151"/>
+        <v>595280.68000000005</v>
+      </c>
       <c r="AC154" s="147">
         <f ca="1">AC153+AC112-AC111+AC50+AC47</f>
-        <v>690271.76</v>
+        <v>688384.52</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -32772,7 +32913,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="187">
         <f ca="1">AC154/AC5</f>
-        <v>1.3928282652999455</v>
+        <v>1.3890201981476624</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -32809,7 +32950,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="187">
         <f ca="1">AC154/AC14</f>
-        <v>201.59806074766357</v>
+        <v>201.04688084112149</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -32837,35 +32978,35 @@
         <v>-13035</v>
       </c>
       <c r="T157" s="64">
-        <f t="shared" ref="T157:Z157" si="150">T61-T56+T114+T67</f>
+        <f t="shared" ref="T157:Z157" si="152">T61-T56+T114+T67</f>
         <v>-12790</v>
       </c>
       <c r="U157" s="64">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>-14922</v>
       </c>
       <c r="V157" s="64">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>-7964</v>
       </c>
       <c r="W157" s="64">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>-9767</v>
       </c>
       <c r="X157" s="64">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>-6597</v>
       </c>
       <c r="Y157" s="64">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>-7158</v>
       </c>
       <c r="Z157" s="64">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>10487</v>
       </c>
       <c r="AA157" s="64">
-        <f t="shared" ref="AA157" si="151">AA61-AA56+AA114+AA67</f>
+        <f t="shared" ref="AA157" si="153">AA61-AA56+AA114+AA67</f>
         <v>2818</v>
       </c>
       <c r="AC157" s="64">
@@ -32919,19 +33060,19 @@
         <v>-10.428876668619713</v>
       </c>
       <c r="N159" s="72">
-        <f t="shared" ref="N159:Q159" si="152">N153/N157</f>
+        <f t="shared" ref="N159:Q159" si="154">N153/N157</f>
         <v>-11.027449586238799</v>
       </c>
       <c r="O159" s="72">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>-11.186718130267725</v>
       </c>
       <c r="P159" s="72">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>-29.04398207317281</v>
       </c>
       <c r="Q159" s="72">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>-64.413515151515142</v>
       </c>
       <c r="T159" s="49"/>
@@ -32943,8 +33084,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="72">
-        <f t="shared" ref="AC159:AC160" ca="1" si="153">AC153/AC157</f>
-        <v>-1498.6083555555556</v>
+        <f t="shared" ref="AC159:AC160" ca="1" si="155">AC153/AC157</f>
+        <v>-1494.4144888888889</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -32956,19 +33097,19 @@
         <v>-8.1218035626781511</v>
       </c>
       <c r="N160" s="72">
-        <f t="shared" ref="N160:Q160" si="154">N154/N158</f>
+        <f t="shared" ref="N160:Q160" si="156">N154/N158</f>
         <v>-9.7187264564592724</v>
       </c>
       <c r="O160" s="72">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>-10.229925893244395</v>
       </c>
       <c r="P160" s="72">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>-26.916931225634531</v>
       </c>
       <c r="Q160" s="72">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>-63.453625238165024</v>
       </c>
       <c r="T160" s="49"/>
@@ -32980,8 +33121,8 @@
       <c r="Z160" s="49"/>
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
-        <f t="shared" ca="1" si="153"/>
-        <v>514.7440417598807</v>
+        <f t="shared" ca="1" si="155"/>
+        <v>513.33670395227443</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32993,19 +33134,19 @@
         <v>-9.5887604367686161E-2</v>
       </c>
       <c r="N161" s="74">
-        <f t="shared" ref="N161:Q161" si="155">N157/N153</f>
+        <f t="shared" ref="N161:Q161" si="157">N157/N153</f>
         <v>-9.0682799515846735E-2</v>
       </c>
       <c r="O161" s="74">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-8.9391722250900016E-2</v>
       </c>
       <c r="P161" s="74">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-3.4430540463791105E-2</v>
       </c>
       <c r="Q161" s="74">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-1.5524692258259374E-2</v>
       </c>
       <c r="T161" s="49"/>
@@ -33017,8 +33158,8 @@
       <c r="Z161" s="49"/>
       <c r="AA161" s="49"/>
       <c r="AC161" s="74">
-        <f t="shared" ref="AC161" ca="1" si="156">AC157/AC153</f>
-        <v>-6.6728574967092429E-4</v>
+        <f t="shared" ref="AC161" ca="1" si="158">AC157/AC153</f>
+        <v>-6.6915839443146014E-4</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -33055,7 +33196,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f ca="1">AC28/AC121</f>
-        <v>-3.5318887051643583E-3</v>
+        <v>-3.5418004601835292E-3</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -33416,35 +33557,35 @@
         <v>1.2150486315685531</v>
       </c>
       <c r="T172" s="72">
-        <f t="shared" ref="T172:Z172" si="157">T111/T77</f>
+        <f t="shared" ref="T172:Z172" si="159">T111/T77</f>
         <v>1.4158516954286604</v>
       </c>
       <c r="U172" s="72">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>1.4063037643658385</v>
       </c>
       <c r="V172" s="72">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>1.4329953038862042</v>
       </c>
       <c r="W172" s="72">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>1.5271410325356278</v>
       </c>
       <c r="X172" s="72">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>1.640117501752512</v>
       </c>
       <c r="Y172" s="72">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>1.7644102376963524</v>
       </c>
       <c r="Z172" s="72">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>1.2150486315685531</v>
       </c>
       <c r="AA172" s="72">
-        <f t="shared" ref="AA172" si="158">AA111/AA77</f>
+        <f t="shared" ref="AA172" si="160">AA111/AA77</f>
         <v>1.2086002717918851</v>
       </c>
       <c r="AC172" s="72">
@@ -33477,35 +33618,35 @@
         <v>0.85583779531555304</v>
       </c>
       <c r="T173" s="158">
-        <f t="shared" ref="T173:Z173" si="159">T56/T61</f>
+        <f t="shared" ref="T173:Z173" si="161">T56/T61</f>
         <v>1.4870264894674985</v>
       </c>
       <c r="U173" s="158">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>2.856525496974935</v>
       </c>
       <c r="V173" s="158">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>1.0557332677165354</v>
       </c>
       <c r="W173" s="158">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>1.15993265993266</v>
       </c>
       <c r="X173" s="158">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>1.0940343781597572</v>
       </c>
       <c r="Y173" s="158">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>1.0318096592745847</v>
       </c>
       <c r="Z173" s="158">
-        <f t="shared" si="159"/>
+        <f t="shared" si="161"/>
         <v>0.53585645535024662</v>
       </c>
       <c r="AA173" s="158">
-        <f t="shared" ref="AA173" si="160">AA56/AA61</f>
+        <f t="shared" ref="AA173" si="162">AA56/AA61</f>
         <v>0.56659142212189617</v>
       </c>
       <c r="AC173" s="158">
@@ -33538,35 +33679,35 @@
         <v>0.14035219136438259</v>
       </c>
       <c r="T174" s="158">
-        <f t="shared" ref="T174:Z174" si="161">T56/T5</f>
+        <f t="shared" ref="T174:Z174" si="163">T56/T5</f>
         <v>0.16107329971111004</v>
       </c>
       <c r="U174" s="158">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>0.15472846441947566</v>
       </c>
       <c r="V174" s="158">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>0.15647195047455803</v>
       </c>
       <c r="W174" s="158">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>0.14857335081424233</v>
       </c>
       <c r="X174" s="158">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>0.13841627222719713</v>
       </c>
       <c r="Y174" s="158">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>0.13262363607655422</v>
       </c>
       <c r="Z174" s="158">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>0.14195660557028969</v>
       </c>
       <c r="AA174" s="158">
-        <f t="shared" ref="AA174" si="162">AA56/AA5</f>
+        <f t="shared" ref="AA174" si="164">AA56/AA5</f>
         <v>0.10351701225799061</v>
       </c>
       <c r="AC174" s="158">
@@ -33599,35 +33740,35 @@
         <v>-0.43213797870414561</v>
       </c>
       <c r="T175" s="72">
-        <f t="shared" ref="T175:Z175" si="163">(T111-T112)/T77</f>
+        <f t="shared" ref="T175:Z175" si="165">(T111-T112)/T77</f>
         <v>1.1657694770913749</v>
       </c>
       <c r="U175" s="72">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>1.0766980937306447</v>
       </c>
       <c r="V175" s="72">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>1.1574729463009596</v>
       </c>
       <c r="W175" s="72">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>1.2832918795375101</v>
       </c>
       <c r="X175" s="72">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>1.4453049370764763</v>
       </c>
       <c r="Y175" s="72">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>1.6059681191633355</v>
       </c>
       <c r="Z175" s="72">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>-0.43213797870414561</v>
       </c>
       <c r="AA175" s="72">
-        <f t="shared" ref="AA175" si="164">(AA111-AA112)/AA77</f>
+        <f t="shared" ref="AA175" si="166">(AA111-AA112)/AA77</f>
         <v>-0.25719924933669835</v>
       </c>
       <c r="AC175" s="72">
@@ -33669,7 +33810,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="158">
         <f ca="1">(AC111-AC112)/AC153</f>
-        <v>-2.3574464107263011E-2</v>
+        <v>-2.3640622565936339E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33697,35 +33838,35 @@
         <v>5.0764579444891808E-2</v>
       </c>
       <c r="T177" s="158">
-        <f t="shared" ref="T177:Z177" si="165">-T114/T5</f>
+        <f t="shared" ref="T177:Z177" si="167">-T114/T5</f>
         <v>7.2496694902805664E-2</v>
       </c>
       <c r="U177" s="158">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>3.9157303370786517E-2</v>
       </c>
       <c r="V177" s="158">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>6.4350252094711027E-2</v>
       </c>
       <c r="W177" s="158">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>6.3759315484405193E-2</v>
       </c>
       <c r="X177" s="158">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>4.4364845848791093E-2</v>
       </c>
       <c r="Y177" s="158">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>5.5396275335942761E-2</v>
       </c>
       <c r="Z177" s="158">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>4.0427491008680462E-2</v>
       </c>
       <c r="AA177" s="158">
-        <f t="shared" ref="AA177" si="166">-AA114/AA5</f>
+        <f t="shared" ref="AA177" si="168">-AA114/AA5</f>
         <v>5.7662198800931763E-2</v>
       </c>
       <c r="AC177" s="158">
@@ -33758,35 +33899,35 @@
         <v>0.30955160250716879</v>
       </c>
       <c r="T178" s="158">
-        <f t="shared" ref="T178:Z178" si="167">-(T114/T61)</f>
+        <f t="shared" ref="T178:Z178" si="169">-(T114/T61)</f>
         <v>0.66928849109483768</v>
       </c>
       <c r="U178" s="158">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.72290406222990489</v>
       </c>
       <c r="V178" s="158">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.43417814960629919</v>
       </c>
       <c r="W178" s="158">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.49777777777777776</v>
       </c>
       <c r="X178" s="158">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.35065722952477252</v>
       </c>
       <c r="Y178" s="158">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.43098209090321327</v>
       </c>
       <c r="Z178" s="158">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>0.15260531162735427</v>
       </c>
       <c r="AA178" s="158">
-        <f t="shared" ref="AA178" si="168">-(AA114/AA61)</f>
+        <f t="shared" ref="AA178" si="170">-(AA114/AA61)</f>
         <v>0.31560906278739237</v>
       </c>
       <c r="AC178" s="158">
@@ -33819,35 +33960,35 @@
         <v>0.77566527835182653</v>
       </c>
       <c r="T179" s="158">
-        <f t="shared" ref="T179:Z179" si="169">-T114/T55</f>
+        <f t="shared" ref="T179:Z179" si="171">-T114/T55</f>
         <v>1.0136930028755307</v>
       </c>
       <c r="U179" s="158">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>0.59009453929730493</v>
       </c>
       <c r="V179" s="158">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>1.0344423274219552</v>
       </c>
       <c r="W179" s="158">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>1.0747310264611807</v>
       </c>
       <c r="X179" s="158">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>0.70211904440545281</v>
       </c>
       <c r="Y179" s="158">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>0.89141481679593471</v>
       </c>
       <c r="Z179" s="158">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>0.53024360033030549</v>
       </c>
       <c r="AA179" s="158">
-        <f t="shared" ref="AA179" si="170">-AA114/AA55</f>
+        <f t="shared" ref="AA179" si="172">-AA114/AA55</f>
         <v>0.75848904962829011</v>
       </c>
       <c r="AC179" s="158">
@@ -34129,7 +34270,7 @@
         <v>41941</v>
       </c>
       <c r="AC188" s="62">
-        <f t="shared" ref="AC188:AC189" si="171">SUM(X188:AA188)</f>
+        <f t="shared" ref="AC188:AC189" si="173">SUM(X188:AA188)</f>
         <v>133475</v>
       </c>
     </row>
@@ -34187,7 +34328,7 @@
         <v>36273</v>
       </c>
       <c r="AC189" s="62">
-        <f t="shared" si="171"/>
+        <f t="shared" si="173"/>
         <v>144288</v>
       </c>
     </row>
@@ -34252,79 +34393,79 @@
       <c r="K193" s="81"/>
       <c r="L193" s="81"/>
       <c r="M193" s="81">
-        <f t="shared" ref="M193:Q195" si="172">IF(L187=0,
+        <f t="shared" ref="M193:Q195" si="174">IF(L187=0,
 IF(M187=0,0,IF(M187&gt;0,1,-1)),
 (M187-L187)/ABS(L187)
 )</f>
         <v>1</v>
       </c>
       <c r="N193" s="81">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>0.35032560671733987</v>
       </c>
       <c r="O193" s="81">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>0.28269819732506302</v>
       </c>
       <c r="P193" s="81">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>0.18783094368819361</v>
       </c>
       <c r="Q193" s="81">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>0.11679303852221261</v>
       </c>
       <c r="T193" s="81">
-        <f t="shared" ref="T193:T195" si="173">IF(S187=0,
+        <f t="shared" ref="T193:T195" si="175">IF(S187=0,
 IF(T187=0,0,IF(T187&gt;0,1,-1)),
 (T187-S187)/ABS(S187)
 )</f>
         <v>1</v>
       </c>
       <c r="U193" s="81">
-        <f t="shared" ref="U193:U195" si="174">IF(T187=0,
+        <f t="shared" ref="U193:U195" si="176">IF(T187=0,
 IF(U187=0,0,IF(U187&gt;0,1,-1)),
 (U187-T187)/ABS(T187)
 )</f>
         <v>1.5448860363696207E-2</v>
       </c>
       <c r="V193" s="81">
-        <f t="shared" ref="V193:V195" si="175">IF(U187=0,
+        <f t="shared" ref="V193:V195" si="177">IF(U187=0,
 IF(V187=0,0,IF(V187&gt;0,1,-1)),
 (V187-U187)/ABS(U187)
 )</f>
         <v>4.9227153941211028E-2</v>
       </c>
       <c r="W193" s="81">
-        <f t="shared" ref="W193:W195" si="176">IF(V187=0,
+        <f t="shared" ref="W193:W195" si="178">IF(V187=0,
 IF(W187=0,0,IF(W187&gt;0,1,-1)),
 (W187-V187)/ABS(V187)
 )</f>
         <v>4.9466144073523448E-2</v>
       </c>
       <c r="X193" s="81">
-        <f t="shared" ref="X193:X195" si="177">IF(W187=0,
+        <f t="shared" ref="X193:X195" si="179">IF(W187=0,
 IF(X187=0,0,IF(X187&gt;0,1,-1)),
 (X187-W187)/ABS(W187)
 )</f>
         <v>-1.2013614202925214E-2</v>
       </c>
       <c r="Y193" s="81">
-        <f t="shared" ref="Y193:Y195" si="178">IF(X187=0,
+        <f t="shared" ref="Y193:Y195" si="180">IF(X187=0,
 IF(Y187=0,0,IF(Y187&gt;0,1,-1)),
 (Y187-X187)/ABS(X187)
 )</f>
         <v>3.310863654984917E-2</v>
       </c>
       <c r="Z193" s="81">
-        <f t="shared" ref="Z193:Z195" si="179">IF(Y187=0,
+        <f t="shared" ref="Z193:Z195" si="181">IF(Y187=0,
 IF(Z187=0,0,IF(Z187&gt;0,1,-1)),
 (Z187-Y187)/ABS(Y187)
 )</f>
         <v>8.0028839221341023E-3</v>
       </c>
       <c r="AA193" s="81">
-        <f t="shared" ref="AA193:AA195" si="180">IF(Z187=0,
+        <f t="shared" ref="AA193:AA195" si="182">IF(Z187=0,
 IF(AA187=0,0,IF(AA187&gt;0,1,-1)),
 (AA187-Z187)/ABS(Z187)
 )</f>
@@ -34334,118 +34475,118 @@
     </row>
     <row r="194" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B194" s="20" t="str">
-        <f t="shared" ref="B194:B195" si="181">B188</f>
+        <f t="shared" ref="B194:B195" si="183">B188</f>
         <v>Payment solutions</v>
       </c>
       <c r="M194" s="81">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>1</v>
       </c>
       <c r="N194" s="81">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>0.20194475544853607</v>
       </c>
       <c r="O194" s="81">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>0.20725296039199673</v>
       </c>
       <c r="P194" s="81">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>7.5362012472254519E-2</v>
       </c>
       <c r="Q194" s="81">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>0.19381757420876744</v>
       </c>
       <c r="T194" s="81">
-        <f t="shared" si="173"/>
+        <f t="shared" si="175"/>
         <v>1</v>
       </c>
       <c r="U194" s="81">
-        <f t="shared" si="174"/>
+        <f t="shared" si="176"/>
         <v>-2.3557312252964428E-2</v>
       </c>
       <c r="V194" s="81">
-        <f t="shared" si="175"/>
+        <f t="shared" si="177"/>
         <v>-1.1334196891191709E-3</v>
       </c>
       <c r="W194" s="81">
-        <f t="shared" si="176"/>
+        <f t="shared" si="178"/>
         <v>0.21271680985573027</v>
       </c>
       <c r="X194" s="81">
-        <f t="shared" si="177"/>
+        <f t="shared" si="179"/>
         <v>-5.1228070175438595E-2</v>
       </c>
       <c r="Y194" s="81">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>-3.4164553395322629E-2</v>
       </c>
       <c r="Z194" s="81">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>0.30260374881482022</v>
       </c>
       <c r="AA194" s="81">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.17416013437849945</v>
       </c>
       <c r="AC194" s="49"/>
     </row>
     <row r="195" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B195" s="20" t="str">
+        <f t="shared" si="183"/>
+        <v>Network solutions</v>
+      </c>
+      <c r="M195" s="81">
+        <f t="shared" si="174"/>
+        <v>1</v>
+      </c>
+      <c r="N195" s="81">
+        <f t="shared" si="174"/>
+        <v>0.40079591759015959</v>
+      </c>
+      <c r="O195" s="81">
+        <f t="shared" si="174"/>
+        <v>0.30837196025391822</v>
+      </c>
+      <c r="P195" s="81">
+        <f t="shared" si="174"/>
+        <v>0.26295284302826927</v>
+      </c>
+      <c r="Q195" s="81">
+        <f t="shared" si="174"/>
+        <v>0.14895979862293626</v>
+      </c>
+      <c r="T195" s="81">
+        <f t="shared" si="175"/>
+        <v>1</v>
+      </c>
+      <c r="U195" s="81">
+        <f t="shared" si="176"/>
+        <v>0.16062121050952027</v>
+      </c>
+      <c r="V195" s="81">
+        <f t="shared" si="177"/>
+        <v>1.4633550239819142E-2</v>
+      </c>
+      <c r="W195" s="81">
+        <f t="shared" si="178"/>
+        <v>-4.6850535950861132E-2</v>
+      </c>
+      <c r="X195" s="81">
+        <f t="shared" si="179"/>
+        <v>0.11072150619155927</v>
+      </c>
+      <c r="Y195" s="81">
+        <f t="shared" si="180"/>
+        <v>6.4560166093114532E-2</v>
+      </c>
+      <c r="Z195" s="81">
         <f t="shared" si="181"/>
-        <v>Network solutions</v>
-      </c>
-      <c r="M195" s="81">
-        <f t="shared" si="172"/>
-        <v>1</v>
-      </c>
-      <c r="N195" s="81">
-        <f t="shared" si="172"/>
-        <v>0.40079591759015959</v>
-      </c>
-      <c r="O195" s="81">
-        <f t="shared" si="172"/>
-        <v>0.30837196025391822</v>
-      </c>
-      <c r="P195" s="81">
-        <f t="shared" si="172"/>
-        <v>0.26295284302826927</v>
-      </c>
-      <c r="Q195" s="81">
-        <f t="shared" si="172"/>
-        <v>0.14895979862293626</v>
-      </c>
-      <c r="T195" s="81">
-        <f t="shared" si="173"/>
-        <v>1</v>
-      </c>
-      <c r="U195" s="81">
-        <f t="shared" si="174"/>
-        <v>0.16062121050952027</v>
-      </c>
-      <c r="V195" s="81">
-        <f t="shared" si="175"/>
-        <v>1.4633550239819142E-2</v>
-      </c>
-      <c r="W195" s="81">
-        <f t="shared" si="176"/>
-        <v>-4.6850535950861132E-2</v>
-      </c>
-      <c r="X195" s="81">
-        <f t="shared" si="177"/>
-        <v>0.11072150619155927</v>
-      </c>
-      <c r="Y195" s="81">
-        <f t="shared" si="178"/>
-        <v>6.4560166093114532E-2</v>
-      </c>
-      <c r="Z195" s="81">
-        <f t="shared" si="179"/>
         <v>-5.3645374155112072E-2</v>
       </c>
       <c r="AA195" s="81">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>2.3995709002625414E-2</v>
       </c>
       <c r="AC195" s="49"/>
@@ -34585,15 +34726,15 @@
         <v>127.2503516174402</v>
       </c>
       <c r="O203" s="147">
-        <f t="shared" ref="O203:Q203" si="182">100*(1+((O121-$M121)/ABS($M121)))</f>
+        <f t="shared" ref="O203:Q203" si="184">100*(1+((O121-$M121)/ABS($M121)))</f>
         <v>90.049226441631504</v>
       </c>
       <c r="P203" s="147">
-        <f t="shared" si="182"/>
+        <f t="shared" si="184"/>
         <v>101.96905766526018</v>
       </c>
       <c r="Q203" s="147">
-        <f t="shared" si="182"/>
+        <f t="shared" si="184"/>
         <v>47.222222222222221</v>
       </c>
       <c r="T203" s="49"/>
@@ -34618,15 +34759,15 @@
         <v>131.73852077305108</v>
       </c>
       <c r="O204" s="147">
-        <f t="shared" ref="O204:Q204" si="183">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O204:Q204" si="185">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>167.09374252578164</v>
       </c>
       <c r="P204" s="147">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>196.87993884623862</v>
       </c>
       <c r="Q204" s="147">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>225.38303170709978</v>
       </c>
       <c r="T204" s="49"/>
@@ -34651,15 +34792,15 @@
         <v>58.227848101265835</v>
       </c>
       <c r="O205" s="147">
-        <f t="shared" ref="O205:Q205" si="184">100*(1+((O28-$M28)/ABS($M28)))</f>
+        <f t="shared" ref="O205:Q205" si="186">100*(1+((O28-$M28)/ABS($M28)))</f>
         <v>94.09282700421943</v>
       </c>
       <c r="P205" s="147">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>156.96202531645568</v>
       </c>
       <c r="Q205" s="147">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>193.24894514767931</v>
       </c>
       <c r="T205" s="49"/>
@@ -34763,51 +34904,51 @@
         <v>46.053037608486015</v>
       </c>
       <c r="N210" s="234">
-        <f t="shared" ref="N210:Q210" si="185">N187/N209</f>
+        <f t="shared" ref="N210:Q210" si="187">N187/N209</f>
         <v>45.159313725490193</v>
       </c>
       <c r="O210" s="234">
-        <f t="shared" si="185"/>
+        <f t="shared" si="187"/>
         <v>45.94168286587059</v>
       </c>
       <c r="P210" s="234">
-        <f t="shared" si="185"/>
+        <f t="shared" si="187"/>
         <v>46.754699024506309</v>
       </c>
       <c r="Q210" s="234">
-        <f t="shared" si="185"/>
+        <f t="shared" si="187"/>
         <v>48.61785556047851</v>
       </c>
       <c r="T210" s="234">
-        <f t="shared" ref="T210" si="186">T187/T209</f>
+        <f t="shared" ref="T210" si="188">T187/T209</f>
         <v>11.660350203885823</v>
       </c>
       <c r="U210" s="234">
-        <f t="shared" ref="U210" si="187">U187/U209</f>
+        <f t="shared" ref="U210" si="189">U187/U209</f>
         <v>11.650460231295728</v>
       </c>
       <c r="V210" s="234">
-        <f t="shared" ref="V210" si="188">V187/V209</f>
+        <f t="shared" ref="V210" si="190">V187/V209</f>
         <v>11.931121861322277</v>
       </c>
       <c r="W210" s="234">
-        <f t="shared" ref="W210" si="189">W187/W209</f>
+        <f t="shared" ref="W210" si="191">W187/W209</f>
         <v>12.322602584447971</v>
       </c>
       <c r="X210" s="234">
-        <f t="shared" ref="X210" si="190">X187/X209</f>
+        <f t="shared" ref="X210" si="192">X187/X209</f>
         <v>12.021938661293934</v>
       </c>
       <c r="Y210" s="234">
-        <f t="shared" ref="Y210" si="191">Y187/Y209</f>
+        <f t="shared" ref="Y210" si="193">Y187/Y209</f>
         <v>12.274336283185841</v>
       </c>
       <c r="Z210" s="234">
-        <f t="shared" ref="Z210:AA210" si="192">Z187/Z209</f>
+        <f t="shared" ref="Z210:AA210" si="194">Z187/Z209</f>
         <v>12.006011163589523</v>
       </c>
       <c r="AA210" s="234">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>11.198173322005097</v>
       </c>
       <c r="AC210" s="235">
@@ -35003,15 +35144,15 @@
         <v>42.016806722689076</v>
       </c>
       <c r="O215" s="57">
-        <f t="shared" ref="O215:Q215" si="193">O214/O209</f>
+        <f t="shared" ref="O215:Q215" si="195">O214/O209</f>
         <v>41.655095806720354</v>
       </c>
       <c r="P215" s="57">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>40.447299547941945</v>
       </c>
       <c r="Q215" s="57">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>39.875941515285774</v>
       </c>
       <c r="T215" s="49"/>
@@ -35034,15 +35175,15 @@
         <v>0.61305833333333337</v>
       </c>
       <c r="O216" s="238">
-        <f t="shared" ref="O216:Q216" si="194">O189/O214</f>
+        <f t="shared" ref="O216:Q216" si="196">O189/O214</f>
         <v>0.64168666666666663</v>
       </c>
       <c r="P216" s="238">
-        <f t="shared" si="194"/>
+        <f t="shared" si="196"/>
         <v>0.71507647058823531</v>
       </c>
       <c r="Q216" s="238">
-        <f t="shared" si="194"/>
+        <f t="shared" si="196"/>
         <v>0.77595000000000003</v>
       </c>
       <c r="T216" s="49"/>
@@ -35070,15 +35211,15 @@
       <c r="K217" s="234"/>
       <c r="L217" s="234"/>
       <c r="M217" s="234">
-        <f t="shared" ref="M217:O217" si="195">M189/M209</f>
+        <f t="shared" ref="M217:O217" si="197">M189/M209</f>
         <v>25.32208293153327</v>
       </c>
       <c r="N217" s="234">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>25.758753501400559</v>
       </c>
       <c r="O217" s="234">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>26.729519577895029</v>
       </c>
       <c r="P217" s="234">
@@ -35090,35 +35231,35 @@
         <v>30.941736818785998</v>
       </c>
       <c r="T217" s="234">
-        <f t="shared" ref="T217:Z217" si="196">T189/T209</f>
+        <f t="shared" ref="T217:Z217" si="198">T189/T209</f>
         <v>6.7649316382825617</v>
       </c>
       <c r="U217" s="234">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>7.7255133349067737</v>
       </c>
       <c r="V217" s="234">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>7.6507717115871916</v>
       </c>
       <c r="W217" s="234">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>7.1766039446837455</v>
       </c>
       <c r="X217" s="234">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>7.8712782628162081</v>
       </c>
       <c r="Y217" s="234">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>8.2811946902654867</v>
       </c>
       <c r="Z217" s="234">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>7.6047659939888366</v>
       </c>
       <c r="AA217" s="234">
-        <f t="shared" ref="AA217" si="197">AA189/AA209</f>
+        <f t="shared" ref="AA217" si="199">AA189/AA209</f>
         <v>7.7045454545454541</v>
       </c>
       <c r="AC217" s="109">
@@ -35128,7 +35269,7 @@
     </row>
     <row r="218" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B218" s="20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C218" s="234"/>
       <c r="D218" s="234"/>
@@ -35145,55 +35286,55 @@
         <v>102.81243972999036</v>
       </c>
       <c r="N218" s="234">
-        <f t="shared" ref="N218:Q218" si="198">N5/N209</f>
+        <f t="shared" ref="N218:Q218" si="200">N5/N209</f>
         <v>98.357843137254903</v>
       </c>
       <c r="O218" s="234">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>98.94445987225771</v>
       </c>
       <c r="P218" s="234">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>99.884130383059713</v>
       </c>
       <c r="Q218" s="234">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>106.46677004873726</v>
       </c>
       <c r="T218" s="234">
-        <f t="shared" ref="T218:AC218" si="199">T5/T209</f>
+        <f t="shared" ref="T218:AC218" si="201">T5/T209</f>
         <v>24.493883425281844</v>
       </c>
       <c r="U218" s="234">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>25.206514042954922</v>
       </c>
       <c r="V218" s="234">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>25.266298087998155</v>
       </c>
       <c r="W218" s="234">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>26.283382452958513</v>
       </c>
       <c r="X218" s="234">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>26.24916051040967</v>
       </c>
       <c r="Y218" s="234">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>26.622345132743362</v>
       </c>
       <c r="Z218" s="234">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>27.279304422498928</v>
       </c>
       <c r="AA218" s="234">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>27.811172472387426</v>
       </c>
       <c r="AC218" s="234">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>105.26550552251487</v>
       </c>
     </row>
@@ -35267,15 +35408,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="261" t="s">
+      <c r="B4" s="263" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="261"/>
-      <c r="E4" s="261" t="s">
+      <c r="C4" s="263"/>
+      <c r="E4" s="263" t="s">
         <v>259</v>
       </c>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
+      <c r="F4" s="263"/>
+      <c r="G4" s="263"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -35283,7 +35424,7 @@
       </c>
       <c r="C5" s="176">
         <f ca="1">Overview!C5</f>
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="136" t="s">
@@ -35299,7 +35440,7 @@
       </c>
       <c r="C6" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>674373.76</v>
+        <v>672486.52</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>20</v>
@@ -35319,7 +35460,7 @@
       </c>
       <c r="C7" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>690271.76</v>
+        <v>688384.52</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>32</v>
@@ -35339,7 +35480,7 @@
       </c>
       <c r="C8" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-283.13462950794326</v>
+        <v>-282.34227513432023</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>262</v>
@@ -35359,7 +35500,7 @@
       </c>
       <c r="C9" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3345328194677051</v>
+        <v>1.3307981194132243</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>263</v>
@@ -35379,7 +35520,7 @@
       </c>
       <c r="C10" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.8452884792113398</v>
+        <v>1.8401244256314571</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -35399,7 +35540,7 @@
       </c>
       <c r="C11" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.3928282652999455</v>
+        <v>1.3890201981476624</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -35408,18 +35549,18 @@
       </c>
       <c r="C12" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>201.59806074766357</v>
+        <v>201.04688084112149</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="261" t="s">
+      <c r="B15" s="263" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="261"/>
-      <c r="E15" s="261" t="s">
+      <c r="C15" s="263"/>
+      <c r="E15" s="263" t="s">
         <v>265</v>
       </c>
-      <c r="F15" s="261"/>
+      <c r="F15" s="263"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -35470,14 +35611,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="261" t="s">
+      <c r="B21" s="263" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="261"/>
-      <c r="E21" s="261" t="s">
+      <c r="C21" s="263"/>
+      <c r="E21" s="263" t="s">
         <v>268</v>
       </c>
-      <c r="F21" s="261"/>
+      <c r="F21" s="263"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -35546,14 +35687,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="261" t="s">
+      <c r="B29" s="263" t="s">
         <v>269</v>
       </c>
-      <c r="C29" s="261"/>
-      <c r="E29" s="261" t="s">
+      <c r="C29" s="263"/>
+      <c r="E29" s="263" t="s">
         <v>275</v>
       </c>
-      <c r="F29" s="261"/>
+      <c r="F29" s="263"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -35629,14 +35770,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="261" t="s">
+      <c r="B37" s="263" t="s">
         <v>287</v>
       </c>
-      <c r="C37" s="261"/>
-      <c r="E37" s="261" t="s">
+      <c r="C37" s="263"/>
+      <c r="E37" s="263" t="s">
         <v>290</v>
       </c>
-      <c r="F37" s="261"/>
+      <c r="F37" s="263"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -35644,7 +35785,7 @@
       </c>
       <c r="C38" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-3.5318887051643583E-3</v>
+        <v>-3.5418004601835292E-3</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>289</v>
@@ -35660,7 +35801,7 @@
       </c>
       <c r="C39" s="219">
         <f ca="1">Statement!AC161</f>
-        <v>-6.6728574967092429E-4</v>
+        <v>-6.6915839443146014E-4</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>291</v>
@@ -35705,14 +35846,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="261" t="s">
+      <c r="B45" s="263" t="s">
         <v>298</v>
       </c>
-      <c r="C45" s="261"/>
-      <c r="E45" s="261" t="s">
+      <c r="C45" s="263"/>
+      <c r="E45" s="263" t="s">
         <v>304</v>
       </c>
-      <c r="F45" s="261"/>
+      <c r="F45" s="263"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -35745,18 +35886,18 @@
       </c>
       <c r="F48" s="179">
         <f ca="1">Statement!AC176</f>
-        <v>-2.3574464107263011E-2</v>
+        <v>-2.3640622565936339E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="261" t="s">
+      <c r="B51" s="263" t="s">
         <v>301</v>
       </c>
-      <c r="C51" s="261"/>
-      <c r="E51" s="261" t="s">
+      <c r="C51" s="263"/>
+      <c r="E51" s="263" t="s">
         <v>322</v>
       </c>
-      <c r="F51" s="261"/>
+      <c r="F51" s="263"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35924,7 +36065,7 @@
       </c>
       <c r="I6" s="176">
         <f ca="1">Statement!AC120</f>
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -35953,7 +36094,7 @@
       </c>
       <c r="I7" s="177">
         <f ca="1">Statement!AC153</f>
-        <v>674373.76</v>
+        <v>672486.52</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -35982,7 +36123,7 @@
       </c>
       <c r="I8" s="177">
         <f ca="1">Statement!AC154</f>
-        <v>690271.76</v>
+        <v>688384.52</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -36011,7 +36152,7 @@
       </c>
       <c r="I9" s="178">
         <f ca="1">Statement!AC150</f>
-        <v>-283.13462950794326</v>
+        <v>-282.34227513432023</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -36040,7 +36181,7 @@
       </c>
       <c r="I10" s="178">
         <f ca="1">Statement!AC151</f>
-        <v>1.3345328194677051</v>
+        <v>1.3307981194132243</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -36069,7 +36210,7 @@
       </c>
       <c r="I11" s="178">
         <f ca="1">Statement!AC152</f>
-        <v>1.8452884792113398</v>
+        <v>1.8401244256314571</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -36098,7 +36239,7 @@
       </c>
       <c r="I12" s="178">
         <f ca="1">Statement!AC155</f>
-        <v>1.3928282652999455</v>
+        <v>1.3890201981476624</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -36127,7 +36268,7 @@
       </c>
       <c r="I13" s="178">
         <f ca="1">Statement!AC156</f>
-        <v>201.59806074766357</v>
+        <v>201.04688084112149</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36900,7 +37041,7 @@
       </c>
       <c r="I51" s="179">
         <f ca="1">Statement!AC162</f>
-        <v>-3.5318887051643583E-3</v>
+        <v>-3.5418004601835292E-3</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36929,7 +37070,7 @@
       </c>
       <c r="I52" s="179">
         <f ca="1">Statement!AC161</f>
-        <v>-6.6728574967092429E-4</v>
+        <v>-6.6915839443146014E-4</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -37252,7 +37393,7 @@
       </c>
       <c r="I68" s="200">
         <f ca="1">Statement!AC176</f>
-        <v>-2.3574464107263011E-2</v>
+        <v>-2.3640622565936339E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37741,14 +37882,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="264" t="s">
+      <c r="C3" s="266" t="s">
         <v>332</v>
       </c>
-      <c r="D3" s="265"/>
-      <c r="F3" s="266" t="s">
+      <c r="D3" s="267"/>
+      <c r="F3" s="268" t="s">
         <v>333</v>
       </c>
-      <c r="G3" s="265"/>
+      <c r="G3" s="267"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37758,7 +37899,7 @@
       </c>
       <c r="D4" s="207" t="str">
         <f>Statement!AA2</f>
-        <v>30.04.2027</v>
+        <v>30.04.2026</v>
       </c>
       <c r="F4" s="208" t="str">
         <f>Statement!W2</f>
@@ -37766,7 +37907,7 @@
       </c>
       <c r="G4" s="207" t="str">
         <f>Statement!AA2</f>
-        <v>30.04.2027</v>
+        <v>30.04.2026</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -37815,19 +37956,19 @@
       <c r="B7" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="262">
+      <c r="C7" s="264">
         <f>Statement!AA91</f>
         <v>3.0440633681443646E-2</v>
       </c>
-      <c r="D7" s="263"/>
-      <c r="F7" s="262">
+      <c r="D7" s="265"/>
+      <c r="F7" s="264">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.12937310240132488</v>
       </c>
-      <c r="G7" s="263"/>
+      <c r="G7" s="265"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="211" t="s">
@@ -37854,19 +37995,19 @@
       <c r="B9" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="262">
+      <c r="C9" s="264">
         <f>Statement!AA92</f>
         <v>7.2889329041842046E-2</v>
       </c>
-      <c r="D9" s="263"/>
-      <c r="F9" s="262">
+      <c r="D9" s="265"/>
+      <c r="F9" s="264">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.13842112176540128</v>
       </c>
-      <c r="G9" s="263"/>
+      <c r="G9" s="265"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="211" t="s">
@@ -37893,19 +38034,19 @@
       <c r="B11" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C11" s="262">
+      <c r="C11" s="264">
         <f>Statement!AA93</f>
         <v>1.0660267429652618E-2</v>
       </c>
-      <c r="D11" s="263"/>
-      <c r="F11" s="262">
+      <c r="D11" s="265"/>
+      <c r="F11" s="264">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.12495023821448292</v>
       </c>
-      <c r="G11" s="263"/>
+      <c r="G11" s="265"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="211" t="s">
@@ -37932,19 +38073,19 @@
       <c r="B13" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C13" s="262">
+      <c r="C13" s="264">
         <f>Statement!AA99</f>
         <v>-0.12340351714118437</v>
       </c>
-      <c r="D13" s="263"/>
-      <c r="F13" s="262">
+      <c r="D13" s="265"/>
+      <c r="F13" s="264">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-3.7704231252618349E-3</v>
       </c>
-      <c r="G13" s="263"/>
+      <c r="G13" s="265"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="211" t="s">
@@ -37971,19 +38112,19 @@
       <c r="B15" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C15" s="262">
+      <c r="C15" s="264">
         <f>Statement!AA100</f>
         <v>2.2145042289004859</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="F15" s="262">
+      <c r="D15" s="265"/>
+      <c r="F15" s="264">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>3.0532400365074537</v>
       </c>
-      <c r="G15" s="263"/>
+      <c r="G15" s="265"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="211" t="s">
@@ -38010,19 +38151,19 @@
       <c r="B17" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C17" s="262">
+      <c r="C17" s="264">
         <f>Statement!AA102</f>
         <v>1.2870289644483193</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="F17" s="262">
+      <c r="D17" s="265"/>
+      <c r="F17" s="264">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>1.7570260602963721</v>
       </c>
-      <c r="G17" s="263"/>
+      <c r="G17" s="265"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="211" t="s">
@@ -38049,22 +38190,22 @@
       <c r="B19" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="262">
+      <c r="C19" s="264">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>8.8459599655267736E-3</v>
       </c>
-      <c r="D19" s="263"/>
-      <c r="F19" s="262">
+      <c r="D19" s="265"/>
+      <c r="F19" s="264">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>5.2952258108314526E-2</v>
       </c>
-      <c r="G19" s="263"/>
+      <c r="G19" s="265"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="211" t="s">
@@ -38091,22 +38232,22 @@
       <c r="B21" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C21" s="262">
+      <c r="C21" s="264">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.2978639930252833</v>
       </c>
-      <c r="D21" s="263"/>
-      <c r="F21" s="262">
+      <c r="D21" s="265"/>
+      <c r="F21" s="264">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>1.7142857142857142</v>
       </c>
-      <c r="G21" s="263"/>
+      <c r="G21" s="265"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -38155,22 +38296,22 @@
       <c r="B25" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C25" s="262">
+      <c r="C25" s="264">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-5.7274157785566125E-2</v>
       </c>
-      <c r="D25" s="263"/>
-      <c r="F25" s="262">
+      <c r="D25" s="265"/>
+      <c r="F25" s="264">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-3.0061631864593874E-2</v>
       </c>
-      <c r="G25" s="263"/>
+      <c r="G25" s="265"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -38198,22 +38339,22 @@
       <c r="B27" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C27" s="262">
+      <c r="C27" s="264">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.17416013437849945</v>
       </c>
-      <c r="D27" s="263"/>
-      <c r="F27" s="262">
+      <c r="D27" s="265"/>
+      <c r="F27" s="264">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.40153717627401836</v>
       </c>
-      <c r="G27" s="263"/>
+      <c r="G27" s="265"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -38241,22 +38382,22 @@
       <c r="B29" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C29" s="262">
+      <c r="C29" s="264">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>2.3995709002625414E-2</v>
       </c>
-      <c r="D29" s="263"/>
-      <c r="F29" s="262">
+      <c r="D29" s="265"/>
+      <c r="F29" s="264">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.14584912812736922</v>
       </c>
-      <c r="G29" s="263"/>
+      <c r="G29" s="265"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="8" t="s">
@@ -38305,22 +38446,22 @@
       <c r="B33" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C33" s="262">
+      <c r="C33" s="264">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>1.0734220695577501E-2</v>
       </c>
-      <c r="D33" s="263"/>
-      <c r="F33" s="262">
+      <c r="D33" s="265"/>
+      <c r="F33" s="264">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>6.7331670822942641E-2</v>
       </c>
-      <c r="G33" s="263"/>
+      <c r="G33" s="265"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="239" t="str">
@@ -38348,22 +38489,22 @@
       <c r="B35" s="210" t="s">
         <v>334</v>
       </c>
-      <c r="C35" s="262">
+      <c r="C35" s="264">
         <f>IF(C34=0,
 IF(D34=0,0,IF(D34&gt;0,1,-1)),
 (D34-C34)/ABS(C34)
 )</f>
         <v>-6.7286114478582681E-2</v>
       </c>
-      <c r="D35" s="263"/>
-      <c r="F35" s="262">
+      <c r="D35" s="265"/>
+      <c r="F35" s="264">
         <f>IF(F34=0,
 IF(G34=0,0,IF(G34&gt;0,1,-1)),
 (G34-F34)/ABS(F34)
 )</f>
         <v>-9.1249332658182622E-2</v>
       </c>
-      <c r="G35" s="263"/>
+      <c r="G35" s="265"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -39315,7 +39456,7 @@
       </c>
       <c r="J55" s="10" t="str">
         <f>Statement!AA2</f>
-        <v>30.04.2027</v>
+        <v>30.04.2026</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.2">
